--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">LUXURY!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">냐락!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">냐락!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">셀린느!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">이콩!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">호러!$A$1:$J$31</definedName>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="559">
   <si>
     <t>guild_name</t>
   </si>
@@ -248,7 +248,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>1경 2948조 1752억 3433만</t>
+    <t>1경 3154조 7936억 9077만</t>
   </si>
   <si>
     <t>2</t>
@@ -281,7 +281,7 @@
     <t>110</t>
   </si>
   <si>
-    <t>2211조 5187억 5797만</t>
+    <t>2248조 2349억 2627만</t>
   </si>
   <si>
     <t>4</t>
@@ -296,7 +296,7 @@
     <t>아크메이지(썬,콜)</t>
   </si>
   <si>
-    <t>2194조 4949억 8899만</t>
+    <t>2195조 9848억 1001만</t>
   </si>
   <si>
     <t>5</t>
@@ -329,7 +329,7 @@
     <t>107</t>
   </si>
   <si>
-    <t>882조 2647억 5698만</t>
+    <t>902조 261억 7971만</t>
   </si>
   <si>
     <t>7</t>
@@ -416,7 +416,7 @@
     <t>106</t>
   </si>
   <si>
-    <t>310조 5226억 5741만</t>
+    <t>315조 6257억 7303만</t>
   </si>
   <si>
     <t>13</t>
@@ -428,7 +428,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%96%A0%EB%84%A4%EC%A8%A9</t>
   </si>
   <si>
-    <t>288조 889억 3277만</t>
+    <t>288조 5336억 5027만</t>
   </si>
   <si>
     <t>14</t>
@@ -455,7 +455,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EC%85%8B%EC%A7%B8</t>
   </si>
   <si>
-    <t>206조 8490억 5257만</t>
+    <t>208조 4043억 9005만</t>
   </si>
   <si>
     <t>16</t>
@@ -512,1068 +512,1056 @@
     <t>133조 5577억 192만</t>
   </si>
   <si>
-    <t>샤미다미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EB%AF%B8%EB%8B%A4%EB%AF%B8</t>
+    <t>안지연</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%A7%80%EC%97%B0</t>
+  </si>
+  <si>
+    <t>116조 9578억 2885만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>냐락뀨리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%80%A8%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>106조 8432억 1451만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Cerberus</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Cerberus</t>
+  </si>
+  <si>
+    <t>103조 5381억 493만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>와칸다검식이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%80%EC%B9%B8%EB%8B%A4%EA%B2%80%EC%8B%9D%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>101조 4237억 4479만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>이강민둥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B0%95%EB%AF%BC%EB%91%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>67조 223억 9864만</t>
+  </si>
+  <si>
+    <t>히들</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EB%93%A4</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>66조 5056억 7788만</t>
+  </si>
+  <si>
+    <t>국레쏘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EB%A0%88%EC%8F%98</t>
+  </si>
+  <si>
+    <t>59조 2958억 2118만</t>
+  </si>
+  <si>
+    <t>김채희</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B1%84%ED%9D%AC</t>
+  </si>
+  <si>
+    <t>38조 900억 7159만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>세정린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%A0%95%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>37조 5529억 1971만</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>거대곤줄박이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B0%EB%8C%80%EA%B3%A4%EC%A4%84%EB%B0%95%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>35조 2232억 1959만</t>
+  </si>
+  <si>
+    <t>스타냥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1경 720조 3865억 2152만</t>
+  </si>
+  <si>
+    <t>돈스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>3322조 3154억 8065만</t>
+  </si>
+  <si>
+    <t>진자이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>2077조 7738억 8253만</t>
+  </si>
+  <si>
+    <t>말레이히어로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>1182조 6684억 3913만</t>
+  </si>
+  <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>1112조 8677억 9360만</t>
+  </si>
+  <si>
+    <t>빌런투킬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
+  </si>
+  <si>
+    <t>960조 7702억 374만</t>
+  </si>
+  <si>
+    <t>스타뎀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%8E%80</t>
+  </si>
+  <si>
+    <t>314조 5879억 8957만</t>
+  </si>
+  <si>
+    <t>여사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
+  </si>
+  <si>
+    <t>305조 8357억 2579만</t>
+  </si>
+  <si>
+    <t>단풍노비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
+  </si>
+  <si>
+    <t>165조 4170억 907만</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>147조 7288억 7111만</t>
+  </si>
+  <si>
+    <t>프리프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>143조 1307억 9972만</t>
+  </si>
+  <si>
+    <t>부엉이없다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>137조 9189억 5210만</t>
+  </si>
+  <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>117조 2807억 9343만</t>
+  </si>
+  <si>
+    <t>쾌감</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
+  </si>
+  <si>
+    <t>85조 1744억 8515만</t>
+  </si>
+  <si>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>73조 9039억 3442만</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>70조 3961억 1459만</t>
+  </si>
+  <si>
+    <t>POSCO</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
+  </si>
+  <si>
+    <t>59조 1651억 31만</t>
+  </si>
+  <si>
+    <t>소소채2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>56조 9226억 6343만</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>37조 1057억 885만</t>
+  </si>
+  <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>36조 8904억 6796만</t>
+  </si>
+  <si>
+    <t>김치싸대기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>36조 7009억 4629만</t>
+  </si>
+  <si>
+    <t>두근푸근연근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>33조 7492억 4506만</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>31조 4997억 1522만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
+  </si>
+  <si>
+    <t>28조 2054억 3268만</t>
+  </si>
+  <si>
+    <t>울힝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
+  </si>
+  <si>
+    <t>26조 3529억 5204만</t>
+  </si>
+  <si>
+    <t>포뇨야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
+  </si>
+  <si>
+    <t>25조 4912억 9969만</t>
+  </si>
+  <si>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>23조 3910억 228만</t>
+  </si>
+  <si>
+    <t>악의꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
+  </si>
+  <si>
+    <t>23조 3285억 9707만</t>
+  </si>
+  <si>
+    <t>몽호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
+  </si>
+  <si>
+    <t>21조 327억 3756만</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>junoflo</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=junoflo</t>
+  </si>
+  <si>
+    <t>10조 5344억 1386만</t>
+  </si>
+  <si>
+    <t>가숭혁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%88%AD%ED%98%81</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>1경 6991조 8873억 8940만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%B4%EB%BD%80%EC%8B%9C</t>
+  </si>
+  <si>
+    <t>2516조 4761억 566만</t>
+  </si>
+  <si>
+    <t>26상탗</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EC%83%81%ED%83%97</t>
+  </si>
+  <si>
+    <t>1442조 8556억 7433만</t>
+  </si>
+  <si>
+    <t>달싹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EC%8B%B9</t>
+  </si>
+  <si>
+    <t>650조 9376억 9597만</t>
+  </si>
+  <si>
+    <t>뇌쉬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%87%8C%EC%89%AC</t>
+  </si>
+  <si>
+    <t>462조 3946억 8834만</t>
+  </si>
+  <si>
+    <t>26길초</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
+  </si>
+  <si>
+    <t>423조 609억 3629만</t>
+  </si>
+  <si>
+    <t>26들박</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EB%93%A4%EB%B0%95</t>
+  </si>
+  <si>
+    <t>329조 7132억 4310만</t>
+  </si>
+  <si>
+    <t>서예슬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
+  </si>
+  <si>
+    <t>311조 8644억 9662만</t>
+  </si>
+  <si>
+    <t>옴짝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%B4%EC%A7%9D</t>
+  </si>
+  <si>
+    <t>267조 4873억 4322만</t>
+  </si>
+  <si>
+    <t>26밍밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%8D%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>146조 2366억 2351만</t>
+  </si>
+  <si>
+    <t>임승민</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
+  </si>
+  <si>
+    <t>146조 1368억 9777만</t>
+  </si>
+  <si>
+    <t>몬함</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
+  </si>
+  <si>
+    <t>124조 7535억 8679만</t>
+  </si>
+  <si>
+    <t>뻔수니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
+  </si>
+  <si>
+    <t>70조 3138억 1542만</t>
+  </si>
+  <si>
+    <t>얼음깨먹기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EC%9D%8C%EA%B9%A8%EB%A8%B9%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>54조 757억 7660만</t>
+  </si>
+  <si>
+    <t>26배털</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
+  </si>
+  <si>
+    <t>37조 4761억 287만</t>
+  </si>
+  <si>
+    <t>쑤삔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%91%A4%EC%82%94</t>
+  </si>
+  <si>
+    <t>28조 3019억 2162만</t>
+  </si>
+  <si>
+    <t>류테</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%8C</t>
+  </si>
+  <si>
+    <t>20조 6247억 8310만</t>
+  </si>
+  <si>
+    <t>26퐝바</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%ED%90%9D%EB%B0%94</t>
+  </si>
+  <si>
+    <t>19조 7244억 2353만</t>
+  </si>
+  <si>
+    <t>아모르파티퀘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
+  </si>
+  <si>
+    <t>18조 1110억 6972만</t>
+  </si>
+  <si>
+    <t>뻐늬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%90%EB%8A%AC</t>
+  </si>
+  <si>
+    <t>16조 5068억 5050만</t>
+  </si>
+  <si>
+    <t>26조선</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EC%A1%B0%EC%84%A0</t>
+  </si>
+  <si>
+    <t>15조 1898억 2101만</t>
+  </si>
+  <si>
+    <t>메키무라딘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%AC%B4%EB%9D%BC%EB%94%98</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>15조 637억 960만</t>
+  </si>
+  <si>
+    <t>브깃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EA%B9%83</t>
+  </si>
+  <si>
+    <t>12조 8151억 908만</t>
+  </si>
+  <si>
+    <t>최씨용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%94%A8%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>12조 1214억 5182만</t>
+  </si>
+  <si>
+    <t>크앙레몬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>11조 3435억 1205만</t>
+  </si>
+  <si>
+    <t>뿜삐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
+  </si>
+  <si>
+    <t>9조 3250억 4217만</t>
+  </si>
+  <si>
+    <t>귬스파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%AC%EC%8A%A4%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>6조 8903억 4281만</t>
+  </si>
+  <si>
+    <t>예라미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>6조 6146억 1716만</t>
+  </si>
+  <si>
+    <t>고영희멈뭄미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%98%81%ED%9D%AC%EB%A9%88%EB%AD%84%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>5조 8558억 8323만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EA%B8%B0%EC%9A%94%EB%B0%8B</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>1경 5982조 1294억 8442만</t>
+  </si>
+  <si>
+    <t>일월마녀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%BC%EC%9B%94%EB%A7%88%EB%85%80</t>
+  </si>
+  <si>
+    <t>4378조 604억 9661만</t>
+  </si>
+  <si>
+    <t>난풍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%ED%92%8D</t>
+  </si>
+  <si>
+    <t>1539조 7438억 6316만</t>
+  </si>
+  <si>
+    <t>로드숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EB%93%9C%EC%88%8D</t>
+  </si>
+  <si>
+    <t>790조 4923억 9555만</t>
+  </si>
+  <si>
+    <t>누짜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%88%84%EC%A7%9C</t>
+  </si>
+  <si>
+    <t>698조 9405억 1129만</t>
+  </si>
+  <si>
+    <t>송곧</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%A1%EA%B3%A7</t>
+  </si>
+  <si>
+    <t>581조 5500억 3401만</t>
+  </si>
+  <si>
+    <t>똥으리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EC%9C%BC%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>266조 8506억 6360만</t>
+  </si>
+  <si>
+    <t>다이사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%9D%B4%EC%82%AC</t>
+  </si>
+  <si>
+    <t>183조 1156억 7543만</t>
+  </si>
+  <si>
+    <t>피몽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EB%AA%BD</t>
+  </si>
+  <si>
+    <t>172조 2611억 5897만</t>
+  </si>
+  <si>
+    <t>진짜지존법사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%A7%9C%EC%A7%80%EC%A1%B4%EB%B2%95%EC%82%AC</t>
+  </si>
+  <si>
+    <t>116조 5809억 6591만</t>
+  </si>
+  <si>
+    <t>원순철</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%88%9C%EC%B2%A0</t>
+  </si>
+  <si>
+    <t>47조 2419억 4473만</t>
+  </si>
+  <si>
+    <t>ADELL</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=ADELL</t>
+  </si>
+  <si>
+    <t>39조 2931억 101만</t>
+  </si>
+  <si>
+    <t>태켱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BC%B1</t>
+  </si>
+  <si>
+    <t>19조 5492억 8560만</t>
+  </si>
+  <si>
+    <t>쿠소가키키</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EC%86%8C%EA%B0%80%ED%82%A4%ED%82%A4</t>
+  </si>
+  <si>
+    <t>19조 3549억 5667만</t>
+  </si>
+  <si>
+    <t>왓쳐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%93%EC%B3%90</t>
+  </si>
+  <si>
+    <t>13조 4225억 797만</t>
+  </si>
+  <si>
+    <t>유디티기찬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%94%94%ED%8B%B0%EA%B8%B0%EC%B0%AC</t>
+  </si>
+  <si>
+    <t>12조 5841억 5205만</t>
+  </si>
+  <si>
+    <t>박미쯔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%AF%B8%EC%AF%94</t>
+  </si>
+  <si>
+    <t>11조 396억 3541만</t>
+  </si>
+  <si>
+    <t>끽코</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%81%BD%EC%BD%94</t>
+  </si>
+  <si>
+    <t>10조 5748억 5807만</t>
+  </si>
+  <si>
+    <t>강띵띵</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%9D%B5%EB%9D%B5</t>
+  </si>
+  <si>
+    <t>8조 5741억 4400만</t>
+  </si>
+  <si>
+    <t>키우는건질색</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%9A%B0%EB%8A%94%EA%B1%B4%EC%A7%88%EC%83%89</t>
+  </si>
+  <si>
+    <t>8조 4789억 5075만</t>
+  </si>
+  <si>
+    <t>악전</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%A0%84</t>
+  </si>
+  <si>
+    <t>6조 9563억 9212만</t>
+  </si>
+  <si>
+    <t>후아멀로하냐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EC%95%84%EB%A9%80%EB%A1%9C%ED%95%98%EB%83%90</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>6조 2410억 1159만</t>
+  </si>
+  <si>
+    <t>SingA</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=SingA</t>
+  </si>
+  <si>
+    <t>6조 326억 8572만</t>
+  </si>
+  <si>
+    <t>햄쓱이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%96%84%EC%93%B1%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>5조 4672억 9243만</t>
+  </si>
+  <si>
+    <t>술취한호랑이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%A0%EC%B7%A8%ED%95%9C%ED%98%B8%EB%9E%91%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>4조 9474억 7543만</t>
+  </si>
+  <si>
+    <t>수년</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%85%84</t>
+  </si>
+  <si>
+    <t>4조 3429억 3876만</t>
+  </si>
+  <si>
+    <t>한Poll</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9CPoll</t>
+  </si>
+  <si>
+    <t>4조 3050억 8452만</t>
+  </si>
+  <si>
+    <t>김치왕뚜껑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%99%95%EB%9A%9C%EA%BB%91</t>
+  </si>
+  <si>
+    <t>3조 8849억 2658만</t>
+  </si>
+  <si>
+    <t>쿠쏘야로로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EC%8F%98%EC%95%BC%EB%A1%9C%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>2조 7321억 5062만</t>
+  </si>
+  <si>
+    <t>치즈왕뚜껑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B9%98%EC%A6%88%EC%99%95%EB%9A%9C%EA%BB%91</t>
+  </si>
+  <si>
+    <t>2조 1846억 5297만</t>
+  </si>
+  <si>
+    <t>싸뤽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%A4%BD</t>
+  </si>
+  <si>
+    <t>9288조 7988억 1546만</t>
+  </si>
+  <si>
+    <t>신궁쨩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EA%B6%81%EC%A8%A9</t>
+  </si>
+  <si>
+    <t>8668조 7855억 1234만</t>
+  </si>
+  <si>
+    <t>실민</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A4%EB%AF%BC</t>
+  </si>
+  <si>
+    <t>1243조 1722억 9668만</t>
+  </si>
+  <si>
+    <t>설즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%A6%88</t>
+  </si>
+  <si>
+    <t>921조 3238억 6430만</t>
+  </si>
+  <si>
+    <t>약한고등어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
+  </si>
+  <si>
+    <t>732조 9186억 8857만</t>
+  </si>
+  <si>
+    <t>앨삐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%A8%EC%82%90</t>
+  </si>
+  <si>
+    <t>317조 9218억 327만</t>
+  </si>
+  <si>
+    <t>문디르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%94%94%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>212조 4834억 8037만</t>
+  </si>
+  <si>
+    <t>항상밝은하루</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%AD%EC%83%81%EB%B0%9D%EC%9D%80%ED%95%98%EB%A3%A8</t>
+  </si>
+  <si>
+    <t>198조 5777억 2328만</t>
+  </si>
+  <si>
+    <t>비트츄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%ED%8A%B8%EC%B8%84</t>
+  </si>
+  <si>
+    <t>160조 5093억 7580만</t>
+  </si>
+  <si>
+    <t>봉튜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%8A%9C</t>
+  </si>
+  <si>
+    <t>101조 5005억 6045만</t>
+  </si>
+  <si>
+    <t>월광사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%94%EA%B4%91%EC%82%AC</t>
+  </si>
+  <si>
+    <t>88조 8232억 3579만</t>
+  </si>
+  <si>
+    <t>공포의오함마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%ED%8F%AC%EC%9D%98%EC%98%A4%ED%95%A8%EB%A7%88</t>
+  </si>
+  <si>
+    <t>75조 662억 2801만</t>
+  </si>
+  <si>
+    <t>꽃나래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EB%82%98%EB%9E%98</t>
+  </si>
+  <si>
+    <t>45조 2828억 2447만</t>
+  </si>
+  <si>
+    <t>은달총</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%8B%AC%EC%B4%9D</t>
   </si>
   <si>
     <t>나이트로드</t>
   </si>
   <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>116조 7764억 2703만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>안지연</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%A7%80%EC%97%B0</t>
-  </si>
-  <si>
-    <t>115조 2976억 5319만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>냐락뀨리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%80%A8%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>104조 9239억 1201만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>Cerberus</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Cerberus</t>
-  </si>
-  <si>
-    <t>103조 5381억 493만</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>와칸다검식이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%99%80%EC%B9%B8%EB%8B%A4%EA%B2%80%EC%8B%9D%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>101조 4237억 4479만</t>
-  </si>
-  <si>
-    <t>이강민둥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B0%95%EB%AF%BC%EB%91%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>67조 223억 9864만</t>
-  </si>
-  <si>
-    <t>히들</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EB%93%A4</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>66조 5056억 7788만</t>
-  </si>
-  <si>
-    <t>국레쏘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EB%A0%88%EC%8F%98</t>
-  </si>
-  <si>
-    <t>59조 2958억 2118만</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>김채희</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B1%84%ED%9D%AC</t>
-  </si>
-  <si>
-    <t>38조 900억 7159만</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>세정린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%A0%95%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>37조 5529억 1971만</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>거대곤줄박이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B0%EB%8C%80%EA%B3%A4%EC%A4%84%EB%B0%95%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>35조 2232억 1959만</t>
-  </si>
-  <si>
-    <t>스타냥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1경 720조 3865억 2152만</t>
-  </si>
-  <si>
-    <t>돈스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>3322조 3154억 8065만</t>
-  </si>
-  <si>
-    <t>진자이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>2077조 7738억 8253만</t>
-  </si>
-  <si>
-    <t>말레이히어로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>1182조 6684억 3913만</t>
-  </si>
-  <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>978조 7665억 8728만</t>
-  </si>
-  <si>
-    <t>빌런투킬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
-  </si>
-  <si>
-    <t>933조 5078억 2755만</t>
-  </si>
-  <si>
-    <t>스타뎀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%8E%80</t>
-  </si>
-  <si>
-    <t>314조 5879억 8957만</t>
-  </si>
-  <si>
-    <t>여사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
-  </si>
-  <si>
-    <t>305조 8357억 2579만</t>
-  </si>
-  <si>
-    <t>단풍노비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
-  </si>
-  <si>
-    <t>165조 4170억 907만</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>147조 7288억 7111만</t>
-  </si>
-  <si>
-    <t>부엉이없다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>137조 9189억 5210만</t>
-  </si>
-  <si>
-    <t>프리프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>133조 9835억 1204만</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>117조 2807억 9343만</t>
-  </si>
-  <si>
-    <t>쾌감</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
-  </si>
-  <si>
-    <t>85조 1744억 8515만</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>71조 5763억 8505만</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>70조 3961억 1459만</t>
-  </si>
-  <si>
-    <t>POSCO</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
-  </si>
-  <si>
-    <t>59조 1651억 31만</t>
-  </si>
-  <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>56조 1022억 3684만</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>37조 1057억 885만</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>36조 8904억 6796만</t>
-  </si>
-  <si>
-    <t>김치싸대기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>36조 6013억 1317만</t>
-  </si>
-  <si>
-    <t>두근푸근연근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>33조 7492억 4506만</t>
-  </si>
-  <si>
-    <t>대방어조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>31조 4997억 1522만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
-  </si>
-  <si>
-    <t>28조 2054억 3268만</t>
-  </si>
-  <si>
-    <t>울힝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
-  </si>
-  <si>
-    <t>26조 3529억 5204만</t>
-  </si>
-  <si>
-    <t>포뇨야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
-  </si>
-  <si>
-    <t>25조 4912억 9969만</t>
-  </si>
-  <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>23조 3910억 228만</t>
-  </si>
-  <si>
-    <t>악의꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
-  </si>
-  <si>
-    <t>23조 3285억 9707만</t>
-  </si>
-  <si>
-    <t>몽호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
-  </si>
-  <si>
-    <t>21조 327억 3756만</t>
-  </si>
-  <si>
-    <t>junoflo</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=junoflo</t>
-  </si>
-  <si>
-    <t>9조 8206억 4671만</t>
-  </si>
-  <si>
-    <t>가숭혁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%88%AD%ED%98%81</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>1경 6991조 8873억 8940만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%B4%EB%BD%80%EC%8B%9C</t>
-  </si>
-  <si>
-    <t>2516조 4761억 566만</t>
-  </si>
-  <si>
-    <t>26상탗</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EC%83%81%ED%83%97</t>
-  </si>
-  <si>
-    <t>1307조 3651억 6640만</t>
-  </si>
-  <si>
-    <t>달싹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EC%8B%B9</t>
-  </si>
-  <si>
-    <t>608조 7932억 5418만</t>
-  </si>
-  <si>
-    <t>뇌쉬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%87%8C%EC%89%AC</t>
-  </si>
-  <si>
-    <t>462조 3946억 8834만</t>
-  </si>
-  <si>
-    <t>26길초</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
-  </si>
-  <si>
-    <t>423조 609억 3629만</t>
-  </si>
-  <si>
-    <t>26들박</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EB%93%A4%EB%B0%95</t>
-  </si>
-  <si>
-    <t>329조 7132억 4310만</t>
-  </si>
-  <si>
-    <t>서예슬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
-  </si>
-  <si>
-    <t>272조 1241억 8322만</t>
-  </si>
-  <si>
-    <t>옴짝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%B4%EC%A7%9D</t>
-  </si>
-  <si>
-    <t>222조 1071억 7012만</t>
-  </si>
-  <si>
-    <t>임승민</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
-  </si>
-  <si>
-    <t>142조 5227억 3133만</t>
-  </si>
-  <si>
-    <t>몬함</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
-  </si>
-  <si>
-    <t>124조 7535억 8679만</t>
-  </si>
-  <si>
-    <t>26밍밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%8D%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>119조 856억 3291만</t>
-  </si>
-  <si>
-    <t>뻔수니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
-  </si>
-  <si>
-    <t>70조 1185억 192만</t>
-  </si>
-  <si>
-    <t>얼음깨먹기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EC%9D%8C%EA%B9%A8%EB%A8%B9%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>54조 757억 7660만</t>
-  </si>
-  <si>
-    <t>26배털</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
-  </si>
-  <si>
-    <t>37조 2242억 936만</t>
-  </si>
-  <si>
-    <t>쑤삔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%91%A4%EC%82%94</t>
-  </si>
-  <si>
-    <t>28조 3019억 2162만</t>
-  </si>
-  <si>
-    <t>류테</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%8C</t>
-  </si>
-  <si>
-    <t>20조 6247억 8310만</t>
-  </si>
-  <si>
-    <t>26퐝바</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%ED%90%9D%EB%B0%94</t>
-  </si>
-  <si>
-    <t>19조 7244억 2353만</t>
-  </si>
-  <si>
-    <t>아모르파티퀘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
-  </si>
-  <si>
-    <t>17조 8709억 3446만</t>
-  </si>
-  <si>
-    <t>뻐늬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%90%EB%8A%AC</t>
-  </si>
-  <si>
-    <t>16조 5068억 5050만</t>
-  </si>
-  <si>
-    <t>26조선</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EC%A1%B0%EC%84%A0</t>
-  </si>
-  <si>
-    <t>15조 1898억 2101만</t>
-  </si>
-  <si>
-    <t>메키무라딘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%AC%B4%EB%9D%BC%EB%94%98</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>15조 637억 960만</t>
-  </si>
-  <si>
-    <t>브깃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EA%B9%83</t>
-  </si>
-  <si>
-    <t>12조 6004억 5926만</t>
-  </si>
-  <si>
-    <t>최씨용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%94%A8%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>12조 1214억 5182만</t>
-  </si>
-  <si>
-    <t>크앙레몬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>9조 5687억 8045만</t>
-  </si>
-  <si>
-    <t>뿜삐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
-  </si>
-  <si>
-    <t>8조 9447억 626만</t>
-  </si>
-  <si>
-    <t>귬스파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%AC%EC%8A%A4%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>6조 8903억 4281만</t>
-  </si>
-  <si>
-    <t>예라미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>6조 6146억 1716만</t>
-  </si>
-  <si>
-    <t>고영희멈뭄미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%98%81%ED%9D%AC%EB%A9%88%EB%AD%84%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>5조 8558억 8323만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EA%B8%B0%EC%9A%94%EB%B0%8B</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>1경 5137조 5318억 6677만</t>
-  </si>
-  <si>
-    <t>일월마녀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%BC%EC%9B%94%EB%A7%88%EB%85%80</t>
-  </si>
-  <si>
-    <t>4378조 604억 9661만</t>
-  </si>
-  <si>
-    <t>난풍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%ED%92%8D</t>
-  </si>
-  <si>
-    <t>1477조 4447억 9081만</t>
-  </si>
-  <si>
-    <t>로드숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EB%93%9C%EC%88%8D</t>
-  </si>
-  <si>
-    <t>790조 4923억 9555만</t>
-  </si>
-  <si>
-    <t>누짜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%88%84%EC%A7%9C</t>
-  </si>
-  <si>
-    <t>691조 3520억 132만</t>
-  </si>
-  <si>
-    <t>송곧</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%A1%EA%B3%A7</t>
-  </si>
-  <si>
-    <t>581조 5500억 3401만</t>
-  </si>
-  <si>
-    <t>똥으리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EC%9C%BC%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>266조 8506억 6360만</t>
-  </si>
-  <si>
-    <t>다이사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%9D%B4%EC%82%AC</t>
-  </si>
-  <si>
-    <t>183조 1156억 7543만</t>
-  </si>
-  <si>
-    <t>피몽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EB%AA%BD</t>
-  </si>
-  <si>
-    <t>172조 2611억 5897만</t>
-  </si>
-  <si>
-    <t>진짜지존법사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%A7%9C%EC%A7%80%EC%A1%B4%EB%B2%95%EC%82%AC</t>
-  </si>
-  <si>
-    <t>116조 5809억 6591만</t>
-  </si>
-  <si>
-    <t>원순철</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%88%9C%EC%B2%A0</t>
-  </si>
-  <si>
-    <t>47조 2419억 4473만</t>
-  </si>
-  <si>
-    <t>ADELL</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=ADELL</t>
-  </si>
-  <si>
-    <t>39조 2155억 5761만</t>
-  </si>
-  <si>
-    <t>태켱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BC%B1</t>
-  </si>
-  <si>
-    <t>19조 5492억 8560만</t>
-  </si>
-  <si>
-    <t>쿠소가키키</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EC%86%8C%EA%B0%80%ED%82%A4%ED%82%A4</t>
-  </si>
-  <si>
-    <t>19조 3549억 5667만</t>
-  </si>
-  <si>
-    <t>왓쳐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%99%93%EC%B3%90</t>
-  </si>
-  <si>
-    <t>13조 226억 8271만</t>
-  </si>
-  <si>
-    <t>유디티기찬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%94%94%ED%8B%B0%EA%B8%B0%EC%B0%AC</t>
-  </si>
-  <si>
-    <t>11조 9560억 3534만</t>
-  </si>
-  <si>
-    <t>박미쯔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%AF%B8%EC%AF%94</t>
-  </si>
-  <si>
-    <t>11조 396억 3541만</t>
-  </si>
-  <si>
-    <t>끽코</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%81%BD%EC%BD%94</t>
-  </si>
-  <si>
-    <t>10조 5748억 5807만</t>
-  </si>
-  <si>
-    <t>강띵띵</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%9D%B5%EB%9D%B5</t>
-  </si>
-  <si>
-    <t>8조 5741억 4400만</t>
-  </si>
-  <si>
-    <t>키우는건질색</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%9A%B0%EB%8A%94%EA%B1%B4%EC%A7%88%EC%83%89</t>
-  </si>
-  <si>
-    <t>8조 4789억 5075만</t>
-  </si>
-  <si>
-    <t>악전</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%A0%84</t>
-  </si>
-  <si>
-    <t>6조 9563억 9212만</t>
-  </si>
-  <si>
-    <t>후아멀로하냐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EC%95%84%EB%A9%80%EB%A1%9C%ED%95%98%EB%83%90</t>
-  </si>
-  <si>
-    <t>99</t>
-  </si>
-  <si>
-    <t>6조 1297억 4182만</t>
-  </si>
-  <si>
-    <t>햄쓱이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%96%84%EC%93%B1%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>5조 4672억 9243만</t>
-  </si>
-  <si>
-    <t>SingA</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=SingA</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>5조 4430억 3652만</t>
-  </si>
-  <si>
-    <t>술취한호랑이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%A0%EC%B7%A8%ED%95%9C%ED%98%B8%EB%9E%91%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>4조 8734억 8870만</t>
-  </si>
-  <si>
-    <t>수년</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%85%84</t>
-  </si>
-  <si>
-    <t>4조 3429억 3876만</t>
-  </si>
-  <si>
-    <t>한Poll</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9CPoll</t>
-  </si>
-  <si>
-    <t>4조 3050억 8452만</t>
-  </si>
-  <si>
-    <t>김치왕뚜껑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%99%95%EB%9A%9C%EA%BB%91</t>
-  </si>
-  <si>
-    <t>3조 8849억 2658만</t>
-  </si>
-  <si>
-    <t>쿠쏘야로로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EC%8F%98%EC%95%BC%EB%A1%9C%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>2조 6663억 6952만</t>
-  </si>
-  <si>
-    <t>치즈왕뚜껑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B9%98%EC%A6%88%EC%99%95%EB%9A%9C%EA%BB%91</t>
-  </si>
-  <si>
-    <t>2조 1846억 5297만</t>
-  </si>
-  <si>
-    <t>싸뤽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%A4%BD</t>
-  </si>
-  <si>
-    <t>9288조 7988억 1546만</t>
-  </si>
-  <si>
-    <t>신궁쨩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EA%B6%81%EC%A8%A9</t>
-  </si>
-  <si>
-    <t>8668조 7855억 1234만</t>
-  </si>
-  <si>
-    <t>실민</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A4%EB%AF%BC</t>
-  </si>
-  <si>
-    <t>1232조 428억 1327만</t>
-  </si>
-  <si>
-    <t>민실</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EC%8B%A4</t>
-  </si>
-  <si>
-    <t>760조 7667억 2010만</t>
-  </si>
-  <si>
-    <t>약한고등어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
-  </si>
-  <si>
-    <t>732조 9186억 8857만</t>
-  </si>
-  <si>
-    <t>앨삐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%A8%EC%82%90</t>
-  </si>
-  <si>
-    <t>317조 9218억 327만</t>
-  </si>
-  <si>
-    <t>문디르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%94%94%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>209조 3802억 6873만</t>
-  </si>
-  <si>
-    <t>항상밝은하루</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%AD%EC%83%81%EB%B0%9D%EC%9D%80%ED%95%98%EB%A3%A8</t>
-  </si>
-  <si>
-    <t>198조 5777억 2328만</t>
-  </si>
-  <si>
-    <t>비트츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%ED%8A%B8%EC%B8%84</t>
-  </si>
-  <si>
-    <t>160조 5093억 7580만</t>
-  </si>
-  <si>
-    <t>봉튜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%8A%9C</t>
-  </si>
-  <si>
-    <t>101조 5005억 6045만</t>
-  </si>
-  <si>
-    <t>월광사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%94%EA%B4%91%EC%82%AC</t>
-  </si>
-  <si>
-    <t>88조 8232억 3579만</t>
-  </si>
-  <si>
-    <t>공포의오함마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%ED%8F%AC%EC%9D%98%EC%98%A4%ED%95%A8%EB%A7%88</t>
-  </si>
-  <si>
-    <t>66조 6160억 1431만</t>
-  </si>
-  <si>
-    <t>꽃나래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EB%82%98%EB%9E%98</t>
-  </si>
-  <si>
-    <t>45조 2828억 2447만</t>
-  </si>
-  <si>
-    <t>은달총</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%8B%AC%EC%B4%9D</t>
-  </si>
-  <si>
     <t>38조 9416억 5281만</t>
   </si>
   <si>
@@ -1583,7 +1571,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%95%A9%EC%BD%A9</t>
   </si>
   <si>
-    <t>25조 6837억 4377만</t>
+    <t>25조 6977억 6223만</t>
   </si>
   <si>
     <t>뽀라비</t>
@@ -1592,7 +1580,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
   </si>
   <si>
-    <t>24조 1275억 9609만</t>
+    <t>24조 6417억 7062만</t>
   </si>
   <si>
     <t>김대협</t>
@@ -1628,7 +1616,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B4%84%EB%85%98</t>
   </si>
   <si>
-    <t>9조 3942억 2359만</t>
+    <t>9조 7577억 4333만</t>
   </si>
   <si>
     <t>다송이</t>
@@ -1637,7 +1625,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%86%A1%EC%9D%B4</t>
   </si>
   <si>
-    <t>8조 6843억 7977만</t>
+    <t>9조 5098억 7158만</t>
   </si>
   <si>
     <t>봉합불가</t>
@@ -1646,7 +1634,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%95%A9%EB%B6%88%EA%B0%80</t>
   </si>
   <si>
-    <t>7조 1372억 9919만</t>
+    <t>7조 2028억 4048만</t>
   </si>
   <si>
     <t>빠나딘</t>
@@ -1655,7 +1643,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%A0%EB%82%98%EB%94%98</t>
   </si>
   <si>
-    <t>7조 541억 2250만</t>
+    <t>7조 1388억 6222만</t>
   </si>
   <si>
     <t>양카오너</t>
@@ -1676,7 +1664,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
   </si>
   <si>
-    <t>2조 4727억 9722만</t>
+    <t>2조 5899억 6994만</t>
   </si>
   <si>
     <t>돌쇠영만</t>
@@ -1688,34 +1676,31 @@
     <t>1조 449억 856만</t>
   </si>
   <si>
+    <t>용광사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EA%B4%91%EC%82%AC</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>7680억 9109만</t>
+  </si>
+  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%AF%94</t>
   </si>
   <si>
-    <t>96</t>
-  </si>
-  <si>
     <t>6424억 6751만</t>
   </si>
   <si>
-    <t>용광사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EA%B4%91%EC%82%AC</t>
+    <t>비어치킨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%96%B4%EC%B9%98%ED%82%A8</t>
   </si>
   <si>
     <t>95</t>
-  </si>
-  <si>
-    <t>6354억 2182만</t>
-  </si>
-  <si>
-    <t>비어치킨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%96%B4%EC%B9%98%ED%82%A8</t>
-  </si>
-  <si>
-    <t>94</t>
   </si>
   <si>
     <t>4074억 222만</t>
@@ -2358,7 +2343,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -3031,13 +3016,13 @@
         <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>165</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3048,16 +3033,16 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>70</v>
@@ -3066,10 +3051,10 @@
         <v>104</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3080,28 +3065,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3112,28 +3097,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3144,16 +3129,16 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>180</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>70</v>
@@ -3165,7 +3150,7 @@
         <v>159</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3179,25 +3164,25 @@
         <v>36</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="I26" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3211,25 +3196,25 @@
         <v>45</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>188</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3243,25 +3228,25 @@
         <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>191</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3272,28 +3257,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>195</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3304,67 +3289,35 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>199</v>
-      </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -3395,7 +3348,6 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
-    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3456,13 +3408,13 @@
         <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>70</v>
@@ -3474,7 +3426,7 @@
         <v>72</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>32</v>
@@ -3488,13 +3440,13 @@
         <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>70</v>
@@ -3506,7 +3458,7 @@
         <v>78</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>32</v>
@@ -3520,13 +3472,13 @@
         <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>70</v>
@@ -3538,7 +3490,7 @@
         <v>78</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>32</v>
@@ -3552,13 +3504,13 @@
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>70</v>
@@ -3570,7 +3522,7 @@
         <v>105</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>32</v>
@@ -3584,13 +3536,13 @@
         <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>70</v>
@@ -3602,7 +3554,7 @@
         <v>105</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>32</v>
@@ -3616,13 +3568,13 @@
         <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>70</v>
@@ -3634,7 +3586,7 @@
         <v>105</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>32</v>
@@ -3648,13 +3600,13 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>70</v>
@@ -3666,7 +3618,7 @@
         <v>99</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>32</v>
@@ -3680,13 +3632,13 @@
         <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>70</v>
@@ -3698,7 +3650,7 @@
         <v>99</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>32</v>
@@ -3712,13 +3664,13 @@
         <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>70</v>
@@ -3730,7 +3682,7 @@
         <v>137</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>32</v>
@@ -3744,13 +3696,13 @@
         <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>70</v>
@@ -3762,7 +3714,7 @@
         <v>137</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>32</v>
@@ -3776,13 +3728,13 @@
         <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>70</v>
@@ -3791,10 +3743,10 @@
         <v>98</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>32</v>
@@ -3808,13 +3760,13 @@
         <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>70</v>
@@ -3823,10 +3775,10 @@
         <v>98</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>32</v>
@@ -3840,13 +3792,13 @@
         <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>70</v>
@@ -3858,7 +3810,7 @@
         <v>137</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>32</v>
@@ -3872,13 +3824,13 @@
         <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>70</v>
@@ -3890,7 +3842,7 @@
         <v>137</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>32</v>
@@ -3904,13 +3856,13 @@
         <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>70</v>
@@ -3919,10 +3871,10 @@
         <v>88</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>32</v>
@@ -3936,13 +3888,13 @@
         <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>70</v>
@@ -3954,7 +3906,7 @@
         <v>159</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>32</v>
@@ -3968,13 +3920,13 @@
         <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>70</v>
@@ -3986,7 +3938,7 @@
         <v>137</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>32</v>
@@ -4000,13 +3952,13 @@
         <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>70</v>
@@ -4015,10 +3967,10 @@
         <v>98</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>164</v>
+        <v>251</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>32</v>
@@ -4032,13 +3984,13 @@
         <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>70</v>
@@ -4050,7 +4002,7 @@
         <v>159</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>32</v>
@@ -4064,13 +4016,13 @@
         <v>17</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>70</v>
@@ -4082,7 +4034,7 @@
         <v>159</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>32</v>
@@ -4093,16 +4045,16 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>70</v>
@@ -4111,10 +4063,10 @@
         <v>104</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>32</v>
@@ -4125,16 +4077,16 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>70</v>
@@ -4143,10 +4095,10 @@
         <v>104</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>164</v>
+        <v>251</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>32</v>
@@ -4157,16 +4109,16 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>70</v>
@@ -4175,10 +4127,10 @@
         <v>98</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>32</v>
@@ -4189,7 +4141,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>31</v>
@@ -4198,7 +4150,7 @@
         <v>31</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>97</v>
@@ -4207,10 +4159,10 @@
         <v>88</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>164</v>
+        <v>251</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>32</v>
@@ -4224,13 +4176,13 @@
         <v>36</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>70</v>
@@ -4239,10 +4191,10 @@
         <v>88</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>164</v>
+        <v>251</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>32</v>
@@ -4256,13 +4208,13 @@
         <v>45</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>70</v>
@@ -4271,10 +4223,10 @@
         <v>88</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>32</v>
@@ -4288,13 +4240,13 @@
         <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>70</v>
@@ -4303,10 +4255,10 @@
         <v>77</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>32</v>
@@ -4317,16 +4269,16 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>70</v>
@@ -4335,10 +4287,10 @@
         <v>110</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>164</v>
+        <v>251</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>32</v>
@@ -4349,16 +4301,16 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>70</v>
@@ -4367,10 +4319,10 @@
         <v>93</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>164</v>
+        <v>251</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>32</v>
@@ -4381,16 +4333,16 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>200</v>
+        <v>285</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>70</v>
@@ -4399,10 +4351,10 @@
         <v>98</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>164</v>
+        <v>251</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>32</v>
@@ -4501,13 +4453,13 @@
         <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>70</v>
@@ -4516,10 +4468,10 @@
         <v>104</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4539,7 +4491,7 @@
         <v>41</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>97</v>
@@ -4551,7 +4503,7 @@
         <v>83</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4565,13 +4517,13 @@
         <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>70</v>
@@ -4583,7 +4535,7 @@
         <v>105</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4597,13 +4549,13 @@
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>70</v>
@@ -4615,7 +4567,7 @@
         <v>128</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4629,13 +4581,13 @@
         <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>70</v>
@@ -4647,7 +4599,7 @@
         <v>128</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4661,13 +4613,13 @@
         <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>70</v>
@@ -4679,7 +4631,7 @@
         <v>128</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4693,13 +4645,13 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>70</v>
@@ -4711,7 +4663,7 @@
         <v>128</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4725,13 +4677,13 @@
         <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>70</v>
@@ -4743,7 +4695,7 @@
         <v>128</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4757,13 +4709,13 @@
         <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>70</v>
@@ -4775,7 +4727,7 @@
         <v>128</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4789,25 +4741,25 @@
         <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4821,25 +4773,25 @@
         <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4853,25 +4805,25 @@
         <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>159</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4885,13 +4837,13 @@
         <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>70</v>
@@ -4900,10 +4852,10 @@
         <v>98</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4917,13 +4869,13 @@
         <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>70</v>
@@ -4932,10 +4884,10 @@
         <v>88</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4949,13 +4901,13 @@
         <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>70</v>
@@ -4964,10 +4916,10 @@
         <v>98</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4981,13 +4933,13 @@
         <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>70</v>
@@ -4996,10 +4948,10 @@
         <v>98</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>164</v>
+        <v>251</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5013,13 +4965,13 @@
         <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>70</v>
@@ -5028,10 +4980,10 @@
         <v>110</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>164</v>
+        <v>251</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5045,13 +4997,13 @@
         <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>70</v>
@@ -5060,10 +5012,10 @@
         <v>88</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5077,13 +5029,13 @@
         <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>70</v>
@@ -5092,10 +5044,10 @@
         <v>88</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>164</v>
+        <v>251</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5109,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>70</v>
@@ -5124,10 +5076,10 @@
         <v>98</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5138,16 +5090,16 @@
         <v>33</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>70</v>
@@ -5156,10 +5108,10 @@
         <v>88</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>164</v>
+        <v>251</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5170,16 +5122,16 @@
         <v>33</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>70</v>
@@ -5188,10 +5140,10 @@
         <v>123</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5202,16 +5154,16 @@
         <v>33</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>70</v>
@@ -5220,10 +5172,10 @@
         <v>154</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>164</v>
+        <v>251</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5234,16 +5186,16 @@
         <v>33</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>70</v>
@@ -5252,10 +5204,10 @@
         <v>71</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5269,13 +5221,13 @@
         <v>36</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>70</v>
@@ -5284,10 +5236,10 @@
         <v>88</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>365</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>369</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5301,13 +5253,13 @@
         <v>45</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>70</v>
@@ -5316,10 +5268,10 @@
         <v>93</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5333,13 +5285,13 @@
         <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>70</v>
@@ -5348,10 +5300,10 @@
         <v>88</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5362,16 +5314,16 @@
         <v>33</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>70</v>
@@ -5380,10 +5332,10 @@
         <v>88</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5394,16 +5346,16 @@
         <v>33</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>70</v>
@@ -5412,10 +5364,10 @@
         <v>104</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5519,7 +5471,7 @@
         <v>48</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>97</v>
@@ -5528,10 +5480,10 @@
         <v>88</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5545,13 +5497,13 @@
         <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>70</v>
@@ -5560,10 +5512,10 @@
         <v>110</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5577,13 +5529,13 @@
         <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>70</v>
@@ -5595,7 +5547,7 @@
         <v>105</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5609,13 +5561,13 @@
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>70</v>
@@ -5627,7 +5579,7 @@
         <v>128</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5641,13 +5593,13 @@
         <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>70</v>
@@ -5659,7 +5611,7 @@
         <v>137</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5673,13 +5625,13 @@
         <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>70</v>
@@ -5691,7 +5643,7 @@
         <v>105</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5705,13 +5657,13 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>70</v>
@@ -5723,7 +5675,7 @@
         <v>128</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5737,13 +5689,13 @@
         <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>70</v>
@@ -5755,7 +5707,7 @@
         <v>128</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5769,13 +5721,13 @@
         <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>70</v>
@@ -5787,7 +5739,7 @@
         <v>137</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5801,13 +5753,13 @@
         <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>70</v>
@@ -5816,10 +5768,10 @@
         <v>88</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5833,13 +5785,13 @@
         <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>70</v>
@@ -5848,10 +5800,10 @@
         <v>98</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5865,13 +5817,13 @@
         <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>70</v>
@@ -5880,10 +5832,10 @@
         <v>93</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>164</v>
+        <v>251</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5897,13 +5849,13 @@
         <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>70</v>
@@ -5912,10 +5864,10 @@
         <v>93</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5929,13 +5881,13 @@
         <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>70</v>
@@ -5944,10 +5896,10 @@
         <v>110</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>164</v>
+        <v>251</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5961,13 +5913,13 @@
         <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>70</v>
@@ -5976,10 +5928,10 @@
         <v>98</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5993,13 +5945,13 @@
         <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>70</v>
@@ -6008,10 +5960,10 @@
         <v>104</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6025,13 +5977,13 @@
         <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>70</v>
@@ -6040,10 +5992,10 @@
         <v>88</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6057,13 +6009,13 @@
         <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>70</v>
@@ -6072,10 +6024,10 @@
         <v>88</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6089,13 +6041,13 @@
         <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>70</v>
@@ -6104,10 +6056,10 @@
         <v>93</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6121,13 +6073,13 @@
         <v>17</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>70</v>
@@ -6136,10 +6088,10 @@
         <v>88</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6150,16 +6102,16 @@
         <v>42</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>70</v>
@@ -6168,10 +6120,10 @@
         <v>110</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6182,16 +6134,16 @@
         <v>42</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>70</v>
@@ -6200,10 +6152,10 @@
         <v>110</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6214,28 +6166,28 @@
         <v>42</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>365</v>
+        <v>443</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6246,28 +6198,28 @@
         <v>42</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>454</v>
+        <v>361</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6281,13 +6233,13 @@
         <v>36</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>70</v>
@@ -6296,10 +6248,10 @@
         <v>98</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6313,13 +6265,13 @@
         <v>45</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>70</v>
@@ -6328,10 +6280,10 @@
         <v>88</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6345,13 +6297,13 @@
         <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>70</v>
@@ -6360,10 +6312,10 @@
         <v>77</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6374,16 +6326,16 @@
         <v>42</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>70</v>
@@ -6392,10 +6344,10 @@
         <v>98</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6406,16 +6358,16 @@
         <v>42</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>70</v>
@@ -6424,10 +6376,10 @@
         <v>88</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6438,16 +6390,16 @@
         <v>42</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>200</v>
+        <v>285</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>70</v>
@@ -6456,10 +6408,10 @@
         <v>98</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6558,13 +6510,13 @@
         <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>70</v>
@@ -6573,10 +6525,10 @@
         <v>71</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6590,13 +6542,13 @@
         <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>70</v>
@@ -6605,10 +6557,10 @@
         <v>93</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6622,13 +6574,13 @@
         <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>70</v>
@@ -6640,7 +6592,7 @@
         <v>78</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6654,13 +6606,13 @@
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>70</v>
@@ -6672,7 +6624,7 @@
         <v>105</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6686,13 +6638,13 @@
         <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>70</v>
@@ -6704,7 +6656,7 @@
         <v>78</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6718,13 +6670,13 @@
         <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>70</v>
@@ -6736,7 +6688,7 @@
         <v>128</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6750,13 +6702,13 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>70</v>
@@ -6768,7 +6720,7 @@
         <v>137</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6782,13 +6734,13 @@
         <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>70</v>
@@ -6800,7 +6752,7 @@
         <v>159</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6814,13 +6766,13 @@
         <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>70</v>
@@ -6832,7 +6784,7 @@
         <v>137</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6846,13 +6798,13 @@
         <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>70</v>
@@ -6864,7 +6816,7 @@
         <v>137</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6878,13 +6830,13 @@
         <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>70</v>
@@ -6893,10 +6845,10 @@
         <v>71</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6910,13 +6862,13 @@
         <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>70</v>
@@ -6925,10 +6877,10 @@
         <v>110</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6942,13 +6894,13 @@
         <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>70</v>
@@ -6957,10 +6909,10 @@
         <v>110</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6974,25 +6926,25 @@
         <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>163</v>
+        <v>510</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -7006,13 +6958,13 @@
         <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>70</v>
@@ -7021,10 +6973,10 @@
         <v>88</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>164</v>
+        <v>251</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -7038,13 +6990,13 @@
         <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>70</v>
@@ -7053,10 +7005,10 @@
         <v>88</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7070,13 +7022,13 @@
         <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>70</v>
@@ -7085,10 +7037,10 @@
         <v>93</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7102,13 +7054,13 @@
         <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>70</v>
@@ -7117,10 +7069,10 @@
         <v>98</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7134,13 +7086,13 @@
         <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>70</v>
@@ -7149,10 +7101,10 @@
         <v>88</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7166,13 +7118,13 @@
         <v>17</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>70</v>
@@ -7181,10 +7133,10 @@
         <v>110</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7195,16 +7147,16 @@
         <v>49</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>70</v>
@@ -7213,10 +7165,10 @@
         <v>110</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7227,16 +7179,16 @@
         <v>49</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>70</v>
@@ -7245,10 +7197,10 @@
         <v>93</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7259,16 +7211,16 @@
         <v>49</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>70</v>
@@ -7277,10 +7229,10 @@
         <v>93</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7291,16 +7243,16 @@
         <v>49</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>70</v>
@@ -7309,10 +7261,10 @@
         <v>104</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7326,25 +7278,25 @@
         <v>36</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>163</v>
+        <v>510</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7358,13 +7310,13 @@
         <v>45</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>70</v>
@@ -7373,10 +7325,10 @@
         <v>93</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7390,25 +7342,25 @@
         <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>58</v>
+        <v>549</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>58</v>
+        <v>549</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>71</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7419,28 +7371,28 @@
         <v>49</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>556</v>
+        <v>58</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>556</v>
+        <v>58</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>71</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -7451,16 +7403,16 @@
         <v>49</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>70</v>
@@ -7469,10 +7421,10 @@
         <v>98</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">LUXURY!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">냐락!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">냐락!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">셀린느!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">이콩!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">호러!$A$1:$J$31</definedName>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="562">
   <si>
     <t>guild_name</t>
   </si>
@@ -173,7 +173,7 @@
     <t>오래 하실분들 환영입니다</t>
   </si>
   <si>
-    <t>애기요밋</t>
+    <t>기요밋</t>
   </si>
   <si>
     <t>이콩</t>
@@ -248,12 +248,27 @@
     <t>113</t>
   </si>
   <si>
-    <t>1경 3154조 7936억 9077만</t>
+    <t>1경 3698조 6829억 2352만</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t>냐락오리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EC%98%A4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>2501조 8002억 9960만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>냐락겅듀</t>
   </si>
   <si>
@@ -266,22 +281,7 @@
     <t>109</t>
   </si>
   <si>
-    <t>2296조 6952억 7221만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>냐락오리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EC%98%A4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>2248조 2349억 2627만</t>
+    <t>2410조 7596억 8543만</t>
   </si>
   <si>
     <t>4</t>
@@ -296,7 +296,7 @@
     <t>아크메이지(썬,콜)</t>
   </si>
   <si>
-    <t>2195조 9848억 1001만</t>
+    <t>2300조 5822억 8475만</t>
   </si>
   <si>
     <t>5</t>
@@ -311,12 +311,30 @@
     <t>다크나이트</t>
   </si>
   <si>
-    <t>1395조 8364억 2120만</t>
+    <t>1485조 1957억 9871만</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
+    <t>냐락바람</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%B0%94%EB%9E%8C</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>964조 9615억 8471만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%A7%90</t>
   </si>
   <si>
@@ -329,25 +347,7 @@
     <t>107</t>
   </si>
   <si>
-    <t>902조 261억 7971만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>냐락바람</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%B0%94%EB%9E%8C</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>875조 7755억 8766만</t>
+    <t>906조 3743억 5904만</t>
   </si>
   <si>
     <t>8</t>
@@ -401,12 +401,24 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>439조 4475억 1469만</t>
+    <t>456조 817억 2556만</t>
   </si>
   <si>
     <t>12</t>
   </si>
   <si>
+    <t>떠네쨩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%96%A0%EB%84%A4%EC%A8%A9</t>
+  </si>
+  <si>
+    <t>448조 9268억 5837만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>냐락크리</t>
   </si>
   <si>
@@ -416,19 +428,7 @@
     <t>106</t>
   </si>
   <si>
-    <t>315조 6257억 7303만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>떠네쨩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%96%A0%EB%84%A4%EC%A8%A9</t>
-  </si>
-  <si>
-    <t>288조 5336억 5027만</t>
+    <t>332조 2211억 9240만</t>
   </si>
   <si>
     <t>14</t>
@@ -443,7 +443,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>276조 590억 1583만</t>
+    <t>282조 628억 1566만</t>
   </si>
   <si>
     <t>15</t>
@@ -455,7 +455,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EC%85%8B%EC%A7%B8</t>
   </si>
   <si>
-    <t>208조 4043억 9005만</t>
+    <t>211조 3286억 9983만</t>
   </si>
   <si>
     <t>16</t>
@@ -467,7 +467,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%A6%B0</t>
   </si>
   <si>
-    <t>188조 9953억 4686만</t>
+    <t>193조 6810억 7098만</t>
   </si>
   <si>
     <t>17</t>
@@ -479,12 +479,24 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EC%BF%A0</t>
   </si>
   <si>
-    <t>168조 8233억 7615만</t>
+    <t>169조 3850억 998만</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
+    <t>욕박고시작</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%95%EB%B0%95%EA%B3%A0%EC%8B%9C%EC%9E%91</t>
+  </si>
+  <si>
+    <t>161조 6395억 7471만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>쀼움</t>
   </si>
   <si>
@@ -497,9 +509,6 @@
     <t>157조 1751억 7341만</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
     <t>삼양일짱</t>
   </si>
   <si>
@@ -512,16 +521,31 @@
     <t>133조 5577억 192만</t>
   </si>
   <si>
+    <t>21</t>
+  </si>
+  <si>
     <t>안지연</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%A7%80%EC%97%B0</t>
   </si>
   <si>
-    <t>116조 9578억 2885만</t>
-  </si>
-  <si>
-    <t>21</t>
+    <t>122조 8232억 5720만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Cerberus</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Cerberus</t>
+  </si>
+  <si>
+    <t>107조 5759억 682만</t>
+  </si>
+  <si>
+    <t>23</t>
   </si>
   <si>
     <t>냐락뀨리</t>
@@ -533,33 +557,18 @@
     <t>106조 8432억 1451만</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>Cerberus</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Cerberus</t>
-  </si>
-  <si>
-    <t>103조 5381억 493만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>와칸다검식이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%99%80%EC%B9%B8%EB%8B%A4%EA%B2%80%EC%8B%9D%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>101조 4237억 4479만</t>
-  </si>
-  <si>
     <t>24</t>
   </si>
   <si>
+    <t>Centauros</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Centauros</t>
+  </si>
+  <si>
+    <t>93조 3803억 4975만</t>
+  </si>
+  <si>
     <t>이강민둥이</t>
   </si>
   <si>
@@ -587,7 +596,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EB%A0%88%EC%8F%98</t>
   </si>
   <si>
-    <t>59조 2958억 2118만</t>
+    <t>59조 3548억 9887만</t>
+  </si>
+  <si>
+    <t>28</t>
   </si>
   <si>
     <t>김채희</t>
@@ -596,10 +608,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B1%84%ED%9D%AC</t>
   </si>
   <si>
-    <t>38조 900억 7159만</t>
-  </si>
-  <si>
-    <t>28</t>
+    <t>38조 9225억 9647만</t>
+  </si>
+  <si>
+    <t>29</t>
   </si>
   <si>
     <t>세정린</t>
@@ -611,7 +623,7 @@
     <t>37조 5529억 1971만</t>
   </si>
   <si>
-    <t>29</t>
+    <t>30</t>
   </si>
   <si>
     <t>거대곤줄박이</t>
@@ -620,7 +632,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B0%EB%8C%80%EA%B3%A4%EC%A4%84%EB%B0%95%EC%9D%B4</t>
   </si>
   <si>
-    <t>35조 2232억 1959만</t>
+    <t>36조 3789억 7842만</t>
   </si>
   <si>
     <t>스타냥이</t>
@@ -647,7 +659,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>2077조 7738억 8253만</t>
+    <t>2202조 8792억 6515만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -674,7 +686,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
   </si>
   <si>
-    <t>960조 7702억 374만</t>
+    <t>1022조 1463억 7965만</t>
   </si>
   <si>
     <t>스타뎀</t>
@@ -683,7 +695,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%8E%80</t>
   </si>
   <si>
-    <t>314조 5879억 8957만</t>
+    <t>315조 3104억 9477만</t>
   </si>
   <si>
     <t>여사</t>
@@ -701,7 +713,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
   </si>
   <si>
-    <t>165조 4170억 907만</t>
+    <t>176조 573억 7249만</t>
   </si>
   <si>
     <t>약어</t>
@@ -728,7 +740,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
   </si>
   <si>
-    <t>137조 9189억 5210만</t>
+    <t>140조 8180억 9133만</t>
   </si>
   <si>
     <t>꽃을든남자</t>
@@ -737,7 +749,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
   </si>
   <si>
-    <t>117조 2807억 9343만</t>
+    <t>123조 7397억 6038만</t>
   </si>
   <si>
     <t>쾌감</t>
@@ -746,7 +758,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
   </si>
   <si>
-    <t>85조 1744억 8515만</t>
+    <t>86조 6580억 5183만</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>74조 5245억 2328만</t>
   </si>
   <si>
     <t>잼포즈</t>
@@ -755,16 +776,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>73조 9039억 3442만</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>70조 3961억 1459만</t>
+    <t>74조 2546억 7807만</t>
   </si>
   <si>
     <t>POSCO</t>
@@ -788,6 +800,24 @@
     <t>56조 9226억 6343만</t>
   </si>
   <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>38조 3694억 6015만</t>
+  </si>
+  <si>
+    <t>김치싸대기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>38조 568억 6620만</t>
+  </si>
+  <si>
     <t>루넨</t>
   </si>
   <si>
@@ -797,24 +827,6 @@
     <t>37조 1057억 885만</t>
   </si>
   <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>36조 8904억 6796만</t>
-  </si>
-  <si>
-    <t>김치싸대기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>36조 7009억 4629만</t>
-  </si>
-  <si>
     <t>두근푸근연근</t>
   </si>
   <si>
@@ -845,7 +857,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
   </si>
   <si>
-    <t>26조 3529억 5204만</t>
+    <t>27조 7168억 210만</t>
+  </si>
+  <si>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>25조 7875억 6068만</t>
   </si>
   <si>
     <t>포뇨야</t>
@@ -857,15 +878,6 @@
     <t>25조 4912억 9969만</t>
   </si>
   <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>23조 3910억 228만</t>
-  </si>
-  <si>
     <t>악의꽃</t>
   </si>
   <si>
@@ -884,16 +896,13 @@
     <t>21조 327억 3756만</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>junoflo</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=junoflo</t>
   </si>
   <si>
-    <t>10조 5344억 1386만</t>
+    <t>10조 7228억 5142만</t>
   </si>
   <si>
     <t>가숭혁</t>
@@ -920,7 +929,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%EC%83%81%ED%83%97</t>
   </si>
   <si>
-    <t>1442조 8556억 7433만</t>
+    <t>1448조 1213억 6213만</t>
   </si>
   <si>
     <t>달싹</t>
@@ -938,7 +947,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%87%8C%EC%89%AC</t>
   </si>
   <si>
-    <t>462조 3946억 8834만</t>
+    <t>473조 935억 9830만</t>
   </si>
   <si>
     <t>26길초</t>
@@ -947,7 +956,16 @@
     <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
   </si>
   <si>
-    <t>423조 609억 3629만</t>
+    <t>427조 2003억 2087만</t>
+  </si>
+  <si>
+    <t>서예슬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
+  </si>
+  <si>
+    <t>355조 4228억 3360만</t>
   </si>
   <si>
     <t>26들박</t>
@@ -956,16 +974,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%EB%93%A4%EB%B0%95</t>
   </si>
   <si>
-    <t>329조 7132억 4310만</t>
-  </si>
-  <si>
-    <t>서예슬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
-  </si>
-  <si>
-    <t>311조 8644억 9662만</t>
+    <t>330조 3801억 9081만</t>
   </si>
   <si>
     <t>옴짝</t>
@@ -977,6 +986,15 @@
     <t>267조 4873억 4322만</t>
   </si>
   <si>
+    <t>몬함</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
+  </si>
+  <si>
+    <t>148조 5059억 7662만</t>
+  </si>
+  <si>
     <t>26밍밍</t>
   </si>
   <si>
@@ -992,16 +1010,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
   </si>
   <si>
-    <t>146조 1368억 9777만</t>
-  </si>
-  <si>
-    <t>몬함</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
-  </si>
-  <si>
-    <t>124조 7535억 8679만</t>
+    <t>146조 2127억 6389만</t>
   </si>
   <si>
     <t>뻔수니</t>
@@ -1010,7 +1019,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
   </si>
   <si>
-    <t>70조 3138억 1542만</t>
+    <t>70조 3640억 3678만</t>
   </si>
   <si>
     <t>얼음깨먹기</t>
@@ -1028,7 +1037,16 @@
     <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
   </si>
   <si>
-    <t>37조 4761억 287만</t>
+    <t>37조 7539억 6445만</t>
+  </si>
+  <si>
+    <t>류테</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%8C</t>
+  </si>
+  <si>
+    <t>29조 4752억 2082만</t>
   </si>
   <si>
     <t>쑤삔</t>
@@ -1040,22 +1058,13 @@
     <t>28조 3019억 2162만</t>
   </si>
   <si>
-    <t>류테</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%8C</t>
-  </si>
-  <si>
-    <t>20조 6247억 8310만</t>
-  </si>
-  <si>
     <t>26퐝바</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=26%ED%90%9D%EB%B0%94</t>
   </si>
   <si>
-    <t>19조 7244억 2353만</t>
+    <t>19조 9013억 2453만</t>
   </si>
   <si>
     <t>아모르파티퀘</t>
@@ -1073,7 +1082,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%90%EB%8A%AC</t>
   </si>
   <si>
-    <t>16조 5068억 5050만</t>
+    <t>16조 6522억 3012만</t>
   </si>
   <si>
     <t>26조선</t>
@@ -1106,15 +1115,24 @@
     <t>12조 8151억 908만</t>
   </si>
   <si>
+    <t>뿜삐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>12조 5345억 9009만</t>
+  </si>
+  <si>
     <t>최씨용</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%94%A8%EC%9A%A9</t>
   </si>
   <si>
-    <t>101</t>
-  </si>
-  <si>
     <t>12조 1214억 5182만</t>
   </si>
   <si>
@@ -1124,16 +1142,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
   </si>
   <si>
-    <t>11조 3435억 1205만</t>
-  </si>
-  <si>
-    <t>뿜삐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
-  </si>
-  <si>
-    <t>9조 3250억 4217만</t>
+    <t>11조 5309억 6647만</t>
   </si>
   <si>
     <t>귬스파파</t>
@@ -1163,13 +1172,13 @@
     <t>5조 8558억 8323만</t>
   </si>
   <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EA%B8%B0%EC%9A%94%EB%B0%8B</t>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%9A%94%EB%B0%8B</t>
   </si>
   <si>
     <t>111</t>
   </si>
   <si>
-    <t>1경 5982조 1294억 8442만</t>
+    <t>1경 6018조 9292억 8956만</t>
   </si>
   <si>
     <t>일월마녀</t>
@@ -1187,7 +1196,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%ED%92%8D</t>
   </si>
   <si>
-    <t>1539조 7438억 6316만</t>
+    <t>2066조 6901억 7240만</t>
+  </si>
+  <si>
+    <t>누짜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%88%84%EC%A7%9C</t>
+  </si>
+  <si>
+    <t>826조 6872억 1556만</t>
   </si>
   <si>
     <t>로드숍</t>
@@ -1199,15 +1217,6 @@
     <t>790조 4923억 9555만</t>
   </si>
   <si>
-    <t>누짜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%88%84%EC%A7%9C</t>
-  </si>
-  <si>
-    <t>698조 9405억 1129만</t>
-  </si>
-  <si>
     <t>송곧</t>
   </si>
   <si>
@@ -1232,7 +1241,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%9D%B4%EC%82%AC</t>
   </si>
   <si>
-    <t>183조 1156억 7543만</t>
+    <t>202조 3173억 1129만</t>
   </si>
   <si>
     <t>피몽</t>
@@ -1241,7 +1250,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EB%AA%BD</t>
   </si>
   <si>
-    <t>172조 2611억 5897만</t>
+    <t>180조 3813억 983만</t>
   </si>
   <si>
     <t>진짜지존법사</t>
@@ -1268,7 +1277,7 @@
     <t>https://mgf.gg/contents/character.php?n=ADELL</t>
   </si>
   <si>
-    <t>39조 2931억 101만</t>
+    <t>39조 3817억 8922만</t>
   </si>
   <si>
     <t>태켱</t>
@@ -1277,7 +1286,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BC%B1</t>
   </si>
   <si>
-    <t>19조 5492억 8560만</t>
+    <t>19조 8609억 6211만</t>
   </si>
   <si>
     <t>쿠소가키키</t>
@@ -1286,7 +1295,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EC%86%8C%EA%B0%80%ED%82%A4%ED%82%A4</t>
   </si>
   <si>
-    <t>19조 3549억 5667만</t>
+    <t>19조 3653억 8609만</t>
+  </si>
+  <si>
+    <t>유디티기찬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%94%94%ED%8B%B0%EA%B8%B0%EC%B0%AC</t>
+  </si>
+  <si>
+    <t>14조 952억 8021만</t>
   </si>
   <si>
     <t>왓쳐</t>
@@ -1298,22 +1316,13 @@
     <t>13조 4225억 797만</t>
   </si>
   <si>
-    <t>유디티기찬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%94%94%ED%8B%B0%EA%B8%B0%EC%B0%AC</t>
-  </si>
-  <si>
-    <t>12조 5841억 5205만</t>
-  </si>
-  <si>
     <t>박미쯔</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%AF%B8%EC%AF%94</t>
   </si>
   <si>
-    <t>11조 396억 3541만</t>
+    <t>11조 1492억 1717만</t>
   </si>
   <si>
     <t>끽코</t>
@@ -1331,7 +1340,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%9D%B5%EB%9D%B5</t>
   </si>
   <si>
-    <t>8조 5741억 4400만</t>
+    <t>9조 1576억 3503만</t>
   </si>
   <si>
     <t>키우는건질색</t>
@@ -1349,7 +1358,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%A0%84</t>
   </si>
   <si>
-    <t>6조 9563억 9212만</t>
+    <t>7조 5150억 8566만</t>
   </si>
   <si>
     <t>후아멀로하냐</t>
@@ -1361,7 +1370,7 @@
     <t>99</t>
   </si>
   <si>
-    <t>6조 2410억 1159만</t>
+    <t>6조 6518억 9389만</t>
   </si>
   <si>
     <t>SingA</t>
@@ -1388,7 +1397,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%A0%EC%B7%A8%ED%95%9C%ED%98%B8%EB%9E%91%EC%9D%B4</t>
   </si>
   <si>
-    <t>4조 9474억 7543만</t>
+    <t>5조 518억 7354만</t>
+  </si>
+  <si>
+    <t>한Poll</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9CPoll</t>
+  </si>
+  <si>
+    <t>4조 5474억 2305만</t>
   </si>
   <si>
     <t>수년</t>
@@ -1400,15 +1418,6 @@
     <t>4조 3429억 3876만</t>
   </si>
   <si>
-    <t>한Poll</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9CPoll</t>
-  </si>
-  <si>
-    <t>4조 3050억 8452만</t>
-  </si>
-  <si>
     <t>김치왕뚜껑</t>
   </si>
   <si>
@@ -1424,7 +1433,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EC%8F%98%EC%95%BC%EB%A1%9C%EB%A1%9C</t>
   </si>
   <si>
-    <t>2조 7321억 5062만</t>
+    <t>2조 7419억 3854만</t>
   </si>
   <si>
     <t>치즈왕뚜껑</t>
@@ -1433,7 +1442,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%98%EC%A6%88%EC%99%95%EB%9A%9C%EA%BB%91</t>
   </si>
   <si>
-    <t>2조 1846억 5297만</t>
+    <t>2조 4200억 4456만</t>
   </si>
   <si>
     <t>싸뤽</t>
@@ -1442,7 +1451,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%A4%BD</t>
   </si>
   <si>
-    <t>9288조 7988억 1546만</t>
+    <t>1경 425조 3870억 640만</t>
   </si>
   <si>
     <t>신궁쨩</t>
@@ -1460,7 +1469,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A4%EB%AF%BC</t>
   </si>
   <si>
-    <t>1243조 1722억 9668만</t>
+    <t>1248조 757억 8818만</t>
   </si>
   <si>
     <t>설즈</t>
@@ -1469,7 +1478,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%A6%88</t>
   </si>
   <si>
-    <t>921조 3238억 6430만</t>
+    <t>932조 7496억 7919만</t>
   </si>
   <si>
     <t>약한고등어</t>
@@ -1496,7 +1505,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%94%94%EB%A5%B4</t>
   </si>
   <si>
-    <t>212조 4834억 8037만</t>
+    <t>218조 1202억 7446만</t>
   </si>
   <si>
     <t>항상밝은하루</t>
@@ -1523,7 +1532,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%8A%9C</t>
   </si>
   <si>
-    <t>101조 5005억 6045만</t>
+    <t>103조 906억 2823만</t>
   </si>
   <si>
     <t>월광사</t>
@@ -1550,7 +1559,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EB%82%98%EB%9E%98</t>
   </si>
   <si>
-    <t>45조 2828억 2447만</t>
+    <t>45조 5262억 6458만</t>
   </si>
   <si>
     <t>은달총</t>
@@ -1565,6 +1574,15 @@
     <t>38조 9416억 5281만</t>
   </si>
   <si>
+    <t>뽀라비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
+  </si>
+  <si>
+    <t>26조 659억 4024만</t>
+  </si>
+  <si>
     <t>땩콩</t>
   </si>
   <si>
@@ -1574,15 +1592,6 @@
     <t>25조 6977억 6223만</t>
   </si>
   <si>
-    <t>뽀라비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
-  </si>
-  <si>
-    <t>24조 6417억 7062만</t>
-  </si>
-  <si>
     <t>김대협</t>
   </si>
   <si>
@@ -1598,7 +1607,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A7%9D</t>
   </si>
   <si>
-    <t>13조 6686억 9958만</t>
+    <t>13조 7847억 942만</t>
   </si>
   <si>
     <t>낭만만듀</t>
@@ -1607,7 +1616,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%EB%A7%8C%EB%93%80</t>
   </si>
   <si>
-    <t>11조 4930억 9873만</t>
+    <t>12조 429억 4007만</t>
   </si>
   <si>
     <t>봄녘</t>
@@ -1628,6 +1637,15 @@
     <t>9조 5098억 7158만</t>
   </si>
   <si>
+    <t>빠나딘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A0%EB%82%98%EB%94%98</t>
+  </si>
+  <si>
+    <t>7조 3040억 619만</t>
+  </si>
+  <si>
     <t>봉합불가</t>
   </si>
   <si>
@@ -1637,15 +1655,6 @@
     <t>7조 2028억 4048만</t>
   </si>
   <si>
-    <t>빠나딘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A0%EB%82%98%EB%94%98</t>
-  </si>
-  <si>
-    <t>7조 1388억 6222만</t>
-  </si>
-  <si>
     <t>양카오너</t>
   </si>
   <si>
@@ -1655,7 +1664,7 @@
     <t>97</t>
   </si>
   <si>
-    <t>3조 9612억 7314만</t>
+    <t>4조 641억 9689만</t>
   </si>
   <si>
     <t>강한고등어</t>
@@ -1673,7 +1682,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EC%87%A0%EC%98%81%EB%A7%8C</t>
   </si>
   <si>
-    <t>1조 449억 856만</t>
+    <t>1조 461억 2138만</t>
   </si>
   <si>
     <t>용광사</t>
@@ -1685,13 +1694,13 @@
     <t>96</t>
   </si>
   <si>
-    <t>7680억 9109만</t>
+    <t>7711억 3776만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%AF%94</t>
   </si>
   <si>
-    <t>6424억 6751만</t>
+    <t>6617억 4476만</t>
   </si>
   <si>
     <t>비어치킨</t>
@@ -1703,7 +1712,7 @@
     <t>95</t>
   </si>
   <si>
-    <t>4074억 222만</t>
+    <t>4591억 8954만</t>
   </si>
 </sst>
 </file>
@@ -2343,7 +2352,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2440,13 +2449,13 @@
         <v>70</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2457,22 +2466,22 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>83</v>
@@ -2507,7 +2516,7 @@
         <v>88</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>89</v>
@@ -2539,7 +2548,7 @@
         <v>93</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>94</v>
@@ -2556,16 +2565,16 @@
         <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>98</v>
@@ -2588,16 +2597,16 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>104</v>
@@ -2635,7 +2644,7 @@
         <v>110</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>111</v>
@@ -2664,10 +2673,10 @@
         <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>115</v>
@@ -2699,7 +2708,7 @@
         <v>93</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>119</v>
@@ -2731,7 +2740,7 @@
         <v>123</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>124</v>
@@ -2760,13 +2769,13 @@
         <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="H13" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>129</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2777,25 +2786,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>133</v>
@@ -2824,7 +2833,7 @@
         <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>137</v>
@@ -2891,7 +2900,7 @@
         <v>93</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>146</v>
@@ -2920,7 +2929,7 @@
         <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>137</v>
@@ -2952,13 +2961,13 @@
         <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2969,28 +2978,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="H20" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3004,22 +3013,22 @@
         <v>17</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>159</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>163</v>
@@ -3048,10 +3057,10 @@
         <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>167</v>
@@ -3115,7 +3124,7 @@
         <v>98</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>175</v>
@@ -3144,10 +3153,10 @@
         <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>179</v>
@@ -3176,13 +3185,13 @@
         <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>154</v>
+        <v>104</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3196,22 +3205,22 @@
         <v>45</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>159</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>186</v>
@@ -3240,10 +3249,10 @@
         <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>189</v>
@@ -3272,10 +3281,10 @@
         <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>193</v>
@@ -3304,10 +3313,10 @@
         <v>70</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>197</v>
@@ -3316,8 +3325,40 @@
         <v>24</v>
       </c>
     </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J31"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -3348,6 +3389,7 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
+    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3408,13 +3450,13 @@
         <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>70</v>
@@ -3426,7 +3468,7 @@
         <v>72</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>32</v>
@@ -3440,13 +3482,13 @@
         <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>70</v>
@@ -3455,10 +3497,10 @@
         <v>71</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>32</v>
@@ -3469,16 +3511,16 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>70</v>
@@ -3487,10 +3529,10 @@
         <v>88</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>32</v>
@@ -3504,25 +3546,25 @@
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>32</v>
@@ -3536,25 +3578,25 @@
         <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>32</v>
@@ -3568,13 +3610,13 @@
         <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>70</v>
@@ -3583,10 +3625,10 @@
         <v>123</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>32</v>
@@ -3600,13 +3642,13 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>70</v>
@@ -3615,10 +3657,10 @@
         <v>93</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>32</v>
@@ -3632,13 +3674,13 @@
         <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>70</v>
@@ -3647,10 +3689,10 @@
         <v>93</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>32</v>
@@ -3664,13 +3706,13 @@
         <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>70</v>
@@ -3682,7 +3724,7 @@
         <v>137</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>32</v>
@@ -3696,13 +3738,13 @@
         <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>70</v>
@@ -3714,7 +3756,7 @@
         <v>137</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>32</v>
@@ -3728,25 +3770,25 @@
         <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>137</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>32</v>
@@ -3760,25 +3802,25 @@
         <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>32</v>
@@ -3789,28 +3831,28 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>137</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>32</v>
@@ -3824,25 +3866,25 @@
         <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>137</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>32</v>
@@ -3856,25 +3898,25 @@
         <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>32</v>
@@ -3888,25 +3930,25 @@
         <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>32</v>
@@ -3920,13 +3962,13 @@
         <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>70</v>
@@ -3938,7 +3980,7 @@
         <v>137</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>32</v>
@@ -3952,25 +3994,25 @@
         <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>32</v>
@@ -3981,28 +4023,28 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>32</v>
@@ -4016,25 +4058,25 @@
         <v>17</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>32</v>
@@ -4048,13 +4090,13 @@
         <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>70</v>
@@ -4063,10 +4105,10 @@
         <v>104</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>32</v>
@@ -4080,25 +4122,25 @@
         <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>32</v>
@@ -4112,25 +4154,25 @@
         <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>32</v>
@@ -4150,19 +4192,19 @@
         <v>31</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>88</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>32</v>
@@ -4176,13 +4218,13 @@
         <v>36</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>70</v>
@@ -4191,10 +4233,10 @@
         <v>88</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>32</v>
@@ -4208,25 +4250,25 @@
         <v>45</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>32</v>
@@ -4240,25 +4282,25 @@
         <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>32</v>
@@ -4272,13 +4314,13 @@
         <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>70</v>
@@ -4287,10 +4329,10 @@
         <v>110</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>32</v>
@@ -4304,13 +4346,13 @@
         <v>194</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>70</v>
@@ -4319,10 +4361,10 @@
         <v>93</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>32</v>
@@ -4333,28 +4375,28 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>285</v>
+        <v>198</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>32</v>
@@ -4453,25 +4495,25 @@
         <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4491,19 +4533,19 @@
         <v>41</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>71</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4514,28 +4556,28 @@
         <v>33</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4549,25 +4591,25 @@
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4581,13 +4623,13 @@
         <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>70</v>
@@ -4596,10 +4638,10 @@
         <v>123</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4613,13 +4655,13 @@
         <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>70</v>
@@ -4628,10 +4670,10 @@
         <v>93</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4645,25 +4687,25 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4677,25 +4719,25 @@
         <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4709,13 +4751,13 @@
         <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>70</v>
@@ -4724,10 +4766,10 @@
         <v>88</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4741,25 +4783,25 @@
         <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4773,25 +4815,25 @@
         <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4805,25 +4847,25 @@
         <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4834,28 +4876,28 @@
         <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4869,13 +4911,13 @@
         <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>70</v>
@@ -4884,10 +4926,10 @@
         <v>88</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4901,25 +4943,25 @@
         <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4933,25 +4975,25 @@
         <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4965,25 +5007,25 @@
         <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -4997,13 +5039,13 @@
         <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>70</v>
@@ -5012,10 +5054,10 @@
         <v>88</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5026,16 +5068,16 @@
         <v>33</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>70</v>
@@ -5044,10 +5086,10 @@
         <v>88</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5061,25 +5103,25 @@
         <v>17</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5093,13 +5135,13 @@
         <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>70</v>
@@ -5108,10 +5150,10 @@
         <v>88</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5125,13 +5167,13 @@
         <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>70</v>
@@ -5140,10 +5182,10 @@
         <v>123</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5157,25 +5199,25 @@
         <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5189,25 +5231,25 @@
         <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5221,25 +5263,25 @@
         <v>36</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E26" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>361</v>
-      </c>
       <c r="I26" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5253,25 +5295,25 @@
         <v>45</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5285,13 +5327,13 @@
         <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>70</v>
@@ -5300,10 +5342,10 @@
         <v>88</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5317,13 +5359,13 @@
         <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>70</v>
@@ -5332,10 +5374,10 @@
         <v>88</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5349,25 +5391,25 @@
         <v>194</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5471,19 +5513,19 @@
         <v>48</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>88</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5497,13 +5539,13 @@
         <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>70</v>
@@ -5512,10 +5554,10 @@
         <v>110</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5526,16 +5568,16 @@
         <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>70</v>
@@ -5544,10 +5586,10 @@
         <v>110</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5561,25 +5603,25 @@
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5593,25 +5635,25 @@
         <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5625,13 +5667,13 @@
         <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>70</v>
@@ -5640,10 +5682,10 @@
         <v>88</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5657,13 +5699,13 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>70</v>
@@ -5672,10 +5714,10 @@
         <v>110</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5689,25 +5731,25 @@
         <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5721,13 +5763,13 @@
         <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>70</v>
@@ -5739,7 +5781,7 @@
         <v>137</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5753,13 +5795,13 @@
         <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>70</v>
@@ -5768,10 +5810,10 @@
         <v>88</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5785,25 +5827,25 @@
         <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5817,13 +5859,13 @@
         <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>70</v>
@@ -5832,10 +5874,10 @@
         <v>93</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5846,16 +5888,16 @@
         <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>70</v>
@@ -5864,10 +5906,10 @@
         <v>93</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5881,13 +5923,13 @@
         <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>70</v>
@@ -5896,10 +5938,10 @@
         <v>110</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5913,13 +5955,13 @@
         <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>70</v>
@@ -5928,10 +5970,10 @@
         <v>98</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>182</v>
+        <v>364</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5945,13 +5987,13 @@
         <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>70</v>
@@ -5960,10 +6002,10 @@
         <v>104</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>361</v>
+        <v>185</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5977,13 +6019,13 @@
         <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>70</v>
@@ -5992,10 +6034,10 @@
         <v>88</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6009,13 +6051,13 @@
         <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>70</v>
@@ -6024,10 +6066,10 @@
         <v>88</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6038,16 +6080,16 @@
         <v>42</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>70</v>
@@ -6056,10 +6098,10 @@
         <v>93</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6073,13 +6115,13 @@
         <v>17</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>70</v>
@@ -6088,10 +6130,10 @@
         <v>88</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6105,13 +6147,13 @@
         <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>70</v>
@@ -6120,10 +6162,10 @@
         <v>110</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6137,13 +6179,13 @@
         <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>70</v>
@@ -6152,10 +6194,10 @@
         <v>110</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6169,13 +6211,13 @@
         <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>70</v>
@@ -6184,10 +6226,10 @@
         <v>71</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6201,25 +6243,25 @@
         <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6233,25 +6275,25 @@
         <v>36</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6265,25 +6307,25 @@
         <v>45</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>361</v>
+        <v>446</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6297,25 +6339,25 @@
         <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>443</v>
+        <v>364</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6329,25 +6371,25 @@
         <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6361,13 +6403,13 @@
         <v>194</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>70</v>
@@ -6376,10 +6418,10 @@
         <v>88</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6390,28 +6432,28 @@
         <v>42</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>285</v>
+        <v>198</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>443</v>
+        <v>357</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6466,7 +6508,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6510,13 +6552,13 @@
         <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>70</v>
@@ -6525,10 +6567,10 @@
         <v>71</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6542,13 +6584,13 @@
         <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>70</v>
@@ -6557,10 +6599,10 @@
         <v>93</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6571,28 +6613,28 @@
         <v>49</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6606,13 +6648,13 @@
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>70</v>
@@ -6621,10 +6663,10 @@
         <v>93</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6638,25 +6680,25 @@
         <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>110</v>
+        <v>158</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6670,25 +6712,25 @@
         <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6702,13 +6744,13 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>70</v>
@@ -6717,10 +6759,10 @@
         <v>71</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6734,13 +6776,13 @@
         <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>70</v>
@@ -6749,10 +6791,10 @@
         <v>71</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6766,13 +6808,13 @@
         <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>70</v>
@@ -6784,7 +6826,7 @@
         <v>137</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6798,25 +6840,25 @@
         <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>137</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6830,13 +6872,13 @@
         <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>70</v>
@@ -6845,10 +6887,10 @@
         <v>71</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6862,13 +6904,13 @@
         <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>70</v>
@@ -6877,10 +6919,10 @@
         <v>110</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6891,16 +6933,16 @@
         <v>49</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>70</v>
@@ -6909,10 +6951,10 @@
         <v>110</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6926,25 +6968,25 @@
         <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6958,13 +7000,13 @@
         <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>70</v>
@@ -6973,10 +7015,10 @@
         <v>88</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>251</v>
+        <v>364</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6990,13 +7032,13 @@
         <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>70</v>
@@ -7005,10 +7047,10 @@
         <v>88</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>361</v>
+        <v>255</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7022,13 +7064,13 @@
         <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>70</v>
@@ -7037,10 +7079,10 @@
         <v>93</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7054,25 +7096,25 @@
         <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7083,16 +7125,16 @@
         <v>49</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>70</v>
@@ -7101,10 +7143,10 @@
         <v>88</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7118,13 +7160,13 @@
         <v>17</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>70</v>
@@ -7133,10 +7175,10 @@
         <v>110</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7150,13 +7192,13 @@
         <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>70</v>
@@ -7165,10 +7207,10 @@
         <v>110</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7182,13 +7224,13 @@
         <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>70</v>
@@ -7197,10 +7239,10 @@
         <v>93</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7214,13 +7256,13 @@
         <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>70</v>
@@ -7229,10 +7271,10 @@
         <v>93</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7246,25 +7288,25 @@
         <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7278,25 +7320,25 @@
         <v>36</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7310,13 +7352,13 @@
         <v>45</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>70</v>
@@ -7325,10 +7367,10 @@
         <v>93</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7342,13 +7384,13 @@
         <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>70</v>
@@ -7357,10 +7399,10 @@
         <v>71</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7380,19 +7422,19 @@
         <v>58</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>71</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -7406,25 +7448,25 @@
         <v>194</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -80,546 +80,549 @@
     <t>Scania 26</t>
   </si>
   <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>2위</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>3경 318조 863억 9244만</t>
+  </si>
+  <si>
+    <t>가입문의 : 닭도리도리탕, 티짐 20조 이상 문의바랍니다.</t>
+  </si>
+  <si>
+    <t>티짐</t>
+  </si>
+  <si>
+    <t>2026.04.15</t>
+  </si>
+  <si>
+    <t>셀린느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%85%80%EB%A6%B0%EB%8A%90</t>
+  </si>
+  <si>
+    <t>Scania 2</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>1위</t>
+  </si>
+  <si>
+    <t>2경 2301조 6004억 1090만</t>
+  </si>
+  <si>
+    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
+  </si>
+  <si>
+    <t>혜영</t>
+  </si>
+  <si>
+    <t>2026.04.14</t>
+  </si>
+  <si>
+    <t>LUXURY</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
+  </si>
+  <si>
+    <t>Scania 16</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Lv.9</t>
+  </si>
+  <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>2경 4536조 7164억 1513만</t>
+  </si>
+  <si>
+    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
+  </si>
+  <si>
+    <t>살뽀시</t>
+  </si>
+  <si>
+    <t>호러</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%ED%98%B8%EB%9F%AC</t>
+  </si>
+  <si>
+    <t>Scania 10</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>2경 5706조 9974억 6737만</t>
+  </si>
+  <si>
+    <t>오래 하실분들 환영입니다</t>
+  </si>
+  <si>
+    <t>기요밋</t>
+  </si>
+  <si>
+    <t>이콩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
+  </si>
+  <si>
+    <t>Scania 28</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>3위</t>
+  </si>
+  <si>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>2경 3611조 9079억 5482만</t>
+  </si>
+  <si>
+    <t>가입문의 - 요쯔</t>
+  </si>
+  <si>
+    <t>요쯔</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>냐락불곰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%B6%88%EA%B3%B0</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>1경 4125조 5992억 2989만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>냐락오리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EC%98%A4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>2633조 5220억 3364만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>썬콜법사님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%AC%EB%8B%98</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>2534조 6580억 8868만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>냐락겅듀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EA%B2%85%EB%93%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>2487조 9861억 8548만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>벽서</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%BD%EC%84%9C</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>1520조 7456억 7835만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>냐락바람</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%B0%94%EB%9E%8C</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>964조 9615억 8471만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%A7%90</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>932조 1239억 4952만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>이대팔가르마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%8C%80%ED%8C%94%EA%B0%80%EB%A5%B4%EB%A7%88</t>
+  </si>
+  <si>
+    <t>841조 9427억 5728만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>닭도리도리탕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AD%EB%8F%84%EB%A6%AC%EB%8F%84%EB%A6%AC%ED%83%95</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>777조 6064억 4990만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>눈꽃체리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%88%88%EA%BD%83%EC%B2%B4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>503조 6027억 4386만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>떠네쨩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%96%A0%EB%84%A4%EC%A8%A9</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>503조 1799억 8663만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>망치두고튀어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EB%91%90%EA%B3%A0%ED%8A%80%EC%96%B4</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>456조 817억 2556만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>냐락크리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%ED%81%AC%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>339조 8320억 9033만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>왕푸맨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%ED%91%B8%EB%A7%A8</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>299조 7077억 8873만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>냐락셋째</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EC%85%8B%EC%A7%B8</t>
+  </si>
+  <si>
+    <t>211조 3286억 9983만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>냐락린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>193조 6810억 7098만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>냐락쿠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EC%BF%A0</t>
+  </si>
+  <si>
+    <t>176조 3550억 4379만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>욕박고시작</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%95%EB%B0%95%EA%B3%A0%EC%8B%9C%EC%9E%91</t>
+  </si>
+  <si>
+    <t>169조 8634억 5863만</t>
+  </si>
+  <si>
+    <t>쀼움</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%80%BC%EC%9B%80</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>169조 8582억 5050만</t>
+  </si>
+  <si>
     <t>20</t>
   </si>
   <si>
-    <t>1위</t>
-  </si>
-  <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>2경 5593조 233억 9645만</t>
-  </si>
-  <si>
-    <t>가입문의 : 닭도리도리탕, 티짐 20조 이상 문의바랍니다.</t>
-  </si>
-  <si>
-    <t>티짐</t>
-  </si>
-  <si>
-    <t>2026.04.10</t>
-  </si>
-  <si>
-    <t>셀린느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%85%80%EB%A6%B0%EB%8A%90</t>
-  </si>
-  <si>
-    <t>Scania 2</t>
+    <t>삼양일짱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%BC%EC%96%91%EC%9D%BC%EC%A7%B1</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>143조 9772억 6301만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>안지연</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%A7%80%EC%97%B0</t>
+  </si>
+  <si>
+    <t>125조 7526억 2938만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Cerberus</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Cerberus</t>
+  </si>
+  <si>
+    <t>107조 5759억 682만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>냐락뀨리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%80%A8%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>106조 8432억 1451만</t>
+  </si>
+  <si>
+    <t>Centauros</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Centauros</t>
+  </si>
+  <si>
+    <t>96조 44억 4021만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>국레쏘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EB%A0%88%EC%8F%98</t>
+  </si>
+  <si>
+    <t>73조 5156억 1979만</t>
+  </si>
+  <si>
+    <t>이강민둥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B0%95%EB%AF%BC%EB%91%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>67조 223억 9864만</t>
   </si>
   <si>
     <t>27</t>
   </si>
   <si>
-    <t>2경 302조 8354억 4885만</t>
-  </si>
-  <si>
-    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
-  </si>
-  <si>
-    <t>혜영</t>
-  </si>
-  <si>
-    <t>2026.04.11</t>
-  </si>
-  <si>
-    <t>LUXURY</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
-  </si>
-  <si>
-    <t>Scania 16</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>Lv.9</t>
-  </si>
-  <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>2경 2185조 8183억 1617만</t>
-  </si>
-  <si>
-    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
-  </si>
-  <si>
-    <t>살뽀시</t>
-  </si>
-  <si>
-    <t>호러</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%ED%98%B8%EB%9F%AC</t>
-  </si>
-  <si>
-    <t>Scania 10</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>2경 1593조 2154억 9496만</t>
-  </si>
-  <si>
-    <t>오래 하실분들 환영입니다</t>
-  </si>
-  <si>
-    <t>기요밋</t>
-  </si>
-  <si>
-    <t>이콩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EC%BD%A9</t>
-  </si>
-  <si>
-    <t>Scania 28</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>4위</t>
-  </si>
-  <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
-    <t>28명</t>
-  </si>
-  <si>
-    <t>1경 9137조 3448억 6787만</t>
-  </si>
-  <si>
-    <t>가입문의 - 요쯔</t>
-  </si>
-  <si>
-    <t>요쯔</t>
-  </si>
-  <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>냐락불곰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%B6%88%EA%B3%B0</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>1경 3698조 6829억 2352만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>냐락오리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EC%98%A4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>2501조 8002억 9960만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>냐락겅듀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EA%B2%85%EB%93%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>2410조 7596억 8543만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>썬콜법사님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%AC%EB%8B%98</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>2300조 5822억 8475만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>벽서</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%BD%EC%84%9C</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>1485조 1957억 9871만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>냐락바람</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%B0%94%EB%9E%8C</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>964조 9615억 8471만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%A7%90</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>906조 3743억 5904만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>닭도리도리탕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AD%EB%8F%84%EB%A6%AC%EB%8F%84%EB%A6%AC%ED%83%95</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>777조 6064억 4990만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>이대팔가르마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%8C%80%ED%8C%94%EA%B0%80%EB%A5%B4%EB%A7%88</t>
-  </si>
-  <si>
-    <t>744조 9863억 2699만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>눈꽃체리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%88%88%EA%BD%83%EC%B2%B4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>502조 6372억 1549만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>망치두고튀어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EB%91%90%EA%B3%A0%ED%8A%80%EC%96%B4</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>456조 817억 2556만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>떠네쨩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%96%A0%EB%84%A4%EC%A8%A9</t>
-  </si>
-  <si>
-    <t>448조 9268억 5837만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>냐락크리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%ED%81%AC%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>332조 2211억 9240만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>왕푸맨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%ED%91%B8%EB%A7%A8</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>282조 628억 1566만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>냐락셋째</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EC%85%8B%EC%A7%B8</t>
-  </si>
-  <si>
-    <t>211조 3286억 9983만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>냐락린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>193조 6810억 7098만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>냐락쿠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EC%BF%A0</t>
-  </si>
-  <si>
-    <t>169조 3850억 998만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>욕박고시작</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%95%EB%B0%95%EA%B3%A0%EC%8B%9C%EC%9E%91</t>
-  </si>
-  <si>
-    <t>161조 6395억 7471만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>쀼움</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%80%BC%EC%9B%80</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>157조 1751억 7341만</t>
-  </si>
-  <si>
-    <t>삼양일짱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%BC%EC%96%91%EC%9D%BC%EC%A7%B1</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>133조 5577억 192만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>안지연</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%A7%80%EC%97%B0</t>
-  </si>
-  <si>
-    <t>122조 8232억 5720만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>Cerberus</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Cerberus</t>
-  </si>
-  <si>
-    <t>107조 5759억 682만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>냐락뀨리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%80%A8%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>106조 8432억 1451만</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>Centauros</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Centauros</t>
-  </si>
-  <si>
-    <t>93조 3803억 4975만</t>
-  </si>
-  <si>
-    <t>이강민둥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B0%95%EB%AF%BC%EB%91%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>67조 223억 9864만</t>
-  </si>
-  <si>
     <t>히들</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EB%93%A4</t>
   </si>
   <si>
+    <t>66조 5056억 7788만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>김채희</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B1%84%ED%9D%AC</t>
+  </si>
+  <si>
+    <t>39조 4280억 9037만</t>
+  </si>
+  <si>
+    <t>세정린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%A0%95%EB%A6%B0</t>
+  </si>
+  <si>
     <t>103</t>
   </si>
   <si>
-    <t>66조 5056억 7788만</t>
-  </si>
-  <si>
-    <t>국레쏘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EB%A0%88%EC%8F%98</t>
-  </si>
-  <si>
-    <t>59조 3548억 9887만</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>김채희</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B1%84%ED%9D%AC</t>
-  </si>
-  <si>
-    <t>38조 9225억 9647만</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>세정린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%A0%95%EB%A6%B0</t>
-  </si>
-  <si>
     <t>37조 5529억 1971만</t>
   </si>
   <si>
@@ -659,7 +662,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>2202조 8792억 6515만</t>
+    <t>2283조 7142억 7674만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -668,7 +671,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
   </si>
   <si>
-    <t>1182조 6684억 3913만</t>
+    <t>1394조 1932억 8825만</t>
+  </si>
+  <si>
+    <t>빌런투킬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
+  </si>
+  <si>
+    <t>1120조 9927억 5165만</t>
   </si>
   <si>
     <t>스타캐치</t>
@@ -680,22 +692,13 @@
     <t>1112조 8677억 9360만</t>
   </si>
   <si>
-    <t>빌런투킬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
-  </si>
-  <si>
-    <t>1022조 1463억 7965만</t>
-  </si>
-  <si>
     <t>스타뎀</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%8E%80</t>
   </si>
   <si>
-    <t>315조 3104억 9477만</t>
+    <t>475조 5893억 7767만</t>
   </si>
   <si>
     <t>여사</t>
@@ -704,7 +707,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
   </si>
   <si>
-    <t>305조 8357억 2579만</t>
+    <t>400조 1307억 6796만</t>
   </si>
   <si>
     <t>단풍노비</t>
@@ -716,13 +719,22 @@
     <t>176조 573억 7249만</t>
   </si>
   <si>
+    <t>부엉이없다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>153조 4242억 2362만</t>
+  </si>
+  <si>
     <t>약어</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
   </si>
   <si>
-    <t>147조 7288억 7111만</t>
+    <t>152조 6744억 2175만</t>
   </si>
   <si>
     <t>프리프리</t>
@@ -734,15 +746,6 @@
     <t>143조 1307억 9972만</t>
   </si>
   <si>
-    <t>부엉이없다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>140조 8180억 9133만</t>
-  </si>
-  <si>
     <t>꽃을든남자</t>
   </si>
   <si>
@@ -758,7 +761,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
   </si>
   <si>
-    <t>86조 6580억 5183만</t>
+    <t>89조 2869억 199만</t>
   </si>
   <si>
     <t>하후돈</t>
@@ -767,7 +770,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
   </si>
   <si>
-    <t>74조 5245억 2328만</t>
+    <t>83조 3411억 4487만</t>
   </si>
   <si>
     <t>잼포즈</t>
@@ -776,7 +779,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>74조 2546억 7807만</t>
+    <t>75조 5035억 6634만</t>
   </si>
   <si>
     <t>POSCO</t>
@@ -785,7 +788,7 @@
     <t>https://mgf.gg/contents/character.php?n=POSCO</t>
   </si>
   <si>
-    <t>59조 1651억 31만</t>
+    <t>65조 7697억 3285만</t>
   </si>
   <si>
     <t>소소채2</t>
@@ -797,7 +800,16 @@
     <t>102</t>
   </si>
   <si>
-    <t>56조 9226억 6343만</t>
+    <t>64조 3897억 2993만</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>42조 7569억 3167만</t>
   </si>
   <si>
     <t>할룽</t>
@@ -815,16 +827,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
   </si>
   <si>
-    <t>38조 568억 6620만</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>37조 1057억 885만</t>
+    <t>38조 1459억 7981만</t>
   </si>
   <si>
     <t>두근푸근연근</t>
@@ -833,7 +836,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
   </si>
   <si>
-    <t>33조 7492억 4506만</t>
+    <t>37조 4329억 7511만</t>
+  </si>
+  <si>
+    <t>포뇨야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
+  </si>
+  <si>
+    <t>35조 3962억 1100만</t>
   </si>
   <si>
     <t>대방어조아</t>
@@ -842,13 +854,22 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
   </si>
   <si>
-    <t>31조 4997억 1522만</t>
+    <t>32조 3503억 166만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
   </si>
   <si>
-    <t>28조 2054억 3268만</t>
+    <t>28조 5128억 7466만</t>
+  </si>
+  <si>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>28조 3422억 4602만</t>
   </si>
   <si>
     <t>울힝</t>
@@ -860,31 +881,13 @@
     <t>27조 7168억 210만</t>
   </si>
   <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>25조 7875억 6068만</t>
-  </si>
-  <si>
-    <t>포뇨야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
-  </si>
-  <si>
-    <t>25조 4912억 9969만</t>
-  </si>
-  <si>
     <t>악의꽃</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
   </si>
   <si>
-    <t>23조 3285억 9707만</t>
+    <t>25조 817억 1488만</t>
   </si>
   <si>
     <t>몽호</t>
@@ -893,7 +896,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
   </si>
   <si>
-    <t>21조 327억 3756만</t>
+    <t>22조 9589억 8035만</t>
   </si>
   <si>
     <t>junoflo</t>
@@ -902,7 +905,7 @@
     <t>https://mgf.gg/contents/character.php?n=junoflo</t>
   </si>
   <si>
-    <t>10조 7228억 5142만</t>
+    <t>10조 9422억 5450만</t>
   </si>
   <si>
     <t>가숭혁</t>
@@ -920,7 +923,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%B4%EB%BD%80%EC%8B%9C</t>
   </si>
   <si>
-    <t>2516조 4761억 566만</t>
+    <t>111</t>
+  </si>
+  <si>
+    <t>2604조 1519억 6474만</t>
   </si>
   <si>
     <t>26상탗</t>
@@ -929,7 +935,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%EC%83%81%ED%83%97</t>
   </si>
   <si>
-    <t>1448조 1213억 6213만</t>
+    <t>1601조 7815억 6566만</t>
   </si>
   <si>
     <t>달싹</t>
@@ -938,7 +944,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EC%8B%B9</t>
   </si>
   <si>
-    <t>650조 9376억 9597만</t>
+    <t>651조 4386억 2995만</t>
   </si>
   <si>
     <t>뇌쉬</t>
@@ -956,7 +962,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
   </si>
   <si>
-    <t>427조 2003억 2087만</t>
+    <t>437조 2061억 5293만</t>
   </si>
   <si>
     <t>서예슬</t>
@@ -974,7 +980,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%EB%93%A4%EB%B0%95</t>
   </si>
   <si>
-    <t>330조 3801억 9081만</t>
+    <t>342조 5420억 8712만</t>
   </si>
   <si>
     <t>옴짝</t>
@@ -992,34 +998,34 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
   </si>
   <si>
-    <t>148조 5059억 7662만</t>
-  </si>
-  <si>
-    <t>26밍밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%8D%EB%B0%8D</t>
+    <t>177조 5670억 5779만</t>
+  </si>
+  <si>
+    <t>임승민</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
+  </si>
+  <si>
+    <t>161조 2593억 1562만</t>
+  </si>
+  <si>
+    <t>중타치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A4%91%ED%83%80%EC%B9%98</t>
   </si>
   <si>
     <t>146조 2366억 2351만</t>
   </si>
   <si>
-    <t>임승민</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
-  </si>
-  <si>
-    <t>146조 2127억 6389만</t>
-  </si>
-  <si>
     <t>뻔수니</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
   </si>
   <si>
-    <t>70조 3640억 3678만</t>
+    <t>83조 6254억 8539만</t>
   </si>
   <si>
     <t>얼음깨먹기</t>
@@ -1028,7 +1034,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EC%9D%8C%EA%B9%A8%EB%A8%B9%EA%B8%B0</t>
   </si>
   <si>
-    <t>54조 757억 7660만</t>
+    <t>59조 6571억 7041만</t>
   </si>
   <si>
     <t>26배털</t>
@@ -1037,7 +1043,16 @@
     <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
   </si>
   <si>
-    <t>37조 7539억 6445만</t>
+    <t>38조 8453억 6606만</t>
+  </si>
+  <si>
+    <t>쑤삔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%91%A4%EC%82%94</t>
+  </si>
+  <si>
+    <t>30조 6445억 1264만</t>
   </si>
   <si>
     <t>류테</t>
@@ -1049,22 +1064,13 @@
     <t>29조 4752억 2082만</t>
   </si>
   <si>
-    <t>쑤삔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%91%A4%EC%82%94</t>
-  </si>
-  <si>
-    <t>28조 3019억 2162만</t>
-  </si>
-  <si>
     <t>26퐝바</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=26%ED%90%9D%EB%B0%94</t>
   </si>
   <si>
-    <t>19조 9013억 2453만</t>
+    <t>21조 2028억 7543만</t>
   </si>
   <si>
     <t>아모르파티퀘</t>
@@ -1073,7 +1079,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
   </si>
   <si>
-    <t>18조 1110억 6972만</t>
+    <t>20조 3738억 8689만</t>
   </si>
   <si>
     <t>뻐늬</t>
@@ -1082,7 +1088,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%90%EB%8A%AC</t>
   </si>
   <si>
-    <t>16조 6522억 3012만</t>
+    <t>17조 6676억 1993만</t>
   </si>
   <si>
     <t>26조선</t>
@@ -1112,7 +1118,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EA%B9%83</t>
   </si>
   <si>
-    <t>12조 8151억 908만</t>
+    <t>13조 8329억 6602만</t>
   </si>
   <si>
     <t>뿜삐</t>
@@ -1127,6 +1133,15 @@
     <t>12조 5345억 9009만</t>
   </si>
   <si>
+    <t>크앙레몬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>12조 3514억 8343만</t>
+  </si>
+  <si>
     <t>최씨용</t>
   </si>
   <si>
@@ -1136,13 +1151,13 @@
     <t>12조 1214억 5182만</t>
   </si>
   <si>
-    <t>크앙레몬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>11조 5309억 6647만</t>
+    <t>예라미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>7조 8227억 8591만</t>
   </si>
   <si>
     <t>귬스파파</t>
@@ -1154,15 +1169,6 @@
     <t>6조 8903억 4281만</t>
   </si>
   <si>
-    <t>예라미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>6조 6146억 1716만</t>
-  </si>
-  <si>
     <t>고영희멈뭄미</t>
   </si>
   <si>
@@ -1175,10 +1181,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%9A%94%EB%B0%8B</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>1경 6018조 9292억 8956만</t>
+    <t>1경 6497조 902억 5584만</t>
   </si>
   <si>
     <t>일월마녀</t>
@@ -1196,7 +1199,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%ED%92%8D</t>
   </si>
   <si>
-    <t>2066조 6901억 7240만</t>
+    <t>2098조 2328억 5174만</t>
   </si>
   <si>
     <t>누짜</t>
@@ -1205,7 +1208,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%88%84%EC%A7%9C</t>
   </si>
   <si>
-    <t>826조 6872억 1556만</t>
+    <t>831조 6038억 4515만</t>
   </si>
   <si>
     <t>로드숍</t>
@@ -1223,7 +1226,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%A1%EA%B3%A7</t>
   </si>
   <si>
-    <t>581조 5500억 3401만</t>
+    <t>585조 4268억 1881만</t>
   </si>
   <si>
     <t>똥으리</t>
@@ -1232,7 +1235,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EC%9C%BC%EB%A6%AC</t>
   </si>
   <si>
-    <t>266조 8506억 6360만</t>
+    <t>285조 322억 2842만</t>
   </si>
   <si>
     <t>다이사</t>
@@ -1241,7 +1244,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%9D%B4%EC%82%AC</t>
   </si>
   <si>
-    <t>202조 3173억 1129만</t>
+    <t>210조 9912억 9752만</t>
   </si>
   <si>
     <t>피몽</t>
@@ -1250,7 +1253,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EB%AA%BD</t>
   </si>
   <si>
-    <t>180조 3813억 983만</t>
+    <t>197조 3967억 6859만</t>
   </si>
   <si>
     <t>진짜지존법사</t>
@@ -1259,7 +1262,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%A7%9C%EC%A7%80%EC%A1%B4%EB%B2%95%EC%82%AC</t>
   </si>
   <si>
-    <t>116조 5809억 6591만</t>
+    <t>121조 6230억 5539만</t>
   </si>
   <si>
     <t>원순철</t>
@@ -1268,7 +1271,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%88%9C%EC%B2%A0</t>
   </si>
   <si>
-    <t>47조 2419억 4473만</t>
+    <t>47조 7024억 8512만</t>
   </si>
   <si>
     <t>ADELL</t>
@@ -1277,7 +1280,7 @@
     <t>https://mgf.gg/contents/character.php?n=ADELL</t>
   </si>
   <si>
-    <t>39조 3817억 8922만</t>
+    <t>42조 5691억 8437만</t>
   </si>
   <si>
     <t>태켱</t>
@@ -1286,7 +1289,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BC%B1</t>
   </si>
   <si>
-    <t>19조 8609억 6211만</t>
+    <t>20조 94억 66만</t>
   </si>
   <si>
     <t>쿠소가키키</t>
@@ -1295,7 +1298,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EC%86%8C%EA%B0%80%ED%82%A4%ED%82%A4</t>
   </si>
   <si>
-    <t>19조 3653억 8609만</t>
+    <t>19조 3948억 273만</t>
   </si>
   <si>
     <t>유디티기찬</t>
@@ -1307,6 +1310,15 @@
     <t>14조 952억 8021만</t>
   </si>
   <si>
+    <t>끽코</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%81%BD%EC%BD%94</t>
+  </si>
+  <si>
+    <t>13조 7773억 9953만</t>
+  </si>
+  <si>
     <t>왓쳐</t>
   </si>
   <si>
@@ -1322,16 +1334,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%AF%B8%EC%AF%94</t>
   </si>
   <si>
-    <t>11조 1492억 1717만</t>
-  </si>
-  <si>
-    <t>끽코</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%81%BD%EC%BD%94</t>
-  </si>
-  <si>
-    <t>10조 5748억 5807만</t>
+    <t>12조 8265억 5390만</t>
   </si>
   <si>
     <t>강띵띵</t>
@@ -1340,7 +1343,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%9D%B5%EB%9D%B5</t>
   </si>
   <si>
-    <t>9조 1576억 3503만</t>
+    <t>9조 1785억 5900만</t>
   </si>
   <si>
     <t>키우는건질색</t>
@@ -1367,19 +1370,19 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EC%95%84%EB%A9%80%EB%A1%9C%ED%95%98%EB%83%90</t>
   </si>
   <si>
+    <t>7조 3244억 896만</t>
+  </si>
+  <si>
+    <t>SingA</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=SingA</t>
+  </si>
+  <si>
     <t>99</t>
   </si>
   <si>
-    <t>6조 6518억 9389만</t>
-  </si>
-  <si>
-    <t>SingA</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=SingA</t>
-  </si>
-  <si>
-    <t>6조 326억 8572만</t>
+    <t>6조 4585억 5406만</t>
   </si>
   <si>
     <t>햄쓱이</t>
@@ -1388,7 +1391,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%96%84%EC%93%B1%EC%9D%B4</t>
   </si>
   <si>
-    <t>5조 4672억 9243만</t>
+    <t>6조 829억 6294만</t>
   </si>
   <si>
     <t>술취한호랑이</t>
@@ -1397,7 +1400,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%A0%EC%B7%A8%ED%95%9C%ED%98%B8%EB%9E%91%EC%9D%B4</t>
   </si>
   <si>
-    <t>5조 518억 7354만</t>
+    <t>5조 4573억 8251만</t>
   </si>
   <si>
     <t>한Poll</t>
@@ -1406,7 +1409,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9CPoll</t>
   </si>
   <si>
-    <t>4조 5474억 2305만</t>
+    <t>4조 8436억 9982만</t>
   </si>
   <si>
     <t>수년</t>
@@ -1415,7 +1418,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%85%84</t>
   </si>
   <si>
-    <t>4조 3429억 3876만</t>
+    <t>4조 5839억 3632만</t>
   </si>
   <si>
     <t>김치왕뚜껑</t>
@@ -1433,7 +1436,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%EC%8F%98%EC%95%BC%EB%A1%9C%EB%A1%9C</t>
   </si>
   <si>
-    <t>2조 7419억 3854만</t>
+    <t>2조 9861억 6830만</t>
   </si>
   <si>
     <t>치즈왕뚜껑</t>
@@ -1442,7 +1445,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%98%EC%A6%88%EC%99%95%EB%9A%9C%EA%BB%91</t>
   </si>
   <si>
-    <t>2조 4200억 4456만</t>
+    <t>2조 5913억 7317만</t>
   </si>
   <si>
     <t>싸뤽</t>
@@ -1451,7 +1454,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EB%A4%BD</t>
   </si>
   <si>
-    <t>1경 425조 3870억 640만</t>
+    <t>1경 466조 380억 5867만</t>
   </si>
   <si>
     <t>신궁쨩</t>
@@ -1469,7 +1472,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A4%EB%AF%BC</t>
   </si>
   <si>
-    <t>1248조 757억 8818만</t>
+    <t>1316조 9476억 443만</t>
   </si>
   <si>
     <t>설즈</t>
@@ -1478,7 +1481,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A4%EC%A6%88</t>
   </si>
   <si>
-    <t>932조 7496억 7919만</t>
+    <t>1057조 1778억 3358만</t>
   </si>
   <si>
     <t>약한고등어</t>
@@ -1496,7 +1499,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%A8%EC%82%90</t>
   </si>
   <si>
-    <t>317조 9218억 327만</t>
+    <t>321조 7864억 5930만</t>
   </si>
   <si>
     <t>문디르</t>
@@ -1505,7 +1508,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%94%94%EB%A5%B4</t>
   </si>
   <si>
-    <t>218조 1202억 7446만</t>
+    <t>236조 6736억 2515만</t>
   </si>
   <si>
     <t>항상밝은하루</t>
@@ -1523,7 +1526,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%ED%8A%B8%EC%B8%84</t>
   </si>
   <si>
-    <t>160조 5093억 7580만</t>
+    <t>191조 5397억 6335만</t>
   </si>
   <si>
     <t>봉튜</t>
@@ -1568,10 +1571,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%8B%AC%EC%B4%9D</t>
   </si>
   <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>38조 9416억 5281만</t>
+    <t>39조 6191억 375만</t>
   </si>
   <si>
     <t>뽀라비</t>
@@ -1580,7 +1580,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%9D%BC%EB%B9%84</t>
   </si>
   <si>
-    <t>26조 659억 4024만</t>
+    <t>28조 9920억 907만</t>
   </si>
   <si>
     <t>땩콩</t>
@@ -1589,7 +1589,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%95%A9%EC%BD%A9</t>
   </si>
   <si>
-    <t>25조 6977억 6223만</t>
+    <t>27조 6839억 965만</t>
   </si>
   <si>
     <t>김대협</t>
@@ -1598,7 +1598,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%8C%80%ED%98%91</t>
   </si>
   <si>
-    <t>24조 343억 8478만</t>
+    <t>25조 4755억 1503만</t>
   </si>
   <si>
     <t>에망</t>
@@ -1607,7 +1607,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%A7%9D</t>
   </si>
   <si>
-    <t>13조 7847억 942만</t>
+    <t>14조 1637억 9802만</t>
   </si>
   <si>
     <t>낭만만듀</t>
@@ -1616,7 +1616,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%EB%A7%8C%EB%93%80</t>
   </si>
   <si>
-    <t>12조 429억 4007만</t>
+    <t>12조 923억 4440만</t>
+  </si>
+  <si>
+    <t>다송이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%86%A1%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>10조 2967억 9982만</t>
   </si>
   <si>
     <t>봄녘</t>
@@ -1625,16 +1634,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B4%84%EB%85%98</t>
   </si>
   <si>
-    <t>9조 7577억 4333만</t>
-  </si>
-  <si>
-    <t>다송이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%86%A1%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>9조 5098억 7158만</t>
+    <t>10조 129억 2470만</t>
+  </si>
+  <si>
+    <t>봉합불가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%95%A9%EB%B6%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>7조 4531억 2484만</t>
   </si>
   <si>
     <t>빠나딘</t>
@@ -1646,15 +1655,6 @@
     <t>7조 3040억 619만</t>
   </si>
   <si>
-    <t>봉합불가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%ED%95%A9%EB%B6%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>7조 2028억 4048만</t>
-  </si>
-  <si>
     <t>양카오너</t>
   </si>
   <si>
@@ -1664,7 +1664,7 @@
     <t>97</t>
   </si>
   <si>
-    <t>4조 641억 9689만</t>
+    <t>4조 1168억 1838만</t>
   </si>
   <si>
     <t>강한고등어</t>
@@ -1673,7 +1673,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%ED%95%9C%EA%B3%A0%EB%93%B1%EC%96%B4</t>
   </si>
   <si>
-    <t>2조 5899억 6994만</t>
+    <t>2조 7268억 3352만</t>
   </si>
   <si>
     <t>돌쇠영만</t>
@@ -1694,13 +1694,13 @@
     <t>96</t>
   </si>
   <si>
-    <t>7711억 3776만</t>
+    <t>8361억 7612만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EC%AF%94</t>
   </si>
   <si>
-    <t>6617억 4476만</t>
+    <t>7146억 2017만</t>
   </si>
   <si>
     <t>비어치킨</t>
@@ -1712,7 +1712,7 @@
     <t>95</t>
   </si>
   <si>
-    <t>4591억 8954만</t>
+    <t>5016억 6902만</t>
   </si>
 </sst>
 </file>
@@ -2193,7 +2193,7 @@
         <v>28</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>19</v>
@@ -2202,54 +2202,54 @@
         <v>20</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>24</v>
@@ -2257,25 +2257,25 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>19</v>
@@ -2284,13 +2284,13 @@
         <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>24</v>
@@ -2298,31 +2298,31 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>56</v>
@@ -2484,10 +2484,10 @@
         <v>82</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2498,25 +2498,25 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>89</v>
@@ -2548,7 +2548,7 @@
         <v>93</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>94</v>
@@ -2641,13 +2641,13 @@
         <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2658,25 +2658,25 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="H10" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>115</v>
@@ -2740,7 +2740,7 @@
         <v>123</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>124</v>
@@ -2769,13 +2769,13 @@
         <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2786,28 +2786,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2818,16 +2818,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>70</v>
@@ -2836,10 +2836,10 @@
         <v>98</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2850,28 +2850,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2882,16 +2882,16 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>70</v>
@@ -2900,10 +2900,10 @@
         <v>93</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2914,16 +2914,16 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>70</v>
@@ -2932,10 +2932,10 @@
         <v>98</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2946,16 +2946,16 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>70</v>
@@ -2964,10 +2964,10 @@
         <v>71</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2978,7 +2978,7 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>156</v>
@@ -2996,7 +2996,7 @@
         <v>158</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>159</v>
@@ -3010,28 +3010,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3042,16 +3042,16 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>70</v>
@@ -3060,10 +3060,10 @@
         <v>98</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3074,16 +3074,16 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>70</v>
@@ -3092,10 +3092,10 @@
         <v>93</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3106,16 +3106,16 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>70</v>
@@ -3124,10 +3124,10 @@
         <v>98</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3138,7 +3138,7 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>176</v>
+        <v>46</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>177</v>
@@ -3156,7 +3156,7 @@
         <v>93</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>179</v>
@@ -3170,28 +3170,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>36</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3202,25 +3202,25 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>158</v>
+        <v>104</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>186</v>
@@ -3234,28 +3234,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>28</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>93</v>
+        <v>158</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3266,28 +3266,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3298,7 +3298,7 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>194</v>
+        <v>53</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>195</v>
@@ -3316,10 +3316,10 @@
         <v>93</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3330,28 +3330,28 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -3450,28 +3450,28 @@
         <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>72</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3482,13 +3482,13 @@
         <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>70</v>
@@ -3497,13 +3497,13 @@
         <v>71</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3514,28 +3514,28 @@
         <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3543,16 +3543,16 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>70</v>
@@ -3561,13 +3561,13 @@
         <v>98</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3578,28 +3578,28 @@
         <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3610,28 +3610,28 @@
         <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>99</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3642,13 +3642,13 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>70</v>
@@ -3660,10 +3660,10 @@
         <v>105</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -3674,13 +3674,13 @@
         <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>70</v>
@@ -3692,10 +3692,10 @@
         <v>105</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -3703,16 +3703,16 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>70</v>
@@ -3721,13 +3721,13 @@
         <v>71</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -3738,28 +3738,28 @@
         <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -3770,28 +3770,28 @@
         <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -3802,13 +3802,13 @@
         <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>70</v>
@@ -3817,13 +3817,13 @@
         <v>104</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -3831,16 +3831,16 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>70</v>
@@ -3849,13 +3849,13 @@
         <v>98</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -3863,16 +3863,16 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>70</v>
@@ -3881,13 +3881,13 @@
         <v>104</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -3895,16 +3895,16 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>70</v>
@@ -3913,13 +3913,13 @@
         <v>104</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -3927,31 +3927,31 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -3959,16 +3959,16 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>70</v>
@@ -3977,13 +3977,13 @@
         <v>93</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -3991,16 +3991,16 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>70</v>
@@ -4009,13 +4009,13 @@
         <v>104</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -4023,31 +4023,31 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -4055,31 +4055,31 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -4087,31 +4087,31 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>162</v>
+        <v>197</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -4119,16 +4119,16 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>70</v>
@@ -4137,13 +4137,13 @@
         <v>98</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>255</v>
+        <v>197</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -4151,31 +4151,31 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -4183,31 +4183,31 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>176</v>
+        <v>46</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>31</v>
+        <v>273</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>31</v>
+        <v>273</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>255</v>
+        <v>197</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -4215,31 +4215,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>36</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>274</v>
+        <v>32</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>274</v>
+        <v>32</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>255</v>
+        <v>197</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -4247,31 +4247,31 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -4279,31 +4279,31 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>28</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>185</v>
+        <v>256</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -4311,31 +4311,31 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -4343,16 +4343,16 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>194</v>
+        <v>53</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>70</v>
@@ -4361,13 +4361,13 @@
         <v>93</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>255</v>
+        <v>197</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -4375,16 +4375,16 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>70</v>
@@ -4393,13 +4393,13 @@
         <v>104</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -4489,19 +4489,19 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>70</v>
@@ -4510,10 +4510,10 @@
         <v>98</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4521,19 +4521,19 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>103</v>
@@ -4542,10 +4542,10 @@
         <v>71</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>77</v>
+        <v>298</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4553,19 +4553,19 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>70</v>
@@ -4577,7 +4577,7 @@
         <v>99</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4585,19 +4585,19 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>70</v>
@@ -4606,10 +4606,10 @@
         <v>104</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4617,31 +4617,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>105</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4649,19 +4649,19 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>70</v>
@@ -4670,10 +4670,10 @@
         <v>93</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4681,31 +4681,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>105</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4713,19 +4713,19 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>70</v>
@@ -4734,10 +4734,10 @@
         <v>93</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4745,31 +4745,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4777,31 +4777,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4809,31 +4809,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4841,31 +4841,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4873,19 +4873,19 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>70</v>
@@ -4894,10 +4894,10 @@
         <v>104</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4905,31 +4905,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4937,19 +4937,19 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>70</v>
@@ -4958,10 +4958,10 @@
         <v>104</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4969,31 +4969,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5001,31 +5001,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5033,31 +5033,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5065,31 +5065,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>255</v>
+        <v>197</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5097,19 +5097,19 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>70</v>
@@ -5118,10 +5118,10 @@
         <v>104</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5129,31 +5129,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5161,31 +5161,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5193,19 +5193,19 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>70</v>
@@ -5214,10 +5214,10 @@
         <v>158</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5225,19 +5225,19 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>176</v>
+        <v>46</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>70</v>
@@ -5246,10 +5246,10 @@
         <v>93</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5257,31 +5257,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>36</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>364</v>
-      </c>
       <c r="I26" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5289,31 +5289,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5321,31 +5321,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>28</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5353,31 +5353,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5385,19 +5385,19 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>194</v>
+        <v>53</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>70</v>
@@ -5406,10 +5406,10 @@
         <v>98</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5463,7 +5463,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5501,31 +5501,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>103</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>382</v>
+        <v>298</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5533,31 +5533,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5565,31 +5565,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>99</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5597,31 +5597,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5629,19 +5629,19 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>70</v>
@@ -5650,10 +5650,10 @@
         <v>71</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5661,31 +5661,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>99</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5693,31 +5693,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5725,19 +5725,19 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>70</v>
@@ -5746,10 +5746,10 @@
         <v>104</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5757,19 +5757,19 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>70</v>
@@ -5778,10 +5778,10 @@
         <v>93</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5789,31 +5789,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5821,19 +5821,19 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>70</v>
@@ -5842,10 +5842,10 @@
         <v>104</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5853,19 +5853,19 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>70</v>
@@ -5874,10 +5874,10 @@
         <v>93</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5885,19 +5885,19 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>70</v>
@@ -5906,10 +5906,10 @@
         <v>93</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5917,31 +5917,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5949,19 +5949,19 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>70</v>
@@ -5970,10 +5970,10 @@
         <v>98</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5981,31 +5981,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>185</v>
+        <v>366</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6013,31 +6013,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>364</v>
+        <v>197</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6045,31 +6045,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6077,19 +6077,19 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>70</v>
@@ -6098,10 +6098,10 @@
         <v>93</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6109,31 +6109,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6141,31 +6141,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6173,28 +6173,28 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>446</v>
+        <v>359</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>447</v>
@@ -6205,10 +6205,10 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>448</v>
@@ -6226,10 +6226,10 @@
         <v>71</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6237,19 +6237,19 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>176</v>
+        <v>46</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>70</v>
@@ -6258,10 +6258,10 @@
         <v>104</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6269,19 +6269,19 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>36</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>70</v>
@@ -6290,10 +6290,10 @@
         <v>104</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6301,31 +6301,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6333,31 +6333,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>28</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6365,19 +6365,19 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>70</v>
@@ -6386,10 +6386,10 @@
         <v>104</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6397,31 +6397,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>194</v>
+        <v>53</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6429,19 +6429,19 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>70</v>
@@ -6450,10 +6450,10 @@
         <v>104</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6546,19 +6546,19 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>70</v>
@@ -6567,10 +6567,10 @@
         <v>71</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>382</v>
+        <v>298</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6578,19 +6578,19 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>70</v>
@@ -6599,10 +6599,10 @@
         <v>93</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>382</v>
+        <v>298</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6610,19 +6610,19 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>70</v>
@@ -6631,10 +6631,10 @@
         <v>104</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6642,19 +6642,19 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>70</v>
@@ -6666,7 +6666,7 @@
         <v>99</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6674,19 +6674,19 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>70</v>
@@ -6695,10 +6695,10 @@
         <v>158</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6706,19 +6706,19 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>70</v>
@@ -6727,10 +6727,10 @@
         <v>98</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6738,19 +6738,19 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>70</v>
@@ -6759,10 +6759,10 @@
         <v>71</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6770,19 +6770,19 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>70</v>
@@ -6791,10 +6791,10 @@
         <v>71</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6802,19 +6802,19 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>70</v>
@@ -6823,10 +6823,10 @@
         <v>71</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6834,19 +6834,19 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>70</v>
@@ -6855,10 +6855,10 @@
         <v>104</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6866,19 +6866,19 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>70</v>
@@ -6887,10 +6887,10 @@
         <v>71</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6898,31 +6898,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6930,31 +6930,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6962,28 +6962,28 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>513</v>
+        <v>123</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>514</v>
@@ -6994,10 +6994,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>515</v>
@@ -7012,10 +7012,10 @@
         <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>364</v>
+        <v>256</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>517</v>
@@ -7026,10 +7026,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>518</v>
@@ -7044,10 +7044,10 @@
         <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>520</v>
@@ -7058,10 +7058,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>521</v>
@@ -7079,7 +7079,7 @@
         <v>93</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>523</v>
@@ -7090,10 +7090,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>524</v>
@@ -7111,7 +7111,7 @@
         <v>104</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>526</v>
@@ -7122,10 +7122,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>527</v>
@@ -7140,10 +7140,10 @@
         <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>529</v>
@@ -7154,10 +7154,10 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>530</v>
@@ -7172,10 +7172,10 @@
         <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>532</v>
@@ -7186,10 +7186,10 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>533</v>
@@ -7204,10 +7204,10 @@
         <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>535</v>
@@ -7218,10 +7218,10 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>536</v>
@@ -7239,7 +7239,7 @@
         <v>93</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>538</v>
@@ -7250,10 +7250,10 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>539</v>
@@ -7271,7 +7271,7 @@
         <v>93</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>541</v>
@@ -7282,10 +7282,10 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>176</v>
+        <v>46</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>542</v>
@@ -7314,10 +7314,10 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>36</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>546</v>
@@ -7332,10 +7332,10 @@
         <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>513</v>
+        <v>123</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>548</v>
@@ -7346,10 +7346,10 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>549</v>
@@ -7378,10 +7378,10 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>28</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>552</v>
@@ -7410,10 +7410,10 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>58</v>
@@ -7442,10 +7442,10 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>194</v>
+        <v>53</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>558</v>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -296,7 +296,7 @@
     <t>109</t>
   </si>
   <si>
-    <t>2487조 9861억 8548만</t>
+    <t>2496조 2648억 1195만</t>
   </si>
   <si>
     <t>5</t>
@@ -386,7 +386,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%88%88%EA%BD%83%EC%B2%B4%EB%A6%AC</t>
   </si>
   <si>
-    <t>503조 6027억 4386만</t>
+    <t>515조 9893억 3522만</t>
   </si>
   <si>
     <t>11</t>
@@ -398,660 +398,660 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%96%A0%EB%84%A4%EC%A8%A9</t>
   </si>
   <si>
+    <t>503조 1799억 8663만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>망치두고튀어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EB%91%90%EA%B3%A0%ED%8A%80%EC%96%B4</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>456조 817억 2556만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>냐락크리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%ED%81%AC%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>339조 8320억 9033만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>왕푸맨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%ED%91%B8%EB%A7%A8</t>
+  </si>
+  <si>
+    <t>316조 183억 9534만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>냐락린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>238조 9527억 186만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>냐락셋째</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EC%85%8B%EC%A7%B8</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>211조 3286억 9983만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>냐락쿠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EC%BF%A0</t>
+  </si>
+  <si>
+    <t>176조 3550억 4379만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>욕박고시작</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%95%EB%B0%95%EA%B3%A0%EC%8B%9C%EC%9E%91</t>
+  </si>
+  <si>
+    <t>169조 9977억 3227만</t>
+  </si>
+  <si>
+    <t>쀼움</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%80%BC%EC%9B%80</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>169조 8582억 5050만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>삼양일짱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%BC%EC%96%91%EC%9D%BC%EC%A7%B1</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>143조 9772억 6301만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>안지연</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%A7%80%EC%97%B0</t>
+  </si>
+  <si>
+    <t>125조 7526억 2938만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Cerberus</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Cerberus</t>
+  </si>
+  <si>
+    <t>107조 5759억 682만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>냐락뀨리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%80%A8%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>106조 8432억 1451만</t>
+  </si>
+  <si>
+    <t>Centauros</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Centauros</t>
+  </si>
+  <si>
+    <t>96조 44억 4021만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>국레쏘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EB%A0%88%EC%8F%98</t>
+  </si>
+  <si>
+    <t>75조 7361억 6845만</t>
+  </si>
+  <si>
+    <t>이강민둥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B0%95%EB%AF%BC%EB%91%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>67조 223억 9864만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>히들</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EB%93%A4</t>
+  </si>
+  <si>
+    <t>66조 5056억 7788만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>김채희</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B1%84%ED%9D%AC</t>
+  </si>
+  <si>
+    <t>40조 3897억 5111만</t>
+  </si>
+  <si>
+    <t>세정린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%A0%95%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>37조 5529억 1971만</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>거대곤줄박이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B0%EB%8C%80%EA%B3%A4%EC%A4%84%EB%B0%95%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>36조 3789억 7842만</t>
+  </si>
+  <si>
+    <t>스타냥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1경 720조 3865억 2152만</t>
+  </si>
+  <si>
+    <t>돈스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>3322조 3154억 8065만</t>
+  </si>
+  <si>
+    <t>진자이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>2283조 7142억 7674만</t>
+  </si>
+  <si>
+    <t>말레이히어로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>1394조 1932억 8825만</t>
+  </si>
+  <si>
+    <t>빌런투킬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
+  </si>
+  <si>
+    <t>1120조 9927억 5165만</t>
+  </si>
+  <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>1112조 8677억 9360만</t>
+  </si>
+  <si>
+    <t>스타뎀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%8E%80</t>
+  </si>
+  <si>
+    <t>475조 5893억 7767만</t>
+  </si>
+  <si>
+    <t>여사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
+  </si>
+  <si>
+    <t>400조 1307억 6796만</t>
+  </si>
+  <si>
+    <t>단풍노비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
+  </si>
+  <si>
+    <t>176조 573억 7249만</t>
+  </si>
+  <si>
+    <t>부엉이없다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>153조 4242억 2362만</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>152조 6744억 2175만</t>
+  </si>
+  <si>
+    <t>프리프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>143조 1307억 9972만</t>
+  </si>
+  <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>123조 7397억 6038만</t>
+  </si>
+  <si>
+    <t>쾌감</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
+  </si>
+  <si>
+    <t>89조 2869억 199만</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>83조 3411억 4487만</t>
+  </si>
+  <si>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>75조 5035억 6634만</t>
+  </si>
+  <si>
+    <t>POSCO</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
+  </si>
+  <si>
+    <t>65조 7697억 3285만</t>
+  </si>
+  <si>
+    <t>소소채2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>64조 3897억 2993만</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>42조 7569억 3167만</t>
+  </si>
+  <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>38조 3694억 6015만</t>
+  </si>
+  <si>
+    <t>김치싸대기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>38조 1459억 7981만</t>
+  </si>
+  <si>
+    <t>두근푸근연근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>37조 4329억 7511만</t>
+  </si>
+  <si>
+    <t>포뇨야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
+  </si>
+  <si>
+    <t>35조 3962억 1100만</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>32조 3503억 166만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
+  </si>
+  <si>
+    <t>28조 5128억 7466만</t>
+  </si>
+  <si>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>28조 3422억 4602만</t>
+  </si>
+  <si>
+    <t>울힝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
+  </si>
+  <si>
+    <t>27조 7168억 210만</t>
+  </si>
+  <si>
+    <t>악의꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
+  </si>
+  <si>
+    <t>25조 817억 1488만</t>
+  </si>
+  <si>
+    <t>몽호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
+  </si>
+  <si>
+    <t>22조 9589억 8035만</t>
+  </si>
+  <si>
+    <t>junoflo</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=junoflo</t>
+  </si>
+  <si>
+    <t>10조 9422억 5450만</t>
+  </si>
+  <si>
+    <t>가숭혁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%88%AD%ED%98%81</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>1경 6991조 8873억 8940만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%B4%EB%BD%80%EC%8B%9C</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>2783조 7486억 5197만</t>
+  </si>
+  <si>
+    <t>26상탗</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EC%83%81%ED%83%97</t>
+  </si>
+  <si>
+    <t>1602조 4421억 8043만</t>
+  </si>
+  <si>
+    <t>달싹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EC%8B%B9</t>
+  </si>
+  <si>
+    <t>651조 4386억 2995만</t>
+  </si>
+  <si>
+    <t>뇌쉬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%87%8C%EC%89%AC</t>
+  </si>
+  <si>
+    <t>473조 935억 9830만</t>
+  </si>
+  <si>
+    <t>26길초</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
+  </si>
+  <si>
+    <t>437조 2061억 5293만</t>
+  </si>
+  <si>
+    <t>서예슬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
+  </si>
+  <si>
+    <t>355조 4228억 3360만</t>
+  </si>
+  <si>
+    <t>26들박</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EB%93%A4%EB%B0%95</t>
+  </si>
+  <si>
+    <t>342조 5420억 8712만</t>
+  </si>
+  <si>
+    <t>옴짝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%B4%EC%A7%9D</t>
+  </si>
+  <si>
+    <t>267조 4873억 4322만</t>
+  </si>
+  <si>
+    <t>몬함</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
+  </si>
+  <si>
+    <t>177조 5670억 5779만</t>
+  </si>
+  <si>
+    <t>임승민</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
+  </si>
+  <si>
+    <t>161조 2593억 1562만</t>
+  </si>
+  <si>
+    <t>중타치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A4%91%ED%83%80%EC%B9%98</t>
+  </si>
+  <si>
+    <t>146조 2366억 2351만</t>
+  </si>
+  <si>
+    <t>뻔수니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
+  </si>
+  <si>
+    <t>83조 6254억 8539만</t>
+  </si>
+  <si>
+    <t>얼음깨먹기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EC%9D%8C%EA%B9%A8%EB%A8%B9%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>59조 6571억 7041만</t>
+  </si>
+  <si>
+    <t>26배털</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
+  </si>
+  <si>
+    <t>38조 8453억 6606만</t>
+  </si>
+  <si>
+    <t>쑤삔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%91%A4%EC%82%94</t>
+  </si>
+  <si>
     <t>나이트로드</t>
   </si>
   <si>
-    <t>503조 1799억 8663만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>망치두고튀어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EB%91%90%EA%B3%A0%ED%8A%80%EC%96%B4</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>456조 817억 2556만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>냐락크리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%ED%81%AC%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>339조 8320억 9033만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>왕푸맨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%ED%91%B8%EB%A7%A8</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>299조 7077억 8873만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>냐락셋째</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EC%85%8B%EC%A7%B8</t>
-  </si>
-  <si>
-    <t>211조 3286억 9983만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>냐락린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>193조 6810억 7098만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>냐락쿠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EC%BF%A0</t>
-  </si>
-  <si>
-    <t>176조 3550억 4379만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>욕박고시작</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%95%EB%B0%95%EA%B3%A0%EC%8B%9C%EC%9E%91</t>
-  </si>
-  <si>
-    <t>169조 8634억 5863만</t>
-  </si>
-  <si>
-    <t>쀼움</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%80%BC%EC%9B%80</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>169조 8582억 5050만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>삼양일짱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%BC%EC%96%91%EC%9D%BC%EC%A7%B1</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>143조 9772억 6301만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>안지연</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%A7%80%EC%97%B0</t>
-  </si>
-  <si>
-    <t>125조 7526억 2938만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>Cerberus</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Cerberus</t>
-  </si>
-  <si>
-    <t>107조 5759억 682만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>냐락뀨리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EB%9D%BD%EB%80%A8%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>106조 8432억 1451만</t>
-  </si>
-  <si>
-    <t>Centauros</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Centauros</t>
-  </si>
-  <si>
-    <t>96조 44억 4021만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>국레쏘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AD%EB%A0%88%EC%8F%98</t>
-  </si>
-  <si>
-    <t>73조 5156억 1979만</t>
-  </si>
-  <si>
-    <t>이강민둥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EA%B0%95%EB%AF%BC%EB%91%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>67조 223억 9864만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>히들</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EB%93%A4</t>
-  </si>
-  <si>
-    <t>66조 5056억 7788만</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>김채희</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B1%84%ED%9D%AC</t>
-  </si>
-  <si>
-    <t>39조 4280억 9037만</t>
-  </si>
-  <si>
-    <t>세정린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%A0%95%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>37조 5529억 1971만</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>거대곤줄박이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B0%EB%8C%80%EA%B3%A4%EC%A4%84%EB%B0%95%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>36조 3789억 7842만</t>
-  </si>
-  <si>
-    <t>스타냥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1경 720조 3865억 2152만</t>
-  </si>
-  <si>
-    <t>돈스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>3322조 3154억 8065만</t>
-  </si>
-  <si>
-    <t>진자이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>2283조 7142억 7674만</t>
-  </si>
-  <si>
-    <t>말레이히어로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>1394조 1932억 8825만</t>
-  </si>
-  <si>
-    <t>빌런투킬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
-  </si>
-  <si>
-    <t>1120조 9927억 5165만</t>
-  </si>
-  <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>1112조 8677억 9360만</t>
-  </si>
-  <si>
-    <t>스타뎀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%8E%80</t>
-  </si>
-  <si>
-    <t>475조 5893억 7767만</t>
-  </si>
-  <si>
-    <t>여사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
-  </si>
-  <si>
-    <t>400조 1307억 6796만</t>
-  </si>
-  <si>
-    <t>단풍노비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
-  </si>
-  <si>
-    <t>176조 573억 7249만</t>
-  </si>
-  <si>
-    <t>부엉이없다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>153조 4242억 2362만</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>152조 6744억 2175만</t>
-  </si>
-  <si>
-    <t>프리프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>143조 1307억 9972만</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>123조 7397억 6038만</t>
-  </si>
-  <si>
-    <t>쾌감</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
-  </si>
-  <si>
-    <t>89조 2869억 199만</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>83조 3411억 4487만</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>75조 5035억 6634만</t>
-  </si>
-  <si>
-    <t>POSCO</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
-  </si>
-  <si>
-    <t>65조 7697억 3285만</t>
-  </si>
-  <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>64조 3897억 2993만</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>42조 7569억 3167만</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>38조 3694억 6015만</t>
-  </si>
-  <si>
-    <t>김치싸대기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>38조 1459억 7981만</t>
-  </si>
-  <si>
-    <t>두근푸근연근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>37조 4329억 7511만</t>
-  </si>
-  <si>
-    <t>포뇨야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
-  </si>
-  <si>
-    <t>35조 3962억 1100만</t>
-  </si>
-  <si>
-    <t>대방어조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>32조 3503억 166만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
-  </si>
-  <si>
-    <t>28조 5128억 7466만</t>
-  </si>
-  <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>28조 3422억 4602만</t>
-  </si>
-  <si>
-    <t>울힝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
-  </si>
-  <si>
-    <t>27조 7168억 210만</t>
-  </si>
-  <si>
-    <t>악의꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
-  </si>
-  <si>
-    <t>25조 817억 1488만</t>
-  </si>
-  <si>
-    <t>몽호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
-  </si>
-  <si>
-    <t>22조 9589억 8035만</t>
-  </si>
-  <si>
-    <t>junoflo</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=junoflo</t>
-  </si>
-  <si>
-    <t>10조 9422억 5450만</t>
-  </si>
-  <si>
-    <t>가숭혁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%88%AD%ED%98%81</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>1경 6991조 8873억 8940만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%B4%EB%BD%80%EC%8B%9C</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>2604조 1519억 6474만</t>
-  </si>
-  <si>
-    <t>26상탗</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EC%83%81%ED%83%97</t>
-  </si>
-  <si>
-    <t>1601조 7815억 6566만</t>
-  </si>
-  <si>
-    <t>달싹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EC%8B%B9</t>
-  </si>
-  <si>
-    <t>651조 4386억 2995만</t>
-  </si>
-  <si>
-    <t>뇌쉬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%87%8C%EC%89%AC</t>
-  </si>
-  <si>
-    <t>473조 935억 9830만</t>
-  </si>
-  <si>
-    <t>26길초</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
-  </si>
-  <si>
-    <t>437조 2061억 5293만</t>
-  </si>
-  <si>
-    <t>서예슬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
-  </si>
-  <si>
-    <t>355조 4228억 3360만</t>
-  </si>
-  <si>
-    <t>26들박</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EB%93%A4%EB%B0%95</t>
-  </si>
-  <si>
-    <t>342조 5420억 8712만</t>
-  </si>
-  <si>
-    <t>옴짝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%B4%EC%A7%9D</t>
-  </si>
-  <si>
-    <t>267조 4873억 4322만</t>
-  </si>
-  <si>
-    <t>몬함</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
-  </si>
-  <si>
-    <t>177조 5670억 5779만</t>
-  </si>
-  <si>
-    <t>임승민</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
-  </si>
-  <si>
-    <t>161조 2593억 1562만</t>
-  </si>
-  <si>
-    <t>중타치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A4%91%ED%83%80%EC%B9%98</t>
-  </si>
-  <si>
-    <t>146조 2366억 2351만</t>
-  </si>
-  <si>
-    <t>뻔수니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
-  </si>
-  <si>
-    <t>83조 6254억 8539만</t>
-  </si>
-  <si>
-    <t>얼음깨먹기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EC%9D%8C%EA%B9%A8%EB%A8%B9%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>59조 6571억 7041만</t>
-  </si>
-  <si>
-    <t>26배털</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
-  </si>
-  <si>
-    <t>38조 8453억 6606만</t>
-  </si>
-  <si>
-    <t>쑤삔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%91%A4%EC%82%94</t>
-  </si>
-  <si>
     <t>30조 6445억 1264만</t>
   </si>
   <si>
@@ -1091,6 +1091,15 @@
     <t>17조 6676억 1993만</t>
   </si>
   <si>
+    <t>브깃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EA%B9%83</t>
+  </si>
+  <si>
+    <t>16조 4521억 4228만</t>
+  </si>
+  <si>
     <t>26조선</t>
   </si>
   <si>
@@ -1110,15 +1119,6 @@
   </si>
   <si>
     <t>15조 637억 960만</t>
-  </si>
-  <si>
-    <t>브깃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EA%B9%83</t>
-  </si>
-  <si>
-    <t>13조 8329억 6602만</t>
   </si>
   <si>
     <t>뿜삐</t>
@@ -2737,13 +2737,13 @@
         <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>105</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2754,28 +2754,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>99</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2786,16 +2786,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>70</v>
@@ -2804,10 +2804,10 @@
         <v>87</v>
       </c>
       <c r="H14" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2818,16 +2818,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>137</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>70</v>
@@ -2836,10 +2836,10 @@
         <v>98</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2850,28 +2850,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2882,28 +2882,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="I17" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2914,16 +2914,16 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>70</v>
@@ -2932,10 +2932,10 @@
         <v>98</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2946,16 +2946,16 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>70</v>
@@ -2964,10 +2964,10 @@
         <v>71</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2981,25 +2981,25 @@
         <v>17</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G20" s="2" t="s">
+      <c r="H20" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>159</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3010,28 +3010,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="H21" s="2" t="s">
+      <c r="I21" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>164</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3042,16 +3042,16 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>70</v>
@@ -3060,10 +3060,10 @@
         <v>98</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3074,16 +3074,16 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>171</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>70</v>
@@ -3092,10 +3092,10 @@
         <v>93</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3106,16 +3106,16 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>175</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>70</v>
@@ -3124,10 +3124,10 @@
         <v>98</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3141,13 +3141,13 @@
         <v>46</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>178</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>70</v>
@@ -3156,10 +3156,10 @@
         <v>93</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3170,16 +3170,16 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>70</v>
@@ -3188,10 +3188,10 @@
         <v>93</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3205,13 +3205,13 @@
         <v>37</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>185</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>70</v>
@@ -3220,10 +3220,10 @@
         <v>104</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3234,28 +3234,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3266,16 +3266,16 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>193</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>70</v>
@@ -3284,10 +3284,10 @@
         <v>114</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3301,13 +3301,13 @@
         <v>53</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>70</v>
@@ -3316,10 +3316,10 @@
         <v>93</v>
       </c>
       <c r="H30" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>198</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3330,16 +3330,16 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>200</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>201</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>70</v>
@@ -3348,10 +3348,10 @@
         <v>82</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -3450,13 +3450,13 @@
         <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>70</v>
@@ -3468,7 +3468,7 @@
         <v>72</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>33</v>
@@ -3482,13 +3482,13 @@
         <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>70</v>
@@ -3500,7 +3500,7 @@
         <v>88</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>33</v>
@@ -3514,13 +3514,13 @@
         <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>70</v>
@@ -3532,7 +3532,7 @@
         <v>77</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>33</v>
@@ -3546,13 +3546,13 @@
         <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>212</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>213</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>70</v>
@@ -3564,7 +3564,7 @@
         <v>88</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>33</v>
@@ -3578,25 +3578,25 @@
         <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>216</v>
-      </c>
       <c r="F6" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>88</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>33</v>
@@ -3610,13 +3610,13 @@
         <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>218</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>219</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>70</v>
@@ -3628,7 +3628,7 @@
         <v>99</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>33</v>
@@ -3642,13 +3642,13 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>70</v>
@@ -3660,7 +3660,7 @@
         <v>105</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>33</v>
@@ -3674,13 +3674,13 @@
         <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>224</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>225</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>70</v>
@@ -3692,7 +3692,7 @@
         <v>105</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>33</v>
@@ -3706,13 +3706,13 @@
         <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>227</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>228</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>70</v>
@@ -3721,10 +3721,10 @@
         <v>71</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>33</v>
@@ -3738,13 +3738,13 @@
         <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>231</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>70</v>
@@ -3753,10 +3753,10 @@
         <v>104</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>33</v>
@@ -3770,13 +3770,13 @@
         <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>233</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>234</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>70</v>
@@ -3785,10 +3785,10 @@
         <v>114</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>33</v>
@@ -3799,16 +3799,16 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>237</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>70</v>
@@ -3817,10 +3817,10 @@
         <v>104</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>33</v>
@@ -3831,16 +3831,16 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>240</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>70</v>
@@ -3849,10 +3849,10 @@
         <v>98</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>33</v>
@@ -3863,16 +3863,16 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>243</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>70</v>
@@ -3881,10 +3881,10 @@
         <v>104</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>33</v>
@@ -3895,16 +3895,16 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>246</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>70</v>
@@ -3913,10 +3913,10 @@
         <v>104</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>33</v>
@@ -3927,16 +3927,16 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>249</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>70</v>
@@ -3945,10 +3945,10 @@
         <v>82</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>33</v>
@@ -3959,16 +3959,16 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>252</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>70</v>
@@ -3977,10 +3977,10 @@
         <v>93</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>33</v>
@@ -3991,16 +3991,16 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>255</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>70</v>
@@ -4009,10 +4009,10 @@
         <v>104</v>
       </c>
       <c r="H19" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>33</v>
@@ -4026,13 +4026,13 @@
         <v>17</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>258</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>259</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>70</v>
@@ -4041,10 +4041,10 @@
         <v>104</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>33</v>
@@ -4055,16 +4055,16 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>261</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>262</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>70</v>
@@ -4073,10 +4073,10 @@
         <v>82</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>33</v>
@@ -4087,16 +4087,16 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>264</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>265</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>70</v>
@@ -4105,10 +4105,10 @@
         <v>98</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>33</v>
@@ -4119,16 +4119,16 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>267</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>268</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>70</v>
@@ -4137,10 +4137,10 @@
         <v>98</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>33</v>
@@ -4151,16 +4151,16 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>271</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>70</v>
@@ -4169,10 +4169,10 @@
         <v>82</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>33</v>
@@ -4186,13 +4186,13 @@
         <v>46</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>273</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>274</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>70</v>
@@ -4201,10 +4201,10 @@
         <v>104</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>33</v>
@@ -4215,7 +4215,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>32</v>
@@ -4224,7 +4224,7 @@
         <v>32</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>103</v>
@@ -4233,10 +4233,10 @@
         <v>82</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>33</v>
@@ -4250,13 +4250,13 @@
         <v>37</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>279</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>70</v>
@@ -4265,10 +4265,10 @@
         <v>87</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>33</v>
@@ -4279,16 +4279,16 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>70</v>
@@ -4297,10 +4297,10 @@
         <v>82</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>33</v>
@@ -4311,16 +4311,16 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>70</v>
@@ -4329,10 +4329,10 @@
         <v>114</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>33</v>
@@ -4346,13 +4346,13 @@
         <v>53</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>288</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>70</v>
@@ -4361,10 +4361,10 @@
         <v>93</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>33</v>
@@ -4375,16 +4375,16 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>291</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>70</v>
@@ -4393,10 +4393,10 @@
         <v>104</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>33</v>
@@ -4495,13 +4495,13 @@
         <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>294</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>70</v>
@@ -4510,10 +4510,10 @@
         <v>98</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>295</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>296</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4533,7 +4533,7 @@
         <v>42</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>103</v>
@@ -4542,10 +4542,10 @@
         <v>71</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>298</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>299</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4559,13 +4559,13 @@
         <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>301</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>70</v>
@@ -4577,7 +4577,7 @@
         <v>99</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4591,13 +4591,13 @@
         <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>70</v>
@@ -4606,10 +4606,10 @@
         <v>104</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4623,25 +4623,25 @@
         <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>307</v>
-      </c>
       <c r="F6" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>105</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4655,13 +4655,13 @@
         <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>310</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>70</v>
@@ -4670,10 +4670,10 @@
         <v>93</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4687,13 +4687,13 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>312</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>313</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>70</v>
@@ -4705,7 +4705,7 @@
         <v>105</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4719,13 +4719,13 @@
         <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>315</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>316</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>70</v>
@@ -4734,10 +4734,10 @@
         <v>93</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4751,13 +4751,13 @@
         <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>318</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>319</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>70</v>
@@ -4766,10 +4766,10 @@
         <v>82</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4783,13 +4783,13 @@
         <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>321</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>322</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>70</v>
@@ -4798,10 +4798,10 @@
         <v>87</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4815,13 +4815,13 @@
         <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>324</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>325</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>70</v>
@@ -4830,10 +4830,10 @@
         <v>104</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4844,16 +4844,16 @@
         <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>328</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>70</v>
@@ -4862,10 +4862,10 @@
         <v>71</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4876,16 +4876,16 @@
         <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>330</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>331</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>70</v>
@@ -4894,10 +4894,10 @@
         <v>104</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4908,16 +4908,16 @@
         <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>333</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>334</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>70</v>
@@ -4926,10 +4926,10 @@
         <v>82</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4940,16 +4940,16 @@
         <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>336</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>337</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>70</v>
@@ -4958,10 +4958,10 @@
         <v>104</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4972,25 +4972,25 @@
         <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="H17" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>341</v>
@@ -5004,7 +5004,7 @@
         <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>342</v>
@@ -5022,7 +5022,7 @@
         <v>114</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>344</v>
@@ -5036,7 +5036,7 @@
         <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>345</v>
@@ -5054,7 +5054,7 @@
         <v>82</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>347</v>
@@ -5086,7 +5086,7 @@
         <v>82</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>350</v>
@@ -5100,7 +5100,7 @@
         <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>351</v>
@@ -5118,7 +5118,7 @@
         <v>104</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>353</v>
@@ -5132,7 +5132,7 @@
         <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>354</v>
@@ -5147,10 +5147,10 @@
         <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>356</v>
@@ -5164,7 +5164,7 @@
         <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>357</v>
@@ -5179,13 +5179,13 @@
         <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="H23" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>359</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>360</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5196,25 +5196,25 @@
         <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>256</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>363</v>
@@ -5260,7 +5260,7 @@
         <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>368</v>
@@ -5324,7 +5324,7 @@
         <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>374</v>
@@ -5356,7 +5356,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>377</v>
@@ -5522,7 +5522,7 @@
         <v>82</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>384</v>
@@ -5554,7 +5554,7 @@
         <v>114</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>387</v>
@@ -5618,7 +5618,7 @@
         <v>82</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>393</v>
@@ -5714,7 +5714,7 @@
         <v>114</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>402</v>
@@ -5778,7 +5778,7 @@
         <v>93</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>408</v>
@@ -5810,7 +5810,7 @@
         <v>82</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>411</v>
@@ -5842,7 +5842,7 @@
         <v>104</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>414</v>
@@ -5856,7 +5856,7 @@
         <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>415</v>
@@ -5874,7 +5874,7 @@
         <v>93</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>417</v>
@@ -5888,7 +5888,7 @@
         <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>418</v>
@@ -5920,7 +5920,7 @@
         <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>421</v>
@@ -5938,7 +5938,7 @@
         <v>114</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>423</v>
@@ -5952,7 +5952,7 @@
         <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>424</v>
@@ -5984,7 +5984,7 @@
         <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>427</v>
@@ -6016,7 +6016,7 @@
         <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>430</v>
@@ -6034,7 +6034,7 @@
         <v>104</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>432</v>
@@ -6048,7 +6048,7 @@
         <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>433</v>
@@ -6112,7 +6112,7 @@
         <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>439</v>
@@ -6144,7 +6144,7 @@
         <v>43</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>442</v>
@@ -6176,7 +6176,7 @@
         <v>43</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>445</v>
@@ -6194,7 +6194,7 @@
         <v>114</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>447</v>
@@ -6208,7 +6208,7 @@
         <v>43</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>448</v>
@@ -6272,7 +6272,7 @@
         <v>43</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>455</v>
@@ -6290,7 +6290,7 @@
         <v>104</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>457</v>
@@ -6336,7 +6336,7 @@
         <v>43</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>461</v>
@@ -6368,7 +6368,7 @@
         <v>43</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>464</v>
@@ -6432,7 +6432,7 @@
         <v>43</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>470</v>
@@ -6450,7 +6450,7 @@
         <v>104</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>472</v>
@@ -6567,7 +6567,7 @@
         <v>71</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>475</v>
@@ -6599,7 +6599,7 @@
         <v>93</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>478</v>
@@ -6692,7 +6692,7 @@
         <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>88</v>
@@ -6727,7 +6727,7 @@
         <v>98</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>490</v>
@@ -6759,7 +6759,7 @@
         <v>71</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>493</v>
@@ -6791,7 +6791,7 @@
         <v>71</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>496</v>
@@ -6823,7 +6823,7 @@
         <v>71</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>499</v>
@@ -6855,7 +6855,7 @@
         <v>104</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>502</v>
@@ -6887,7 +6887,7 @@
         <v>71</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>505</v>
@@ -6901,7 +6901,7 @@
         <v>50</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>506</v>
@@ -6919,7 +6919,7 @@
         <v>114</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>508</v>
@@ -6933,7 +6933,7 @@
         <v>50</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>509</v>
@@ -6951,7 +6951,7 @@
         <v>114</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>511</v>
@@ -6965,7 +6965,7 @@
         <v>50</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>512</v>
@@ -6980,10 +6980,10 @@
         <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>123</v>
+        <v>340</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>514</v>
@@ -6997,7 +6997,7 @@
         <v>50</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>515</v>
@@ -7015,7 +7015,7 @@
         <v>82</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>517</v>
@@ -7029,7 +7029,7 @@
         <v>50</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>518</v>
@@ -7047,7 +7047,7 @@
         <v>82</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>520</v>
@@ -7061,7 +7061,7 @@
         <v>50</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>521</v>
@@ -7079,7 +7079,7 @@
         <v>93</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>523</v>
@@ -7093,7 +7093,7 @@
         <v>50</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>524</v>
@@ -7111,7 +7111,7 @@
         <v>104</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>526</v>
@@ -7157,7 +7157,7 @@
         <v>50</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>530</v>
@@ -7189,7 +7189,7 @@
         <v>50</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>533</v>
@@ -7221,7 +7221,7 @@
         <v>50</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>536</v>
@@ -7239,7 +7239,7 @@
         <v>93</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>538</v>
@@ -7253,7 +7253,7 @@
         <v>50</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>539</v>
@@ -7271,7 +7271,7 @@
         <v>93</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>541</v>
@@ -7317,7 +7317,7 @@
         <v>50</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>546</v>
@@ -7332,7 +7332,7 @@
         <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>123</v>
+        <v>340</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>450</v>
@@ -7381,7 +7381,7 @@
         <v>50</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>552</v>
@@ -7413,7 +7413,7 @@
         <v>50</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>58</v>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -9,25 +9,25 @@
   <sheets>
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="별곰부대" sheetId="2" r:id="rId2"/>
-    <sheet name="셀린느" sheetId="3" r:id="rId3"/>
-    <sheet name="블링블리" sheetId="4" r:id="rId4"/>
+    <sheet name="블링블리" sheetId="3" r:id="rId3"/>
+    <sheet name="셀린느" sheetId="4" r:id="rId4"/>
     <sheet name="LUXURY" sheetId="5" r:id="rId5"/>
     <sheet name="item" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">item!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">LUXURY!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">LUXURY!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">별곰부대!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">블링블리!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">셀린느!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">블링블리!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">셀린느!$A$1:$J$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="564">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,7 +80,7 @@
     <t>Scania 30</t>
   </si>
   <si>
-    <t>33</t>
+    <t>35</t>
   </si>
   <si>
     <t>2위</t>
@@ -89,19 +89,49 @@
     <t>Lv.7</t>
   </si>
   <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>1경 8436조 3967억 1957만</t>
+  </si>
+  <si>
+    <t>가입문의 : 별곰띠</t>
+  </si>
+  <si>
+    <t>별곰띠</t>
+  </si>
+  <si>
+    <t>2026.04.17</t>
+  </si>
+  <si>
+    <t>블링블리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B8%94%EB%A7%81%EB%B8%94%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>Scania 27</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>3위</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
     <t>30명</t>
   </si>
   <si>
-    <t>1경 9465조 8043억 4264만</t>
-  </si>
-  <si>
-    <t>가입문의 : 별곰띠</t>
-  </si>
-  <si>
-    <t>별곰띠</t>
-  </si>
-  <si>
-    <t>2026.04.16</t>
+    <t>2경 1091조 6973억 9788만</t>
+  </si>
+  <si>
+    <t>토벌 3위 1군 투력 50조 이상 / 토벌 13위 2군 블리블링 10조 이상 / 3군 블링불링 3000억이상 닉변 필수 공헌도 미달 길본 미업글 1일 미접 추방</t>
+  </si>
+  <si>
+    <t>꼴래링</t>
   </si>
   <si>
     <t>셀린느</t>
@@ -113,514 +143,487 @@
     <t>Scania 2</t>
   </si>
   <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>1위</t>
+  </si>
+  <si>
+    <t>2경 4659조 4565억 6859만</t>
+  </si>
+  <si>
+    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
+  </si>
+  <si>
+    <t>혜영</t>
+  </si>
+  <si>
+    <t>LUXURY</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
+  </si>
+  <si>
+    <t>Scania 16</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Lv.9</t>
+  </si>
+  <si>
+    <t>2경 5624조 8913억 5301만</t>
+  </si>
+  <si>
+    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
+  </si>
+  <si>
+    <t>살뽀시</t>
+  </si>
+  <si>
+    <t>item</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=item</t>
+  </si>
+  <si>
+    <t>Scania 34</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>2경 6501조 1108억 3368만</t>
+  </si>
+  <si>
+    <t>We Go Together !</t>
+  </si>
+  <si>
+    <t>템이</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>별뽕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%BD%95</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>6702조 2457억 8696만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>도얍스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%96%8D%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>2695조 8599억 2831만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>원빉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EB%B9%89</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>2103조 9436억 5062만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EA%B3%B0%EB%9D%A0</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>2038조 3208억 5895만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>꿀까배기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EA%B9%8C%EB%B0%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>1510조 7114억 1106만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>KR#18TIDK8BQ6</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=KR%2318TIDK8BQ6</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>1213조 186억 9436만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>팝중이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%9D%EC%A4%91%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>624조 5307억 1559만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>BJ규리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=BJ%EA%B7%9C%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>529조 2704억 5535만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>삭제합니다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AD%EC%A0%9C%ED%95%A9%EB%8B%88%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>471조 6952억 8316만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>웅스턴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%8A%A4%ED%84%B4</t>
+  </si>
+  <si>
+    <t>469조 3660억 7368만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>적환</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%81%ED%99%98</t>
+  </si>
+  <si>
+    <t>462조 8085억 8080만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>슈기리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EA%B8%B0%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>265조 6426억 7458만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>처돌2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%98%EB%8F%8C2</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>197조 5784억 1392만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>소풍족</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%ED%92%8D%EC%A1%B1</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>112조 8656억 767만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>순수띵귤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%9C%EC%88%98%EB%9D%B5%EA%B7%A4</t>
+  </si>
+  <si>
+    <t>106조 5179억 6719만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>안바</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%B0%94</t>
+  </si>
+  <si>
+    <t>99조 9217억 4015만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>별뿡</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%BF%A1</t>
+  </si>
+  <si>
+    <t>90조 7071억 5235만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>리세라</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EC%84%B8%EB%9D%BC</t>
+  </si>
+  <si>
+    <t>83조 3466억 2610만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>검환</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%80%ED%99%98</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>73조 5894억 2690만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>재기리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%AC%EA%B8%B0%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>58조 4855억 4450만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>동키링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%ED%82%A4%EB%A7%81</t>
+  </si>
+  <si>
+    <t>57조 8763억 574만</t>
+  </si>
+  <si>
+    <t>기데</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%8D%B0</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>51조 4112억 4948만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>혀로우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%80%EB%A1%9C%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>50조 5361억 9525만</t>
+  </si>
+  <si>
+    <t>무열대</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%97%B4%EB%8C%80</t>
+  </si>
+  <si>
+    <t>49조 9126억 1957만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>쿧임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A7%EC%9E%84</t>
+  </si>
+  <si>
+    <t>39조 7418억 6382만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>허이다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%97%88%EC%9D%B4%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>36조 6805억 691만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>별빛낭만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%B9%9B%EB%82%AD%EB%A7%8C</t>
+  </si>
+  <si>
+    <t>35조 52억 1617만</t>
+  </si>
+  <si>
+    <t>공격느림</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EA%B2%A9%EB%8A%90%EB%A6%BC</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>32조 2415억 8501만</t>
+  </si>
+  <si>
     <t>29</t>
   </si>
   <si>
-    <t>1위</t>
-  </si>
-  <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>2경 2417조 1198억 8472만</t>
-  </si>
-  <si>
-    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
-  </si>
-  <si>
-    <t>혜영</t>
-  </si>
-  <si>
-    <t>블링블리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B8%94%EB%A7%81%EB%B8%94%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>Scania 27</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>3위</t>
-  </si>
-  <si>
-    <t>2경 376조 8886억 90만</t>
-  </si>
-  <si>
-    <t>토벌 3위 1군 투력 50조 이상 / 토벌 13위 2군 블리블링 10조 이상 / 3군 블링불링 3000억이상 닉변 필수 공헌도 미달 길본 미업글 1일 미접 추방</t>
-  </si>
-  <si>
-    <t>꼴래링</t>
-  </si>
-  <si>
-    <t>LUXURY</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
-  </si>
-  <si>
-    <t>Scania 16</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>Lv.9</t>
-  </si>
-  <si>
-    <t>2경 4923조 4300억 835만</t>
-  </si>
-  <si>
-    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
-  </si>
-  <si>
-    <t>살뽀시</t>
-  </si>
-  <si>
-    <t>item</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=item</t>
-  </si>
-  <si>
-    <t>Scania 34</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>2경 3902조 8715억 115만</t>
-  </si>
-  <si>
-    <t>We Go Together !</t>
-  </si>
-  <si>
-    <t>템이</t>
-  </si>
-  <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>별뽕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%BD%95</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>5478조 3131억 5763만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>도얍스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%96%8D%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>2541조 9921억 9713만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>원빉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EB%B9%89</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>2103조 9436억 5062만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EA%B3%B0%EB%9D%A0</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>2038조 3208억 5895만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>꿀까배기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EA%B9%8C%EB%B0%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>1510조 7114억 1106만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>KR#18TIDK8BQ6</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=KR%2318TIDK8BQ6</t>
-  </si>
-  <si>
-    <t>1202조 9003억 1165만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>팝중이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%9D%EC%A4%91%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>624조 5307억 1559만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>BJ규리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=BJ%EA%B7%9C%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>529조 2704억 5535만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>웅스턴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%8A%A4%ED%84%B4</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>469조 3660억 7368만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>삭제합니다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AD%EC%A0%9C%ED%95%A9%EB%8B%88%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>465조 7601억 1554만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>적환</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%81%ED%99%98</t>
-  </si>
-  <si>
-    <t>381조 1547억 750만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>울산선</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%EC%82%B0%EC%84%A0</t>
-  </si>
-  <si>
-    <t>342조 6624억 8831만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>슈기리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EA%B8%B0%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>202조 6917억 281만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>처돌2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%98%EB%8F%8C2</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>197조 5784억 1392만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>소풍족</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%ED%92%8D%EC%A1%B1</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>112조 8656억 767만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>순수띵귤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%9C%EC%88%98%EB%9D%B5%EA%B7%A4</t>
-  </si>
-  <si>
-    <t>106조 5179억 6719만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>안바</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%B0%94</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>90조 1049억 8003만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>별뿡</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%BF%A1</t>
-  </si>
-  <si>
-    <t>82조 3828억 3891만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>리세라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EC%84%B8%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>75조 9546억 5861만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>검환</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%80%ED%99%98</t>
-  </si>
-  <si>
-    <t>73조 5894억 2690만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>동키링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%ED%82%A4%EB%A7%81</t>
-  </si>
-  <si>
-    <t>57조 8763억 574만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>재기리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%AC%EA%B8%B0%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>54조 6542억 218만</t>
-  </si>
-  <si>
-    <t>무열대</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%97%B4%EB%8C%80</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>49조 5361억 9724만</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>기데</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%8D%B0</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>47조 2928억 1660만</t>
-  </si>
-  <si>
-    <t>혀로우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%80%EB%A1%9C%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>40조 2267억 533만</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>쿧임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A7%EC%9E%84</t>
-  </si>
-  <si>
-    <t>39조 7418억 6382만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>공격느림</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EA%B2%A9%EB%8A%90%EB%A6%BC</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>32조 2415억 8501만</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>허이다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%97%88%EC%9D%B4%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>31조 9810억 3162만</t>
-  </si>
-  <si>
     <t>별득</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%93%9D</t>
   </si>
   <si>
-    <t>12조 1302억 4222만</t>
+    <t>12조 6105억 2359만</t>
   </si>
   <si>
     <t>30</t>
@@ -632,7 +635,277 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%A7%81%EB%AF%B8%EB%85%80</t>
   </si>
   <si>
-    <t>8조 6446억 4978만</t>
+    <t>9조 5278억 9241만</t>
+  </si>
+  <si>
+    <t>얼래링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EB%9E%98%EB%A7%81</t>
+  </si>
+  <si>
+    <t>1경 1276조 5679억 8351만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BC%B4%EB%9E%98%EB%A7%81</t>
+  </si>
+  <si>
+    <t>2549조 7653억 8770만</t>
+  </si>
+  <si>
+    <t>미오링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%98%A4%EB%A7%81</t>
+  </si>
+  <si>
+    <t>1342조 6458억 7093만</t>
+  </si>
+  <si>
+    <t>독수링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EC%88%98%EB%A7%81</t>
+  </si>
+  <si>
+    <t>693조 6092억 5762만</t>
+  </si>
+  <si>
+    <t>별빛링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%B9%9B%EB%A7%81</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>654조 4196억 2809만</t>
+  </si>
+  <si>
+    <t>아마링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A7%88%EB%A7%81</t>
+  </si>
+  <si>
+    <t>513조 5371억 6968만</t>
+  </si>
+  <si>
+    <t>아가링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EA%B0%80%EB%A7%81</t>
+  </si>
+  <si>
+    <t>439조 9232억 481만</t>
+  </si>
+  <si>
+    <t>츄르링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B8%84%EB%A5%B4%EB%A7%81</t>
+  </si>
+  <si>
+    <t>420조 9084억 9514만</t>
+  </si>
+  <si>
+    <t>송보링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%A1%EB%B3%B4%EB%A7%81</t>
+  </si>
+  <si>
+    <t>352조 267억 8567만</t>
+  </si>
+  <si>
+    <t>네버링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EB%B2%84%EB%A7%81</t>
+  </si>
+  <si>
+    <t>338조 645억 327만</t>
+  </si>
+  <si>
+    <t>키플링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%ED%94%8C%EB%A7%81</t>
+  </si>
+  <si>
+    <t>330조 422억 7499만</t>
+  </si>
+  <si>
+    <t>도트링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%ED%8A%B8%EB%A7%81</t>
+  </si>
+  <si>
+    <t>236조 5992억 9221만</t>
+  </si>
+  <si>
+    <t>콕끼링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BD%95%EB%81%BC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>226조 6532억 5236만</t>
+  </si>
+  <si>
+    <t>시러링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%9F%AC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>221조 7270억 9824만</t>
+  </si>
+  <si>
+    <t>멍때링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%8D%EB%95%8C%EB%A7%81</t>
+  </si>
+  <si>
+    <t>203조 8617억 741만</t>
+  </si>
+  <si>
+    <t>무뇌링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%87%8C%EB%A7%81</t>
+  </si>
+  <si>
+    <t>183조 548억 5555만</t>
+  </si>
+  <si>
+    <t>드릴링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%93%9C%EB%A6%B4%EB%A7%81</t>
+  </si>
+  <si>
+    <t>154조 7020억 2136만</t>
+  </si>
+  <si>
+    <t>모꼬링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EA%BC%AC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>137조 3840억 2432만</t>
+  </si>
+  <si>
+    <t>엠오링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%A0%EC%98%A4%EB%A7%81</t>
+  </si>
+  <si>
+    <t>111조 3082억 6404만</t>
+  </si>
+  <si>
+    <t>모델링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%8D%B8%EB%A7%81</t>
+  </si>
+  <si>
+    <t>91조 6914억 7173만</t>
+  </si>
+  <si>
+    <t>해오링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%98%A4%EB%A7%81</t>
+  </si>
+  <si>
+    <t>90조 9706억 1195만</t>
+  </si>
+  <si>
+    <t>푸르링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%A5%B4%EB%A7%81</t>
+  </si>
+  <si>
+    <t>86조 2022억 4374만</t>
+  </si>
+  <si>
+    <t>커포링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%8F%AC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>71조 3512억 145만</t>
+  </si>
+  <si>
+    <t>싸가링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EA%B0%80%EB%A7%81</t>
+  </si>
+  <si>
+    <t>63조 5122억 9773만</t>
+  </si>
+  <si>
+    <t>대가링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EA%B0%80%EB%A7%81</t>
+  </si>
+  <si>
+    <t>60조 3174억 4264만</t>
+  </si>
+  <si>
+    <t>술샘링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%A0%EC%83%98%EB%A7%81</t>
+  </si>
+  <si>
+    <t>55조 3123억 1004만</t>
+  </si>
+  <si>
+    <t>깨구링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%A8%EA%B5%AC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>52조 4315억 1042만</t>
+  </si>
+  <si>
+    <t>꼬물링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%AC%BC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>48조 217억 1160만</t>
+  </si>
+  <si>
+    <t>펭구링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8E%AD%EA%B5%AC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>37조 1968억 6576만</t>
+  </si>
+  <si>
+    <t>링가링가링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%81%EA%B0%80%EB%A7%81%EA%B0%80%EB%A7%81</t>
+  </si>
+  <si>
+    <t>29조 4384억 8796만</t>
   </si>
   <si>
     <t>스타냥이</t>
@@ -662,7 +935,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>2283조 7142억 7674만</t>
+    <t>2291조 1697억 43만</t>
   </si>
   <si>
     <t>말레이히어로</t>
@@ -674,6 +947,15 @@
     <t>1394조 1932억 8825만</t>
   </si>
   <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>1351조 3377억 9806만</t>
+  </si>
+  <si>
     <t>빌런투킬</t>
   </si>
   <si>
@@ -683,15 +965,6 @@
     <t>1120조 9927억 5165만</t>
   </si>
   <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>1112조 8677억 9360만</t>
-  </si>
-  <si>
     <t>스타뎀</t>
   </si>
   <si>
@@ -716,7 +989,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
   </si>
   <si>
-    <t>176조 573억 7249만</t>
+    <t>278조 3832억 696만</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>174조 1025억 3447만</t>
   </si>
   <si>
     <t>부엉이없다</t>
@@ -725,16 +1007,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
   </si>
   <si>
-    <t>153조 6705억 5861만</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>152조 6744억 2175만</t>
+    <t>162조 1649억 2915만</t>
   </si>
   <si>
     <t>프리프리</t>
@@ -743,7 +1016,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
   </si>
   <si>
-    <t>146조 2887억 8379만</t>
+    <t>150조 7025억 6128만</t>
   </si>
   <si>
     <t>꽃을든남자</t>
@@ -752,7 +1025,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
   </si>
   <si>
-    <t>123조 7397억 6038만</t>
+    <t>135조 4527억 1903만</t>
   </si>
   <si>
     <t>쾌감</t>
@@ -764,6 +1037,15 @@
     <t>89조 2869억 199만</t>
   </si>
   <si>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>84조 776억 5946만</t>
+  </si>
+  <si>
     <t>하후돈</t>
   </si>
   <si>
@@ -773,13 +1055,13 @@
     <t>83조 3411억 4487만</t>
   </si>
   <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>75조 5035억 6634만</t>
+    <t>소소채2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
+  </si>
+  <si>
+    <t>77조 1302억 5026만</t>
   </si>
   <si>
     <t>POSCO</t>
@@ -791,13 +1073,13 @@
     <t>65조 7697억 3285만</t>
   </si>
   <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>64조 9867억 9737만</t>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>42조 7791억 4344만</t>
   </si>
   <si>
     <t>루넨</t>
@@ -809,15 +1091,6 @@
     <t>42조 7569억 3167만</t>
   </si>
   <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>38조 3694억 6015만</t>
-  </si>
-  <si>
     <t>김치싸대기</t>
   </si>
   <si>
@@ -833,7 +1106,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
   </si>
   <si>
-    <t>37조 4329억 7511만</t>
+    <t>37조 5548억 7023만</t>
   </si>
   <si>
     <t>포뇨야</t>
@@ -854,31 +1127,28 @@
     <t>32조 3503억 166만</t>
   </si>
   <si>
+    <t>울힝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
+  </si>
+  <si>
+    <t>30조 2709억 4719만</t>
+  </si>
+  <si>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>29조 9578억 9214만</t>
+  </si>
+  <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
   </si>
   <si>
-    <t>28조 5128억 7466만</t>
-  </si>
-  <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>28조 3422억 4602만</t>
-  </si>
-  <si>
-    <t>울힝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
-  </si>
-  <si>
-    <t>27조 7168억 210만</t>
+    <t>29조 2978억 7327만</t>
   </si>
   <si>
     <t>악의꽃</t>
@@ -887,7 +1157,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
   </si>
   <si>
-    <t>25조 817억 1488만</t>
+    <t>28조 3643억 3420만</t>
   </si>
   <si>
     <t>몽호</t>
@@ -896,274 +1166,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
   </si>
   <si>
-    <t>22조 9589억 8035만</t>
-  </si>
-  <si>
-    <t>junoflo</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=junoflo</t>
-  </si>
-  <si>
-    <t>10조 9422억 5450만</t>
-  </si>
-  <si>
-    <t>얼래링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EB%9E%98%EB%A7%81</t>
-  </si>
-  <si>
-    <t>1경 166조 1516억 7490만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BC%B4%EB%9E%98%EB%A7%81</t>
-  </si>
-  <si>
-    <t>2549조 7653억 8770만</t>
-  </si>
-  <si>
-    <t>미오링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%98%A4%EB%A7%81</t>
-  </si>
-  <si>
-    <t>1131조 6516억 3529만</t>
-  </si>
-  <si>
-    <t>별빛링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%B9%9B%EB%A7%81</t>
-  </si>
-  <si>
-    <t>654조 4196억 2809만</t>
-  </si>
-  <si>
-    <t>아마링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A7%88%EB%A7%81</t>
-  </si>
-  <si>
-    <t>513조 5371억 6968만</t>
-  </si>
-  <si>
-    <t>아가링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EA%B0%80%EB%A7%81</t>
-  </si>
-  <si>
-    <t>439조 9232억 481만</t>
-  </si>
-  <si>
-    <t>독수링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EC%88%98%EB%A7%81</t>
-  </si>
-  <si>
-    <t>361조 6342억 3673만</t>
-  </si>
-  <si>
-    <t>송보링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%A1%EB%B3%B4%EB%A7%81</t>
-  </si>
-  <si>
-    <t>350조 9928억 8717만</t>
-  </si>
-  <si>
-    <t>츄르링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B8%84%EB%A5%B4%EB%A7%81</t>
-  </si>
-  <si>
-    <t>328조 4583억 4570만</t>
-  </si>
-  <si>
-    <t>네버링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EB%B2%84%EB%A7%81</t>
-  </si>
-  <si>
-    <t>300조 447억 6414만</t>
-  </si>
-  <si>
-    <t>키플링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%ED%94%8C%EB%A7%81</t>
-  </si>
-  <si>
-    <t>287조 3416억 4521만</t>
-  </si>
-  <si>
-    <t>도트링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%ED%8A%B8%EB%A7%81</t>
-  </si>
-  <si>
-    <t>227조 4428억 5962만</t>
-  </si>
-  <si>
-    <t>시러링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%9F%AC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>221조 7270억 9824만</t>
-  </si>
-  <si>
-    <t>콕끼링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BD%95%EB%81%BC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>220조 3936억 1739만</t>
-  </si>
-  <si>
-    <t>멍때링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%8D%EB%95%8C%EB%A7%81</t>
-  </si>
-  <si>
-    <t>190조 8214억 9286만</t>
-  </si>
-  <si>
-    <t>무뇌링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%87%8C%EB%A7%81</t>
-  </si>
-  <si>
-    <t>173조 5650억 9285만</t>
-  </si>
-  <si>
-    <t>모꼬링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EA%BC%AC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>137조 3840억 2432만</t>
-  </si>
-  <si>
-    <t>드릴링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%93%9C%EB%A6%B4%EB%A7%81</t>
-  </si>
-  <si>
-    <t>129조 9535억 2913만</t>
-  </si>
-  <si>
-    <t>엠오링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%A0%EC%98%A4%EB%A7%81</t>
-  </si>
-  <si>
-    <t>109조 1260억 4151만</t>
-  </si>
-  <si>
-    <t>모델링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%8D%B8%EB%A7%81</t>
-  </si>
-  <si>
-    <t>83조 7155억 2035만</t>
-  </si>
-  <si>
-    <t>해오링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%98%A4%EB%A7%81</t>
-  </si>
-  <si>
-    <t>71조 5247억 3341만</t>
-  </si>
-  <si>
-    <t>싸가링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EA%B0%80%EB%A7%81</t>
-  </si>
-  <si>
-    <t>63조 5122억 9773만</t>
-  </si>
-  <si>
-    <t>커포링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%8F%AC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>61조 1950억 45만</t>
-  </si>
-  <si>
-    <t>푸르링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%A5%B4%EB%A7%81</t>
-  </si>
-  <si>
-    <t>58조 4644억 2830만</t>
-  </si>
-  <si>
-    <t>대가링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EA%B0%80%EB%A7%81</t>
-  </si>
-  <si>
-    <t>55조 2270억 1144만</t>
-  </si>
-  <si>
-    <t>술샘링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%A0%EC%83%98%EB%A7%81</t>
-  </si>
-  <si>
-    <t>52조 9493억 9910만</t>
-  </si>
-  <si>
-    <t>깨구링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%A8%EA%B5%AC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>52조 4315억 1042만</t>
-  </si>
-  <si>
-    <t>펭구링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8E%AD%EA%B5%AC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>37조 1968억 6576만</t>
-  </si>
-  <si>
-    <t>꼬물링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%AC%BC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>34조 8374억 4624만</t>
+    <t>24조 3071억 135만</t>
   </si>
   <si>
     <t>가숭혁</t>
@@ -1181,9 +1184,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%B4%EB%BD%80%EC%8B%9C</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>2783조 7486억 5197만</t>
   </si>
   <si>
@@ -1193,7 +1193,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%83%B8%EC%B9%98</t>
   </si>
   <si>
-    <t>1602조 4421억 8043만</t>
+    <t>1675조 2080억 6401만</t>
   </si>
   <si>
     <t>달싹</t>
@@ -1205,6 +1205,15 @@
     <t>651조 4386억 2995만</t>
   </si>
   <si>
+    <t>김우이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%9A%B0%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>516조 9172억 9058만</t>
+  </si>
+  <si>
     <t>뇌쉬</t>
   </si>
   <si>
@@ -1220,7 +1229,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
   </si>
   <si>
-    <t>438조 5942억 9056만</t>
+    <t>457조 7446억 1398만</t>
   </si>
   <si>
     <t>서예슬</t>
@@ -1229,7 +1238,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
   </si>
   <si>
-    <t>364조 5041억 7581만</t>
+    <t>380조 3833억 3836만</t>
   </si>
   <si>
     <t>덜박</t>
@@ -1238,7 +1247,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%9C%EB%B0%95</t>
   </si>
   <si>
-    <t>342조 8915억 4459만</t>
+    <t>345조 6593억 1885만</t>
   </si>
   <si>
     <t>옴짝</t>
@@ -1250,31 +1259,31 @@
     <t>267조 4873억 4322만</t>
   </si>
   <si>
+    <t>임승민</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
+  </si>
+  <si>
+    <t>216조 5819억 7929만</t>
+  </si>
+  <si>
+    <t>중탸치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A4%91%ED%83%B8%EC%B9%98</t>
+  </si>
+  <si>
+    <t>196조 911억 5708만</t>
+  </si>
+  <si>
     <t>몬함</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
   </si>
   <si>
-    <t>180조 8530억 1673만</t>
-  </si>
-  <si>
-    <t>임승민</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
-  </si>
-  <si>
-    <t>161조 2593억 1562만</t>
-  </si>
-  <si>
-    <t>중타치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A4%91%ED%83%80%EC%B9%98</t>
-  </si>
-  <si>
-    <t>146조 2366억 2351만</t>
+    <t>181조 4736억 2563만</t>
   </si>
   <si>
     <t>뻔수니</t>
@@ -1283,7 +1292,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
   </si>
   <si>
-    <t>83조 6254억 8539만</t>
+    <t>85조 7125억 8889만</t>
   </si>
   <si>
     <t>하탸치</t>
@@ -1301,7 +1310,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
   </si>
   <si>
-    <t>38조 8453억 6606만</t>
+    <t>41조 4388억 7692만</t>
   </si>
   <si>
     <t>쑤삔</t>
@@ -1313,7 +1322,7 @@
     <t>나이트로드</t>
   </si>
   <si>
-    <t>30조 6445억 1264만</t>
+    <t>34조 7192억 7265만</t>
   </si>
   <si>
     <t>류테</t>
@@ -1325,6 +1334,15 @@
     <t>29조 4752억 2082만</t>
   </si>
   <si>
+    <t>26퐝바</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%ED%90%9D%EB%B0%94</t>
+  </si>
+  <si>
+    <t>23조 1264억 4895만</t>
+  </si>
+  <si>
     <t>브깃</t>
   </si>
   <si>
@@ -1334,22 +1352,13 @@
     <t>21조 9533억 9367만</t>
   </si>
   <si>
-    <t>26퐝바</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%ED%90%9D%EB%B0%94</t>
-  </si>
-  <si>
-    <t>21조 2028억 7543만</t>
-  </si>
-  <si>
     <t>아모르파티퀘</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
   </si>
   <si>
-    <t>20조 3738억 8689만</t>
+    <t>21조 3943억 1549만</t>
   </si>
   <si>
     <t>뻐늬</t>
@@ -1358,7 +1367,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%90%EB%8A%AC</t>
   </si>
   <si>
-    <t>17조 6676억 1993만</t>
+    <t>19조 728억 950만</t>
+  </si>
+  <si>
+    <t>메키무라딘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%AC%B4%EB%9D%BC%EB%94%98</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>18조 7407억 6984만</t>
   </si>
   <si>
     <t>26조선</t>
@@ -1370,25 +1391,13 @@
     <t>15조 1898억 2101만</t>
   </si>
   <si>
-    <t>메키무라딘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%AC%B4%EB%9D%BC%EB%94%98</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>15조 637억 960만</t>
-  </si>
-  <si>
     <t>뿜삐</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
   </si>
   <si>
-    <t>12조 5345억 9009만</t>
+    <t>13조 2695억 2748만</t>
   </si>
   <si>
     <t>크앙레몬</t>
@@ -1397,7 +1406,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
   </si>
   <si>
-    <t>12조 3514억 8343만</t>
+    <t>12조 4978억 3574만</t>
   </si>
   <si>
     <t>최씨용</t>
@@ -1415,7 +1424,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
   </si>
   <si>
-    <t>7조 8227억 8591만</t>
+    <t>8조 6161억 9253만</t>
   </si>
   <si>
     <t>귬스파파</t>
@@ -1433,7 +1442,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%98%81%ED%9D%AC%EB%A9%88%EB%AD%84%EB%AF%B8</t>
   </si>
   <si>
-    <t>5조 8558억 8323만</t>
+    <t>5조 9125억 826만</t>
   </si>
   <si>
     <t>코로드</t>
@@ -1442,7 +1451,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EB%A1%9C%EB%93%9C</t>
   </si>
   <si>
-    <t>1경 3094조 6438억 3447만</t>
+    <t>1경 6280조 4127억 4609만</t>
   </si>
   <si>
     <t>맠스맨</t>
@@ -1460,7 +1469,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A8%EB%85%80</t>
   </si>
   <si>
-    <t>4137조 662억 9711만</t>
+    <t>4173조 6151억 3152만</t>
   </si>
   <si>
     <t>빌린</t>
@@ -1469,7 +1478,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%A6%B0</t>
   </si>
   <si>
-    <t>227조 2347억 3543만</t>
+    <t>241조 1262억 6903만</t>
   </si>
   <si>
     <t>Bit숍</t>
@@ -1478,7 +1487,7 @@
     <t>https://mgf.gg/contents/character.php?n=Bit%EC%88%8D</t>
   </si>
   <si>
-    <t>206조 183억 6859만</t>
+    <t>217조 4514억 1006만</t>
   </si>
   <si>
     <t>김해님</t>
@@ -1487,7 +1496,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%95%B4%EB%8B%98</t>
   </si>
   <si>
-    <t>180조 6142억 3026만</t>
+    <t>187조 7550억 4787만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%85%9C%EC%9D%B4</t>
@@ -1502,7 +1511,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%ED%83%80%EC%84%A0%EB%AC%BC</t>
   </si>
   <si>
-    <t>69조 9420억 6520만</t>
+    <t>90조 4873억 5756만</t>
   </si>
   <si>
     <t>아마날</t>
@@ -1511,7 +1520,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A7%88%EB%82%A0</t>
   </si>
   <si>
-    <t>67조 4055억 473만</t>
+    <t>70조 9072억 6367만</t>
   </si>
   <si>
     <t>도령3</t>
@@ -1520,7 +1529,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A0%B93</t>
   </si>
   <si>
-    <t>62조 5165억 8158만</t>
+    <t>63조 443억 7659만</t>
   </si>
   <si>
     <t>조콩나무</t>
@@ -1532,13 +1541,22 @@
     <t>59조 8696억 1836만</t>
   </si>
   <si>
+    <t>이러는거아냐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%9F%AC%EB%8A%94%EA%B1%B0%EC%95%84%EB%83%90</t>
+  </si>
+  <si>
+    <t>36조 4798억 6021만</t>
+  </si>
+  <si>
     <t>숮2</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%88%AE2</t>
   </si>
   <si>
-    <t>30조 1571억 5512만</t>
+    <t>32조 6148억 5962만</t>
   </si>
   <si>
     <t>백엄경</t>
@@ -1547,16 +1565,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%EC%97%84%EA%B2%BD</t>
   </si>
   <si>
-    <t>29조 8088억 2900만</t>
-  </si>
-  <si>
-    <t>이러는거아냐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%9F%AC%EB%8A%94%EA%B1%B0%EC%95%84%EB%83%90</t>
-  </si>
-  <si>
-    <t>28조 236억 7493만</t>
+    <t>30조 4285억 9777만</t>
   </si>
   <si>
     <t>키움맨</t>
@@ -1565,7 +1574,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%9B%80%EB%A7%A8</t>
   </si>
   <si>
-    <t>21조 2617억 8155만</t>
+    <t>24조 258억 2609만</t>
   </si>
   <si>
     <t>시프님</t>
@@ -1574,7 +1583,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%ED%94%84%EB%8B%98</t>
   </si>
   <si>
-    <t>19조 7147억 5854만</t>
+    <t>21조 8490억 9889만</t>
+  </si>
+  <si>
+    <t>한유화</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EC%9C%A0%ED%99%94</t>
+  </si>
+  <si>
+    <t>18조 6435억 9613만</t>
+  </si>
+  <si>
+    <t>최소뎀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%86%8C%EB%8E%80</t>
+  </si>
+  <si>
+    <t>18조 5838억 1558만</t>
   </si>
   <si>
     <t>천칸</t>
@@ -1583,25 +1610,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B9%B8</t>
   </si>
   <si>
-    <t>17조 8681억 7133만</t>
-  </si>
-  <si>
-    <t>최소뎀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%86%8C%EB%8E%80</t>
-  </si>
-  <si>
-    <t>17조 5039억 9837만</t>
-  </si>
-  <si>
-    <t>한유화</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EC%9C%A0%ED%99%94</t>
-  </si>
-  <si>
-    <t>16조 3190억 3028만</t>
+    <t>18조 3643억 1370만</t>
   </si>
   <si>
     <t>95도도</t>
@@ -1610,7 +1619,7 @@
     <t>https://mgf.gg/contents/character.php?n=95%EB%8F%84%EB%8F%84</t>
   </si>
   <si>
-    <t>15조 4977억 3408만</t>
+    <t>16조 5765억 2997만</t>
   </si>
   <si>
     <t>혈마신</t>
@@ -1619,7 +1628,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%88%EB%A7%88%EC%8B%A0</t>
   </si>
   <si>
-    <t>8조 8287억 706만</t>
+    <t>9조 5421억 6790만</t>
   </si>
   <si>
     <t>숑당</t>
@@ -1628,7 +1637,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%91%EB%8B%B9</t>
   </si>
   <si>
-    <t>8조 4629억 6911만</t>
+    <t>9조 1500억 1948만</t>
   </si>
   <si>
     <t>리얼크크</t>
@@ -1637,7 +1646,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EC%96%BC%ED%81%AC%ED%81%AC</t>
   </si>
   <si>
-    <t>7조 9879억 1938만</t>
+    <t>8조 8174억 2290만</t>
   </si>
   <si>
     <t>현즈</t>
@@ -1646,7 +1655,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%A6%88</t>
   </si>
   <si>
-    <t>5조 5442억 6289만</t>
+    <t>5조 7647억 9211만</t>
   </si>
   <si>
     <t>박하민린</t>
@@ -1658,7 +1667,7 @@
     <t>99</t>
   </si>
   <si>
-    <t>4조 4710억 2212만</t>
+    <t>5조 2369억 4118만</t>
   </si>
   <si>
     <t>군명</t>
@@ -1670,7 +1679,7 @@
     <t>98</t>
   </si>
   <si>
-    <t>3조 7959억 1965만</t>
+    <t>4조 1286억 2116만</t>
   </si>
   <si>
     <t>김똔똔</t>
@@ -1679,7 +1688,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%98%94%EB%98%94</t>
   </si>
   <si>
-    <t>3조 5614억 3503만</t>
+    <t>3조 8769억 8616만</t>
   </si>
   <si>
     <t>장수흙침대</t>
@@ -1688,7 +1697,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EC%88%98%ED%9D%99%EC%B9%A8%EB%8C%80</t>
   </si>
   <si>
-    <t>3조 620억 6174만</t>
+    <t>3조 1329억 8847만</t>
   </si>
   <si>
     <t>니코짱</t>
@@ -1697,22 +1706,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EC%BD%94%EC%A7%B1</t>
   </si>
   <si>
+    <t>2조 6604억 3946만</t>
+  </si>
+  <si>
+    <t>뉴맹우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%89%B4%EB%A7%B9%EC%9A%B0</t>
+  </si>
+  <si>
     <t>97</t>
   </si>
   <si>
-    <t>2조 4031억 3620만</t>
-  </si>
-  <si>
-    <t>뉴맹우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%89%B4%EB%A7%B9%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>1조 1323억 8185만</t>
+    <t>1조 1804억 9938만</t>
   </si>
 </sst>
 </file>
@@ -2240,7 +2246,7 @@
         <v>30</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>40</v>
@@ -2275,7 +2281,7 @@
         <v>46</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>47</v>
@@ -2316,13 +2322,13 @@
         <v>54</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>55</v>
@@ -2579,10 +2585,10 @@
         <v>86</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2593,28 +2599,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2625,28 +2631,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2657,28 +2663,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="I10" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2689,28 +2695,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="H11" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2721,28 +2727,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2753,28 +2759,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2785,28 +2791,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2817,28 +2823,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2849,28 +2855,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2881,28 +2887,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2913,25 +2919,25 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>149</v>
@@ -2960,10 +2966,10 @@
         <v>69</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>153</v>
@@ -2992,13 +2998,13 @@
         <v>69</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3009,28 +3015,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3041,16 +3047,16 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>69</v>
@@ -3059,10 +3065,10 @@
         <v>81</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3073,7 +3079,7 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
+        <v>54</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>167</v>
@@ -3088,13 +3094,13 @@
         <v>69</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3105,28 +3111,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>46</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3137,7 +3143,7 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>46</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>175</v>
@@ -3152,13 +3158,13 @@
         <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="H25" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>178</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3169,7 +3175,7 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>54</v>
+        <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>179</v>
@@ -3184,10 +3190,10 @@
         <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>181</v>
@@ -3216,10 +3222,10 @@
         <v>69</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>185</v>
@@ -3248,13 +3254,13 @@
         <v>69</v>
       </c>
       <c r="G28" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3265,25 +3271,25 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="H29" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>194</v>
@@ -3297,28 +3303,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>28</v>
+        <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3329,28 +3335,28 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -3405,7 +3411,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3449,22 +3455,22 @@
         <v>66</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>204</v>
+        <v>97</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>205</v>
@@ -3481,25 +3487,25 @@
         <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>208</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -3513,25 +3519,25 @@
         <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3545,13 +3551,13 @@
         <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>212</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>213</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>69</v>
@@ -3560,10 +3566,10 @@
         <v>70</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3577,22 +3583,22 @@
         <v>88</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>217</v>
@@ -3621,10 +3627,10 @@
         <v>69</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>220</v>
@@ -3638,7 +3644,7 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>221</v>
@@ -3653,10 +3659,10 @@
         <v>69</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>223</v>
@@ -3670,7 +3676,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>224</v>
@@ -3685,10 +3691,10 @@
         <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>226</v>
@@ -3702,7 +3708,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>227</v>
@@ -3717,10 +3723,10 @@
         <v>69</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>229</v>
@@ -3734,7 +3740,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>230</v>
@@ -3749,10 +3755,10 @@
         <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>232</v>
@@ -3766,7 +3772,7 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>233</v>
@@ -3781,10 +3787,10 @@
         <v>69</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>235</v>
@@ -3798,7 +3804,7 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>236</v>
@@ -3813,10 +3819,10 @@
         <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>101</v>
+        <v>216</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>238</v>
@@ -3830,7 +3836,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>239</v>
@@ -3845,10 +3851,10 @@
         <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>241</v>
@@ -3862,7 +3868,7 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>242</v>
@@ -3877,10 +3883,10 @@
         <v>69</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>244</v>
@@ -3894,7 +3900,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>245</v>
@@ -3909,10 +3915,10 @@
         <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>247</v>
@@ -3926,7 +3932,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>248</v>
@@ -3941,10 +3947,10 @@
         <v>69</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>250</v>
@@ -3958,7 +3964,7 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>251</v>
@@ -3973,10 +3979,10 @@
         <v>69</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>253</v>
@@ -4005,10 +4011,10 @@
         <v>69</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>256</v>
@@ -4037,10 +4043,10 @@
         <v>69</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>259</v>
@@ -4054,7 +4060,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>260</v>
@@ -4069,10 +4075,10 @@
         <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>262</v>
@@ -4086,7 +4092,7 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>263</v>
@@ -4101,10 +4107,10 @@
         <v>69</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>265</v>
@@ -4118,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
+        <v>54</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>266</v>
@@ -4133,10 +4139,10 @@
         <v>69</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>268</v>
@@ -4150,7 +4156,7 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>46</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>269</v>
@@ -4165,10 +4171,10 @@
         <v>69</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>271</v>
@@ -4182,7 +4188,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>46</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>272</v>
@@ -4197,10 +4203,10 @@
         <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>274</v>
@@ -4214,28 +4220,28 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>54</v>
+        <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>34</v>
+        <v>275</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>34</v>
+        <v>275</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>112</v>
+        <v>216</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4249,22 +4255,22 @@
         <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>279</v>
+        <v>114</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>280</v>
@@ -4293,10 +4299,10 @@
         <v>69</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>283</v>
@@ -4310,7 +4316,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>38</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>284</v>
@@ -4325,10 +4331,10 @@
         <v>69</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>286</v>
@@ -4342,7 +4348,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>28</v>
+        <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>287</v>
@@ -4357,10 +4363,10 @@
         <v>69</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>289</v>
@@ -4374,7 +4380,7 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>290</v>
@@ -4389,10 +4395,10 @@
         <v>69</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>292</v>
@@ -4506,13 +4512,13 @@
         <v>69</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>71</v>
+        <v>295</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4526,25 +4532,25 @@
         <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>42</v>
+        <v>297</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>42</v>
+        <v>297</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4558,25 +4564,25 @@
         <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4590,25 +4596,25 @@
         <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>279</v>
+        <v>86</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4622,25 +4628,25 @@
         <v>88</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4654,25 +4660,25 @@
         <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4683,28 +4689,28 @@
         <v>35</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4715,28 +4721,28 @@
         <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4747,28 +4753,28 @@
         <v>35</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4779,28 +4785,28 @@
         <v>35</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4811,28 +4817,28 @@
         <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4843,28 +4849,28 @@
         <v>35</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>279</v>
+        <v>102</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4875,28 +4881,28 @@
         <v>35</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4907,28 +4913,28 @@
         <v>35</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4939,28 +4945,28 @@
         <v>35</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4971,28 +4977,28 @@
         <v>35</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5003,28 +5009,28 @@
         <v>35</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5038,25 +5044,25 @@
         <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5070,25 +5076,25 @@
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5099,28 +5105,28 @@
         <v>35</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5131,28 +5137,28 @@
         <v>35</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5163,28 +5169,28 @@
         <v>35</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
+        <v>54</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5195,28 +5201,28 @@
         <v>35</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>46</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5227,28 +5233,28 @@
         <v>35</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>46</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>189</v>
+        <v>102</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5259,28 +5265,28 @@
         <v>35</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>54</v>
+        <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>279</v>
+        <v>114</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5294,25 +5300,25 @@
         <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>112</v>
+        <v>216</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5326,25 +5332,25 @@
         <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>370</v>
+        <v>42</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>370</v>
+        <v>42</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5355,28 +5361,28 @@
         <v>35</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>38</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5387,28 +5393,28 @@
         <v>35</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>28</v>
+        <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5453,7 +5459,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -5506,13 +5512,13 @@
         <v>66</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>69</v>
@@ -5521,10 +5527,10 @@
         <v>70</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5544,7 +5550,7 @@
         <v>50</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>85</v>
@@ -5553,7 +5559,7 @@
         <v>81</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>384</v>
+        <v>71</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>385</v>
@@ -5582,7 +5588,7 @@
         <v>69</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>76</v>
@@ -5614,10 +5620,10 @@
         <v>69</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>391</v>
@@ -5646,10 +5652,10 @@
         <v>69</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>394</v>
@@ -5678,10 +5684,10 @@
         <v>69</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>397</v>
@@ -5695,7 +5701,7 @@
         <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>398</v>
@@ -5710,10 +5716,10 @@
         <v>69</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>400</v>
@@ -5727,7 +5733,7 @@
         <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>401</v>
@@ -5742,10 +5748,10 @@
         <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>403</v>
@@ -5759,7 +5765,7 @@
         <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>404</v>
@@ -5774,10 +5780,10 @@
         <v>69</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>406</v>
@@ -5791,7 +5797,7 @@
         <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>407</v>
@@ -5806,10 +5812,10 @@
         <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>279</v>
+        <v>114</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>409</v>
@@ -5823,7 +5829,7 @@
         <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>410</v>
@@ -5838,10 +5844,10 @@
         <v>69</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>412</v>
@@ -5855,7 +5861,7 @@
         <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>413</v>
@@ -5873,7 +5879,7 @@
         <v>81</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>415</v>
@@ -5887,7 +5893,7 @@
         <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>416</v>
@@ -5902,10 +5908,10 @@
         <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>101</v>
+        <v>216</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>418</v>
@@ -5919,7 +5925,7 @@
         <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>419</v>
@@ -5934,10 +5940,10 @@
         <v>69</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>421</v>
@@ -5951,7 +5957,7 @@
         <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>422</v>
@@ -5966,10 +5972,10 @@
         <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>424</v>
@@ -5983,7 +5989,7 @@
         <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>425</v>
@@ -5998,13 +6004,13 @@
         <v>69</v>
       </c>
       <c r="G17" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>427</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>428</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6015,25 +6021,25 @@
         <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="H18" s="2" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>431</v>
@@ -6062,10 +6068,10 @@
         <v>69</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>434</v>
@@ -6094,10 +6100,10 @@
         <v>69</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>437</v>
@@ -6111,7 +6117,7 @@
         <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>438</v>
@@ -6126,10 +6132,10 @@
         <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>112</v>
+        <v>192</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>440</v>
@@ -6143,7 +6149,7 @@
         <v>43</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>441</v>
@@ -6158,10 +6164,10 @@
         <v>69</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>443</v>
@@ -6175,7 +6181,7 @@
         <v>43</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
+        <v>54</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>444</v>
@@ -6190,10 +6196,10 @@
         <v>69</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>446</v>
@@ -6207,7 +6213,7 @@
         <v>43</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>46</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>447</v>
@@ -6222,7 +6228,7 @@
         <v>69</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>449</v>
@@ -6239,7 +6245,7 @@
         <v>43</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>46</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>451</v>
@@ -6254,10 +6260,10 @@
         <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>453</v>
@@ -6271,7 +6277,7 @@
         <v>43</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>54</v>
+        <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>454</v>
@@ -6286,10 +6292,10 @@
         <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>456</v>
@@ -6318,10 +6324,10 @@
         <v>69</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>459</v>
@@ -6350,10 +6356,10 @@
         <v>69</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>462</v>
@@ -6367,7 +6373,7 @@
         <v>43</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>38</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>463</v>
@@ -6382,10 +6388,10 @@
         <v>69</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>465</v>
@@ -6399,7 +6405,7 @@
         <v>43</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>28</v>
+        <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>466</v>
@@ -6414,10 +6420,10 @@
         <v>69</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>468</v>
@@ -6426,8 +6432,40 @@
         <v>24</v>
       </c>
     </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J31"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -6458,6 +6496,7 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
+    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6518,25 +6557,25 @@
         <v>66</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6550,13 +6589,13 @@
         <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>69</v>
@@ -6565,10 +6604,10 @@
         <v>91</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6582,25 +6621,25 @@
         <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6614,25 +6653,25 @@
         <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6646,13 +6685,13 @@
         <v>88</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>69</v>
@@ -6661,10 +6700,10 @@
         <v>81</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6678,13 +6717,13 @@
         <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>69</v>
@@ -6693,10 +6732,10 @@
         <v>86</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6707,7 +6746,7 @@
         <v>51</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>57</v>
@@ -6716,7 +6755,7 @@
         <v>57</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>85</v>
@@ -6725,10 +6764,10 @@
         <v>81</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6739,16 +6778,16 @@
         <v>51</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>69</v>
@@ -6757,10 +6796,10 @@
         <v>70</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6771,28 +6810,28 @@
         <v>51</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6803,16 +6842,16 @@
         <v>51</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>69</v>
@@ -6821,10 +6860,10 @@
         <v>70</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6835,28 +6874,28 @@
         <v>51</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6867,28 +6906,28 @@
         <v>51</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>427</v>
+        <v>86</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6899,28 +6938,28 @@
         <v>51</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>112</v>
+        <v>430</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>449</v>
+        <v>169</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6931,28 +6970,28 @@
         <v>51</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>172</v>
+        <v>449</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6963,28 +7002,28 @@
         <v>51</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6995,16 +7034,16 @@
         <v>51</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>69</v>
@@ -7013,10 +7052,10 @@
         <v>86</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7027,28 +7066,28 @@
         <v>51</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7062,13 +7101,13 @@
         <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>69</v>
@@ -7077,10 +7116,10 @@
         <v>70</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7094,25 +7133,25 @@
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>449</v>
+        <v>169</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7123,16 +7162,16 @@
         <v>51</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>69</v>
@@ -7141,10 +7180,10 @@
         <v>70</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7155,16 +7194,16 @@
         <v>51</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>69</v>
@@ -7173,10 +7212,10 @@
         <v>81</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7187,28 +7226,28 @@
         <v>51</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
+        <v>54</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>449</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7219,16 +7258,16 @@
         <v>51</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>46</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>69</v>
@@ -7240,7 +7279,7 @@
         <v>449</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7251,28 +7290,28 @@
         <v>51</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>46</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>449</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7283,28 +7322,28 @@
         <v>51</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>54</v>
+        <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7318,13 +7357,13 @@
         <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>69</v>
@@ -7333,10 +7372,10 @@
         <v>91</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7350,13 +7389,13 @@
         <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>69</v>
@@ -7365,10 +7404,10 @@
         <v>81</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7379,28 +7418,28 @@
         <v>51</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>38</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -7411,28 +7450,28 @@
         <v>51</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>28</v>
+        <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -7443,16 +7482,16 @@
         <v>51</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>69</v>
@@ -7461,10 +7500,10 @@
         <v>70</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -149,7 +149,7 @@
     <t>1위</t>
   </si>
   <si>
-    <t>2경 4659조 4565억 6859만</t>
+    <t>2경 4688조 3717억 8454만</t>
   </si>
   <si>
     <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
@@ -938,6 +938,15 @@
     <t>2291조 1697억 43만</t>
   </si>
   <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>1407조 6499억 5640만</t>
+  </si>
+  <si>
     <t>말레이히어로</t>
   </si>
   <si>
@@ -947,15 +956,6 @@
     <t>1394조 1932억 8825만</t>
   </si>
   <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>1351조 3377억 9806만</t>
-  </si>
-  <si>
     <t>빌런투킬</t>
   </si>
   <si>
@@ -1007,7 +1007,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
   </si>
   <si>
-    <t>162조 1649억 2915만</t>
+    <t>162조 5886억 9598만</t>
   </si>
   <si>
     <t>프리프리</t>
@@ -1034,7 +1034,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
   </si>
   <si>
-    <t>89조 2869억 199만</t>
+    <t>101조 3300억 3895만</t>
   </si>
   <si>
     <t>잼포즈</t>
@@ -1043,7 +1043,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>84조 776억 5946만</t>
+    <t>84조 4353억 6632만</t>
   </si>
   <si>
     <t>하후돈</t>
@@ -1052,7 +1052,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
   </si>
   <si>
-    <t>83조 3411억 4487만</t>
+    <t>83조 4958억 6972만</t>
   </si>
   <si>
     <t>소소채2</t>
@@ -1061,7 +1061,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
   </si>
   <si>
-    <t>77조 1302억 5026만</t>
+    <t>79조 606억 7880만</t>
   </si>
   <si>
     <t>POSCO</t>
@@ -1073,22 +1073,40 @@
     <t>65조 7697억 3285만</t>
   </si>
   <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>46조 4973억 6304만</t>
+  </si>
+  <si>
     <t>할룽</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
   </si>
   <si>
-    <t>42조 7791억 4344만</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>42조 7569억 3167만</t>
+    <t>43조 9302억 789만</t>
+  </si>
+  <si>
+    <t>포뇨야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
+  </si>
+  <si>
+    <t>40조 6065억 2233만</t>
+  </si>
+  <si>
+    <t>두근푸근연근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>40조 3193억 9244만</t>
   </si>
   <si>
     <t>김치싸대기</t>
@@ -1100,22 +1118,13 @@
     <t>38조 1459억 7981만</t>
   </si>
   <si>
-    <t>두근푸근연근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>37조 5548억 7023만</t>
-  </si>
-  <si>
-    <t>포뇨야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
-  </si>
-  <si>
-    <t>35조 3962억 1100만</t>
+    <t>악의꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
+  </si>
+  <si>
+    <t>36조 6837억 5297만</t>
   </si>
   <si>
     <t>대방어조아</t>
@@ -1124,7 +1133,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
   </si>
   <si>
-    <t>32조 3503억 166만</t>
+    <t>33조 1885억 3176만</t>
   </si>
   <si>
     <t>울힝</t>
@@ -1133,7 +1142,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
   </si>
   <si>
-    <t>30조 2709억 4719만</t>
+    <t>32조 2430억 2723만</t>
   </si>
   <si>
     <t>제로슈가</t>
@@ -1142,22 +1151,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
   </si>
   <si>
-    <t>29조 9578억 9214만</t>
+    <t>31조 4662억 190만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
   </si>
   <si>
-    <t>29조 2978억 7327만</t>
-  </si>
-  <si>
-    <t>악의꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
-  </si>
-  <si>
-    <t>28조 3643억 3420만</t>
+    <t>29조 5789억 1997만</t>
   </si>
   <si>
     <t>몽호</t>
@@ -1184,7 +1184,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%B4%EB%BD%80%EC%8B%9C</t>
   </si>
   <si>
-    <t>2783조 7486억 5197만</t>
+    <t>2831조 1506억 5892만</t>
   </si>
   <si>
     <t>상탸치</t>
@@ -1193,7 +1193,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%83%B8%EC%B9%98</t>
   </si>
   <si>
-    <t>1675조 2080억 6401만</t>
+    <t>1676조 5414억 1837만</t>
   </si>
   <si>
     <t>달싹</t>
@@ -1202,7 +1202,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EC%8B%B9</t>
   </si>
   <si>
-    <t>651조 4386억 2995만</t>
+    <t>708조 1355억 7402만</t>
   </si>
   <si>
     <t>김우이</t>
@@ -1238,7 +1238,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
   </si>
   <si>
-    <t>380조 3833억 3836만</t>
+    <t>381조 6871억 2231만</t>
   </si>
   <si>
     <t>덜박</t>
@@ -1247,7 +1247,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%9C%EB%B0%95</t>
   </si>
   <si>
-    <t>345조 6593억 1885만</t>
+    <t>353조 4051억 6458만</t>
   </si>
   <si>
     <t>옴짝</t>
@@ -1292,7 +1292,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
   </si>
   <si>
-    <t>85조 7125억 8889만</t>
+    <t>88조 5232억 4641만</t>
   </si>
   <si>
     <t>하탸치</t>
@@ -1301,7 +1301,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%83%B8%EC%B9%98</t>
   </si>
   <si>
-    <t>59조 6571억 7041만</t>
+    <t>73조 6589억 4898만</t>
   </si>
   <si>
     <t>26배털</t>
@@ -1310,7 +1310,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
   </si>
   <si>
-    <t>41조 4388억 7692만</t>
+    <t>43조 5788억 651만</t>
   </si>
   <si>
     <t>쑤삔</t>
@@ -1322,7 +1322,7 @@
     <t>나이트로드</t>
   </si>
   <si>
-    <t>34조 7192억 7265만</t>
+    <t>37조 4179억 3701만</t>
   </si>
   <si>
     <t>류테</t>
@@ -1376,193 +1376,193 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%AC%B4%EB%9D%BC%EB%94%98</t>
   </si>
   <si>
+    <t>18조 7407억 6984만</t>
+  </si>
+  <si>
+    <t>26조선</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EC%A1%B0%EC%84%A0</t>
+  </si>
+  <si>
+    <t>18조 1871억 4713만</t>
+  </si>
+  <si>
+    <t>뿜삐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
+  </si>
+  <si>
+    <t>17조 1535억 3231만</t>
+  </si>
+  <si>
+    <t>최씨용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%94%A8%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>14조 623억 4943만</t>
+  </si>
+  <si>
+    <t>크앙레몬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>13조 7002억 6087만</t>
+  </si>
+  <si>
+    <t>예라미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>8조 6489억 2060만</t>
+  </si>
+  <si>
+    <t>귬스파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%AC%EC%8A%A4%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>7조 905억 306만</t>
+  </si>
+  <si>
+    <t>고영희멈뭄미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%98%81%ED%9D%AC%EB%A9%88%EB%AD%84%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>5조 9661억 9494만</t>
+  </si>
+  <si>
+    <t>코로드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EB%A1%9C%EB%93%9C</t>
+  </si>
+  <si>
+    <t>1경 6280조 4127억 4609만</t>
+  </si>
+  <si>
+    <t>맠스맨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A0%EC%8A%A4%EB%A7%A8</t>
+  </si>
+  <si>
+    <t>4719조 300억 9804만</t>
+  </si>
+  <si>
+    <t>슨녀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A8%EB%85%80</t>
+  </si>
+  <si>
+    <t>4173조 6151억 3152만</t>
+  </si>
+  <si>
+    <t>빌린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>241조 1262억 6903만</t>
+  </si>
+  <si>
+    <t>Bit숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Bit%EC%88%8D</t>
+  </si>
+  <si>
+    <t>217조 4514억 1006만</t>
+  </si>
+  <si>
+    <t>김해님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%95%B4%EB%8B%98</t>
+  </si>
+  <si>
+    <t>187조 7550억 4787만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%85%9C%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>123조 5425억 2061만</t>
+  </si>
+  <si>
+    <t>산타선물</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%ED%83%80%EC%84%A0%EB%AC%BC</t>
+  </si>
+  <si>
+    <t>90조 4873억 5756만</t>
+  </si>
+  <si>
+    <t>아마날</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A7%88%EB%82%A0</t>
+  </si>
+  <si>
+    <t>70조 9072억 6367만</t>
+  </si>
+  <si>
+    <t>도령3</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A0%B93</t>
+  </si>
+  <si>
+    <t>63조 443억 7659만</t>
+  </si>
+  <si>
+    <t>조콩나무</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%BD%A9%EB%82%98%EB%AC%B4</t>
+  </si>
+  <si>
+    <t>59조 8696억 1836만</t>
+  </si>
+  <si>
+    <t>이러는거아냐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%9F%AC%EB%8A%94%EA%B1%B0%EC%95%84%EB%83%90</t>
+  </si>
+  <si>
+    <t>36조 4798억 6021만</t>
+  </si>
+  <si>
+    <t>숮2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%AE2</t>
+  </si>
+  <si>
+    <t>32조 6148억 5962만</t>
+  </si>
+  <si>
+    <t>백엄경</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%EC%97%84%EA%B2%BD</t>
+  </si>
+  <si>
     <t>100</t>
-  </si>
-  <si>
-    <t>18조 7407억 6984만</t>
-  </si>
-  <si>
-    <t>26조선</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EC%A1%B0%EC%84%A0</t>
-  </si>
-  <si>
-    <t>15조 1898억 2101만</t>
-  </si>
-  <si>
-    <t>뿜삐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
-  </si>
-  <si>
-    <t>13조 2695억 2748만</t>
-  </si>
-  <si>
-    <t>크앙레몬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>12조 4978억 3574만</t>
-  </si>
-  <si>
-    <t>최씨용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%94%A8%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>12조 1214억 5182만</t>
-  </si>
-  <si>
-    <t>예라미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>8조 6161억 9253만</t>
-  </si>
-  <si>
-    <t>귬스파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%AC%EC%8A%A4%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>7조 905억 306만</t>
-  </si>
-  <si>
-    <t>고영희멈뭄미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%98%81%ED%9D%AC%EB%A9%88%EB%AD%84%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>5조 9125억 826만</t>
-  </si>
-  <si>
-    <t>코로드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EB%A1%9C%EB%93%9C</t>
-  </si>
-  <si>
-    <t>1경 6280조 4127억 4609만</t>
-  </si>
-  <si>
-    <t>맠스맨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A0%EC%8A%A4%EB%A7%A8</t>
-  </si>
-  <si>
-    <t>4719조 300억 9804만</t>
-  </si>
-  <si>
-    <t>슨녀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A8%EB%85%80</t>
-  </si>
-  <si>
-    <t>4173조 6151억 3152만</t>
-  </si>
-  <si>
-    <t>빌린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>241조 1262억 6903만</t>
-  </si>
-  <si>
-    <t>Bit숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Bit%EC%88%8D</t>
-  </si>
-  <si>
-    <t>217조 4514억 1006만</t>
-  </si>
-  <si>
-    <t>김해님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%95%B4%EB%8B%98</t>
-  </si>
-  <si>
-    <t>187조 7550억 4787만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%85%9C%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>123조 5425억 2061만</t>
-  </si>
-  <si>
-    <t>산타선물</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%ED%83%80%EC%84%A0%EB%AC%BC</t>
-  </si>
-  <si>
-    <t>90조 4873억 5756만</t>
-  </si>
-  <si>
-    <t>아마날</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A7%88%EB%82%A0</t>
-  </si>
-  <si>
-    <t>70조 9072억 6367만</t>
-  </si>
-  <si>
-    <t>도령3</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A0%B93</t>
-  </si>
-  <si>
-    <t>63조 443억 7659만</t>
-  </si>
-  <si>
-    <t>조콩나무</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%BD%A9%EB%82%98%EB%AC%B4</t>
-  </si>
-  <si>
-    <t>59조 8696억 1836만</t>
-  </si>
-  <si>
-    <t>이러는거아냐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%9F%AC%EB%8A%94%EA%B1%B0%EC%95%84%EB%83%90</t>
-  </si>
-  <si>
-    <t>36조 4798억 6021만</t>
-  </si>
-  <si>
-    <t>숮2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%AE2</t>
-  </si>
-  <si>
-    <t>32조 6148억 5962만</t>
-  </si>
-  <si>
-    <t>백엄경</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%EC%97%84%EA%B2%BD</t>
   </si>
   <si>
     <t>30조 4285억 9777만</t>
@@ -4547,7 +4547,7 @@
         <v>81</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>299</v>
@@ -4608,7 +4608,7 @@
         <v>69</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>76</v>
@@ -4640,7 +4640,7 @@
         <v>69</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>76</v>
@@ -4867,7 +4867,7 @@
         <v>102</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>329</v>
@@ -4899,7 +4899,7 @@
         <v>70</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>332</v>
@@ -5088,10 +5088,10 @@
         <v>69</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>350</v>
@@ -5120,7 +5120,7 @@
         <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>131</v>
@@ -5152,10 +5152,10 @@
         <v>69</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>356</v>
@@ -5216,7 +5216,7 @@
         <v>69</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>157</v>
@@ -5248,10 +5248,10 @@
         <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>365</v>
@@ -5280,10 +5280,10 @@
         <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>368</v>
@@ -5312,10 +5312,10 @@
         <v>69</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>216</v>
+        <v>114</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>371</v>
@@ -5332,25 +5332,25 @@
         <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>42</v>
+        <v>372</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>42</v>
+        <v>372</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>114</v>
+        <v>216</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5364,22 +5364,22 @@
         <v>38</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>374</v>
+        <v>42</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>374</v>
+        <v>42</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>375</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>376</v>
@@ -5783,7 +5783,7 @@
         <v>86</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>406</v>
@@ -6231,10 +6231,10 @@
         <v>108</v>
       </c>
       <c r="H24" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>450</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6248,13 +6248,13 @@
         <v>46</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>451</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>452</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>69</v>
@@ -6266,7 +6266,7 @@
         <v>169</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6280,13 +6280,13 @@
         <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>454</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>455</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>69</v>
@@ -6298,7 +6298,7 @@
         <v>193</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6312,25 +6312,25 @@
         <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>458</v>
-      </c>
       <c r="F27" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>169</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6344,25 +6344,25 @@
         <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>461</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>462</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6376,13 +6376,13 @@
         <v>38</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>463</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>464</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>69</v>
@@ -6394,7 +6394,7 @@
         <v>193</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6408,13 +6408,13 @@
         <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>466</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>467</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>69</v>
@@ -6426,7 +6426,7 @@
         <v>193</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6440,13 +6440,13 @@
         <v>199</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>469</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>470</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>69</v>
@@ -6458,7 +6458,7 @@
         <v>193</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6557,13 +6557,13 @@
         <v>66</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>472</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>473</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>69</v>
@@ -6575,7 +6575,7 @@
         <v>382</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6589,13 +6589,13 @@
         <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>475</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>476</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>69</v>
@@ -6607,7 +6607,7 @@
         <v>97</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6621,13 +6621,13 @@
         <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>478</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>479</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>69</v>
@@ -6639,7 +6639,7 @@
         <v>97</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6653,13 +6653,13 @@
         <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>481</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>482</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>69</v>
@@ -6671,7 +6671,7 @@
         <v>131</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6685,13 +6685,13 @@
         <v>88</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>485</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>69</v>
@@ -6703,7 +6703,7 @@
         <v>109</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6717,13 +6717,13 @@
         <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>487</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>488</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>69</v>
@@ -6735,7 +6735,7 @@
         <v>136</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6755,7 +6755,7 @@
         <v>57</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>85</v>
@@ -6767,7 +6767,7 @@
         <v>136</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6781,13 +6781,13 @@
         <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>492</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>493</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>69</v>
@@ -6799,7 +6799,7 @@
         <v>131</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6813,13 +6813,13 @@
         <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>495</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>496</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>69</v>
@@ -6831,7 +6831,7 @@
         <v>157</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6845,13 +6845,13 @@
         <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>499</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>69</v>
@@ -6863,7 +6863,7 @@
         <v>157</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6877,13 +6877,13 @@
         <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>501</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>502</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>69</v>
@@ -6895,7 +6895,7 @@
         <v>169</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6909,13 +6909,13 @@
         <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>504</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>505</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>69</v>
@@ -6927,7 +6927,7 @@
         <v>169</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6941,13 +6941,13 @@
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>507</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>508</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>69</v>
@@ -6959,7 +6959,7 @@
         <v>169</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6973,13 +6973,13 @@
         <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>511</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>69</v>
@@ -6988,7 +6988,7 @@
         <v>114</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>449</v>
+        <v>511</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>512</v>
@@ -7244,7 +7244,7 @@
         <v>102</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>449</v>
+        <v>511</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>536</v>
@@ -7276,7 +7276,7 @@
         <v>70</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>449</v>
+        <v>511</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>539</v>
@@ -7308,7 +7308,7 @@
         <v>102</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>449</v>
+        <v>511</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>542</v>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -8,9 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
-    <sheet name="별곰부대" sheetId="2" r:id="rId2"/>
-    <sheet name="블링블리" sheetId="3" r:id="rId3"/>
-    <sheet name="셀린느" sheetId="4" r:id="rId4"/>
+    <sheet name="셀린느" sheetId="2" r:id="rId2"/>
+    <sheet name="별곰부대" sheetId="3" r:id="rId3"/>
+    <sheet name="블링블리" sheetId="4" r:id="rId4"/>
     <sheet name="LUXURY" sheetId="5" r:id="rId5"/>
     <sheet name="item" sheetId="6" r:id="rId6"/>
   </sheets>
@@ -18,16 +18,16 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">item!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">LUXURY!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">별곰부대!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">블링블리!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">셀린느!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">별곰부대!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">블링블리!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">셀린느!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="566">
   <si>
     <t>guild_name</t>
   </si>
@@ -68,19 +68,52 @@
     <t>data_date</t>
   </si>
   <si>
+    <t>셀린느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%85%80%EB%A6%B0%EB%8A%90</t>
+  </si>
+  <si>
+    <t>Scania</t>
+  </si>
+  <si>
+    <t>Scania 2</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>1위</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>2경 4997조 8297억 61만</t>
+  </si>
+  <si>
+    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
+  </si>
+  <si>
+    <t>혜영</t>
+  </si>
+  <si>
+    <t>2026.04.19</t>
+  </si>
+  <si>
     <t>별곰부대</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B3%84%EA%B3%B0%EB%B6%80%EB%8C%80</t>
   </si>
   <si>
-    <t>Scania</t>
-  </si>
-  <si>
     <t>Scania 30</t>
   </si>
   <si>
-    <t>35</t>
+    <t>38</t>
   </si>
   <si>
     <t>2위</t>
@@ -95,7 +128,7 @@
     <t>1경 8436조 3967억 1957만</t>
   </si>
   <si>
-    <t>가입문의 : 별곰띠</t>
+    <t>가입문의 : 리세라, 별뿡</t>
   </si>
   <si>
     <t>별곰띠</t>
@@ -113,19 +146,13 @@
     <t>Scania 27</t>
   </si>
   <si>
-    <t>32</t>
+    <t>33</t>
   </si>
   <si>
     <t>3위</t>
   </si>
   <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>2경 1091조 6973억 9788만</t>
+    <t>2경 1789조 1060억 4000만</t>
   </si>
   <si>
     <t>토벌 3위 1군 투력 50조 이상 / 토벌 13위 2군 블리블링 10조 이상 / 3군 블링불링 3000억이상 닉변 필수 공헌도 미달 길본 미업글 1일 미접 추방</t>
@@ -134,100 +161,484 @@
     <t>꼴래링</t>
   </si>
   <si>
-    <t>셀린느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%85%80%EB%A6%B0%EB%8A%90</t>
-  </si>
-  <si>
-    <t>Scania 2</t>
+    <t>LUXURY</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
+  </si>
+  <si>
+    <t>Scania 16</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Lv.9</t>
+  </si>
+  <si>
+    <t>2경 6893조 1820억 1379만</t>
+  </si>
+  <si>
+    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
+  </si>
+  <si>
+    <t>살뽀시</t>
+  </si>
+  <si>
+    <t>item</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=item</t>
+  </si>
+  <si>
+    <t>Scania 34</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>2경 6501조 1108억 3368만</t>
+  </si>
+  <si>
+    <t>We Go Together !</t>
+  </si>
+  <si>
+    <t>템이</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>스타냥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>1경 720조 3865억 2152만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>진자이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>4143조 7347억 1708만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>돈스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>3322조 3154억 8065만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>1407조 6499억 5640만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>말레이히어로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>1394조 1932억 8825만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>빌런투킬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>1120조 9927억 5165만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>스타뎀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%8E%80</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>475조 5893억 7767만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>여사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>400조 1307억 6796만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>단풍노비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>296조 8725억 4131만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>228조 665억 3930만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>부엉이없다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>203조 538억 3069만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>174조 1025억 3447만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>프리프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>150조 7025억 6128만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>135조 4527억 1903만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>쾌감</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
+  </si>
+  <si>
+    <t>103조 3764억 2883만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>87조 8655억 3844만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>83조 5339억 4959만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>소소채2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>80조 1967억 9470만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>POSCO</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
+  </si>
+  <si>
+    <t>65조 7697억 3285만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>46조 6512억 8057만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>두근푸근연근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>45조 9368억 846만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>포뇨야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
+  </si>
+  <si>
+    <t>45조 2469억 9216만</t>
+  </si>
+  <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>44조 535억 2685만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>김치싸대기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>38조 1459억 7981만</t>
+  </si>
+  <si>
+    <t>악의꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>36조 6837억 5297만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>33조 3718억 3936만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>32조 3589억 4341만</t>
   </si>
   <si>
     <t>28</t>
   </si>
   <si>
-    <t>1위</t>
-  </si>
-  <si>
-    <t>2경 4688조 3717억 8454만</t>
-  </si>
-  <si>
-    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
-  </si>
-  <si>
-    <t>혜영</t>
-  </si>
-  <si>
-    <t>LUXURY</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
-  </si>
-  <si>
-    <t>Scania 16</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>Lv.9</t>
-  </si>
-  <si>
-    <t>2경 5624조 8913억 5301만</t>
-  </si>
-  <si>
-    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
-  </si>
-  <si>
-    <t>살뽀시</t>
-  </si>
-  <si>
-    <t>item</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=item</t>
-  </si>
-  <si>
-    <t>Scania 34</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>2경 6501조 1108억 3368만</t>
-  </si>
-  <si>
-    <t>We Go Together !</t>
-  </si>
-  <si>
-    <t>템이</t>
-  </si>
-  <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
+    <t>울힝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
+  </si>
+  <si>
+    <t>32조 3033억 5769만</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>29조 5789억 1997만</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>몽호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
+  </si>
+  <si>
+    <t>25조 3889억 7104만</t>
   </si>
   <si>
     <t>별뽕</t>
@@ -236,19 +647,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%BD%95</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
     <t>111</t>
   </si>
   <si>
-    <t>6702조 2457억 8696만</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>6712조 4731억 9272만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EA%B3%B0%EB%9D%A0</t>
+  </si>
+  <si>
+    <t>2955조 3191억 4144만</t>
   </si>
   <si>
     <t>도얍스</t>
@@ -257,43 +665,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%96%8D%EC%8A%A4</t>
   </si>
   <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>2695조 8599억 2831만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>원빉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EB%B9%89</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>2103조 9436억 5062만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EA%B3%B0%EB%9D%A0</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>2038조 3208억 5895만</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t>2904조 4073억 4102만</t>
   </si>
   <si>
     <t>꿀까배기</t>
@@ -302,16 +674,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EA%B9%8C%EB%B0%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>1510조 7114억 1106만</t>
-  </si>
-  <si>
-    <t>6</t>
+    <t>1640조 9351억 8517만</t>
   </si>
   <si>
     <t>KR#18TIDK8BQ6</t>
@@ -320,13 +683,7 @@
     <t>https://mgf.gg/contents/character.php?n=KR%2318TIDK8BQ6</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>1213조 186억 9436만</t>
-  </si>
-  <si>
-    <t>7</t>
+    <t>1213조 1372억 2746만</t>
   </si>
   <si>
     <t>팝중이</t>
@@ -335,16 +692,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%9D%EC%A4%91%EC%9D%B4</t>
   </si>
   <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>624조 5307억 1559만</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>902조 4590억 2561만</t>
   </si>
   <si>
     <t>BJ규리</t>
@@ -353,16 +701,16 @@
     <t>https://mgf.gg/contents/character.php?n=BJ%EA%B7%9C%EB%A6%AC</t>
   </si>
   <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
     <t>529조 2704억 5535만</t>
   </si>
   <si>
-    <t>9</t>
+    <t>웅스턴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%8A%A4%ED%84%B4</t>
+  </si>
+  <si>
+    <t>505조 9558억 3517만</t>
   </si>
   <si>
     <t>삭제합니다</t>
@@ -371,25 +719,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AD%EC%A0%9C%ED%95%A9%EB%8B%88%EB%8B%A4</t>
   </si>
   <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>471조 6952억 8316만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>웅스턴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%8A%A4%ED%84%B4</t>
-  </si>
-  <si>
-    <t>469조 3660억 7368만</t>
-  </si>
-  <si>
-    <t>11</t>
+    <t>490조 7257억 2782만</t>
   </si>
   <si>
     <t>적환</t>
@@ -401,7 +731,13 @@
     <t>462조 8085억 8080만</t>
   </si>
   <si>
-    <t>12</t>
+    <t>처돌2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%98%EB%8F%8C2</t>
+  </si>
+  <si>
+    <t>377조 1897억 751만</t>
   </si>
   <si>
     <t>슈기리</t>
@@ -410,25 +746,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EA%B8%B0%EB%A6%AC</t>
   </si>
   <si>
-    <t>265조 6426억 7458만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>처돌2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%98%EB%8F%8C2</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>197조 5784억 1392만</t>
-  </si>
-  <si>
-    <t>14</t>
+    <t>271조 798억 7369만</t>
   </si>
   <si>
     <t>소풍족</t>
@@ -437,13 +755,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%ED%92%8D%EC%A1%B1</t>
   </si>
   <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>112조 8656억 767만</t>
-  </si>
-  <si>
-    <t>15</t>
+    <t>124조 5275억 4403만</t>
+  </si>
+  <si>
+    <t>안바</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%B0%94</t>
+  </si>
+  <si>
+    <t>107조 6064억 7229만</t>
   </si>
   <si>
     <t>순수띵귤</t>
@@ -455,31 +776,13 @@
     <t>106조 5179억 6719만</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>안바</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%B0%94</t>
-  </si>
-  <si>
-    <t>99조 9217억 4015만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>별뿡</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%BF%A1</t>
   </si>
   <si>
-    <t>90조 7071억 5235만</t>
-  </si>
-  <si>
-    <t>18</t>
+    <t>93조 6082억 2804만</t>
   </si>
   <si>
     <t>리세라</t>
@@ -488,10 +791,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EC%84%B8%EB%9D%BC</t>
   </si>
   <si>
-    <t>83조 3466억 2610만</t>
-  </si>
-  <si>
-    <t>19</t>
+    <t>91조 4421억 1480만</t>
+  </si>
+  <si>
+    <t>동키링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%ED%82%A4%EB%A7%81</t>
+  </si>
+  <si>
+    <t>78조 595억 9240만</t>
   </si>
   <si>
     <t>검환</t>
@@ -500,34 +809,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%80%ED%99%98</t>
   </si>
   <si>
-    <t>103</t>
-  </si>
-  <si>
     <t>73조 5894억 2690만</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>재기리</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%AC%EA%B8%B0%EB%A6%AC</t>
   </si>
   <si>
-    <t>58조 4855억 4450만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>동키링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%ED%82%A4%EB%A7%81</t>
-  </si>
-  <si>
-    <t>57조 8763억 574만</t>
+    <t>61조 3846억 759만</t>
+  </si>
+  <si>
+    <t>무열대</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%97%B4%EB%8C%80</t>
+  </si>
+  <si>
+    <t>55조 3755억 7643만</t>
   </si>
   <si>
     <t>기데</t>
@@ -536,13 +836,22 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%8D%B0</t>
   </si>
   <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>51조 4112억 4948만</t>
-  </si>
-  <si>
-    <t>23</t>
+    <t>52조 2183억 2775만</t>
+  </si>
+  <si>
+    <t>공격느림</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EA%B2%A9%EB%8A%90%EB%A6%BC</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>52조 1885억 3384만</t>
   </si>
   <si>
     <t>혀로우기</t>
@@ -554,18 +863,6 @@
     <t>50조 5361억 9525만</t>
   </si>
   <si>
-    <t>무열대</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%97%B4%EB%8C%80</t>
-  </si>
-  <si>
-    <t>49조 9126억 1957만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
     <t>쿧임</t>
   </si>
   <si>
@@ -575,7 +872,13 @@
     <t>39조 7418억 6382만</t>
   </si>
   <si>
-    <t>26</t>
+    <t>별빛낭만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%B9%9B%EB%82%AD%EB%A7%8C</t>
+  </si>
+  <si>
+    <t>38조 8119억 8644만</t>
   </si>
   <si>
     <t>허이다</t>
@@ -587,36 +890,6 @@
     <t>36조 6805억 691만</t>
   </si>
   <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>별빛낭만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%B9%9B%EB%82%AD%EB%A7%8C</t>
-  </si>
-  <si>
-    <t>35조 52억 1617만</t>
-  </si>
-  <si>
-    <t>공격느림</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EA%B2%A9%EB%8A%90%EB%A6%BC</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>32조 2415억 8501만</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
     <t>별득</t>
   </si>
   <si>
@@ -626,16 +899,13 @@
     <t>12조 6105억 2359만</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>전직미녀</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%A7%81%EB%AF%B8%EB%85%80</t>
   </si>
   <si>
-    <t>9조 5278억 9241만</t>
+    <t>11조 5332억 3396만</t>
   </si>
   <si>
     <t>얼래링</t>
@@ -644,7 +914,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EB%9E%98%EB%A7%81</t>
   </si>
   <si>
-    <t>1경 1276조 5679억 8351만</t>
+    <t>1경 1472조 8006억 6664만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%BC%B4%EB%9E%98%EB%A7%81</t>
@@ -668,7 +938,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EC%88%98%EB%A7%81</t>
   </si>
   <si>
-    <t>693조 6092억 5762만</t>
+    <t>793조 8911억 467만</t>
   </si>
   <si>
     <t>별빛링</t>
@@ -677,9 +947,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%B9%9B%EB%A7%81</t>
   </si>
   <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
     <t>654조 4196억 2809만</t>
   </si>
   <si>
@@ -692,6 +959,15 @@
     <t>513조 5371억 6968만</t>
   </si>
   <si>
+    <t>키플링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%ED%94%8C%EB%A7%81</t>
+  </si>
+  <si>
+    <t>453조 6164억 7346만</t>
+  </si>
+  <si>
     <t>아가링</t>
   </si>
   <si>
@@ -716,7 +992,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%A1%EB%B3%B4%EB%A7%81</t>
   </si>
   <si>
-    <t>352조 267억 8567만</t>
+    <t>374조 4625억 7493만</t>
   </si>
   <si>
     <t>네버링</t>
@@ -728,13 +1004,31 @@
     <t>338조 645억 327만</t>
   </si>
   <si>
-    <t>키플링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%ED%94%8C%EB%A7%81</t>
-  </si>
-  <si>
-    <t>330조 422억 7499만</t>
+    <t>멍때링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%8D%EB%95%8C%EB%A7%81</t>
+  </si>
+  <si>
+    <t>305조 6567억 7447만</t>
+  </si>
+  <si>
+    <t>콕끼링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BD%95%EB%81%BC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>242조 7963억 3890만</t>
+  </si>
+  <si>
+    <t>시러링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%9F%AC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>239조 6714억 5917만</t>
   </si>
   <si>
     <t>도트링</t>
@@ -746,31 +1040,13 @@
     <t>236조 5992억 9221만</t>
   </si>
   <si>
-    <t>콕끼링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BD%95%EB%81%BC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>226조 6532억 5236만</t>
-  </si>
-  <si>
-    <t>시러링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%9F%AC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>221조 7270억 9824만</t>
-  </si>
-  <si>
-    <t>멍때링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%8D%EB%95%8C%EB%A7%81</t>
-  </si>
-  <si>
-    <t>203조 8617억 741만</t>
+    <t>모꼬링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EA%BC%AC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>202조 5389억 64만</t>
   </si>
   <si>
     <t>무뇌링</t>
@@ -788,16 +1064,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%93%9C%EB%A6%B4%EB%A7%81</t>
   </si>
   <si>
-    <t>154조 7020억 2136만</t>
-  </si>
-  <si>
-    <t>모꼬링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EA%BC%AC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>137조 3840억 2432만</t>
+    <t>173조 1953억 1787만</t>
   </si>
   <si>
     <t>엠오링</t>
@@ -806,7 +1073,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%A0%EC%98%A4%EB%A7%81</t>
   </si>
   <si>
-    <t>111조 3082억 6404만</t>
+    <t>142조 8227억 8570만</t>
+  </si>
+  <si>
+    <t>푸르링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%A5%B4%EB%A7%81</t>
+  </si>
+  <si>
+    <t>99조 6338억 6153만</t>
+  </si>
+  <si>
+    <t>해오링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%98%A4%EB%A7%81</t>
+  </si>
+  <si>
+    <t>96조 9598억 7223만</t>
   </si>
   <si>
     <t>모델링</t>
@@ -818,24 +1103,6 @@
     <t>91조 6914억 7173만</t>
   </si>
   <si>
-    <t>해오링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%98%A4%EB%A7%81</t>
-  </si>
-  <si>
-    <t>90조 9706억 1195만</t>
-  </si>
-  <si>
-    <t>푸르링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%A5%B4%EB%A7%81</t>
-  </si>
-  <si>
-    <t>86조 2022억 4374만</t>
-  </si>
-  <si>
     <t>커포링</t>
   </si>
   <si>
@@ -851,7 +1118,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EA%B0%80%EB%A7%81</t>
   </si>
   <si>
-    <t>63조 5122억 9773만</t>
+    <t>66조 5279억 9387만</t>
   </si>
   <si>
     <t>대가링</t>
@@ -869,7 +1136,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%A0%EC%83%98%EB%A7%81</t>
   </si>
   <si>
-    <t>55조 3123억 1004만</t>
+    <t>57조 8645억 832만</t>
   </si>
   <si>
     <t>깨구링</t>
@@ -887,7 +1154,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%AC%BC%EB%A7%81</t>
   </si>
   <si>
-    <t>48조 217억 1160만</t>
+    <t>50조 1653억 6801만</t>
   </si>
   <si>
     <t>펭구링</t>
@@ -905,268 +1172,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%81%EA%B0%80%EB%A7%81%EA%B0%80%EB%A7%81</t>
   </si>
   <si>
-    <t>29조 4384억 8796만</t>
-  </si>
-  <si>
-    <t>스타냥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>1경 720조 3865억 2152만</t>
-  </si>
-  <si>
-    <t>돈스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>3322조 3154억 8065만</t>
-  </si>
-  <si>
-    <t>진자이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>2291조 1697억 43만</t>
-  </si>
-  <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>1407조 6499억 5640만</t>
-  </si>
-  <si>
-    <t>말레이히어로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>1394조 1932억 8825만</t>
-  </si>
-  <si>
-    <t>빌런투킬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
-  </si>
-  <si>
-    <t>1120조 9927억 5165만</t>
-  </si>
-  <si>
-    <t>스타뎀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%8E%80</t>
-  </si>
-  <si>
-    <t>475조 5893억 7767만</t>
-  </si>
-  <si>
-    <t>여사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
-  </si>
-  <si>
-    <t>400조 1307억 6796만</t>
-  </si>
-  <si>
-    <t>단풍노비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
-  </si>
-  <si>
-    <t>278조 3832억 696만</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>174조 1025억 3447만</t>
-  </si>
-  <si>
-    <t>부엉이없다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>162조 5886억 9598만</t>
-  </si>
-  <si>
-    <t>프리프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>150조 7025억 6128만</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>135조 4527억 1903만</t>
-  </si>
-  <si>
-    <t>쾌감</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
-  </si>
-  <si>
-    <t>101조 3300억 3895만</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>84조 4353억 6632만</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>83조 4958억 6972만</t>
-  </si>
-  <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>79조 606억 7880만</t>
-  </si>
-  <si>
-    <t>POSCO</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
-  </si>
-  <si>
-    <t>65조 7697억 3285만</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>46조 4973억 6304만</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>43조 9302억 789만</t>
-  </si>
-  <si>
-    <t>포뇨야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
-  </si>
-  <si>
-    <t>40조 6065억 2233만</t>
-  </si>
-  <si>
-    <t>두근푸근연근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>40조 3193억 9244만</t>
-  </si>
-  <si>
-    <t>김치싸대기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>38조 1459억 7981만</t>
-  </si>
-  <si>
-    <t>악의꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
-  </si>
-  <si>
-    <t>36조 6837억 5297만</t>
-  </si>
-  <si>
-    <t>대방어조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>33조 1885억 3176만</t>
-  </si>
-  <si>
-    <t>울힝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
-  </si>
-  <si>
-    <t>32조 2430억 2723만</t>
-  </si>
-  <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>31조 4662억 190만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
-  </si>
-  <si>
-    <t>29조 5789억 1997만</t>
-  </si>
-  <si>
-    <t>몽호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
-  </si>
-  <si>
-    <t>24조 3071억 135만</t>
+    <t>32조 9466억 3052만</t>
   </si>
   <si>
     <t>가숭혁</t>
@@ -1178,7 +1184,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>1경 6991조 8873억 8940만</t>
+    <t>1경 8086조 9055억 5923만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%82%B4%EB%BD%80%EC%8B%9C</t>
@@ -1193,7 +1199,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%83%B8%EC%B9%98</t>
   </si>
   <si>
-    <t>1676조 5414억 1837만</t>
+    <t>1726조 1961억 1645만</t>
   </si>
   <si>
     <t>달싹</t>
@@ -1214,6 +1220,15 @@
     <t>516조 9172억 9058만</t>
   </si>
   <si>
+    <t>26길초</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
+  </si>
+  <si>
+    <t>482조 679억 891만</t>
+  </si>
+  <si>
     <t>뇌쉬</t>
   </si>
   <si>
@@ -1223,22 +1238,13 @@
     <t>473조 935억 9830만</t>
   </si>
   <si>
-    <t>26길초</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
-  </si>
-  <si>
-    <t>457조 7446억 1398만</t>
-  </si>
-  <si>
     <t>서예슬</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
   </si>
   <si>
-    <t>381조 6871억 2231만</t>
+    <t>386조 1275억 3929만</t>
   </si>
   <si>
     <t>덜박</t>
@@ -1292,7 +1298,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
   </si>
   <si>
-    <t>88조 5232억 4641만</t>
+    <t>90조 4165억 1503만</t>
   </si>
   <si>
     <t>하탸치</t>
@@ -1310,7 +1316,7 @@
     <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
   </si>
   <si>
-    <t>43조 5788억 651만</t>
+    <t>44조 825억 4027만</t>
   </si>
   <si>
     <t>쑤삔</t>
@@ -1322,7 +1328,7 @@
     <t>나이트로드</t>
   </si>
   <si>
-    <t>37조 4179억 3701만</t>
+    <t>38조 6185억 6952만</t>
   </si>
   <si>
     <t>류테</t>
@@ -1361,6 +1367,15 @@
     <t>21조 3943억 1549만</t>
   </si>
   <si>
+    <t>메키무라딘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%AC%B4%EB%9D%BC%EB%94%98</t>
+  </si>
+  <si>
+    <t>20조 8757억 2658만</t>
+  </si>
+  <si>
     <t>뻐늬</t>
   </si>
   <si>
@@ -1370,15 +1385,6 @@
     <t>19조 728억 950만</t>
   </si>
   <si>
-    <t>메키무라딘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%AC%B4%EB%9D%BC%EB%94%98</t>
-  </si>
-  <si>
-    <t>18조 7407억 6984만</t>
-  </si>
-  <si>
     <t>26조선</t>
   </si>
   <si>
@@ -1412,7 +1418,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
   </si>
   <si>
-    <t>13조 7002억 6087만</t>
+    <t>13조 7339억 1482만</t>
   </si>
   <si>
     <t>예라미</t>
@@ -1421,7 +1427,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
   </si>
   <si>
-    <t>8조 6489억 2060만</t>
+    <t>8조 8509억 6783만</t>
   </si>
   <si>
     <t>귬스파파</t>
@@ -1439,7 +1445,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%98%81%ED%9D%AC%EB%A9%88%EB%AD%84%EB%AF%B8</t>
   </si>
   <si>
-    <t>5조 9661억 9494만</t>
+    <t>5조 9710억 6492만</t>
   </si>
   <si>
     <t>코로드</t>
@@ -1466,7 +1472,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A8%EB%85%80</t>
   </si>
   <si>
-    <t>4173조 6151억 3152만</t>
+    <t>4241조 5410억 8862만</t>
   </si>
   <si>
     <t>빌린</t>
@@ -1475,7 +1481,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%A6%B0</t>
   </si>
   <si>
-    <t>241조 1262억 6903만</t>
+    <t>245조 866억 4946만</t>
   </si>
   <si>
     <t>Bit숍</t>
@@ -1484,7 +1490,7 @@
     <t>https://mgf.gg/contents/character.php?n=Bit%EC%88%8D</t>
   </si>
   <si>
-    <t>217조 4514억 1006만</t>
+    <t>222조 947억 9369만</t>
   </si>
   <si>
     <t>김해님</t>
@@ -1493,7 +1499,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%95%B4%EB%8B%98</t>
   </si>
   <si>
-    <t>187조 7550억 4787만</t>
+    <t>189조 3135억 3734만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%85%9C%EC%9D%B4</t>
@@ -1508,7 +1514,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%ED%83%80%EC%84%A0%EB%AC%BC</t>
   </si>
   <si>
-    <t>90조 4873억 5756만</t>
+    <t>95조 4083억 3220만</t>
   </si>
   <si>
     <t>아마날</t>
@@ -1517,7 +1523,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A7%88%EB%82%A0</t>
   </si>
   <si>
-    <t>70조 9072억 6367만</t>
+    <t>87조 7177억 691만</t>
   </si>
   <si>
     <t>도령3</t>
@@ -1526,7 +1532,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A0%B93</t>
   </si>
   <si>
-    <t>63조 443억 7659만</t>
+    <t>65조 8166억 9332만</t>
   </si>
   <si>
     <t>조콩나무</t>
@@ -1544,7 +1550,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%9F%AC%EB%8A%94%EA%B1%B0%EC%95%84%EB%83%90</t>
   </si>
   <si>
-    <t>36조 4798억 6021만</t>
+    <t>42조 7660억 9022만</t>
   </si>
   <si>
     <t>숮2</t>
@@ -1553,7 +1559,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%AE2</t>
   </si>
   <si>
-    <t>32조 6148억 5962만</t>
+    <t>32조 8627억 5390만</t>
   </si>
   <si>
     <t>백엄경</t>
@@ -1562,82 +1568,82 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%EC%97%84%EA%B2%BD</t>
   </si>
   <si>
+    <t>31조 4200억 5326만</t>
+  </si>
+  <si>
+    <t>키움맨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%9B%80%EB%A7%A8</t>
+  </si>
+  <si>
+    <t>24조 258억 2609만</t>
+  </si>
+  <si>
+    <t>최소뎀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%86%8C%EB%8E%80</t>
+  </si>
+  <si>
+    <t>22조 2347억 2935만</t>
+  </si>
+  <si>
+    <t>시프님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%ED%94%84%EB%8B%98</t>
+  </si>
+  <si>
+    <t>22조 492억 4164만</t>
+  </si>
+  <si>
+    <t>한유화</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EC%9C%A0%ED%99%94</t>
+  </si>
+  <si>
+    <t>19조 1070억 1544만</t>
+  </si>
+  <si>
+    <t>95도도</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=95%EB%8F%84%EB%8F%84</t>
+  </si>
+  <si>
+    <t>18조 6046억 873만</t>
+  </si>
+  <si>
+    <t>천칸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B9%B8</t>
+  </si>
+  <si>
+    <t>18조 3643억 1370만</t>
+  </si>
+  <si>
+    <t>혈마신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%88%EB%A7%88%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>9조 5421억 6790만</t>
+  </si>
+  <si>
+    <t>숑당</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%91%EB%8B%B9</t>
+  </si>
+  <si>
     <t>100</t>
   </si>
   <si>
-    <t>30조 4285억 9777만</t>
-  </si>
-  <si>
-    <t>키움맨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%9B%80%EB%A7%A8</t>
-  </si>
-  <si>
-    <t>24조 258억 2609만</t>
-  </si>
-  <si>
-    <t>시프님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%ED%94%84%EB%8B%98</t>
-  </si>
-  <si>
-    <t>21조 8490억 9889만</t>
-  </si>
-  <si>
-    <t>한유화</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EC%9C%A0%ED%99%94</t>
-  </si>
-  <si>
-    <t>18조 6435억 9613만</t>
-  </si>
-  <si>
-    <t>최소뎀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%86%8C%EB%8E%80</t>
-  </si>
-  <si>
-    <t>18조 5838억 1558만</t>
-  </si>
-  <si>
-    <t>천칸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B9%B8</t>
-  </si>
-  <si>
-    <t>18조 3643억 1370만</t>
-  </si>
-  <si>
-    <t>95도도</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=95%EB%8F%84%EB%8F%84</t>
-  </si>
-  <si>
-    <t>16조 5765억 2997만</t>
-  </si>
-  <si>
-    <t>혈마신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%88%EB%A7%88%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>9조 5421억 6790만</t>
-  </si>
-  <si>
-    <t>숑당</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%91%EB%8B%B9</t>
-  </si>
-  <si>
-    <t>9조 1500억 1948만</t>
+    <t>9조 1928억 2161만</t>
   </si>
   <si>
     <t>리얼크크</t>
@@ -1646,7 +1652,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EC%96%BC%ED%81%AC%ED%81%AC</t>
   </si>
   <si>
-    <t>8조 8174억 2290만</t>
+    <t>8조 9539억 7333만</t>
   </si>
   <si>
     <t>현즈</t>
@@ -1655,7 +1661,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%A6%88</t>
   </si>
   <si>
-    <t>5조 7647억 9211만</t>
+    <t>5조 8451억 4956만</t>
   </si>
   <si>
     <t>박하민린</t>
@@ -1667,7 +1673,7 @@
     <t>99</t>
   </si>
   <si>
-    <t>5조 2369억 4118만</t>
+    <t>5조 2480억 4212만</t>
   </si>
   <si>
     <t>군명</t>
@@ -1676,37 +1682,37 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EB%AA%85</t>
   </si>
   <si>
+    <t>4조 8085억 7122만</t>
+  </si>
+  <si>
+    <t>장수흙침대</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EC%88%98%ED%9D%99%EC%B9%A8%EB%8C%80</t>
+  </si>
+  <si>
+    <t>4조 1413억 3850만</t>
+  </si>
+  <si>
+    <t>김똔똔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%98%94%EB%98%94</t>
+  </si>
+  <si>
+    <t>3조 9222억 2332만</t>
+  </si>
+  <si>
+    <t>니코짱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EC%BD%94%EC%A7%B1</t>
+  </si>
+  <si>
     <t>98</t>
   </si>
   <si>
-    <t>4조 1286억 2116만</t>
-  </si>
-  <si>
-    <t>김똔똔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%98%94%EB%98%94</t>
-  </si>
-  <si>
-    <t>3조 8769억 8616만</t>
-  </si>
-  <si>
-    <t>장수흙침대</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EC%88%98%ED%9D%99%EC%B9%A8%EB%8C%80</t>
-  </si>
-  <si>
-    <t>3조 1329억 8847만</t>
-  </si>
-  <si>
-    <t>니코짱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EC%BD%94%EC%A7%B1</t>
-  </si>
-  <si>
-    <t>2조 6604억 3946만</t>
+    <t>2조 7950억 2744만</t>
   </si>
   <si>
     <t>뉴맹우</t>
@@ -1718,7 +1724,7 @@
     <t>97</t>
   </si>
   <si>
-    <t>1조 1804억 9938만</t>
+    <t>1조 2374억 3820만</t>
   </si>
 </sst>
 </file>
@@ -2217,45 +2223,45 @@
         <v>34</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>24</v>
@@ -2263,40 +2269,40 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>24</v>
@@ -2304,43 +2310,43 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -2363,10 +2369,11 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="4" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2375,28 +2382,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -2407,28 +2414,28 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -2439,28 +2446,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2471,28 +2478,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2503,28 +2510,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2535,28 +2542,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="I6" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2567,28 +2574,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2599,28 +2606,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2631,22 +2638,22 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>109</v>
@@ -2675,13 +2682,13 @@
         <v>113</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>115</v>
@@ -2707,16 +2714,16 @@
         <v>118</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2727,28 +2734,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2759,28 +2766,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2791,25 +2798,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>132</v>
@@ -2835,13 +2842,13 @@
         <v>135</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>137</v>
@@ -2867,13 +2874,13 @@
         <v>140</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>141</v>
@@ -2899,16 +2906,16 @@
         <v>144</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2919,28 +2926,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2951,28 +2958,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2983,28 +2990,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>157</v>
+        <v>119</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3015,28 +3022,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>157</v>
+        <v>119</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3047,28 +3054,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3079,28 +3086,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>54</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3111,7 +3118,7 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>171</v>
+        <v>47</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>172</v>
@@ -3123,13 +3130,13 @@
         <v>173</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>174</v>
@@ -3143,28 +3150,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>46</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3175,7 +3182,7 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>55</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>179</v>
@@ -3187,16 +3194,16 @@
         <v>180</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3207,28 +3214,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3239,28 +3246,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>114</v>
+        <v>190</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3271,28 +3278,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>38</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>192</v>
+        <v>77</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>193</v>
+        <v>154</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3303,28 +3310,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>196</v>
+        <v>23</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>196</v>
+        <v>23</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>197</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>69</v>
+        <v>198</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3335,28 +3342,28 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>193</v>
+        <v>154</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -3402,6 +3409,1017 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J30"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -3420,28 +4438,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3449,31 +4467,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>203</v>
+        <v>293</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>203</v>
+        <v>293</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>204</v>
+        <v>294</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>205</v>
+        <v>295</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -3481,31 +4499,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>206</v>
+        <v>296</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>85</v>
+        <v>198</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>207</v>
+        <v>297</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -3513,31 +4531,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>208</v>
+        <v>298</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>208</v>
+        <v>298</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>209</v>
+        <v>299</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>109</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>210</v>
+        <v>300</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3545,31 +4563,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>211</v>
+        <v>301</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>211</v>
+        <v>301</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>212</v>
+        <v>302</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>70</v>
+        <v>136</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>213</v>
+        <v>303</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3577,31 +4595,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>214</v>
+        <v>304</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>214</v>
+        <v>304</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>215</v>
+        <v>305</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>217</v>
+        <v>306</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3609,31 +4627,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>218</v>
+        <v>307</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>218</v>
+        <v>307</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>219</v>
+        <v>308</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>109</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>220</v>
+        <v>309</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -3641,31 +4659,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>221</v>
+        <v>310</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>221</v>
+        <v>310</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>222</v>
+        <v>311</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>223</v>
+        <v>312</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -3673,31 +4691,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>224</v>
+        <v>313</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>224</v>
+        <v>313</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>225</v>
+        <v>314</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="I9" s="2" t="s">
-        <v>226</v>
+        <v>315</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3705,31 +4723,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>227</v>
+        <v>316</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>227</v>
+        <v>316</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>228</v>
+        <v>317</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="I10" s="2" t="s">
-        <v>229</v>
+        <v>318</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3737,31 +4755,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>230</v>
+        <v>319</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>230</v>
+        <v>319</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>231</v>
+        <v>320</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>232</v>
+        <v>321</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3769,31 +4787,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>233</v>
+        <v>322</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>233</v>
+        <v>322</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>234</v>
+        <v>323</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>235</v>
+        <v>324</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3801,31 +4819,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>236</v>
+        <v>325</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>236</v>
+        <v>325</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>237</v>
+        <v>326</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>216</v>
+        <v>88</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>238</v>
+        <v>327</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3833,31 +4851,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>239</v>
+        <v>328</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>239</v>
+        <v>328</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>240</v>
+        <v>329</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>241</v>
+        <v>330</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -3865,31 +4883,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>242</v>
+        <v>331</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>242</v>
+        <v>331</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>243</v>
+        <v>332</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>244</v>
+        <v>333</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3897,31 +4915,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>245</v>
+        <v>334</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>245</v>
+        <v>334</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>246</v>
+        <v>335</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>102</v>
+        <v>190</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>247</v>
+        <v>336</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3929,31 +4947,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>248</v>
+        <v>337</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>248</v>
+        <v>337</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>249</v>
+        <v>338</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>250</v>
+        <v>339</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3961,31 +4979,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>251</v>
+        <v>340</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>251</v>
+        <v>340</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>252</v>
+        <v>341</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>253</v>
+        <v>342</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3993,31 +5011,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>254</v>
+        <v>343</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>254</v>
+        <v>343</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>255</v>
+        <v>344</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>256</v>
+        <v>345</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4025,31 +5043,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>257</v>
+        <v>346</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>257</v>
+        <v>346</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>258</v>
+        <v>347</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>259</v>
+        <v>348</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4057,31 +5075,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>260</v>
+        <v>349</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>260</v>
+        <v>349</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>261</v>
+        <v>350</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>70</v>
+        <v>272</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>262</v>
+        <v>351</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4089,31 +5107,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>263</v>
+        <v>352</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>263</v>
+        <v>352</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>264</v>
+        <v>353</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>265</v>
+        <v>354</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4121,31 +5139,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>54</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>266</v>
+        <v>355</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>266</v>
+        <v>355</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>267</v>
+        <v>356</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>192</v>
+        <v>136</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>268</v>
+        <v>357</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -4153,31 +5171,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>171</v>
+        <v>47</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>269</v>
+        <v>358</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>269</v>
+        <v>358</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>270</v>
+        <v>359</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>70</v>
+        <v>136</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>271</v>
+        <v>360</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4185,31 +5203,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>46</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>272</v>
+        <v>361</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>272</v>
+        <v>361</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>273</v>
+        <v>362</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>274</v>
+        <v>363</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -4217,31 +5235,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>55</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>275</v>
+        <v>364</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>275</v>
+        <v>364</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>276</v>
+        <v>365</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>277</v>
+        <v>366</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4249,31 +5267,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>278</v>
+        <v>367</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>278</v>
+        <v>367</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>279</v>
+        <v>368</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>280</v>
+        <v>369</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -4281,31 +5299,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>281</v>
+        <v>370</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>281</v>
+        <v>370</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>282</v>
+        <v>371</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>283</v>
+        <v>372</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -4313,31 +5331,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>38</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>284</v>
+        <v>373</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>284</v>
+        <v>373</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>285</v>
+        <v>374</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>70</v>
+        <v>136</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>286</v>
+        <v>375</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -4345,31 +5363,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>287</v>
+        <v>376</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>287</v>
+        <v>376</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>288</v>
+        <v>377</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>289</v>
+        <v>378</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -4377,31 +5395,31 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>290</v>
+        <v>379</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>290</v>
+        <v>379</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>291</v>
+        <v>380</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>292</v>
+        <v>381</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -4445,1018 +5463,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J30"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
-    <hyperlink ref="E20" r:id="rId19"/>
-    <hyperlink ref="E21" r:id="rId20"/>
-    <hyperlink ref="E22" r:id="rId21"/>
-    <hyperlink ref="E23" r:id="rId22"/>
-    <hyperlink ref="E24" r:id="rId23"/>
-    <hyperlink ref="E25" r:id="rId24"/>
-    <hyperlink ref="E26" r:id="rId25"/>
-    <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
@@ -5477,28 +5483,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -5506,31 +5512,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>70</v>
+        <v>136</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5538,31 +5544,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>85</v>
+        <v>198</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>71</v>
+        <v>206</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5570,31 +5576,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5602,31 +5608,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5634,31 +5640,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5666,31 +5672,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>109</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5698,31 +5704,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>109</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5730,31 +5736,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>109</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5762,31 +5768,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>109</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5794,31 +5800,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="I11" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5826,31 +5832,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5858,31 +5864,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5890,31 +5896,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5922,31 +5928,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5954,31 +5960,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5986,31 +5992,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6018,31 +6024,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6050,31 +6056,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6082,31 +6088,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6114,31 +6120,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>192</v>
+        <v>272</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6146,31 +6152,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6178,31 +6184,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>54</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>157</v>
+        <v>273</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6210,31 +6216,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>171</v>
+        <v>47</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>193</v>
+        <v>154</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6242,31 +6248,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>46</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6274,31 +6280,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>55</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>193</v>
+        <v>273</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6306,31 +6312,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6338,31 +6344,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6370,31 +6376,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>38</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>193</v>
+        <v>273</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6402,31 +6408,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>193</v>
+        <v>273</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6434,31 +6440,31 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>70</v>
+        <v>136</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>193</v>
+        <v>273</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6522,28 +6528,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -6551,962 +6557,962 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>97</v>
+        <v>206</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>109</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>85</v>
+        <v>198</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>70</v>
+        <v>136</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>70</v>
+        <v>136</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>511</v>
+        <v>273</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>169</v>
+        <v>273</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>193</v>
+        <v>273</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>91</v>
+        <v>136</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>169</v>
+        <v>273</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>193</v>
+        <v>273</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>54</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>511</v>
+        <v>537</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>171</v>
+        <v>47</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>511</v>
-      </c>
       <c r="I24" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>46</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>511</v>
+        <v>537</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>55</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>549</v>
-      </c>
       <c r="I27" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>38</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>70</v>
+        <v>136</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -9,8 +9,8 @@
   <sheets>
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="셀린느" sheetId="2" r:id="rId2"/>
-    <sheet name="별곰부대" sheetId="3" r:id="rId3"/>
-    <sheet name="블링블리" sheetId="4" r:id="rId4"/>
+    <sheet name="블링블리" sheetId="3" r:id="rId3"/>
+    <sheet name="별곰부대" sheetId="4" r:id="rId4"/>
     <sheet name="LUXURY" sheetId="5" r:id="rId5"/>
     <sheet name="item" sheetId="6" r:id="rId6"/>
   </sheets>
@@ -18,8 +18,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">item!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">LUXURY!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">별곰부대!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">블링블리!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">별곰부대!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">블링블리!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">셀린느!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="563">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,7 +80,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>31</t>
+    <t>30</t>
   </si>
   <si>
     <t>1위</t>
@@ -92,7 +92,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>2경 4997조 8297억 61만</t>
+    <t>2경 5003조 7064억 412만</t>
   </si>
   <si>
     <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
@@ -104,6 +104,30 @@
     <t>2026.04.19</t>
   </si>
   <si>
+    <t>블링블리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B8%94%EB%A7%81%EB%B8%94%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>Scania 27</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>3위</t>
+  </si>
+  <si>
+    <t>2경 1789조 1060억 4000만</t>
+  </si>
+  <si>
+    <t>토벌 3위 1군 투력 50조 이상 / 토벌 13위 2군 블리블링 10조 이상 / 3군 블링불링 3000억이상 닉변 필수 공헌도 미달 길본 미업글 1일 미접 추방</t>
+  </si>
+  <si>
+    <t>꼴래링</t>
+  </si>
+  <si>
     <t>별곰부대</t>
   </si>
   <si>
@@ -113,7 +137,7 @@
     <t>Scania 30</t>
   </si>
   <si>
-    <t>38</t>
+    <t>37</t>
   </si>
   <si>
     <t>2위</t>
@@ -131,541 +155,790 @@
     <t>가입문의 : 리세라, 별뿡</t>
   </si>
   <si>
+    <t>별뿡</t>
+  </si>
+  <si>
+    <t>2026.04.17</t>
+  </si>
+  <si>
+    <t>LUXURY</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
+  </si>
+  <si>
+    <t>Scania 16</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>Lv.9</t>
+  </si>
+  <si>
+    <t>2경 7507조 6989억 2112만</t>
+  </si>
+  <si>
+    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
+  </si>
+  <si>
+    <t>살뽀시</t>
+  </si>
+  <si>
+    <t>2026.04.20</t>
+  </si>
+  <si>
+    <t>item</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=item</t>
+  </si>
+  <si>
+    <t>Scania 34</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>2경 6501조 1108억 3368만</t>
+  </si>
+  <si>
+    <t>We Go Together !</t>
+  </si>
+  <si>
+    <t>템이</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>스타냥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>1경 720조 3865억 2152만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>진자이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>4143조 7347억 1708만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>돈스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>3322조 3154억 8065만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>말레이히어로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>1676조 9718억 7183만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>1519조 1682억 4663만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>빌런투킬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>1120조 9927억 5165만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>스타뎀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%8E%80</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>475조 5893억 7767만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>여사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>400조 1307억 6796만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>단풍노비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>341조 312억 1190만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>228조 665억 3930만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>부엉이없다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>212조 5275억 4448만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>174조 1025억 3447만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>프리프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>150조 7025억 6128만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>143조 287억 8179만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>쾌감</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
+  </si>
+  <si>
+    <t>113조 8757억 8651만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>소소채2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>92조 589억 5971만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>88조 7167억 3645만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>88조 6379억 49만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>POSCO</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
+  </si>
+  <si>
+    <t>65조 7697억 3285만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>51조 3869억 2011만</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>46조 7938억 7081만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>포뇨야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
+  </si>
+  <si>
+    <t>46조 2787억 8294만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>두근푸근연근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>45조 9368억 846만</t>
+  </si>
+  <si>
+    <t>울힝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
+  </si>
+  <si>
+    <t>39조 1111억 1972만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>김치싸대기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>38조 1459억 7981만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>악의꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>36조 6837억 5297만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>36조 474억 2125만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>34조 8711억 1818만</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>32조 5239억 3292만</t>
+  </si>
+  <si>
+    <t>몽호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
+  </si>
+  <si>
+    <t>25조 3889억 7104만</t>
+  </si>
+  <si>
+    <t>얼래링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EB%9E%98%EB%A7%81</t>
+  </si>
+  <si>
+    <t>1경 1472조 8006억 6664만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BC%B4%EB%9E%98%EB%A7%81</t>
+  </si>
+  <si>
+    <t>2840조 3802억 6526만</t>
+  </si>
+  <si>
+    <t>미오링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%98%A4%EB%A7%81</t>
+  </si>
+  <si>
+    <t>1497조 7025억 2757만</t>
+  </si>
+  <si>
+    <t>독수링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EC%88%98%EB%A7%81</t>
+  </si>
+  <si>
+    <t>974조 1557억 8886만</t>
+  </si>
+  <si>
+    <t>별빛링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%B9%9B%EB%A7%81</t>
+  </si>
+  <si>
+    <t>654조 4196억 2809만</t>
+  </si>
+  <si>
+    <t>아마링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A7%88%EB%A7%81</t>
+  </si>
+  <si>
+    <t>513조 5371억 6968만</t>
+  </si>
+  <si>
+    <t>키플링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%ED%94%8C%EB%A7%81</t>
+  </si>
+  <si>
+    <t>481조 7353억 2826만</t>
+  </si>
+  <si>
+    <t>아가링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EA%B0%80%EB%A7%81</t>
+  </si>
+  <si>
+    <t>439조 9232억 481만</t>
+  </si>
+  <si>
+    <t>츄르링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B8%84%EB%A5%B4%EB%A7%81</t>
+  </si>
+  <si>
+    <t>420조 9084억 9514만</t>
+  </si>
+  <si>
+    <t>송보링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%A1%EB%B3%B4%EB%A7%81</t>
+  </si>
+  <si>
+    <t>389조 1966억 9816만</t>
+  </si>
+  <si>
+    <t>네버링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EB%B2%84%EB%A7%81</t>
+  </si>
+  <si>
+    <t>346조 3459억 2495만</t>
+  </si>
+  <si>
+    <t>멍때링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%8D%EB%95%8C%EB%A7%81</t>
+  </si>
+  <si>
+    <t>305조 6567억 7447만</t>
+  </si>
+  <si>
+    <t>콕끼링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BD%95%EB%81%BC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>279조 9902억 2917만</t>
+  </si>
+  <si>
+    <t>도트링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%ED%8A%B8%EB%A7%81</t>
+  </si>
+  <si>
+    <t>248조 4101억 6785만</t>
+  </si>
+  <si>
+    <t>시러링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%9F%AC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>239조 6714억 5917만</t>
+  </si>
+  <si>
+    <t>모꼬링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EA%BC%AC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>202조 5389억 64만</t>
+  </si>
+  <si>
+    <t>무뇌링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%87%8C%EB%A7%81</t>
+  </si>
+  <si>
+    <t>183조 548억 5555만</t>
+  </si>
+  <si>
+    <t>드릴링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%93%9C%EB%A6%B4%EB%A7%81</t>
+  </si>
+  <si>
+    <t>181조 683억 1110만</t>
+  </si>
+  <si>
+    <t>엠오링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%A0%EC%98%A4%EB%A7%81</t>
+  </si>
+  <si>
+    <t>144조 5807억 9489만</t>
+  </si>
+  <si>
+    <t>푸르링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%A5%B4%EB%A7%81</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>99조 6338억 6153만</t>
+  </si>
+  <si>
+    <t>해오링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%98%A4%EB%A7%81</t>
+  </si>
+  <si>
+    <t>96조 9598억 7223만</t>
+  </si>
+  <si>
+    <t>모델링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%8D%B8%EB%A7%81</t>
+  </si>
+  <si>
+    <t>91조 6914억 7173만</t>
+  </si>
+  <si>
+    <t>커포링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%8F%AC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>76조 4530억 3398만</t>
+  </si>
+  <si>
+    <t>술샘링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%A0%EC%83%98%EB%A7%81</t>
+  </si>
+  <si>
+    <t>72조 7177억 4612만</t>
+  </si>
+  <si>
+    <t>싸가링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EA%B0%80%EB%A7%81</t>
+  </si>
+  <si>
+    <t>66조 5279억 9387만</t>
+  </si>
+  <si>
+    <t>대가링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EA%B0%80%EB%A7%81</t>
+  </si>
+  <si>
+    <t>60조 3174억 4264만</t>
+  </si>
+  <si>
+    <t>깨구링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%A8%EA%B5%AC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>52조 4315억 1042만</t>
+  </si>
+  <si>
+    <t>꼬물링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%AC%BC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>50조 1653억 6801만</t>
+  </si>
+  <si>
+    <t>펭구링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8E%AD%EA%B5%AC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>38조 5985억 7538만</t>
+  </si>
+  <si>
+    <t>링가링가링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%81%EA%B0%80%EB%A7%81%EA%B0%80%EB%A7%81</t>
+  </si>
+  <si>
+    <t>37조 7119억 3674만</t>
+  </si>
+  <si>
+    <t>별뽕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%BD%95</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>6712조 4731억 9272만</t>
+  </si>
+  <si>
+    <t>도얍스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%96%8D%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>3156조 4193억 9418만</t>
+  </si>
+  <si>
     <t>별곰띠</t>
   </si>
   <si>
-    <t>2026.04.17</t>
-  </si>
-  <si>
-    <t>블링블리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B8%94%EB%A7%81%EB%B8%94%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>Scania 27</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>3위</t>
-  </si>
-  <si>
-    <t>2경 1789조 1060억 4000만</t>
-  </si>
-  <si>
-    <t>토벌 3위 1군 투력 50조 이상 / 토벌 13위 2군 블리블링 10조 이상 / 3군 블링불링 3000억이상 닉변 필수 공헌도 미달 길본 미업글 1일 미접 추방</t>
-  </si>
-  <si>
-    <t>꼴래링</t>
-  </si>
-  <si>
-    <t>LUXURY</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
-  </si>
-  <si>
-    <t>Scania 16</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>Lv.9</t>
-  </si>
-  <si>
-    <t>2경 6893조 1820억 1379만</t>
-  </si>
-  <si>
-    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
-  </si>
-  <si>
-    <t>살뽀시</t>
-  </si>
-  <si>
-    <t>item</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=item</t>
-  </si>
-  <si>
-    <t>Scania 34</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>2경 6501조 1108억 3368만</t>
-  </si>
-  <si>
-    <t>We Go Together !</t>
-  </si>
-  <si>
-    <t>템이</t>
-  </si>
-  <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>스타냥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>1경 720조 3865억 2152만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>진자이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>4143조 7347억 1708만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>돈스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>3322조 3154억 8065만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>1407조 6499억 5640만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>말레이히어로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>1394조 1932억 8825만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>빌런투킬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>1120조 9927억 5165만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>스타뎀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%8E%80</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>475조 5893억 7767만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>여사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>400조 1307억 6796만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>단풍노비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>296조 8725억 4131만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>니달리신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>228조 665억 3930만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>부엉이없다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>203조 538억 3069만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>174조 1025억 3447만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>프리프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>150조 7025억 6128만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>135조 4527억 1903만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>쾌감</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
-  </si>
-  <si>
-    <t>103조 3764억 2883만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>87조 8655억 3844만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>83조 5339억 4959만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>80조 1967억 9470만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>POSCO</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
-  </si>
-  <si>
-    <t>65조 7697억 3285만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>46조 6512억 8057만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>두근푸근연근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>45조 9368억 846만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>포뇨야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
-  </si>
-  <si>
-    <t>45조 2469억 9216만</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>44조 535억 2685만</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>김치싸대기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>38조 1459억 7981만</t>
-  </si>
-  <si>
-    <t>악의꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>36조 6837억 5297만</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>대방어조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>33조 3718억 3936만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>32조 3589억 4341만</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>울힝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
-  </si>
-  <si>
-    <t>32조 3033억 5769만</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>29조 5789억 1997만</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>몽호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
-  </si>
-  <si>
-    <t>25조 3889억 7104만</t>
-  </si>
-  <si>
-    <t>별뽕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%BD%95</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>6712조 4731억 9272만</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EA%B3%B0%EB%9D%A0</t>
   </si>
   <si>
-    <t>2955조 3191억 4144만</t>
-  </si>
-  <si>
-    <t>도얍스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EC%96%8D%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>2904조 4073억 4102만</t>
+    <t>3103조 4381억 4407만</t>
   </si>
   <si>
     <t>꿀까배기</t>
@@ -674,7 +947,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EA%B9%8C%EB%B0%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>1640조 9351억 8517만</t>
+    <t>1798조 5637억 671만</t>
   </si>
   <si>
     <t>KR#18TIDK8BQ6</t>
@@ -683,7 +956,7 @@
     <t>https://mgf.gg/contents/character.php?n=KR%2318TIDK8BQ6</t>
   </si>
   <si>
-    <t>1213조 1372억 2746만</t>
+    <t>1237조 2389억 1992만</t>
   </si>
   <si>
     <t>팝중이</t>
@@ -713,15 +986,6 @@
     <t>505조 9558억 3517만</t>
   </si>
   <si>
-    <t>삭제합니다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AD%EC%A0%9C%ED%95%A9%EB%8B%88%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>490조 7257억 2782만</t>
-  </si>
-  <si>
     <t>적환</t>
   </si>
   <si>
@@ -755,7 +1019,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%ED%92%8D%EC%A1%B1</t>
   </si>
   <si>
-    <t>124조 5275억 4403만</t>
+    <t>133조 1155억 1579만</t>
   </si>
   <si>
     <t>안바</t>
@@ -764,7 +1028,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%B0%94</t>
   </si>
   <si>
-    <t>107조 6064억 7229만</t>
+    <t>113조 7228억 4179만</t>
+  </si>
+  <si>
+    <t>리세라</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EC%84%B8%EB%9D%BC</t>
+  </si>
+  <si>
+    <t>110조 8436억 3588만</t>
   </si>
   <si>
     <t>순수띵귤</t>
@@ -776,22 +1049,10 @@
     <t>106조 5179억 6719만</t>
   </si>
   <si>
-    <t>별뿡</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%BF%A1</t>
   </si>
   <si>
-    <t>93조 6082억 2804만</t>
-  </si>
-  <si>
-    <t>리세라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EC%84%B8%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>91조 4421억 1480만</t>
+    <t>103조 2646억 5103만</t>
   </si>
   <si>
     <t>동키링</t>
@@ -800,7 +1061,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%ED%82%A4%EB%A7%81</t>
   </si>
   <si>
-    <t>78조 595억 9240만</t>
+    <t>78조 639억 3423만</t>
   </si>
   <si>
     <t>검환</t>
@@ -818,7 +1079,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%AC%EA%B8%B0%EB%A6%AC</t>
   </si>
   <si>
-    <t>61조 3846억 759만</t>
+    <t>72조 3804억 8993만</t>
   </si>
   <si>
     <t>무열대</t>
@@ -827,7 +1088,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%97%B4%EB%8C%80</t>
   </si>
   <si>
-    <t>55조 3755억 7643만</t>
+    <t>63조 7990억 8998만</t>
   </si>
   <si>
     <t>기데</t>
@@ -845,499 +1106,238 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EA%B2%A9%EB%8A%90%EB%A6%BC</t>
   </si>
   <si>
-    <t>보우마스터</t>
+    <t>52조 1885억 3384만</t>
+  </si>
+  <si>
+    <t>혀로우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%80%EB%A1%9C%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>50조 5361억 9525만</t>
+  </si>
+  <si>
+    <t>별빛낭만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%B9%9B%EB%82%AD%EB%A7%8C</t>
+  </si>
+  <si>
+    <t>40조 6832억 4988만</t>
+  </si>
+  <si>
+    <t>쿧임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A7%EC%9E%84</t>
+  </si>
+  <si>
+    <t>39조 7418억 6382만</t>
+  </si>
+  <si>
+    <t>허이다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%97%88%EC%9D%B4%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>36조 6805억 691만</t>
+  </si>
+  <si>
+    <t>전직미녀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%A7%81%EB%AF%B8%EB%85%80</t>
+  </si>
+  <si>
+    <t>16조 4197억 1188만</t>
+  </si>
+  <si>
+    <t>별득</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%93%9D</t>
+  </si>
+  <si>
+    <t>12조 6105억 2359만</t>
+  </si>
+  <si>
+    <t>가숭혁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%88%AD%ED%98%81</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>1경 8086조 9055억 5923만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%B4%EB%BD%80%EC%8B%9C</t>
+  </si>
+  <si>
+    <t>2831조 1506억 5892만</t>
+  </si>
+  <si>
+    <t>상탸치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%83%B8%EC%B9%98</t>
+  </si>
+  <si>
+    <t>1973조 5069억 3860만</t>
+  </si>
+  <si>
+    <t>달싹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EC%8B%B9</t>
+  </si>
+  <si>
+    <t>768조 2633억 6459만</t>
+  </si>
+  <si>
+    <t>김우이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%9A%B0%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>525조 431억 8929만</t>
+  </si>
+  <si>
+    <t>서예슬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
+  </si>
+  <si>
+    <t>518조 1251억 4726만</t>
+  </si>
+  <si>
+    <t>26길초</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
+  </si>
+  <si>
+    <t>484조 5861억 9002만</t>
+  </si>
+  <si>
+    <t>뇌쉬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%87%8C%EC%89%AC</t>
+  </si>
+  <si>
+    <t>477조 6715억 7462만</t>
+  </si>
+  <si>
+    <t>덜박</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%9C%EB%B0%95</t>
+  </si>
+  <si>
+    <t>373조 2967억 3028만</t>
+  </si>
+  <si>
+    <t>중탸치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A4%91%ED%83%B8%EC%B9%98</t>
+  </si>
+  <si>
+    <t>361조 9366억 5942만</t>
+  </si>
+  <si>
+    <t>옴짝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%B4%EC%A7%9D</t>
+  </si>
+  <si>
+    <t>267조 4873억 4322만</t>
+  </si>
+  <si>
+    <t>임승민</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
+  </si>
+  <si>
+    <t>216조 5819억 7929만</t>
+  </si>
+  <si>
+    <t>몬함</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
+  </si>
+  <si>
+    <t>213조 8180억 1111만</t>
+  </si>
+  <si>
+    <t>뻔수니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
+  </si>
+  <si>
+    <t>91조 5462억 5890만</t>
+  </si>
+  <si>
+    <t>하탸치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%83%B8%EC%B9%98</t>
+  </si>
+  <si>
+    <t>82조 2996억 4164만</t>
+  </si>
+  <si>
+    <t>26배털</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
+  </si>
+  <si>
+    <t>47조 8997억 9450만</t>
+  </si>
+  <si>
+    <t>쑤삔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%91%A4%EC%82%94</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>38조 6185억 6952만</t>
+  </si>
+  <si>
+    <t>류테</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%8C</t>
+  </si>
+  <si>
+    <t>29조 4752억 2082만</t>
+  </si>
+  <si>
+    <t>메키무라딘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%AC%B4%EB%9D%BC%EB%94%98</t>
   </si>
   <si>
     <t>101</t>
   </si>
   <si>
-    <t>52조 1885억 3384만</t>
-  </si>
-  <si>
-    <t>혀로우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%80%EB%A1%9C%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>50조 5361억 9525만</t>
-  </si>
-  <si>
-    <t>쿧임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A7%EC%9E%84</t>
-  </si>
-  <si>
-    <t>39조 7418억 6382만</t>
-  </si>
-  <si>
-    <t>별빛낭만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%B9%9B%EB%82%AD%EB%A7%8C</t>
-  </si>
-  <si>
-    <t>38조 8119억 8644만</t>
-  </si>
-  <si>
-    <t>허이다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%97%88%EC%9D%B4%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>36조 6805억 691만</t>
-  </si>
-  <si>
-    <t>별득</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%93%9D</t>
-  </si>
-  <si>
-    <t>12조 6105억 2359만</t>
-  </si>
-  <si>
-    <t>전직미녀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%A7%81%EB%AF%B8%EB%85%80</t>
-  </si>
-  <si>
-    <t>11조 5332억 3396만</t>
-  </si>
-  <si>
-    <t>얼래링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EB%9E%98%EB%A7%81</t>
-  </si>
-  <si>
-    <t>1경 1472조 8006억 6664만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BC%B4%EB%9E%98%EB%A7%81</t>
-  </si>
-  <si>
-    <t>2549조 7653억 8770만</t>
-  </si>
-  <si>
-    <t>미오링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%98%A4%EB%A7%81</t>
-  </si>
-  <si>
-    <t>1342조 6458억 7093만</t>
-  </si>
-  <si>
-    <t>독수링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EC%88%98%EB%A7%81</t>
-  </si>
-  <si>
-    <t>793조 8911억 467만</t>
-  </si>
-  <si>
-    <t>별빛링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%B9%9B%EB%A7%81</t>
-  </si>
-  <si>
-    <t>654조 4196억 2809만</t>
-  </si>
-  <si>
-    <t>아마링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A7%88%EB%A7%81</t>
-  </si>
-  <si>
-    <t>513조 5371억 6968만</t>
-  </si>
-  <si>
-    <t>키플링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%ED%94%8C%EB%A7%81</t>
-  </si>
-  <si>
-    <t>453조 6164억 7346만</t>
-  </si>
-  <si>
-    <t>아가링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EA%B0%80%EB%A7%81</t>
-  </si>
-  <si>
-    <t>439조 9232억 481만</t>
-  </si>
-  <si>
-    <t>츄르링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B8%84%EB%A5%B4%EB%A7%81</t>
-  </si>
-  <si>
-    <t>420조 9084억 9514만</t>
-  </si>
-  <si>
-    <t>송보링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%A1%EB%B3%B4%EB%A7%81</t>
-  </si>
-  <si>
-    <t>374조 4625억 7493만</t>
-  </si>
-  <si>
-    <t>네버링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EB%B2%84%EB%A7%81</t>
-  </si>
-  <si>
-    <t>338조 645억 327만</t>
-  </si>
-  <si>
-    <t>멍때링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%8D%EB%95%8C%EB%A7%81</t>
-  </si>
-  <si>
-    <t>305조 6567억 7447만</t>
-  </si>
-  <si>
-    <t>콕끼링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BD%95%EB%81%BC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>242조 7963억 3890만</t>
-  </si>
-  <si>
-    <t>시러링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%9F%AC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>239조 6714억 5917만</t>
-  </si>
-  <si>
-    <t>도트링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%ED%8A%B8%EB%A7%81</t>
-  </si>
-  <si>
-    <t>236조 5992억 9221만</t>
-  </si>
-  <si>
-    <t>모꼬링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EA%BC%AC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>202조 5389억 64만</t>
-  </si>
-  <si>
-    <t>무뇌링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%87%8C%EB%A7%81</t>
-  </si>
-  <si>
-    <t>183조 548억 5555만</t>
-  </si>
-  <si>
-    <t>드릴링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%93%9C%EB%A6%B4%EB%A7%81</t>
-  </si>
-  <si>
-    <t>173조 1953억 1787만</t>
-  </si>
-  <si>
-    <t>엠오링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%A0%EC%98%A4%EB%A7%81</t>
-  </si>
-  <si>
-    <t>142조 8227억 8570만</t>
-  </si>
-  <si>
-    <t>푸르링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EB%A5%B4%EB%A7%81</t>
-  </si>
-  <si>
-    <t>99조 6338억 6153만</t>
-  </si>
-  <si>
-    <t>해오링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%98%A4%EB%A7%81</t>
-  </si>
-  <si>
-    <t>96조 9598억 7223만</t>
-  </si>
-  <si>
-    <t>모델링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%8D%B8%EB%A7%81</t>
-  </si>
-  <si>
-    <t>91조 6914억 7173만</t>
-  </si>
-  <si>
-    <t>커포링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%8F%AC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>71조 3512억 145만</t>
-  </si>
-  <si>
-    <t>싸가링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EA%B0%80%EB%A7%81</t>
-  </si>
-  <si>
-    <t>66조 5279억 9387만</t>
-  </si>
-  <si>
-    <t>대가링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EA%B0%80%EB%A7%81</t>
-  </si>
-  <si>
-    <t>60조 3174억 4264만</t>
-  </si>
-  <si>
-    <t>술샘링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%A0%EC%83%98%EB%A7%81</t>
-  </si>
-  <si>
-    <t>57조 8645억 832만</t>
-  </si>
-  <si>
-    <t>깨구링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%A8%EA%B5%AC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>52조 4315억 1042만</t>
-  </si>
-  <si>
-    <t>꼬물링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%AC%BC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>50조 1653억 6801만</t>
-  </si>
-  <si>
-    <t>펭구링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8E%AD%EA%B5%AC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>37조 1968억 6576만</t>
-  </si>
-  <si>
-    <t>링가링가링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%81%EA%B0%80%EB%A7%81%EA%B0%80%EB%A7%81</t>
-  </si>
-  <si>
-    <t>32조 9466억 3052만</t>
-  </si>
-  <si>
-    <t>가숭혁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%88%AD%ED%98%81</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>1경 8086조 9055억 5923만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%B4%EB%BD%80%EC%8B%9C</t>
-  </si>
-  <si>
-    <t>2831조 1506억 5892만</t>
-  </si>
-  <si>
-    <t>상탸치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%83%B8%EC%B9%98</t>
-  </si>
-  <si>
-    <t>1726조 1961억 1645만</t>
-  </si>
-  <si>
-    <t>달싹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EC%8B%B9</t>
-  </si>
-  <si>
-    <t>708조 1355억 7402만</t>
-  </si>
-  <si>
-    <t>김우이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%9A%B0%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>516조 9172억 9058만</t>
-  </si>
-  <si>
-    <t>26길초</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
-  </si>
-  <si>
-    <t>482조 679억 891만</t>
-  </si>
-  <si>
-    <t>뇌쉬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%87%8C%EC%89%AC</t>
-  </si>
-  <si>
-    <t>473조 935억 9830만</t>
-  </si>
-  <si>
-    <t>서예슬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
-  </si>
-  <si>
-    <t>386조 1275억 3929만</t>
-  </si>
-  <si>
-    <t>덜박</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%9C%EB%B0%95</t>
-  </si>
-  <si>
-    <t>353조 4051억 6458만</t>
-  </si>
-  <si>
-    <t>옴짝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%B4%EC%A7%9D</t>
-  </si>
-  <si>
-    <t>267조 4873억 4322만</t>
-  </si>
-  <si>
-    <t>임승민</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
-  </si>
-  <si>
-    <t>216조 5819억 7929만</t>
-  </si>
-  <si>
-    <t>중탸치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A4%91%ED%83%B8%EC%B9%98</t>
-  </si>
-  <si>
-    <t>196조 911억 5708만</t>
-  </si>
-  <si>
-    <t>몬함</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
-  </si>
-  <si>
-    <t>181조 4736억 2563만</t>
-  </si>
-  <si>
-    <t>뻔수니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
-  </si>
-  <si>
-    <t>90조 4165억 1503만</t>
-  </si>
-  <si>
-    <t>하탸치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%83%B8%EC%B9%98</t>
-  </si>
-  <si>
-    <t>73조 6589억 4898만</t>
-  </si>
-  <si>
-    <t>26배털</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
-  </si>
-  <si>
-    <t>44조 825억 4027만</t>
-  </si>
-  <si>
-    <t>쑤삔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%91%A4%EC%82%94</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>38조 6185억 6952만</t>
-  </si>
-  <si>
-    <t>류테</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%8C</t>
-  </si>
-  <si>
-    <t>29조 4752억 2082만</t>
+    <t>23조 1931억 726만</t>
   </si>
   <si>
     <t>26퐝바</t>
@@ -1367,15 +1367,6 @@
     <t>21조 3943억 1549만</t>
   </si>
   <si>
-    <t>메키무라딘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%AC%B4%EB%9D%BC%EB%94%98</t>
-  </si>
-  <si>
-    <t>20조 8757억 2658만</t>
-  </si>
-  <si>
     <t>뻐늬</t>
   </si>
   <si>
@@ -1400,7 +1391,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
   </si>
   <si>
-    <t>17조 1535억 3231만</t>
+    <t>17조 1902억 8827만</t>
+  </si>
+  <si>
+    <t>크앙레몬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>14조 4673억 9169만</t>
   </si>
   <si>
     <t>최씨용</t>
@@ -1412,15 +1412,6 @@
     <t>14조 623억 4943만</t>
   </si>
   <si>
-    <t>크앙레몬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>13조 7339억 1482만</t>
-  </si>
-  <si>
     <t>예라미</t>
   </si>
   <si>
@@ -1436,7 +1427,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%AC%EC%8A%A4%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>7조 905억 306만</t>
+    <t>8조 3044억 7219만</t>
   </si>
   <si>
     <t>고영희멈뭄미</t>
@@ -1445,7 +1436,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%98%81%ED%9D%AC%EB%A9%88%EB%AD%84%EB%AF%B8</t>
   </si>
   <si>
-    <t>5조 9710억 6492만</t>
+    <t>6조 622억 6177만</t>
   </si>
   <si>
     <t>코로드</t>
@@ -1454,7 +1445,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EB%A1%9C%EB%93%9C</t>
   </si>
   <si>
-    <t>1경 6280조 4127억 4609만</t>
+    <t>1경 8810조 198억 7908만</t>
+  </si>
+  <si>
+    <t>슨녀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A8%EB%85%80</t>
+  </si>
+  <si>
+    <t>4870조 771억 3004만</t>
   </si>
   <si>
     <t>맠스맨</t>
@@ -1466,13 +1466,13 @@
     <t>4719조 300억 9804만</t>
   </si>
   <si>
-    <t>슨녀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A8%EB%85%80</t>
-  </si>
-  <si>
-    <t>4241조 5410억 8862만</t>
+    <t>김해님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%95%B4%EB%8B%98</t>
+  </si>
+  <si>
+    <t>248조 7671억 2085만</t>
   </si>
   <si>
     <t>빌린</t>
@@ -1490,16 +1490,7 @@
     <t>https://mgf.gg/contents/character.php?n=Bit%EC%88%8D</t>
   </si>
   <si>
-    <t>222조 947억 9369만</t>
-  </si>
-  <si>
-    <t>김해님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%95%B4%EB%8B%98</t>
-  </si>
-  <si>
-    <t>189조 3135억 3734만</t>
+    <t>238조 3054억 5141만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%85%9C%EC%9D%B4</t>
@@ -1508,22 +1499,22 @@
     <t>123조 5425억 2061만</t>
   </si>
   <si>
+    <t>아마날</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A7%88%EB%82%A0</t>
+  </si>
+  <si>
+    <t>109조 7611억 6219만</t>
+  </si>
+  <si>
     <t>산타선물</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%ED%83%80%EC%84%A0%EB%AC%BC</t>
   </si>
   <si>
-    <t>95조 4083억 3220만</t>
-  </si>
-  <si>
-    <t>아마날</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A7%88%EB%82%A0</t>
-  </si>
-  <si>
-    <t>87조 7177억 691만</t>
+    <t>101조 8868억 7437만</t>
   </si>
   <si>
     <t>도령3</t>
@@ -1532,7 +1523,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A0%B93</t>
   </si>
   <si>
-    <t>65조 8166억 9332만</t>
+    <t>71조 9253억 1220만</t>
   </si>
   <si>
     <t>조콩나무</t>
@@ -1550,7 +1541,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%9F%AC%EB%8A%94%EA%B1%B0%EC%95%84%EB%83%90</t>
   </si>
   <si>
-    <t>42조 7660억 9022만</t>
+    <t>43조 5872억 3576만</t>
   </si>
   <si>
     <t>숮2</t>
@@ -1559,7 +1550,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%AE2</t>
   </si>
   <si>
-    <t>32조 8627억 5390만</t>
+    <t>32조 9705억 5239만</t>
   </si>
   <si>
     <t>백엄경</t>
@@ -1580,6 +1571,15 @@
     <t>24조 258억 2609만</t>
   </si>
   <si>
+    <t>시프님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%ED%94%84%EB%8B%98</t>
+  </si>
+  <si>
+    <t>22조 4947억 7204만</t>
+  </si>
+  <si>
     <t>최소뎀</t>
   </si>
   <si>
@@ -1589,22 +1589,13 @@
     <t>22조 2347억 2935만</t>
   </si>
   <si>
-    <t>시프님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%ED%94%84%EB%8B%98</t>
-  </si>
-  <si>
-    <t>22조 492억 4164만</t>
-  </si>
-  <si>
     <t>한유화</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EC%9C%A0%ED%99%94</t>
   </si>
   <si>
-    <t>19조 1070억 1544만</t>
+    <t>19조 1742억 331만</t>
   </si>
   <si>
     <t>95도도</t>
@@ -1613,7 +1604,7 @@
     <t>https://mgf.gg/contents/character.php?n=95%EB%8F%84%EB%8F%84</t>
   </si>
   <si>
-    <t>18조 6046억 873만</t>
+    <t>18조 9214억 6765만</t>
   </si>
   <si>
     <t>천칸</t>
@@ -1631,7 +1622,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%88%EB%A7%88%EC%8B%A0</t>
   </si>
   <si>
-    <t>9조 5421억 6790만</t>
+    <t>9조 5453억 6927만</t>
   </si>
   <si>
     <t>숑당</t>
@@ -1661,7 +1652,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%A6%88</t>
   </si>
   <si>
-    <t>5조 8451억 4956만</t>
+    <t>6조 3498억 1848만</t>
+  </si>
+  <si>
+    <t>장수흙침대</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EC%88%98%ED%9D%99%EC%B9%A8%EB%8C%80</t>
+  </si>
+  <si>
+    <t>5조 3176억 4154만</t>
   </si>
   <si>
     <t>박하민린</t>
@@ -1673,7 +1673,7 @@
     <t>99</t>
   </si>
   <si>
-    <t>5조 2480억 4212만</t>
+    <t>5조 3172억 8138만</t>
   </si>
   <si>
     <t>군명</t>
@@ -1682,16 +1682,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EB%AA%85</t>
   </si>
   <si>
-    <t>4조 8085억 7122만</t>
-  </si>
-  <si>
-    <t>장수흙침대</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EC%88%98%ED%9D%99%EC%B9%A8%EB%8C%80</t>
-  </si>
-  <si>
-    <t>4조 1413억 3850만</t>
+    <t>5조 1644억 1414만</t>
   </si>
   <si>
     <t>김똔똔</t>
@@ -1700,7 +1691,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%98%94%EB%98%94</t>
   </si>
   <si>
-    <t>3조 9222억 2332만</t>
+    <t>4조 4910억 4536만</t>
   </si>
   <si>
     <t>니코짱</t>
@@ -1712,7 +1703,7 @@
     <t>98</t>
   </si>
   <si>
-    <t>2조 7950억 2744만</t>
+    <t>3조 2634억 9108만</t>
   </si>
   <si>
     <t>뉴맹우</t>
@@ -1724,7 +1715,7 @@
     <t>97</t>
   </si>
   <si>
-    <t>1조 2374억 3820만</t>
+    <t>1조 3283억 3290만</t>
   </si>
 </sst>
 </file>
@@ -2208,63 +2199,63 @@
         <v>29</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="M3" s="2" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2305,48 +2296,48 @@
         <v>51</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2382,28 +2373,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -2414,28 +2405,28 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -2446,28 +2437,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2478,28 +2469,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2510,28 +2501,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2542,28 +2533,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2574,28 +2565,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2606,28 +2597,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2638,28 +2629,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2670,28 +2661,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2702,28 +2693,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2734,28 +2725,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>119</v>
-      </c>
       <c r="I12" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2766,28 +2757,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2798,28 +2789,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2830,28 +2821,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2862,28 +2853,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2894,28 +2885,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2926,28 +2917,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2958,25 +2949,25 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>155</v>
@@ -3002,13 +2993,13 @@
         <v>158</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>159</v>
@@ -3034,13 +3025,13 @@
         <v>162</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>163</v>
@@ -3054,28 +3045,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3086,28 +3077,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>171</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3118,7 +3109,7 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>47</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>172</v>
@@ -3130,16 +3121,16 @@
         <v>173</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3150,7 +3141,7 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>175</v>
+        <v>56</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>176</v>
@@ -3162,13 +3153,13 @@
         <v>177</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>178</v>
@@ -3182,25 +3173,25 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>55</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>182</v>
@@ -3226,16 +3217,16 @@
         <v>185</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>145</v>
+        <v>186</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3246,25 +3237,25 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>188</v>
+        <v>23</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>188</v>
+        <v>23</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>189</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>70</v>
+        <v>190</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>191</v>
@@ -3290,13 +3281,13 @@
         <v>194</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>195</v>
@@ -3313,25 +3304,25 @@
         <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>23</v>
+        <v>197</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>23</v>
+        <v>197</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>198</v>
+        <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3342,7 +3333,7 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>201</v>
@@ -3354,13 +3345,13 @@
         <v>202</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>203</v>
@@ -3409,1017 +3400,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J30"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
-    <hyperlink ref="E20" r:id="rId19"/>
-    <hyperlink ref="E21" r:id="rId20"/>
-    <hyperlink ref="E22" r:id="rId21"/>
-    <hyperlink ref="E23" r:id="rId22"/>
-    <hyperlink ref="E24" r:id="rId23"/>
-    <hyperlink ref="E25" r:id="rId24"/>
-    <hyperlink ref="E26" r:id="rId25"/>
-    <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -4438,28 +3418,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -4467,31 +3447,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>293</v>
+        <v>204</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>293</v>
+        <v>204</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>294</v>
+        <v>205</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>295</v>
+        <v>206</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4499,31 +3479,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>296</v>
+        <v>207</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>297</v>
+        <v>208</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4531,31 +3511,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>298</v>
+        <v>209</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>298</v>
+        <v>209</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>299</v>
+        <v>210</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>300</v>
+        <v>211</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4563,31 +3543,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>301</v>
+        <v>212</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>301</v>
+        <v>212</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>302</v>
+        <v>213</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>303</v>
+        <v>214</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4595,31 +3575,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>304</v>
+        <v>215</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>304</v>
+        <v>215</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>305</v>
+        <v>216</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>306</v>
+        <v>217</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4627,31 +3607,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>307</v>
+        <v>218</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>307</v>
+        <v>218</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>308</v>
+        <v>219</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>309</v>
+        <v>220</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4659,31 +3639,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>310</v>
+        <v>221</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>310</v>
+        <v>221</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>311</v>
+        <v>222</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>312</v>
+        <v>223</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4691,31 +3671,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>313</v>
+        <v>224</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>313</v>
+        <v>224</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>314</v>
+        <v>225</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>315</v>
+        <v>226</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4723,31 +3703,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>316</v>
+        <v>227</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>316</v>
+        <v>227</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>317</v>
+        <v>228</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>318</v>
+        <v>229</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4755,31 +3735,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>319</v>
+        <v>230</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>319</v>
+        <v>230</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>320</v>
+        <v>231</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>321</v>
+        <v>232</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4787,31 +3767,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>119</v>
-      </c>
       <c r="I12" s="2" t="s">
-        <v>324</v>
+        <v>235</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4819,31 +3799,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>325</v>
+        <v>236</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>325</v>
+        <v>236</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>326</v>
+        <v>237</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>327</v>
+        <v>238</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4851,31 +3831,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>328</v>
+        <v>239</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>328</v>
+        <v>239</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>329</v>
+        <v>240</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>330</v>
+        <v>241</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4883,31 +3863,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>331</v>
+        <v>242</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>331</v>
+        <v>242</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>332</v>
+        <v>243</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>71</v>
+        <v>199</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>333</v>
+        <v>244</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4915,31 +3895,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>334</v>
+        <v>245</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>334</v>
+        <v>245</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>335</v>
+        <v>246</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>190</v>
+        <v>72</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>336</v>
+        <v>247</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4947,31 +3927,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>337</v>
+        <v>248</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>337</v>
+        <v>248</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>338</v>
+        <v>249</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>339</v>
+        <v>250</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4979,31 +3959,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>340</v>
+        <v>251</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>340</v>
+        <v>251</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>341</v>
+        <v>252</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>342</v>
+        <v>253</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5011,31 +3991,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>343</v>
+        <v>254</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>343</v>
+        <v>254</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>344</v>
+        <v>255</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>345</v>
+        <v>256</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5043,31 +4023,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>346</v>
+        <v>257</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>346</v>
+        <v>257</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>347</v>
+        <v>258</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>348</v>
+        <v>259</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5075,31 +4055,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>349</v>
+        <v>260</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>349</v>
+        <v>260</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>350</v>
+        <v>261</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>351</v>
+        <v>263</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5107,31 +4087,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>47</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>352</v>
+        <v>264</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>352</v>
+        <v>264</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>353</v>
+        <v>265</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>354</v>
+        <v>266</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5139,31 +4119,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>355</v>
+        <v>267</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>355</v>
+        <v>267</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>356</v>
+        <v>268</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>357</v>
+        <v>269</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5171,31 +4151,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>47</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>358</v>
+        <v>270</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>358</v>
+        <v>270</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>359</v>
+        <v>271</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>360</v>
+        <v>272</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5203,31 +4183,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>175</v>
+        <v>56</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>361</v>
+        <v>273</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>361</v>
+        <v>273</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>362</v>
+        <v>274</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>363</v>
+        <v>275</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5235,31 +4215,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>55</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>364</v>
+        <v>276</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>364</v>
+        <v>276</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>365</v>
+        <v>277</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>366</v>
+        <v>278</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5267,31 +4247,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>367</v>
+        <v>279</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>367</v>
+        <v>279</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>368</v>
+        <v>280</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>369</v>
+        <v>281</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5299,31 +4279,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>370</v>
+        <v>282</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>370</v>
+        <v>282</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>371</v>
+        <v>283</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>372</v>
+        <v>284</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5331,31 +4311,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>373</v>
+        <v>285</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>373</v>
+        <v>285</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>374</v>
+        <v>286</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>375</v>
+        <v>287</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5363,31 +4343,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>376</v>
+        <v>288</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>376</v>
+        <v>288</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>377</v>
+        <v>289</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>378</v>
+        <v>290</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5395,31 +4375,31 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>379</v>
+        <v>291</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>379</v>
+        <v>291</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>380</v>
+        <v>292</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>381</v>
+        <v>293</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5463,6 +4443,984 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J29"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J29"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
@@ -5483,28 +5441,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -5515,31 +5473,31 @@
         <v>44</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5547,7 +5505,7 @@
         <v>44</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>51</v>
@@ -5556,22 +5514,22 @@
         <v>51</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>206</v>
+        <v>296</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -5579,31 +5537,31 @@
         <v>44</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -5611,31 +5569,31 @@
         <v>44</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -5643,31 +5601,31 @@
         <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -5675,31 +5633,31 @@
         <v>44</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -5707,31 +5665,31 @@
         <v>44</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -5739,31 +5697,31 @@
         <v>44</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -5771,31 +5729,31 @@
         <v>44</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="I10" s="2" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -5803,31 +5761,31 @@
         <v>44</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="I11" s="2" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -5835,31 +5793,31 @@
         <v>44</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -5867,31 +5825,31 @@
         <v>44</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -5899,31 +5857,31 @@
         <v>44</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -5931,31 +5889,31 @@
         <v>44</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -5963,31 +5921,31 @@
         <v>44</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -5995,31 +5953,31 @@
         <v>44</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -6027,31 +5985,31 @@
         <v>44</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -6059,31 +6017,31 @@
         <v>44</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -6094,28 +6052,28 @@
         <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>145</v>
+        <v>435</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -6126,28 +6084,28 @@
         <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>272</v>
+        <v>78</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>181</v>
+        <v>146</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -6155,31 +6113,31 @@
         <v>44</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>47</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>77</v>
+        <v>262</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -6187,31 +6145,31 @@
         <v>44</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>273</v>
+        <v>174</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -6219,31 +6177,31 @@
         <v>44</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>47</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -6251,31 +6209,31 @@
         <v>44</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>175</v>
+        <v>56</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -6283,31 +6241,31 @@
         <v>44</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>55</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>273</v>
+        <v>435</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -6318,28 +6276,28 @@
         <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -6347,31 +6305,31 @@
         <v>44</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -6382,28 +6340,28 @@
         <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>273</v>
+        <v>435</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -6414,28 +6372,28 @@
         <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>273</v>
+        <v>435</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -6443,31 +6401,31 @@
         <v>44</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>273</v>
+        <v>435</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -6519,7 +6477,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6528,28 +6486,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -6557,962 +6515,962 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>206</v>
+        <v>296</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>78</v>
+        <v>296</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>136</v>
+        <v>95</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>273</v>
+        <v>435</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>273</v>
+        <v>186</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>181</v>
+        <v>435</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>273</v>
+        <v>435</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>273</v>
+        <v>186</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>164</v>
+        <v>47</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>273</v>
+        <v>435</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>538</v>
-      </c>
       <c r="J23" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>47</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>175</v>
+        <v>56</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>55</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>432</v>
+        <v>95</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>547</v>
+        <v>534</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>71</v>
+        <v>428</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>547</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>547</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>547</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>561</v>
-      </c>
       <c r="J30" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>200</v>
+        <v>17</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>565</v>
-      </c>
       <c r="J31" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -10,15 +10,15 @@
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="셀린느" sheetId="2" r:id="rId2"/>
     <sheet name="블링블리" sheetId="3" r:id="rId3"/>
-    <sheet name="별곰부대" sheetId="4" r:id="rId4"/>
-    <sheet name="LUXURY" sheetId="5" r:id="rId5"/>
+    <sheet name="LUXURY" sheetId="4" r:id="rId4"/>
+    <sheet name="별곰부대" sheetId="5" r:id="rId5"/>
     <sheet name="item" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">item!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">LUXURY!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">별곰부대!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">LUXURY!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">별곰부대!$A$1:$J$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">블링블리!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">셀린느!$A$1:$J$31</definedName>
   </definedNames>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="559">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,609 +80,618 @@
     <t>Scania 2</t>
   </si>
   <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>1위</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>2경 5003조 7064억 412만</t>
+  </si>
+  <si>
+    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
+  </si>
+  <si>
+    <t>혜영</t>
+  </si>
+  <si>
+    <t>2026.04.19</t>
+  </si>
+  <si>
+    <t>블링블리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B8%94%EB%A7%81%EB%B8%94%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>Scania 27</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>3위</t>
+  </si>
+  <si>
+    <t>2경 2654조 3955억 6740만</t>
+  </si>
+  <si>
+    <t>토벌 3위 1군 투력 50조 이상 / 토벌 13위 2군 블리블링 10조 이상 / 3군 블링불링 3000억이상 닉변 필수 공헌도 미달 길본 미업글 1일 미접 추방</t>
+  </si>
+  <si>
+    <t>꼴래링</t>
+  </si>
+  <si>
+    <t>2026.04.20</t>
+  </si>
+  <si>
+    <t>LUXURY</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
+  </si>
+  <si>
+    <t>Scania 16</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Lv.9</t>
+  </si>
+  <si>
+    <t>2경 7507조 6989억 2112만</t>
+  </si>
+  <si>
+    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
+  </si>
+  <si>
+    <t>살뽀시</t>
+  </si>
+  <si>
+    <t>별곰부대</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B3%84%EA%B3%B0%EB%B6%80%EB%8C%80</t>
+  </si>
+  <si>
+    <t>Scania 30</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>2위</t>
+  </si>
+  <si>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>28명</t>
+  </si>
+  <si>
+    <t>2경 340조 9927억 1769만</t>
+  </si>
+  <si>
+    <t>가입문의 : 리세라, 별뿡</t>
+  </si>
+  <si>
+    <t>별뿡</t>
+  </si>
+  <si>
+    <t>item</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=item</t>
+  </si>
+  <si>
+    <t>Scania 34</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>2경 9978조 4835억 6234만</t>
+  </si>
+  <si>
+    <t>We Go Together !</t>
+  </si>
+  <si>
+    <t>템이</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>스타냥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>1경 720조 3865억 2152만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>진자이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>4143조 7347억 1708만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>돈스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>3322조 3154억 8065만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>말레이히어로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>1744조 8442억 4005만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>1540조 3596억 8447만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>빌런투킬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>1123조 3986억 1263만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>스타뎀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%8E%80</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>475조 5893억 7767만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>여사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
+  </si>
+  <si>
+    <t>400조 1307억 6796만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>단풍노비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>348조 1289억 3205만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>228조 665억 3930만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>부엉이없다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>225조 316억 7503만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>213조 2895억 1154만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>프리프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>163조 5754억 4231만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>143조 6668억 6475만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>쾌감</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
+  </si>
+  <si>
+    <t>114조 2396억 3369만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>소소채2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>101조 6267억 648만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>88조 9672억 2946만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>88조 6379억 49만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>POSCO</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
+  </si>
+  <si>
+    <t>65조 7697억 3285만</t>
+  </si>
+  <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>51조 5399억 1217만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>두근푸근연근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>49조 4912억 6649만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>46조 8231억 8034만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>포뇨야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
+  </si>
+  <si>
+    <t>46조 2787억 8294만</t>
+  </si>
+  <si>
+    <t>울힝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>39조 1111억 1972만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>김치싸대기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>38조 1459억 7981만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>악의꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>36조 6837억 5297만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>36조 474억 2125만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>34조 8711억 1818만</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>33조 231억 7698만</t>
+  </si>
+  <si>
     <t>30</t>
   </si>
   <si>
-    <t>1위</t>
-  </si>
-  <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>2경 5003조 7064억 412만</t>
-  </si>
-  <si>
-    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
-  </si>
-  <si>
-    <t>혜영</t>
-  </si>
-  <si>
-    <t>2026.04.19</t>
-  </si>
-  <si>
-    <t>블링블리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B8%94%EB%A7%81%EB%B8%94%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>Scania 27</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>3위</t>
-  </si>
-  <si>
-    <t>2경 1789조 1060억 4000만</t>
-  </si>
-  <si>
-    <t>토벌 3위 1군 투력 50조 이상 / 토벌 13위 2군 블리블링 10조 이상 / 3군 블링불링 3000억이상 닉변 필수 공헌도 미달 길본 미업글 1일 미접 추방</t>
-  </si>
-  <si>
-    <t>꼴래링</t>
-  </si>
-  <si>
-    <t>별곰부대</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B3%84%EA%B3%B0%EB%B6%80%EB%8C%80</t>
-  </si>
-  <si>
-    <t>Scania 30</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>2위</t>
-  </si>
-  <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>1경 8436조 3967억 1957만</t>
-  </si>
-  <si>
-    <t>가입문의 : 리세라, 별뿡</t>
-  </si>
-  <si>
-    <t>별뿡</t>
-  </si>
-  <si>
-    <t>2026.04.17</t>
-  </si>
-  <si>
-    <t>LUXURY</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=LUXURY</t>
-  </si>
-  <si>
-    <t>Scania 16</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>Lv.9</t>
-  </si>
-  <si>
-    <t>2경 7507조 6989억 2112만</t>
-  </si>
-  <si>
-    <t>*[100LV] 이상/활동,일일 업그레이드 필수* 대기 가능 문의 귓</t>
-  </si>
-  <si>
-    <t>살뽀시</t>
-  </si>
-  <si>
-    <t>2026.04.20</t>
-  </si>
-  <si>
-    <t>item</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=item</t>
-  </si>
-  <si>
-    <t>Scania 34</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>2경 6501조 1108억 3368만</t>
-  </si>
-  <si>
-    <t>We Go Together !</t>
-  </si>
-  <si>
-    <t>템이</t>
-  </si>
-  <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>스타냥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>1경 720조 3865억 2152만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>진자이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>4143조 7347억 1708만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>돈스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>3322조 3154억 8065만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>말레이히어로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>1676조 9718억 7183만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>1519조 1682억 4663만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>빌런투킬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>1120조 9927억 5165만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>스타뎀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%8E%80</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>475조 5893억 7767만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>여사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
+    <t>몽호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
+  </si>
+  <si>
+    <t>25조 8550억 2155만</t>
+  </si>
+  <si>
+    <t>얼래링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EB%9E%98%EB%A7%81</t>
+  </si>
+  <si>
+    <t>1경 1472조 8006억 6664만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BC%B4%EB%9E%98%EB%A7%81</t>
+  </si>
+  <si>
+    <t>2840조 3802억 6526만</t>
+  </si>
+  <si>
+    <t>미오링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%98%A4%EB%A7%81</t>
+  </si>
+  <si>
+    <t>1497조 7025억 2757만</t>
+  </si>
+  <si>
+    <t>독수링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EC%88%98%EB%A7%81</t>
+  </si>
+  <si>
+    <t>974조 1557억 8886만</t>
+  </si>
+  <si>
+    <t>별빛링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%B9%9B%EB%A7%81</t>
   </si>
   <si>
     <t>107</t>
   </si>
   <si>
-    <t>400조 1307억 6796만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>단풍노비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>341조 312억 1190만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>니달리신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>228조 665억 3930만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>부엉이없다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>212조 5275억 4448만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>174조 1025억 3447만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>프리프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>150조 7025억 6128만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>143조 287억 8179만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>쾌감</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
-  </si>
-  <si>
-    <t>113조 8757억 8651만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>92조 589억 5971만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>88조 7167억 3645만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>88조 6379억 49만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>POSCO</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
-  </si>
-  <si>
-    <t>65조 7697억 3285만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>51조 3869억 2011만</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>46조 7938억 7081만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>포뇨야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
-  </si>
-  <si>
-    <t>46조 2787억 8294만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>두근푸근연근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>45조 9368억 846만</t>
-  </si>
-  <si>
-    <t>울힝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
-  </si>
-  <si>
-    <t>39조 1111억 1972만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>김치싸대기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>38조 1459억 7981만</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>악의꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>36조 6837억 5297만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>36조 474억 2125만</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>대방어조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>34조 8711억 1818만</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>32조 5239억 3292만</t>
-  </si>
-  <si>
-    <t>몽호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
-  </si>
-  <si>
-    <t>25조 3889억 7104만</t>
-  </si>
-  <si>
-    <t>얼래링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%BC%EB%9E%98%EB%A7%81</t>
-  </si>
-  <si>
-    <t>1경 1472조 8006억 6664만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BC%B4%EB%9E%98%EB%A7%81</t>
-  </si>
-  <si>
-    <t>2840조 3802억 6526만</t>
-  </si>
-  <si>
-    <t>미오링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%98%A4%EB%A7%81</t>
-  </si>
-  <si>
-    <t>1497조 7025억 2757만</t>
-  </si>
-  <si>
-    <t>독수링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EC%88%98%EB%A7%81</t>
-  </si>
-  <si>
-    <t>974조 1557억 8886만</t>
-  </si>
-  <si>
-    <t>별빛링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%B9%9B%EB%A7%81</t>
-  </si>
-  <si>
     <t>654조 4196억 2809만</t>
   </si>
   <si>
+    <t>키플링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%ED%94%8C%EB%A7%81</t>
+  </si>
+  <si>
+    <t>523조 8138억 2033만</t>
+  </si>
+  <si>
     <t>아마링</t>
   </si>
   <si>
@@ -692,15 +701,6 @@
     <t>513조 5371억 6968만</t>
   </si>
   <si>
-    <t>키플링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%ED%94%8C%EB%A7%81</t>
-  </si>
-  <si>
-    <t>481조 7353억 2826만</t>
-  </si>
-  <si>
     <t>아가링</t>
   </si>
   <si>
@@ -710,6 +710,15 @@
     <t>439조 9232억 481만</t>
   </si>
   <si>
+    <t>송보링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%A1%EB%B3%B4%EB%A7%81</t>
+  </si>
+  <si>
+    <t>428조 3475억 7694만</t>
+  </si>
+  <si>
     <t>츄르링</t>
   </si>
   <si>
@@ -719,22 +728,13 @@
     <t>420조 9084억 9514만</t>
   </si>
   <si>
-    <t>송보링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%A1%EB%B3%B4%EB%A7%81</t>
-  </si>
-  <si>
-    <t>389조 1966억 9816만</t>
-  </si>
-  <si>
     <t>네버링</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EB%B2%84%EB%A7%81</t>
   </si>
   <si>
-    <t>346조 3459억 2495만</t>
+    <t>364조 3533억 1160만</t>
   </si>
   <si>
     <t>멍때링</t>
@@ -752,7 +752,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%95%EB%81%BC%EB%A7%81</t>
   </si>
   <si>
-    <t>279조 9902억 2917만</t>
+    <t>290조 310억 9845만</t>
   </si>
   <si>
     <t>도트링</t>
@@ -761,7 +761,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%ED%8A%B8%EB%A7%81</t>
   </si>
   <si>
-    <t>248조 4101억 6785만</t>
+    <t>258조 3577억 202만</t>
+  </si>
+  <si>
+    <t>드릴링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%93%9C%EB%A6%B4%EB%A7%81</t>
+  </si>
+  <si>
+    <t>246조 5252억 2296만</t>
   </si>
   <si>
     <t>시러링</t>
@@ -788,16 +797,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%87%8C%EB%A7%81</t>
   </si>
   <si>
-    <t>183조 548억 5555만</t>
-  </si>
-  <si>
-    <t>드릴링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%93%9C%EB%A6%B4%EB%A7%81</t>
-  </si>
-  <si>
-    <t>181조 683억 1110만</t>
+    <t>184조 7592억 4334만</t>
   </si>
   <si>
     <t>엠오링</t>
@@ -809,6 +809,15 @@
     <t>144조 5807억 9489만</t>
   </si>
   <si>
+    <t>해오링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%98%A4%EB%A7%81</t>
+  </si>
+  <si>
+    <t>99조 7603억 9766만</t>
+  </si>
+  <si>
     <t>푸르링</t>
   </si>
   <si>
@@ -821,15 +830,6 @@
     <t>99조 6338억 6153만</t>
   </si>
   <si>
-    <t>해오링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%98%A4%EB%A7%81</t>
-  </si>
-  <si>
-    <t>96조 9598억 7223만</t>
-  </si>
-  <si>
     <t>모델링</t>
   </si>
   <si>
@@ -854,7 +854,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%A0%EC%83%98%EB%A7%81</t>
   </si>
   <si>
-    <t>72조 7177억 4612만</t>
+    <t>72조 8806억 8203만</t>
   </si>
   <si>
     <t>싸가링</t>
@@ -911,16 +911,292 @@
     <t>37조 7119억 3674만</t>
   </si>
   <si>
+    <t>가숭혁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%88%AD%ED%98%81</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>1경 8086조 9055억 5923만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%B4%EB%BD%80%EC%8B%9C</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>2831조 1506억 5892만</t>
+  </si>
+  <si>
+    <t>상탸치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%83%B8%EC%B9%98</t>
+  </si>
+  <si>
+    <t>1974조 233억 937만</t>
+  </si>
+  <si>
+    <t>달싹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EC%8B%B9</t>
+  </si>
+  <si>
+    <t>809조 5985억 7097만</t>
+  </si>
+  <si>
+    <t>김우이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%9A%B0%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>525조 431억 8929만</t>
+  </si>
+  <si>
+    <t>서예슬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
+  </si>
+  <si>
+    <t>519조 4897억 3481만</t>
+  </si>
+  <si>
+    <t>26길초</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
+  </si>
+  <si>
+    <t>484조 5861억 9002만</t>
+  </si>
+  <si>
+    <t>뇌쉬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%87%8C%EC%89%AC</t>
+  </si>
+  <si>
+    <t>477조 6715억 7462만</t>
+  </si>
+  <si>
+    <t>옴짝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%B4%EC%A7%9D</t>
+  </si>
+  <si>
+    <t>404조 9826억 7892만</t>
+  </si>
+  <si>
+    <t>덜박</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%9C%EB%B0%95</t>
+  </si>
+  <si>
+    <t>373조 2967억 3028만</t>
+  </si>
+  <si>
+    <t>중탸치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A4%91%ED%83%B8%EC%B9%98</t>
+  </si>
+  <si>
+    <t>370조 6979억 9727만</t>
+  </si>
+  <si>
+    <t>몬함</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
+  </si>
+  <si>
+    <t>241조 7005억 7985만</t>
+  </si>
+  <si>
+    <t>임승민</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
+  </si>
+  <si>
+    <t>225조 7671억 6693만</t>
+  </si>
+  <si>
+    <t>뻔수니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
+  </si>
+  <si>
+    <t>92조 27억 6340만</t>
+  </si>
+  <si>
+    <t>하탸치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%83%B8%EC%B9%98</t>
+  </si>
+  <si>
+    <t>82조 2996억 4164만</t>
+  </si>
+  <si>
+    <t>26배털</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
+  </si>
+  <si>
+    <t>48조 129억 4261만</t>
+  </si>
+  <si>
+    <t>쑤삔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%91%A4%EC%82%94</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>41조 3143억 1479만</t>
+  </si>
+  <si>
+    <t>류테</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%8C</t>
+  </si>
+  <si>
+    <t>29조 4752억 2082만</t>
+  </si>
+  <si>
+    <t>메키무라딘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%AC%B4%EB%9D%BC%EB%94%98</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>23조 1931억 726만</t>
+  </si>
+  <si>
+    <t>26퐝바</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%ED%90%9D%EB%B0%94</t>
+  </si>
+  <si>
+    <t>23조 1264억 4895만</t>
+  </si>
+  <si>
+    <t>브깃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EA%B9%83</t>
+  </si>
+  <si>
+    <t>21조 9533억 9367만</t>
+  </si>
+  <si>
+    <t>아모르파티퀘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
+  </si>
+  <si>
+    <t>21조 4013억 3703만</t>
+  </si>
+  <si>
+    <t>뻐늬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%90%EB%8A%AC</t>
+  </si>
+  <si>
+    <t>19조 728억 950만</t>
+  </si>
+  <si>
+    <t>26조선</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=26%EC%A1%B0%EC%84%A0</t>
+  </si>
+  <si>
+    <t>18조 1871억 4713만</t>
+  </si>
+  <si>
+    <t>뿜삐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
+  </si>
+  <si>
+    <t>18조 734억 9249만</t>
+  </si>
+  <si>
+    <t>크앙레몬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>14조 4673억 9169만</t>
+  </si>
+  <si>
+    <t>최씨용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%94%A8%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>14조 623억 4943만</t>
+  </si>
+  <si>
+    <t>예라미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>9조 832억 341만</t>
+  </si>
+  <si>
+    <t>귬스파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%AC%EC%8A%A4%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>8조 3044억 7219만</t>
+  </si>
+  <si>
+    <t>고영희멈뭄미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%98%81%ED%9D%AC%EB%A9%88%EB%AD%84%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>6조 754억 4971만</t>
+  </si>
+  <si>
     <t>별뽕</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%BD%95</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>6712조 4731억 9272만</t>
+    <t>7359조 4642억 6598만</t>
   </si>
   <si>
     <t>도얍스</t>
@@ -932,15 +1208,6 @@
     <t>3156조 4193억 9418만</t>
   </si>
   <si>
-    <t>별곰띠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EA%B3%B0%EB%9D%A0</t>
-  </si>
-  <si>
-    <t>3103조 4381억 4407만</t>
-  </si>
-  <si>
     <t>꿀까배기</t>
   </si>
   <si>
@@ -956,7 +1223,7 @@
     <t>https://mgf.gg/contents/character.php?n=KR%2318TIDK8BQ6</t>
   </si>
   <si>
-    <t>1237조 2389억 1992만</t>
+    <t>1282조 7229억 6678만</t>
   </si>
   <si>
     <t>팝중이</t>
@@ -965,7 +1232,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%9D%EC%A4%91%EC%9D%B4</t>
   </si>
   <si>
-    <t>902조 4590억 2561만</t>
+    <t>1015조 3325억 2250만</t>
   </si>
   <si>
     <t>BJ규리</t>
@@ -983,7 +1250,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%8A%A4%ED%84%B4</t>
   </si>
   <si>
-    <t>505조 9558억 3517만</t>
+    <t>523조 4287억 8480만</t>
   </si>
   <si>
     <t>적환</t>
@@ -1019,7 +1286,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%ED%92%8D%EC%A1%B1</t>
   </si>
   <si>
-    <t>133조 1155억 1579만</t>
+    <t>136조 3672억 6965만</t>
   </si>
   <si>
     <t>안바</t>
@@ -1028,7 +1295,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%B0%94</t>
   </si>
   <si>
-    <t>113조 7228억 4179만</t>
+    <t>116조 9612억 5982만</t>
   </si>
   <si>
     <t>리세라</t>
@@ -1061,7 +1328,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%ED%82%A4%EB%A7%81</t>
   </si>
   <si>
-    <t>78조 639억 3423만</t>
+    <t>79조 7638억 7763만</t>
+  </si>
+  <si>
+    <t>재기리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%AC%EA%B8%B0%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>73조 6223억 4894만</t>
   </si>
   <si>
     <t>검환</t>
@@ -1073,15 +1349,6 @@
     <t>73조 5894억 2690만</t>
   </si>
   <si>
-    <t>재기리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%AC%EA%B8%B0%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>72조 3804억 8993만</t>
-  </si>
-  <si>
     <t>무열대</t>
   </si>
   <si>
@@ -1091,13 +1358,22 @@
     <t>63조 7990억 8998만</t>
   </si>
   <si>
+    <t>혀로우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%80%EB%A1%9C%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>59조 1098억 6203만</t>
+  </si>
+  <si>
     <t>기데</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%8D%B0</t>
   </si>
   <si>
-    <t>52조 2183억 2775만</t>
+    <t>53조 7549억 8799만</t>
   </si>
   <si>
     <t>공격느림</t>
@@ -1109,22 +1385,13 @@
     <t>52조 1885억 3384만</t>
   </si>
   <si>
-    <t>혀로우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%80%EB%A1%9C%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>50조 5361억 9525만</t>
-  </si>
-  <si>
     <t>별빛낭만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%B9%9B%EB%82%AD%EB%A7%8C</t>
   </si>
   <si>
-    <t>40조 6832억 4988만</t>
+    <t>40조 7303억 5934만</t>
   </si>
   <si>
     <t>쿧임</t>
@@ -1160,283 +1427,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%93%9D</t>
   </si>
   <si>
-    <t>12조 6105억 2359만</t>
-  </si>
-  <si>
-    <t>가숭혁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%88%AD%ED%98%81</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>1경 8086조 9055억 5923만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%B4%EB%BD%80%EC%8B%9C</t>
-  </si>
-  <si>
-    <t>2831조 1506억 5892만</t>
-  </si>
-  <si>
-    <t>상탸치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%83%B8%EC%B9%98</t>
-  </si>
-  <si>
-    <t>1973조 5069억 3860만</t>
-  </si>
-  <si>
-    <t>달싹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EC%8B%B9</t>
-  </si>
-  <si>
-    <t>768조 2633억 6459만</t>
-  </si>
-  <si>
-    <t>김우이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%9A%B0%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>525조 431억 8929만</t>
-  </si>
-  <si>
-    <t>서예슬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
-  </si>
-  <si>
-    <t>518조 1251억 4726만</t>
-  </si>
-  <si>
-    <t>26길초</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
-  </si>
-  <si>
-    <t>484조 5861억 9002만</t>
-  </si>
-  <si>
-    <t>뇌쉬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%87%8C%EC%89%AC</t>
-  </si>
-  <si>
-    <t>477조 6715억 7462만</t>
-  </si>
-  <si>
-    <t>덜박</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%9C%EB%B0%95</t>
-  </si>
-  <si>
-    <t>373조 2967억 3028만</t>
-  </si>
-  <si>
-    <t>중탸치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A4%91%ED%83%B8%EC%B9%98</t>
-  </si>
-  <si>
-    <t>361조 9366억 5942만</t>
-  </si>
-  <si>
-    <t>옴짝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%B4%EC%A7%9D</t>
-  </si>
-  <si>
-    <t>267조 4873억 4322만</t>
-  </si>
-  <si>
-    <t>임승민</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EC%8A%B9%EB%AF%BC</t>
-  </si>
-  <si>
-    <t>216조 5819억 7929만</t>
-  </si>
-  <si>
-    <t>몬함</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%AC%ED%95%A8</t>
-  </si>
-  <si>
-    <t>213조 8180억 1111만</t>
-  </si>
-  <si>
-    <t>뻔수니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
-  </si>
-  <si>
-    <t>91조 5462억 5890만</t>
-  </si>
-  <si>
-    <t>하탸치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%83%B8%EC%B9%98</t>
-  </si>
-  <si>
-    <t>82조 2996억 4164만</t>
-  </si>
-  <si>
-    <t>26배털</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
-  </si>
-  <si>
-    <t>47조 8997억 9450만</t>
-  </si>
-  <si>
-    <t>쑤삔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%91%A4%EC%82%94</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>38조 6185억 6952만</t>
-  </si>
-  <si>
-    <t>류테</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%ED%85%8C</t>
-  </si>
-  <si>
-    <t>29조 4752억 2082만</t>
-  </si>
-  <si>
-    <t>메키무라딘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%ED%82%A4%EB%AC%B4%EB%9D%BC%EB%94%98</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>23조 1931억 726만</t>
-  </si>
-  <si>
-    <t>26퐝바</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%ED%90%9D%EB%B0%94</t>
-  </si>
-  <si>
-    <t>23조 1264억 4895만</t>
-  </si>
-  <si>
-    <t>브깃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B8%8C%EA%B9%83</t>
-  </si>
-  <si>
-    <t>21조 9533억 9367만</t>
-  </si>
-  <si>
-    <t>아모르파티퀘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
-  </si>
-  <si>
-    <t>21조 3943억 1549만</t>
-  </si>
-  <si>
-    <t>뻐늬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%90%EB%8A%AC</t>
-  </si>
-  <si>
-    <t>19조 728억 950만</t>
-  </si>
-  <si>
-    <t>26조선</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=26%EC%A1%B0%EC%84%A0</t>
-  </si>
-  <si>
-    <t>18조 1871억 4713만</t>
-  </si>
-  <si>
-    <t>뿜삐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
-  </si>
-  <si>
-    <t>17조 1902억 8827만</t>
-  </si>
-  <si>
-    <t>크앙레몬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EC%95%99%EB%A0%88%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>14조 4673억 9169만</t>
-  </si>
-  <si>
-    <t>최씨용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%94%A8%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>14조 623억 4943만</t>
-  </si>
-  <si>
-    <t>예라미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>8조 8509억 6783만</t>
-  </si>
-  <si>
-    <t>귬스파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%AC%EC%8A%A4%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>8조 3044억 7219만</t>
-  </si>
-  <si>
-    <t>고영희멈뭄미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%98%81%ED%9D%AC%EB%A9%88%EB%AD%84%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>6조 622억 6177만</t>
+    <t>13조 4223억 7723만</t>
   </si>
   <si>
     <t>코로드</t>
@@ -1466,22 +1457,22 @@
     <t>4719조 300억 9804만</t>
   </si>
   <si>
+    <t>빌린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>342조 6664억 8824만</t>
+  </si>
+  <si>
     <t>김해님</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%95%B4%EB%8B%98</t>
   </si>
   <si>
-    <t>248조 7671억 2085만</t>
-  </si>
-  <si>
-    <t>빌린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>245조 866억 4946만</t>
+    <t>249조 8430억 9289만</t>
   </si>
   <si>
     <t>Bit숍</t>
@@ -1490,7 +1481,7 @@
     <t>https://mgf.gg/contents/character.php?n=Bit%EC%88%8D</t>
   </si>
   <si>
-    <t>238조 3054억 5141만</t>
+    <t>238조 5426억 2824만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%85%9C%EC%9D%B4</t>
@@ -1499,6 +1490,15 @@
     <t>123조 5425억 2061만</t>
   </si>
   <si>
+    <t>산타선물</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%ED%83%80%EC%84%A0%EB%AC%BC</t>
+  </si>
+  <si>
+    <t>110조 8806억 7922만</t>
+  </si>
+  <si>
     <t>아마날</t>
   </si>
   <si>
@@ -1508,15 +1508,6 @@
     <t>109조 7611억 6219만</t>
   </si>
   <si>
-    <t>산타선물</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%ED%83%80%EC%84%A0%EB%AC%BC</t>
-  </si>
-  <si>
-    <t>101조 8868억 7437만</t>
-  </si>
-  <si>
     <t>도령3</t>
   </si>
   <si>
@@ -1541,7 +1532,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%9F%AC%EB%8A%94%EA%B1%B0%EC%95%84%EB%83%90</t>
   </si>
   <si>
-    <t>43조 5872억 3576만</t>
+    <t>43조 7380억 383만</t>
   </si>
   <si>
     <t>숮2</t>
@@ -1559,7 +1550,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%EC%97%84%EA%B2%BD</t>
   </si>
   <si>
-    <t>31조 4200억 5326만</t>
+    <t>32조 3727억 1625만</t>
   </si>
   <si>
     <t>키움맨</t>
@@ -1577,7 +1568,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%ED%94%84%EB%8B%98</t>
   </si>
   <si>
-    <t>22조 4947억 7204만</t>
+    <t>23조 9216억 4679만</t>
   </si>
   <si>
     <t>최소뎀</t>
@@ -1595,7 +1586,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EC%9C%A0%ED%99%94</t>
   </si>
   <si>
-    <t>19조 1742억 331만</t>
+    <t>19조 2110억 2748만</t>
   </si>
   <si>
     <t>95도도</t>
@@ -1622,7 +1613,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%88%EB%A7%88%EC%8B%A0</t>
   </si>
   <si>
-    <t>9조 5453억 6927만</t>
+    <t>9조 6595억 8976만</t>
   </si>
   <si>
     <t>숑당</t>
@@ -1652,7 +1643,25 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%A6%88</t>
   </si>
   <si>
-    <t>6조 3498억 1848만</t>
+    <t>6조 3688억 7001만</t>
+  </si>
+  <si>
+    <t>박하민린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%ED%95%98%EB%AF%BC%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>5조 6469억 2753만</t>
+  </si>
+  <si>
+    <t>군명</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EB%AA%85</t>
+  </si>
+  <si>
+    <t>5조 4353억 5588만</t>
   </si>
   <si>
     <t>장수흙침대</t>
@@ -1664,34 +1673,13 @@
     <t>5조 3176억 4154만</t>
   </si>
   <si>
-    <t>박하민린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%ED%95%98%EB%AF%BC%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>99</t>
-  </si>
-  <si>
-    <t>5조 3172억 8138만</t>
-  </si>
-  <si>
-    <t>군명</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EB%AA%85</t>
-  </si>
-  <si>
-    <t>5조 1644억 1414만</t>
-  </si>
-  <si>
     <t>김똔똔</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%98%94%EB%98%94</t>
   </si>
   <si>
-    <t>4조 4910억 4536만</t>
+    <t>5조 2710억 5768만</t>
   </si>
   <si>
     <t>니코짱</t>
@@ -2214,77 +2202,77 @@
         <v>32</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>38</v>
       </c>
       <c r="I4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="M4" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>49</v>
@@ -2296,48 +2284,48 @@
         <v>51</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="M6" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2373,28 +2361,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -2405,28 +2393,28 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="F2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -2437,28 +2425,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>80</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2469,28 +2457,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2501,28 +2489,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2533,28 +2521,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2565,28 +2553,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2597,28 +2585,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2629,28 +2617,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2661,28 +2649,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="I10" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2693,28 +2681,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2725,28 +2713,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2757,28 +2745,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2789,28 +2777,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2821,28 +2809,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2853,28 +2841,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2885,28 +2873,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="I17" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2917,28 +2905,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2949,28 +2937,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2981,28 +2969,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>159</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3013,28 +3001,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>163</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3045,28 +3033,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>47</v>
+        <v>161</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>166</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3077,28 +3065,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3109,28 +3097,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>175</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3141,28 +3129,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>178</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3173,28 +3161,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3205,28 +3193,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="I27" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3237,7 +3225,7 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>23</v>
@@ -3246,19 +3234,19 @@
         <v>23</v>
       </c>
       <c r="E28" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>191</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3269,28 +3257,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>195</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3301,28 +3289,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="H30" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3333,28 +3321,28 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>17</v>
+        <v>199</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>203</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -3418,28 +3406,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3450,31 +3438,31 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>206</v>
-      </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3482,7 +3470,7 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>32</v>
@@ -3491,22 +3479,22 @@
         <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3514,31 +3502,31 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>211</v>
-      </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3546,31 +3534,31 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>214</v>
-      </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3578,31 +3566,31 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>217</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3610,7 +3598,7 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>218</v>
@@ -3622,19 +3610,19 @@
         <v>219</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>220</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3642,7 +3630,7 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>221</v>
@@ -3654,19 +3642,19 @@
         <v>222</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>116</v>
+        <v>216</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>223</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -3674,7 +3662,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>224</v>
@@ -3686,19 +3674,19 @@
         <v>225</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>226</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -3706,7 +3694,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>227</v>
@@ -3718,19 +3706,19 @@
         <v>228</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>229</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -3738,7 +3726,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>230</v>
@@ -3750,19 +3738,19 @@
         <v>231</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>232</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -3770,7 +3758,7 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>233</v>
@@ -3782,19 +3770,19 @@
         <v>234</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>235</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -3802,7 +3790,7 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>236</v>
@@ -3814,19 +3802,19 @@
         <v>237</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>238</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -3834,7 +3822,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>239</v>
@@ -3846,19 +3834,19 @@
         <v>240</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>241</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -3866,7 +3854,7 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>242</v>
@@ -3878,19 +3866,19 @@
         <v>243</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>244</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -3898,7 +3886,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>245</v>
@@ -3910,19 +3898,19 @@
         <v>246</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>247</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -3930,7 +3918,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>248</v>
@@ -3942,19 +3930,19 @@
         <v>249</v>
       </c>
       <c r="F17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="H17" s="2" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>250</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -3962,7 +3950,7 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>251</v>
@@ -3974,19 +3962,19 @@
         <v>252</v>
       </c>
       <c r="F18" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="H18" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>253</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -3994,7 +3982,7 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>254</v>
@@ -4006,19 +3994,19 @@
         <v>255</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>121</v>
+        <v>216</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>256</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -4026,7 +4014,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>257</v>
@@ -4038,19 +4026,19 @@
         <v>258</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>259</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -4058,7 +4046,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>260</v>
@@ -4070,19 +4058,19 @@
         <v>261</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="H21" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -4090,31 +4078,31 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>47</v>
+        <v>161</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="H22" s="2" t="s">
-        <v>121</v>
+        <v>175</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>266</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -4122,7 +4110,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>267</v>
@@ -4134,19 +4122,19 @@
         <v>268</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>269</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -4154,7 +4142,7 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>270</v>
@@ -4166,19 +4154,19 @@
         <v>271</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>272</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -4186,7 +4174,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>273</v>
@@ -4198,19 +4186,19 @@
         <v>274</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>275</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -4218,7 +4206,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>276</v>
@@ -4230,19 +4218,19 @@
         <v>277</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>278</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -4250,7 +4238,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>279</v>
@@ -4262,19 +4250,19 @@
         <v>280</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>281</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -4282,7 +4270,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>282</v>
@@ -4294,19 +4282,19 @@
         <v>283</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>284</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -4314,7 +4302,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>285</v>
@@ -4326,19 +4314,19 @@
         <v>286</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>287</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -4346,7 +4334,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>288</v>
@@ -4358,19 +4346,19 @@
         <v>289</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>290</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -4378,7 +4366,7 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>17</v>
+        <v>199</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>291</v>
@@ -4390,19 +4378,19 @@
         <v>292</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>293</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -4445,984 +4433,6 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J29"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
-    <hyperlink ref="E20" r:id="rId19"/>
-    <hyperlink ref="E21" r:id="rId20"/>
-    <hyperlink ref="E22" r:id="rId21"/>
-    <hyperlink ref="E23" r:id="rId22"/>
-    <hyperlink ref="E24" r:id="rId23"/>
-    <hyperlink ref="E25" r:id="rId24"/>
-    <hyperlink ref="E26" r:id="rId25"/>
-    <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -5441,28 +4451,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -5470,962 +4480,962 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>378</v>
+        <v>294</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>378</v>
+        <v>294</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>379</v>
+        <v>295</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>380</v>
+        <v>296</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>381</v>
+        <v>297</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>382</v>
+        <v>298</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>383</v>
+        <v>300</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>384</v>
+        <v>301</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>384</v>
+        <v>301</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>385</v>
+        <v>302</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>386</v>
+        <v>303</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>387</v>
+        <v>304</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>387</v>
+        <v>304</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>388</v>
+        <v>305</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>111</v>
+        <v>216</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>389</v>
+        <v>306</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>390</v>
+        <v>307</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>390</v>
+        <v>307</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>391</v>
+        <v>308</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>111</v>
+        <v>216</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>392</v>
+        <v>309</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>393</v>
+        <v>310</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>393</v>
+        <v>310</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>394</v>
+        <v>311</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>111</v>
+        <v>216</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>395</v>
+        <v>312</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>396</v>
+        <v>313</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>396</v>
+        <v>313</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>397</v>
+        <v>314</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>111</v>
+        <v>216</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>398</v>
+        <v>315</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>399</v>
+        <v>316</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>399</v>
+        <v>316</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>400</v>
+        <v>317</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>111</v>
+        <v>216</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>401</v>
+        <v>318</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>402</v>
+        <v>319</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>402</v>
+        <v>319</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>403</v>
+        <v>320</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>111</v>
+        <v>216</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>404</v>
+        <v>321</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>405</v>
+        <v>322</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>405</v>
+        <v>322</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>406</v>
+        <v>323</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>116</v>
+        <v>216</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>407</v>
+        <v>324</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>408</v>
+        <v>325</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>408</v>
+        <v>325</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>409</v>
+        <v>326</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>410</v>
+        <v>327</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>411</v>
+        <v>328</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>411</v>
+        <v>328</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>412</v>
+        <v>329</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>95</v>
+        <v>197</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>413</v>
+        <v>330</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>414</v>
+        <v>331</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>414</v>
+        <v>331</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>415</v>
+        <v>332</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>199</v>
+        <v>93</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>116</v>
+        <v>216</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>416</v>
+        <v>333</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>417</v>
+        <v>334</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>417</v>
+        <v>334</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>418</v>
+        <v>335</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>419</v>
+        <v>336</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>420</v>
+        <v>337</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>420</v>
+        <v>337</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>421</v>
+        <v>338</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>422</v>
+        <v>339</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>423</v>
+        <v>340</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>423</v>
+        <v>340</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>424</v>
+        <v>341</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>425</v>
+        <v>342</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>426</v>
+        <v>343</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>426</v>
+        <v>343</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>427</v>
+        <v>344</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>428</v>
+        <v>345</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>429</v>
+        <v>346</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>430</v>
+        <v>347</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>430</v>
+        <v>347</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>431</v>
+        <v>348</v>
       </c>
       <c r="F19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="H19" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>432</v>
+        <v>349</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>433</v>
+        <v>350</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>433</v>
+        <v>350</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>434</v>
+        <v>351</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>435</v>
+        <v>352</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>436</v>
+        <v>353</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>437</v>
+        <v>354</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>437</v>
+        <v>354</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>438</v>
+        <v>355</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>439</v>
+        <v>356</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>47</v>
+        <v>161</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>440</v>
+        <v>357</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>440</v>
+        <v>357</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>441</v>
+        <v>358</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>442</v>
+        <v>359</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>443</v>
+        <v>360</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>443</v>
+        <v>360</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>444</v>
+        <v>361</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>445</v>
+        <v>362</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>446</v>
+        <v>363</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>446</v>
+        <v>363</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>447</v>
+        <v>364</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>448</v>
+        <v>365</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>449</v>
+        <v>366</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>449</v>
+        <v>366</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>450</v>
+        <v>367</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>451</v>
+        <v>368</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>452</v>
+        <v>369</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>452</v>
+        <v>369</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>453</v>
+        <v>370</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>435</v>
+        <v>184</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>454</v>
+        <v>371</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>455</v>
+        <v>372</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>455</v>
+        <v>372</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>456</v>
+        <v>373</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>457</v>
+        <v>374</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>458</v>
+        <v>375</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>458</v>
+        <v>375</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>459</v>
+        <v>376</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>460</v>
+        <v>377</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>461</v>
+        <v>378</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>461</v>
+        <v>378</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>462</v>
+        <v>379</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>435</v>
+        <v>352</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>463</v>
+        <v>380</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>464</v>
+        <v>381</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>464</v>
+        <v>381</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>465</v>
+        <v>382</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>435</v>
+        <v>352</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>466</v>
+        <v>383</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>17</v>
+        <v>199</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>467</v>
+        <v>384</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>467</v>
+        <v>384</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>468</v>
+        <v>385</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>435</v>
+        <v>352</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>469</v>
+        <v>386</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -6466,6 +5476,951 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J28"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
@@ -6486,28 +6441,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -6515,962 +6470,962 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>380</v>
+        <v>296</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>111</v>
+        <v>216</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>428</v>
+        <v>345</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>435</v>
+        <v>352</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>435</v>
+        <v>352</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>435</v>
+        <v>352</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="F21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="H21" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>47</v>
+        <v>161</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>435</v>
+        <v>352</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>535</v>
-      </c>
       <c r="J23" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>95</v>
+        <v>345</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="F27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>428</v>
-      </c>
       <c r="H27" s="2" t="s">
-        <v>547</v>
+        <v>531</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="H28" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="I28" s="2" t="s">
-        <v>551</v>
-      </c>
       <c r="J28" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>547</v>
+        <v>531</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>17</v>
+        <v>199</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -425,7 +425,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
   </si>
   <si>
-    <t>163조 5754억 4231만</t>
+    <t>179조 9670억 2979만</t>
   </si>
   <si>
     <t>14</t>
@@ -503,6 +503,18 @@
     <t>65조 7697억 3285만</t>
   </si>
   <si>
+    <t>두근푸근연근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>52조 9036억 6306만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
     <t>할룽</t>
   </si>
   <si>
@@ -512,18 +524,6 @@
     <t>51조 5399억 1217만</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>두근푸근연근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>49조 4912억 6649만</t>
-  </si>
-  <si>
     <t>22</t>
   </si>
   <si>
@@ -1214,7 +1214,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EA%B9%8C%EB%B0%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>1798조 5637억 671만</t>
+    <t>1801조 6798억 5398만</t>
   </si>
   <si>
     <t>KR#18TIDK8BQ6</t>
@@ -1223,7 +1223,7 @@
     <t>https://mgf.gg/contents/character.php?n=KR%2318TIDK8BQ6</t>
   </si>
   <si>
-    <t>1282조 7229억 6678만</t>
+    <t>1287조 1522억 572만</t>
   </si>
   <si>
     <t>팝중이</t>
@@ -1295,7 +1295,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%B0%94</t>
   </si>
   <si>
-    <t>116조 9612억 5982만</t>
+    <t>117조 9202만</t>
   </si>
   <si>
     <t>리세라</t>
@@ -1418,7 +1418,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%A7%81%EB%AF%B8%EB%85%80</t>
   </si>
   <si>
-    <t>16조 4197억 1188만</t>
+    <t>16조 7230억 5913만</t>
   </si>
   <si>
     <t>별득</t>
@@ -1427,7 +1427,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%93%9D</t>
   </si>
   <si>
-    <t>13조 4223억 7723만</t>
+    <t>13조 4859억 5413만</t>
   </si>
   <si>
     <t>코로드</t>
@@ -1541,7 +1541,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%AE2</t>
   </si>
   <si>
-    <t>32조 9705억 5239만</t>
+    <t>34조 3682억 1143만</t>
   </si>
   <si>
     <t>백엄경</t>
@@ -1580,6 +1580,15 @@
     <t>22조 2347억 2935만</t>
   </si>
   <si>
+    <t>95도도</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=95%EB%8F%84%EB%8F%84</t>
+  </si>
+  <si>
+    <t>19조 4756억 6791만</t>
+  </si>
+  <si>
     <t>한유화</t>
   </si>
   <si>
@@ -1589,15 +1598,6 @@
     <t>19조 2110억 2748만</t>
   </si>
   <si>
-    <t>95도도</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=95%EB%8F%84%EB%8F%84</t>
-  </si>
-  <si>
-    <t>18조 9214억 6765만</t>
-  </si>
-  <si>
     <t>천칸</t>
   </si>
   <si>
@@ -1652,7 +1652,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%ED%95%98%EB%AF%BC%EB%A6%B0</t>
   </si>
   <si>
-    <t>5조 6469억 2753만</t>
+    <t>6조 609억 8475만</t>
   </si>
   <si>
     <t>군명</t>
@@ -1691,7 +1691,7 @@
     <t>98</t>
   </si>
   <si>
-    <t>3조 2634억 9108만</t>
+    <t>3조 2714억 3896만</t>
   </si>
   <si>
     <t>뉴맹우</t>
@@ -3016,7 +3016,7 @@
         <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>144</v>
@@ -3048,7 +3048,7 @@
         <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>144</v>
@@ -6377,7 +6377,7 @@
         <v>99</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>466</v>
@@ -7032,10 +7032,10 @@
         <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>352</v>
+        <v>184</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>519</v>
@@ -7064,10 +7064,10 @@
         <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>184</v>
+        <v>352</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>522</v>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -179,7 +179,7 @@
     <t>2경 340조 9927억 1769만</t>
   </si>
   <si>
-    <t>가입문의 : 리세라, 별뿡</t>
+    <t>토벌전 30만점이상 가입문의 : 리세라, 별뿡</t>
   </si>
   <si>
     <t>별뿡</t>
@@ -245,7 +245,7 @@
     <t>신궁</t>
   </si>
   <si>
-    <t>113</t>
+    <t>114</t>
   </si>
   <si>
     <t>1경 720조 3865억 2152만</t>
@@ -314,7 +314,7 @@
     <t>109</t>
   </si>
   <si>
-    <t>1540조 3596억 8447만</t>
+    <t>1549조 1560억 6234만</t>
   </si>
   <si>
     <t>6</t>
@@ -371,48 +371,51 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
   </si>
   <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>348조 1289억 3205만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>부엉이없다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>257조 1107억 752만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>228조 665억 3930만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
     <t>106</t>
   </si>
   <si>
-    <t>348조 1289억 3205만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>니달리신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>228조 665억 3930만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>부엉이없다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>225조 316억 7503만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
     <t>213조 2895억 1154만</t>
   </si>
   <si>
@@ -437,7 +440,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
   </si>
   <si>
-    <t>143조 6668억 6475만</t>
+    <t>144조 1150억 6923만</t>
   </si>
   <si>
     <t>15</t>
@@ -449,7 +452,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
   </si>
   <si>
-    <t>114조 2396억 3369만</t>
+    <t>114조 4296억 9140만</t>
   </si>
   <si>
     <t>16</t>
@@ -464,36 +467,45 @@
     <t>104</t>
   </si>
   <si>
-    <t>101조 6267억 648만</t>
+    <t>102조 7914억 2403만</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>96조 8446억 9775만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
     <t>잼포즈</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
   </si>
   <si>
-    <t>88조 9672억 2946만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>88조 6379억 49만</t>
+    <t>89조 3419억 3056만</t>
   </si>
   <si>
     <t>19</t>
   </si>
   <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>87조 8872억 604만</t>
+  </si>
+  <si>
     <t>POSCO</t>
   </si>
   <si>
@@ -503,37 +515,28 @@
     <t>65조 7697억 3285만</t>
   </si>
   <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>53조 5004억 3815만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>두근푸근연근</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
   </si>
   <si>
-    <t>52조 9036억 6306만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>51조 5399억 1217만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>46조 8231억 8034만</t>
+    <t>53조 4067억 7706만</t>
   </si>
   <si>
     <t>23</t>
@@ -557,7 +560,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>39조 1111억 1972만</t>
+    <t>39조 6669억 6476만</t>
   </si>
   <si>
     <t>25</t>
@@ -569,7 +572,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
   </si>
   <si>
-    <t>38조 1459억 7981만</t>
+    <t>38조 1924억 9359만</t>
   </si>
   <si>
     <t>26</t>
@@ -602,6 +605,21 @@
     <t>28</t>
   </si>
   <si>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>35조 5257억 7876만</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
     <t>대방어조아</t>
   </si>
   <si>
@@ -611,21 +629,6 @@
     <t>34조 8711억 1818만</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>33조 231억 7698만</t>
-  </si>
-  <si>
     <t>30</t>
   </si>
   <si>
@@ -668,7 +671,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EC%88%98%EB%A7%81</t>
   </si>
   <si>
-    <t>974조 1557억 8886만</t>
+    <t>1030조 7359억 4917만</t>
   </si>
   <si>
     <t>별빛링</t>
@@ -677,9 +680,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%B9%9B%EB%A7%81</t>
   </si>
   <si>
-    <t>107</t>
-  </si>
-  <si>
     <t>654조 4196억 2809만</t>
   </si>
   <si>
@@ -716,7 +716,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%A1%EB%B3%B4%EB%A7%81</t>
   </si>
   <si>
-    <t>428조 3475억 7694만</t>
+    <t>438조 7038억 8562만</t>
   </si>
   <si>
     <t>츄르링</t>
@@ -743,7 +743,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%8D%EB%95%8C%EB%A7%81</t>
   </si>
   <si>
-    <t>305조 6567억 7447만</t>
+    <t>341조 3188억 7509만</t>
   </si>
   <si>
     <t>콕끼링</t>
@@ -752,7 +752,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%95%EB%81%BC%EB%A7%81</t>
   </si>
   <si>
-    <t>290조 310억 9845만</t>
+    <t>313조 2692억 7284만</t>
   </si>
   <si>
     <t>도트링</t>
@@ -761,7 +761,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%ED%8A%B8%EB%A7%81</t>
   </si>
   <si>
-    <t>258조 3577억 202만</t>
+    <t>310조 96억 2617만</t>
+  </si>
+  <si>
+    <t>시러링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%9F%AC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>264조 4368억 5111만</t>
   </si>
   <si>
     <t>드릴링</t>
@@ -770,16 +779,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%93%9C%EB%A6%B4%EB%A7%81</t>
   </si>
   <si>
-    <t>246조 5252억 2296만</t>
-  </si>
-  <si>
-    <t>시러링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%9F%AC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>239조 6714억 5917만</t>
+    <t>247조 8703억 6870만</t>
   </si>
   <si>
     <t>모꼬링</t>
@@ -797,7 +797,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%87%8C%EB%A7%81</t>
   </si>
   <si>
-    <t>184조 7592억 4334만</t>
+    <t>188조 947억 9928만</t>
   </si>
   <si>
     <t>엠오링</t>
@@ -806,7 +806,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%A0%EC%98%A4%EB%A7%81</t>
   </si>
   <si>
-    <t>144조 5807억 9489만</t>
+    <t>145조 2410억 4832만</t>
   </si>
   <si>
     <t>해오링</t>
@@ -815,7 +815,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%98%A4%EB%A7%81</t>
   </si>
   <si>
-    <t>99조 7603억 9766만</t>
+    <t>101조 3773억 307만</t>
   </si>
   <si>
     <t>푸르링</t>
@@ -836,7 +836,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%8D%B8%EB%A7%81</t>
   </si>
   <si>
-    <t>91조 6914억 7173만</t>
+    <t>94조 7846억 4053만</t>
   </si>
   <si>
     <t>커포링</t>
@@ -854,7 +854,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%A0%EC%83%98%EB%A7%81</t>
   </si>
   <si>
-    <t>72조 8806억 8203만</t>
+    <t>74조 9123억 7087만</t>
   </si>
   <si>
     <t>싸가링</t>
@@ -863,7 +863,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%EA%B0%80%EB%A7%81</t>
   </si>
   <si>
-    <t>66조 5279억 9387만</t>
+    <t>70조 6764억 2154만</t>
   </si>
   <si>
     <t>대가링</t>
@@ -893,6 +893,15 @@
     <t>50조 1653억 6801만</t>
   </si>
   <si>
+    <t>링가링가링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%81%EA%B0%80%EB%A7%81%EA%B0%80%EB%A7%81</t>
+  </si>
+  <si>
+    <t>39조 4173억 8686만</t>
+  </si>
+  <si>
     <t>펭구링</t>
   </si>
   <si>
@@ -902,15 +911,6 @@
     <t>38조 5985억 7538만</t>
   </si>
   <si>
-    <t>링가링가링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%81%EA%B0%80%EB%A7%81%EA%B0%80%EB%A7%81</t>
-  </si>
-  <si>
-    <t>37조 7119억 3674만</t>
-  </si>
-  <si>
     <t>가숭혁</t>
   </si>
   <si>
@@ -938,7 +938,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%ED%83%B8%EC%B9%98</t>
   </si>
   <si>
-    <t>1974조 233억 937만</t>
+    <t>1980조 6362억 7930만</t>
   </si>
   <si>
     <t>달싹</t>
@@ -956,7 +956,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%9A%B0%EC%9D%B4</t>
   </si>
   <si>
-    <t>525조 431억 8929만</t>
+    <t>610조 7151억 5119만</t>
   </si>
   <si>
     <t>서예슬</t>
@@ -965,7 +965,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%98%88%EC%8A%AC</t>
   </si>
   <si>
-    <t>519조 4897억 3481만</t>
+    <t>555조 8163억 1781만</t>
+  </si>
+  <si>
+    <t>중탸치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A4%91%ED%83%B8%EC%B9%98</t>
+  </si>
+  <si>
+    <t>537조 9392억 417만</t>
   </si>
   <si>
     <t>26길초</t>
@@ -974,7 +983,16 @@
     <t>https://mgf.gg/contents/character.php?n=26%EA%B8%B8%EC%B4%88</t>
   </si>
   <si>
-    <t>484조 5861억 9002만</t>
+    <t>484조 8510억 4884만</t>
+  </si>
+  <si>
+    <t>옴짝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%B4%EC%A7%9D</t>
+  </si>
+  <si>
+    <t>481조 1298억 3265만</t>
   </si>
   <si>
     <t>뇌쉬</t>
@@ -986,15 +1004,6 @@
     <t>477조 6715억 7462만</t>
   </si>
   <si>
-    <t>옴짝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%B4%EC%A7%9D</t>
-  </si>
-  <si>
-    <t>404조 9826억 7892만</t>
-  </si>
-  <si>
     <t>덜박</t>
   </si>
   <si>
@@ -1004,15 +1013,6 @@
     <t>373조 2967억 3028만</t>
   </si>
   <si>
-    <t>중탸치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A4%91%ED%83%B8%EC%B9%98</t>
-  </si>
-  <si>
-    <t>370조 6979억 9727만</t>
-  </si>
-  <si>
     <t>몬함</t>
   </si>
   <si>
@@ -1037,7 +1037,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%94%EC%88%98%EB%8B%88</t>
   </si>
   <si>
-    <t>92조 27억 6340만</t>
+    <t>109조 531억 9126만</t>
   </si>
   <si>
     <t>하탸치</t>
@@ -1049,25 +1049,25 @@
     <t>82조 2996억 4164만</t>
   </si>
   <si>
+    <t>쑤삔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%91%A4%EC%82%94</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>52조 5398억 4286만</t>
+  </si>
+  <si>
     <t>26배털</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=26%EB%B0%B0%ED%84%B8</t>
   </si>
   <si>
-    <t>48조 129억 4261만</t>
-  </si>
-  <si>
-    <t>쑤삔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%91%A4%EC%82%94</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>41조 3143억 1479만</t>
+    <t>48조 3657억 8560만</t>
   </si>
   <si>
     <t>류테</t>
@@ -1100,6 +1100,15 @@
     <t>23조 1264억 4895만</t>
   </si>
   <si>
+    <t>아모르파티퀘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
+  </si>
+  <si>
+    <t>22조 8461억 2869만</t>
+  </si>
+  <si>
     <t>브깃</t>
   </si>
   <si>
@@ -1109,13 +1118,13 @@
     <t>21조 9533억 9367만</t>
   </si>
   <si>
-    <t>아모르파티퀘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AA%A8%EB%A5%B4%ED%8C%8C%ED%8B%B0%ED%80%98</t>
-  </si>
-  <si>
-    <t>21조 4013억 3703만</t>
+    <t>뿜삐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
+  </si>
+  <si>
+    <t>20조 5223억 8240만</t>
   </si>
   <si>
     <t>뻐늬</t>
@@ -1136,15 +1145,6 @@
     <t>18조 1871억 4713만</t>
   </si>
   <si>
-    <t>뿜삐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%9C%EC%82%90</t>
-  </si>
-  <si>
-    <t>18조 734억 9249만</t>
-  </si>
-  <si>
     <t>크앙레몬</t>
   </si>
   <si>
@@ -1169,7 +1169,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%9D%BC%EB%AF%B8</t>
   </si>
   <si>
-    <t>9조 832억 341만</t>
+    <t>9조 2773억 9881만</t>
   </si>
   <si>
     <t>귬스파파</t>
@@ -1187,7 +1187,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%98%81%ED%9D%AC%EB%A9%88%EB%AD%84%EB%AF%B8</t>
   </si>
   <si>
-    <t>6조 754억 4971만</t>
+    <t>6조 1706억 6032만</t>
   </si>
   <si>
     <t>별뽕</t>
@@ -1196,7 +1196,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%BD%95</t>
   </si>
   <si>
-    <t>7359조 4642억 6598만</t>
+    <t>7373조 8847억 4579만</t>
   </si>
   <si>
     <t>도얍스</t>
@@ -1214,7 +1214,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EA%B9%8C%EB%B0%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>1801조 6798억 5398만</t>
+    <t>1965조 3632억 9845만</t>
   </si>
   <si>
     <t>KR#18TIDK8BQ6</t>
@@ -1223,7 +1223,7 @@
     <t>https://mgf.gg/contents/character.php?n=KR%2318TIDK8BQ6</t>
   </si>
   <si>
-    <t>1287조 1522억 572만</t>
+    <t>1376조 2063억 7369만</t>
   </si>
   <si>
     <t>팝중이</t>
@@ -1286,7 +1286,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%ED%92%8D%EC%A1%B1</t>
   </si>
   <si>
-    <t>136조 3672억 6965만</t>
+    <t>137조 853억 8352만</t>
   </si>
   <si>
     <t>안바</t>
@@ -1295,7 +1295,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%B0%94</t>
   </si>
   <si>
-    <t>117조 9202만</t>
+    <t>124조 351억 8200만</t>
   </si>
   <si>
     <t>리세라</t>
@@ -1319,7 +1319,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%BF%A1</t>
   </si>
   <si>
-    <t>103조 2646억 5103만</t>
+    <t>103조 5428억 7584만</t>
   </si>
   <si>
     <t>동키링</t>
@@ -1328,7 +1328,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%ED%82%A4%EB%A7%81</t>
   </si>
   <si>
-    <t>79조 7638억 7763만</t>
+    <t>80조 1597억 1019만</t>
   </si>
   <si>
     <t>재기리</t>
@@ -1337,7 +1337,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%AC%EA%B8%B0%EB%A6%AC</t>
   </si>
   <si>
-    <t>73조 6223억 4894만</t>
+    <t>77조 1363억 9626만</t>
   </si>
   <si>
     <t>검환</t>
@@ -1355,7 +1355,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%97%B4%EB%8C%80</t>
   </si>
   <si>
-    <t>63조 7990억 8998만</t>
+    <t>64조 6041억 3384만</t>
   </si>
   <si>
     <t>혀로우기</t>
@@ -1367,6 +1367,15 @@
     <t>59조 1098억 6203만</t>
   </si>
   <si>
+    <t>공격느림</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EA%B2%A9%EB%8A%90%EB%A6%BC</t>
+  </si>
+  <si>
+    <t>56조 7353억 7041만</t>
+  </si>
+  <si>
     <t>기데</t>
   </si>
   <si>
@@ -1376,15 +1385,6 @@
     <t>53조 7549억 8799만</t>
   </si>
   <si>
-    <t>공격느림</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EA%B2%A9%EB%8A%90%EB%A6%BC</t>
-  </si>
-  <si>
-    <t>52조 1885억 3384만</t>
-  </si>
-  <si>
     <t>별빛낭만</t>
   </si>
   <si>
@@ -1409,7 +1409,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%97%88%EC%9D%B4%EB%8B%A4</t>
   </si>
   <si>
-    <t>36조 6805억 691만</t>
+    <t>39조 6126억 9189만</t>
   </si>
   <si>
     <t>전직미녀</t>
@@ -1418,7 +1418,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%A7%81%EB%AF%B8%EB%85%80</t>
   </si>
   <si>
-    <t>16조 7230억 5913만</t>
+    <t>17조 461억 1670만</t>
   </si>
   <si>
     <t>별득</t>
@@ -1427,7 +1427,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%93%9D</t>
   </si>
   <si>
-    <t>13조 4859억 5413만</t>
+    <t>13조 8214억 1652만</t>
   </si>
   <si>
     <t>코로드</t>
@@ -1445,7 +1445,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A8%EB%85%80</t>
   </si>
   <si>
-    <t>4870조 771억 3004만</t>
+    <t>5125조 4520억 7374만</t>
   </si>
   <si>
     <t>맠스맨</t>
@@ -1472,7 +1472,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%95%B4%EB%8B%98</t>
   </si>
   <si>
-    <t>249조 8430억 9289만</t>
+    <t>252조 1274억 668만</t>
   </si>
   <si>
     <t>Bit숍</t>
@@ -1481,7 +1481,7 @@
     <t>https://mgf.gg/contents/character.php?n=Bit%EC%88%8D</t>
   </si>
   <si>
-    <t>238조 5426억 2824만</t>
+    <t>239조 1837억 6769만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%85%9C%EC%9D%B4</t>
@@ -1490,22 +1490,22 @@
     <t>123조 5425억 2061만</t>
   </si>
   <si>
+    <t>아마날</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A7%88%EB%82%A0</t>
+  </si>
+  <si>
+    <t>113조 9353억 3723만</t>
+  </si>
+  <si>
     <t>산타선물</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%82%B0%ED%83%80%EC%84%A0%EB%AC%BC</t>
   </si>
   <si>
-    <t>110조 8806억 7922만</t>
-  </si>
-  <si>
-    <t>아마날</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A7%88%EB%82%A0</t>
-  </si>
-  <si>
-    <t>109조 7611억 6219만</t>
+    <t>113조 4804억 941만</t>
   </si>
   <si>
     <t>도령3</t>
@@ -1532,7 +1532,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%9F%AC%EB%8A%94%EA%B1%B0%EC%95%84%EB%83%90</t>
   </si>
   <si>
-    <t>43조 7380억 383만</t>
+    <t>44조 8798억 3985만</t>
   </si>
   <si>
     <t>숮2</t>
@@ -1553,6 +1553,15 @@
     <t>32조 3727억 1625만</t>
   </si>
   <si>
+    <t>시프님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%ED%94%84%EB%8B%98</t>
+  </si>
+  <si>
+    <t>25조 8406억 5137만</t>
+  </si>
+  <si>
     <t>키움맨</t>
   </si>
   <si>
@@ -1562,15 +1571,6 @@
     <t>24조 258억 2609만</t>
   </si>
   <si>
-    <t>시프님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%ED%94%84%EB%8B%98</t>
-  </si>
-  <si>
-    <t>23조 9216억 4679만</t>
-  </si>
-  <si>
     <t>최소뎀</t>
   </si>
   <si>
@@ -1586,7 +1586,7 @@
     <t>https://mgf.gg/contents/character.php?n=95%EB%8F%84%EB%8F%84</t>
   </si>
   <si>
-    <t>19조 4756억 6791만</t>
+    <t>20조 6589억 3669만</t>
   </si>
   <si>
     <t>한유화</t>
@@ -1595,7 +1595,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EC%9C%A0%ED%99%94</t>
   </si>
   <si>
-    <t>19조 2110억 2748만</t>
+    <t>19조 3767억 3870만</t>
   </si>
   <si>
     <t>천칸</t>
@@ -1613,7 +1613,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%88%EB%A7%88%EC%8B%A0</t>
   </si>
   <si>
-    <t>9조 6595억 8976만</t>
+    <t>9조 8844억 3317만</t>
   </si>
   <si>
     <t>숑당</t>
@@ -1637,22 +1637,22 @@
     <t>8조 9539억 7333만</t>
   </si>
   <si>
+    <t>박하민린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%ED%95%98%EB%AF%BC%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>6조 7647억 6987만</t>
+  </si>
+  <si>
     <t>현즈</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%84%EC%A6%88</t>
   </si>
   <si>
-    <t>6조 3688억 7001만</t>
-  </si>
-  <si>
-    <t>박하민린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%ED%95%98%EB%AF%BC%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>6조 609억 8475만</t>
+    <t>6조 4248억 3691만</t>
   </si>
   <si>
     <t>군명</t>
@@ -1661,7 +1661,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EB%AA%85</t>
   </si>
   <si>
-    <t>5조 4353억 5588만</t>
+    <t>5조 9236억 759만</t>
   </si>
   <si>
     <t>장수흙침대</t>
@@ -1691,7 +1691,7 @@
     <t>98</t>
   </si>
   <si>
-    <t>3조 2714억 3896만</t>
+    <t>3조 4359억 236만</t>
   </si>
   <si>
     <t>뉴맹우</t>
@@ -1703,7 +1703,7 @@
     <t>97</t>
   </si>
   <si>
-    <t>1조 3283억 3290만</t>
+    <t>1조 3580억 6833만</t>
   </si>
 </sst>
 </file>
@@ -2696,7 +2696,7 @@
         <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>119</v>
@@ -2728,7 +2728,7 @@
         <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>119</v>
@@ -2763,10 +2763,10 @@
         <v>71</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2777,16 +2777,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>70</v>
@@ -2795,10 +2795,10 @@
         <v>93</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2809,16 +2809,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>70</v>
@@ -2827,10 +2827,10 @@
         <v>88</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2841,16 +2841,16 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>70</v>
@@ -2859,10 +2859,10 @@
         <v>93</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2873,16 +2873,16 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>70</v>
@@ -2891,10 +2891,10 @@
         <v>93</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2905,28 +2905,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2937,28 +2937,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2969,28 +2969,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>119</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3004,25 +3004,25 @@
         <v>55</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3033,28 +3033,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3065,28 +3065,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3097,16 +3097,16 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>70</v>
@@ -3115,10 +3115,10 @@
         <v>77</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3132,13 +3132,13 @@
         <v>37</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>70</v>
@@ -3147,10 +3147,10 @@
         <v>77</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3161,16 +3161,16 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>70</v>
@@ -3179,10 +3179,10 @@
         <v>88</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3193,16 +3193,16 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>70</v>
@@ -3211,10 +3211,10 @@
         <v>71</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3225,7 +3225,7 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>23</v>
@@ -3234,19 +3234,19 @@
         <v>23</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>77</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3257,28 +3257,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>93</v>
+        <v>194</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3289,28 +3289,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>197</v>
+        <v>93</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3321,16 +3321,16 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>70</v>
@@ -3339,10 +3339,10 @@
         <v>104</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -3441,13 +3441,13 @@
         <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>70</v>
@@ -3459,7 +3459,7 @@
         <v>78</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>33</v>
@@ -3479,19 +3479,19 @@
         <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>93</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>33</v>
@@ -3505,13 +3505,13 @@
         <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>70</v>
@@ -3523,7 +3523,7 @@
         <v>105</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>33</v>
@@ -3537,13 +3537,13 @@
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>70</v>
@@ -3552,10 +3552,10 @@
         <v>88</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>33</v>
@@ -3569,22 +3569,22 @@
         <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>216</v>
+        <v>114</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>217</v>
@@ -3616,7 +3616,7 @@
         <v>104</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>220</v>
@@ -3648,7 +3648,7 @@
         <v>83</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>216</v>
+        <v>114</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>223</v>
@@ -3744,7 +3744,7 @@
         <v>77</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>232</v>
@@ -3776,7 +3776,7 @@
         <v>77</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>235</v>
@@ -3822,7 +3822,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>239</v>
@@ -3854,7 +3854,7 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>242</v>
@@ -3869,10 +3869,10 @@
         <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>244</v>
@@ -3886,7 +3886,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>245</v>
@@ -3901,7 +3901,7 @@
         <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>119</v>
@@ -3918,7 +3918,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>248</v>
@@ -3933,10 +3933,10 @@
         <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>250</v>
@@ -3950,7 +3950,7 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>251</v>
@@ -3982,7 +3982,7 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>254</v>
@@ -4000,7 +4000,7 @@
         <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>216</v>
+        <v>114</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>256</v>
@@ -4014,7 +4014,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>257</v>
@@ -4078,7 +4078,7 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>263</v>
@@ -4096,7 +4096,7 @@
         <v>265</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>266</v>
@@ -4110,7 +4110,7 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>267</v>
@@ -4128,7 +4128,7 @@
         <v>88</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>269</v>
@@ -4142,7 +4142,7 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>270</v>
@@ -4160,7 +4160,7 @@
         <v>88</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>272</v>
@@ -4206,7 +4206,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>276</v>
@@ -4224,7 +4224,7 @@
         <v>77</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>278</v>
@@ -4238,7 +4238,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>279</v>
@@ -4253,10 +4253,10 @@
         <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>281</v>
@@ -4270,7 +4270,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>282</v>
@@ -4288,7 +4288,7 @@
         <v>83</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>284</v>
@@ -4302,7 +4302,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>285</v>
@@ -4320,7 +4320,7 @@
         <v>88</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>287</v>
@@ -4334,7 +4334,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>288</v>
@@ -4352,7 +4352,7 @@
         <v>77</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>290</v>
@@ -4366,7 +4366,7 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>291</v>
@@ -4384,7 +4384,7 @@
         <v>77</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>293</v>
@@ -4527,7 +4527,7 @@
         <v>298</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>83</v>
@@ -4597,7 +4597,7 @@
         <v>93</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>216</v>
+        <v>114</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>306</v>
@@ -4629,7 +4629,7 @@
         <v>71</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>216</v>
+        <v>114</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>309</v>
@@ -4661,7 +4661,7 @@
         <v>77</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>216</v>
+        <v>105</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>312</v>
@@ -4690,10 +4690,10 @@
         <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>216</v>
+        <v>128</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>315</v>
@@ -4722,10 +4722,10 @@
         <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>216</v>
+        <v>114</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>318</v>
@@ -4757,7 +4757,7 @@
         <v>77</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>216</v>
+        <v>114</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>321</v>
@@ -4786,10 +4786,10 @@
         <v>70</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>216</v>
+        <v>114</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>324</v>
@@ -4818,7 +4818,7 @@
         <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>114</v>
@@ -4850,10 +4850,10 @@
         <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>330</v>
@@ -4867,7 +4867,7 @@
         <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>331</v>
@@ -4885,7 +4885,7 @@
         <v>93</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>216</v>
+        <v>114</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>333</v>
@@ -4899,7 +4899,7 @@
         <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>334</v>
@@ -4917,7 +4917,7 @@
         <v>93</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>336</v>
@@ -4931,7 +4931,7 @@
         <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>337</v>
@@ -4949,7 +4949,7 @@
         <v>77</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>339</v>
@@ -4963,7 +4963,7 @@
         <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>340</v>
@@ -4978,13 +4978,13 @@
         <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>93</v>
+        <v>342</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>33</v>
@@ -4995,25 +4995,25 @@
         <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>345</v>
+        <v>93</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>346</v>
@@ -5027,7 +5027,7 @@
         <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>347</v>
@@ -5045,7 +5045,7 @@
         <v>71</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>349</v>
@@ -5059,7 +5059,7 @@
         <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>350</v>
@@ -5109,7 +5109,7 @@
         <v>77</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>356</v>
@@ -5123,7 +5123,7 @@
         <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>357</v>
@@ -5138,10 +5138,10 @@
         <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>265</v>
+        <v>77</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>359</v>
@@ -5155,7 +5155,7 @@
         <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>360</v>
@@ -5170,10 +5170,10 @@
         <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>77</v>
+        <v>265</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>362</v>
@@ -5187,7 +5187,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>363</v>
@@ -5202,10 +5202,10 @@
         <v>70</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>365</v>
@@ -5234,10 +5234,10 @@
         <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>368</v>
@@ -5251,7 +5251,7 @@
         <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>369</v>
@@ -5266,10 +5266,10 @@
         <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>371</v>
@@ -5283,7 +5283,7 @@
         <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>372</v>
@@ -5301,7 +5301,7 @@
         <v>77</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>374</v>
@@ -5315,7 +5315,7 @@
         <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>375</v>
@@ -5333,7 +5333,7 @@
         <v>83</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>377</v>
@@ -5347,7 +5347,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>378</v>
@@ -5365,7 +5365,7 @@
         <v>77</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>352</v>
+        <v>185</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>380</v>
@@ -5379,7 +5379,7 @@
         <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>381</v>
@@ -5411,7 +5411,7 @@
         <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>384</v>
@@ -5429,7 +5429,7 @@
         <v>88</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>352</v>
+        <v>185</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>386</v>
@@ -5673,7 +5673,7 @@
         <v>93</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>216</v>
+        <v>114</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>401</v>
@@ -5705,7 +5705,7 @@
         <v>99</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>216</v>
+        <v>114</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>404</v>
@@ -5737,7 +5737,7 @@
         <v>77</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>216</v>
+        <v>114</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>407</v>
@@ -5769,7 +5769,7 @@
         <v>77</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>216</v>
+        <v>114</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>410</v>
@@ -5801,7 +5801,7 @@
         <v>93</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>413</v>
@@ -5833,7 +5833,7 @@
         <v>99</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>416</v>
@@ -5897,7 +5897,7 @@
         <v>88</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>422</v>
@@ -5911,7 +5911,7 @@
         <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>423</v>
@@ -5943,7 +5943,7 @@
         <v>42</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>426</v>
@@ -5961,7 +5961,7 @@
         <v>77</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>428</v>
@@ -5975,7 +5975,7 @@
         <v>42</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>51</v>
@@ -5987,13 +5987,13 @@
         <v>429</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>93</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>430</v>
@@ -6007,7 +6007,7 @@
         <v>42</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>431</v>
@@ -6025,7 +6025,7 @@
         <v>83</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>433</v>
@@ -6039,7 +6039,7 @@
         <v>42</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>434</v>
@@ -6057,7 +6057,7 @@
         <v>77</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>436</v>
@@ -6071,7 +6071,7 @@
         <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>437</v>
@@ -6089,7 +6089,7 @@
         <v>88</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>439</v>
@@ -6103,7 +6103,7 @@
         <v>42</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>440</v>
@@ -6121,7 +6121,7 @@
         <v>93</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>442</v>
@@ -6153,7 +6153,7 @@
         <v>99</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>445</v>
@@ -6167,7 +6167,7 @@
         <v>42</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>446</v>
@@ -6182,10 +6182,10 @@
         <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>77</v>
+        <v>265</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>448</v>
@@ -6199,7 +6199,7 @@
         <v>42</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>449</v>
@@ -6214,10 +6214,10 @@
         <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>265</v>
+        <v>77</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>451</v>
@@ -6231,7 +6231,7 @@
         <v>42</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>452</v>
@@ -6249,7 +6249,7 @@
         <v>77</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>454</v>
@@ -6281,7 +6281,7 @@
         <v>93</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>457</v>
@@ -6295,7 +6295,7 @@
         <v>42</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>458</v>
@@ -6313,7 +6313,7 @@
         <v>93</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>460</v>
@@ -6327,7 +6327,7 @@
         <v>42</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>461</v>
@@ -6345,7 +6345,7 @@
         <v>77</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>463</v>
@@ -6359,7 +6359,7 @@
         <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>464</v>
@@ -6377,7 +6377,7 @@
         <v>99</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>466</v>
@@ -6619,7 +6619,7 @@
         <v>104</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>481</v>
@@ -6651,7 +6651,7 @@
         <v>83</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>216</v>
+        <v>114</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>484</v>
@@ -6677,7 +6677,7 @@
         <v>485</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>83</v>
@@ -6712,10 +6712,10 @@
         <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>489</v>
@@ -6744,10 +6744,10 @@
         <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>492</v>
@@ -6779,7 +6779,7 @@
         <v>88</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>495</v>
@@ -6811,7 +6811,7 @@
         <v>93</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>498</v>
@@ -6843,7 +6843,7 @@
         <v>104</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>501</v>
@@ -6857,7 +6857,7 @@
         <v>52</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>502</v>
@@ -6872,10 +6872,10 @@
         <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>504</v>
@@ -6889,7 +6889,7 @@
         <v>52</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>505</v>
@@ -6921,7 +6921,7 @@
         <v>52</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>508</v>
@@ -6936,10 +6936,10 @@
         <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>510</v>
@@ -6953,7 +6953,7 @@
         <v>52</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>511</v>
@@ -6968,10 +6968,10 @@
         <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>513</v>
@@ -6985,7 +6985,7 @@
         <v>52</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>514</v>
@@ -7003,7 +7003,7 @@
         <v>88</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>352</v>
+        <v>185</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>516</v>
@@ -7017,7 +7017,7 @@
         <v>52</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>517</v>
@@ -7035,7 +7035,7 @@
         <v>88</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>519</v>
@@ -7049,7 +7049,7 @@
         <v>52</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>520</v>
@@ -7099,7 +7099,7 @@
         <v>71</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>525</v>
@@ -7113,7 +7113,7 @@
         <v>52</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>526</v>
@@ -7145,7 +7145,7 @@
         <v>52</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>529</v>
@@ -7177,7 +7177,7 @@
         <v>52</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>533</v>
@@ -7195,7 +7195,7 @@
         <v>88</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>531</v>
+        <v>352</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>535</v>
@@ -7224,7 +7224,7 @@
         <v>70</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>93</v>
+        <v>342</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>531</v>
@@ -7241,7 +7241,7 @@
         <v>52</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>539</v>
@@ -7256,7 +7256,7 @@
         <v>70</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>345</v>
+        <v>93</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>531</v>
@@ -7273,7 +7273,7 @@
         <v>52</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>542</v>
@@ -7305,7 +7305,7 @@
         <v>52</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>545</v>
@@ -7337,7 +7337,7 @@
         <v>52</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>548</v>
@@ -7369,7 +7369,7 @@
         <v>52</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>551</v>
@@ -7401,7 +7401,7 @@
         <v>52</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>555</v>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -9,16 +9,16 @@
   <sheets>
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="셀린느" sheetId="2" r:id="rId2"/>
-    <sheet name="RAINBOW" sheetId="3" r:id="rId3"/>
-    <sheet name="동물들의낙원" sheetId="4" r:id="rId4"/>
-    <sheet name="빠따" sheetId="5" r:id="rId5"/>
+    <sheet name="빠따" sheetId="3" r:id="rId3"/>
+    <sheet name="RAINBOW" sheetId="4" r:id="rId4"/>
+    <sheet name="동물들의낙원" sheetId="5" r:id="rId5"/>
     <sheet name="친구들" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">RAINBOW!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">동물들의낙원!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">빠따!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">RAINBOW!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">동물들의낙원!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">빠따!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">셀린느!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">친구들!$A$1:$J$30</definedName>
   </definedNames>
@@ -80,1459 +80,1462 @@
     <t>Scania 2</t>
   </si>
   <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>1위</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>2경 6540조 1317억 3567만</t>
+  </si>
+  <si>
+    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
+  </si>
+  <si>
+    <t>혜영</t>
+  </si>
+  <si>
+    <t>2026.04.24</t>
+  </si>
+  <si>
+    <t>빠따</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%A0%EB%94%B0</t>
+  </si>
+  <si>
+    <t>Scania 12</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>1경 7729조 8595억 5527만</t>
+  </si>
+  <si>
+    <t>자유가입</t>
+  </si>
+  <si>
+    <t>o볼륨o</t>
+  </si>
+  <si>
+    <t>RAINBOW</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=RAINBOW</t>
+  </si>
+  <si>
+    <t>Scania 6</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>2위</t>
+  </si>
+  <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>2경 318조 2661억 789만</t>
+  </si>
+  <si>
+    <t>가입문의: 한딸기, 화질, 람볼기니 토벌100등 안쪽 귓 주세요</t>
+  </si>
+  <si>
+    <t>한딸기</t>
+  </si>
+  <si>
+    <t>동물들의낙원</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%8F%99%EB%AC%BC%EB%93%A4%EC%9D%98%EB%82%99%EC%9B%90</t>
+  </si>
+  <si>
+    <t>Scania 13</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>1경 7619조 7683억 2136만</t>
+  </si>
+  <si>
+    <t>일일연구 길드토벌 길드대전 하루이상 안하시거나 이틀미접시 통지없이 내보냅니다</t>
+  </si>
+  <si>
+    <t>곶감말이</t>
+  </si>
+  <si>
+    <t>친구들</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%B9%9C%EA%B5%AC%EB%93%A4</t>
+  </si>
+  <si>
+    <t>Scania 11</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>3위</t>
+  </si>
+  <si>
+    <t>Lv.10</t>
+  </si>
+  <si>
+    <t>1경 7160조 3903억 5403만</t>
+  </si>
+  <si>
+    <t>www.친구들.com 보고 가입 문의</t>
+  </si>
+  <si>
+    <t>친구둘리</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>스타냥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>1경 720조 3865억 2152만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>진자이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>4143조 7347억 1708만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>돈스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>3322조 3154억 8065만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>말레이히어로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>1744조 8442억 4005만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>1618조 8914억 2140만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>빌런투킬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>1126조 6292억 5948만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>스타뎀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%8E%80</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>475조 5893억 7767만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>여사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
+  </si>
+  <si>
+    <t>400조 1307억 6796만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>단풍노비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>348조 1289억 3205만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>부엉이없다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>301조 1417억 6857만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>228조 9399억 6339만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>213조 2895억 1154만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>프리프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>186조 1628억 3024만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>145조 9670억 5980만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>쾌감</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
+  </si>
+  <si>
+    <t>138조 322억 6447만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>소소채2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>110조 2424억 1921만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>98조 5974억 8085만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>96조 4965억 8645만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>88조 2570억 6478만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>POSCO</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
+  </si>
+  <si>
+    <t>65조 7697억 3285만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>두근푸근연근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>55조 2480억 5502만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>53조 5004억 3815만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>포뇨야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
+  </si>
+  <si>
+    <t>46조 2787억 8294만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>울힝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>41조 2396억 8935만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>김치싸대기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>39조 8824억 3269만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>38조 8158억 1231만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>37조 9202억 5357만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>악의꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>36조 6837억 5297만</t>
+  </si>
+  <si>
     <t>29</t>
   </si>
   <si>
-    <t>1위</t>
-  </si>
-  <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>2경 5854조 4054억 4762만</t>
-  </si>
-  <si>
-    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
-  </si>
-  <si>
-    <t>혜영</t>
-  </si>
-  <si>
-    <t>2026.04.23</t>
-  </si>
-  <si>
-    <t>RAINBOW</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=RAINBOW</t>
-  </si>
-  <si>
-    <t>Scania 6</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>2위</t>
-  </si>
-  <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>2경 132조 4803억 4846만</t>
-  </si>
-  <si>
-    <t>가입문의: 한딸기, 화질, 람볼기니 토벌100등 안쪽 귓 주세요</t>
-  </si>
-  <si>
-    <t>한딸기</t>
-  </si>
-  <si>
-    <t>동물들의낙원</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%8F%99%EB%AC%BC%EB%93%A4%EC%9D%98%EB%82%99%EC%9B%90</t>
-  </si>
-  <si>
-    <t>Scania 13</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>1경 7513조 4264억 676만</t>
-  </si>
-  <si>
-    <t>일일연구 길드토벌 길드대전 하루이상 안하시거나 이틀미접시 통지없이 내보냅니다</t>
-  </si>
-  <si>
-    <t>곶감말이</t>
-  </si>
-  <si>
-    <t>빠따</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%A0%EB%94%B0</t>
-  </si>
-  <si>
-    <t>Scania 12</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>1경 7289조 367억 4829만</t>
-  </si>
-  <si>
-    <t>자유가입</t>
-  </si>
-  <si>
-    <t>o볼륨o</t>
-  </si>
-  <si>
-    <t>친구들</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%B9%9C%EA%B5%AC%EB%93%A4</t>
-  </si>
-  <si>
-    <t>Scania 11</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>3위</t>
-  </si>
-  <si>
-    <t>Lv.10</t>
-  </si>
-  <si>
-    <t>1경 7156조 7692억 7610만</t>
-  </si>
-  <si>
-    <t>www.친구들.com 보고 가입 문의</t>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>35조 7411억 3365만</t>
+  </si>
+  <si>
+    <t>몽호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
+  </si>
+  <si>
+    <t>31조 9151억 3336만</t>
+  </si>
+  <si>
+    <t>o빠이o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EB%B9%A0%EC%9D%B4o</t>
+  </si>
+  <si>
+    <t>5170조 7801억 5796만</t>
+  </si>
+  <si>
+    <t>양먼지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%A8%BC%EC%A7%80</t>
+  </si>
+  <si>
+    <t>3255조 8744억 1510만</t>
+  </si>
+  <si>
+    <t>요르v</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EB%A5%B4v</t>
+  </si>
+  <si>
+    <t>2710조 4846억 3760만</t>
+  </si>
+  <si>
+    <t>o베베o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EB%B2%A0%EB%B2%A0o</t>
+  </si>
+  <si>
+    <t>2214조 2393억 964만</t>
+  </si>
+  <si>
+    <t>o원기o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EC%9B%90%EA%B8%B0o</t>
+  </si>
+  <si>
+    <t>1619조 1355억 9048만</t>
+  </si>
+  <si>
+    <t>집단범죄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%91%EB%8B%A8%EB%B2%94%EC%A3%84</t>
+  </si>
+  <si>
+    <t>583조 4549억 1044만</t>
+  </si>
+  <si>
+    <t>마법사김영욱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%B2%95%EC%82%AC%EA%B9%80%EC%98%81%EC%9A%B1</t>
+  </si>
+  <si>
+    <t>301조 9364억 5330만</t>
+  </si>
+  <si>
+    <t>워워이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%8C%EC%9B%8C%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>195조 4934억 6315만</t>
+  </si>
+  <si>
+    <t>캔느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BA%94%EB%8A%90</t>
+  </si>
+  <si>
+    <t>189조 9962억 510만</t>
+  </si>
+  <si>
+    <t>o후국o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%ED%9B%84%EA%B5%ADo</t>
+  </si>
+  <si>
+    <t>182조 3363억 5373만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EB%B3%BC%EB%A5%A8o</t>
+  </si>
+  <si>
+    <t>180조 6234억 842만</t>
+  </si>
+  <si>
+    <t>이원일</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9B%90%EC%9D%BC</t>
+  </si>
+  <si>
+    <t>143조 5472억 4797만</t>
+  </si>
+  <si>
+    <t>빵섭이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%EC%84%AD%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>124조 9974억 2134만</t>
+  </si>
+  <si>
+    <t>김규평</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B7%9C%ED%8F%89</t>
+  </si>
+  <si>
+    <t>115조 7340억 3872만</t>
+  </si>
+  <si>
+    <t>o진이o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EC%A7%84%EC%9D%B4o</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>108조 2832억 3996만</t>
+  </si>
+  <si>
+    <t>화욤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%9A%A4</t>
+  </si>
+  <si>
+    <t>85조 6670억 293만</t>
+  </si>
+  <si>
+    <t>뭥끼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AD%A5%EB%81%BC</t>
+  </si>
+  <si>
+    <t>82조 313억 638만</t>
+  </si>
+  <si>
+    <t>후니와동동</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EB%8B%88%EC%99%80%EB%8F%99%EB%8F%99</t>
+  </si>
+  <si>
+    <t>72조 9493억 7864만</t>
+  </si>
+  <si>
+    <t>o엉댕o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EC%97%89%EB%8C%95o</t>
+  </si>
+  <si>
+    <t>71조 6042억 609만</t>
+  </si>
+  <si>
+    <t>FFFK</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=FFFK</t>
+  </si>
+  <si>
+    <t>66조 5786억 899만</t>
+  </si>
+  <si>
+    <t>o아윤o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EC%95%84%EC%9C%A4o</t>
+  </si>
+  <si>
+    <t>58조 6086억 2075만</t>
+  </si>
+  <si>
+    <t>보마할래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%A7%88%ED%95%A0%EB%9E%98</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>50조 3678억 2760만</t>
+  </si>
+  <si>
+    <t>호이호이포이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9D%B4%ED%98%B8%EC%9D%B4%ED%8F%AC%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>30조 770억 4470만</t>
+  </si>
+  <si>
+    <t>동부마트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%B6%80%EB%A7%88%ED%8A%B8</t>
+  </si>
+  <si>
+    <t>28조 7639억 2637만</t>
+  </si>
+  <si>
+    <t>옹이잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%B9%EC%9D%B4%EC%9E%89</t>
+  </si>
+  <si>
+    <t>17조 7165억 8053만</t>
+  </si>
+  <si>
+    <t>겨울난방</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%EB%82%9C%EB%B0%A9</t>
+  </si>
+  <si>
+    <t>17조 5844억 3259만</t>
+  </si>
+  <si>
+    <t>우패밀리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%8C%A8%EB%B0%80%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>15조 9007억 5609만</t>
+  </si>
+  <si>
+    <t>담훌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%B4%ED%9B%8C</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>14조 256억 4755만</t>
+  </si>
+  <si>
+    <t>뚠뚠냥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9A%A0%EB%9A%A0%EB%83%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>11조 4025억 5100만</t>
+  </si>
+  <si>
+    <t>비뉴송</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%89%B4%EC%86%A1</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>9조 6648억 1204만</t>
+  </si>
+  <si>
+    <t>람볼기니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9E%8C%EB%B3%BC%EA%B8%B0%EB%8B%88</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>1경 430조 6210억 5429만</t>
+  </si>
+  <si>
+    <t>봉띤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%EB%9D%A4</t>
+  </si>
+  <si>
+    <t>5499조 5083억 2830만</t>
+  </si>
+  <si>
+    <t>레몬깜바뉴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EB%AA%AC%EA%B9%9C%EB%B0%94%EB%89%B4</t>
+  </si>
+  <si>
+    <t>1197조 330억 5524만</t>
+  </si>
+  <si>
+    <t>예나는못말려</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%82%98%EB%8A%94%EB%AA%BB%EB%A7%90%EB%A0%A4</t>
+  </si>
+  <si>
+    <t>1141조 4696억 7703만</t>
+  </si>
+  <si>
+    <t>불풍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%ED%92%8D</t>
+  </si>
+  <si>
+    <t>730조 6494억 130만</t>
+  </si>
+  <si>
+    <t>허동</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%97%88%EB%8F%99</t>
+  </si>
+  <si>
+    <t>426조 2541억 1873만</t>
+  </si>
+  <si>
+    <t>삼뚝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%BC%EB%9A%9D</t>
+  </si>
+  <si>
+    <t>158조 5282억 6438만</t>
+  </si>
+  <si>
+    <t>똑순</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%91%EC%88%9C</t>
+  </si>
+  <si>
+    <t>115조 8519억 5949만</t>
+  </si>
+  <si>
+    <t>매워요</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EC%9B%8C%EC%9A%94</t>
+  </si>
+  <si>
+    <t>91조 4052억 2736만</t>
+  </si>
+  <si>
+    <t>문군</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EA%B5%B0</t>
+  </si>
+  <si>
+    <t>79조 5173억 3429만</t>
+  </si>
+  <si>
+    <t>클이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%81%B4%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>72조 9268억 5948만</t>
+  </si>
+  <si>
+    <t>지흠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%ED%9D%A0</t>
+  </si>
+  <si>
+    <t>49조 4805억 9760만</t>
+  </si>
+  <si>
+    <t>이클릿</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%ED%81%B4%EB%A6%BF</t>
+  </si>
+  <si>
+    <t>46조 4119억 1969만</t>
+  </si>
+  <si>
+    <t>해로니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%A1%9C%EB%8B%88</t>
+  </si>
+  <si>
+    <t>38조 3367억 8619만</t>
+  </si>
+  <si>
+    <t>조업</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%97%85</t>
+  </si>
+  <si>
+    <t>31조 4877억 5588만</t>
+  </si>
+  <si>
+    <t>오버츄어리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%B2%84%EC%B8%84%EC%96%B4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>29조 1577억 9107만</t>
+  </si>
+  <si>
+    <t>매스리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EC%8A%A4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>26조 995억 5897만</t>
+  </si>
+  <si>
+    <t>썬콜미르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%AF%B8%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>22조 7314억 3436만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%94%B8%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>19조 1698억 9413만</t>
+  </si>
+  <si>
+    <t>화질</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A7%88</t>
+  </si>
+  <si>
+    <t>18조 8033억 7854만</t>
+  </si>
+  <si>
+    <t>꽁칫</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EC%B9%AB</t>
+  </si>
+  <si>
+    <t>18조 3265억 9096만</t>
+  </si>
+  <si>
+    <t>앵찬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%B5%EC%B0%AC</t>
+  </si>
+  <si>
+    <t>16조 3268억 463만</t>
+  </si>
+  <si>
+    <t>레펠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%ED%8E%A0</t>
+  </si>
+  <si>
+    <t>15조 5426억 1436만</t>
+  </si>
+  <si>
+    <t>LifeLegend</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=LifeLegend</t>
+  </si>
+  <si>
+    <t>10조 1668억 6473만</t>
+  </si>
+  <si>
+    <t>ArtCoin</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=ArtCoin</t>
+  </si>
+  <si>
+    <t>9조 1974억 3957만</t>
+  </si>
+  <si>
+    <t>멍눈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%8D%EB%88%88</t>
+  </si>
+  <si>
+    <t>8조 8514억 3584만</t>
+  </si>
+  <si>
+    <t>할거없곰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EA%B1%B0%EC%97%86%EA%B3%B0</t>
+  </si>
+  <si>
+    <t>5조 8875억 2959만</t>
+  </si>
+  <si>
+    <t>무지성사냥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%A7%80%EC%84%B1%EC%82%AC%EB%83%A5</t>
+  </si>
+  <si>
+    <t>4조 5207억 8343만</t>
+  </si>
+  <si>
+    <t>때꾸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%95%8C%EA%BE%B8</t>
+  </si>
+  <si>
+    <t>4조 16억 4833만</t>
+  </si>
+  <si>
+    <t>딱뎀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%B1%EB%8E%80</t>
+  </si>
+  <si>
+    <t>1경 427조 4390억 9252만</t>
+  </si>
+  <si>
+    <t>왕이된사나이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EC%9D%B4%EB%90%9C%EC%82%AC%EB%82%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>3180조 8876억 2671만</t>
+  </si>
+  <si>
+    <t>또르뱅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%A5%B4%EB%B1%85</t>
+  </si>
+  <si>
+    <t>2720조 5494억 7647만</t>
+  </si>
+  <si>
+    <t>Hoood</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Hoood</t>
+  </si>
+  <si>
+    <t>376조 4200억 6821만</t>
+  </si>
+  <si>
+    <t>클리닝티슈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%81%B4%EB%A6%AC%EB%8B%9D%ED%8B%B0%EC%8A%88</t>
+  </si>
+  <si>
+    <t>182조 4025억 7396만</t>
+  </si>
+  <si>
+    <t>상깅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B9%85</t>
+  </si>
+  <si>
+    <t>158조 6598억 942만</t>
+  </si>
+  <si>
+    <t>내사랑로제</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%B4%EC%82%AC%EB%9E%91%EB%A1%9C%EC%A0%9C</t>
+  </si>
+  <si>
+    <t>105조 4797억 1819만</t>
+  </si>
+  <si>
+    <t>유대표</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%8C%80%ED%91%9C</t>
+  </si>
+  <si>
+    <t>103조 1493억 1597만</t>
+  </si>
+  <si>
+    <t>손끝의예리함</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%90%EB%81%9D%EC%9D%98%EC%98%88%EB%A6%AC%ED%95%A8</t>
+  </si>
+  <si>
+    <t>55조 226억 9129만</t>
+  </si>
+  <si>
+    <t>얘인</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%98%EC%9D%B8</t>
+  </si>
+  <si>
+    <t>53조 5972억 1240만</t>
+  </si>
+  <si>
+    <t>쌈싸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8C%88%EC%8B%B8</t>
+  </si>
+  <si>
+    <t>34조 1766억 2670만</t>
+  </si>
+  <si>
+    <t>쑹쓩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%91%B9%EC%93%A9</t>
+  </si>
+  <si>
+    <t>30조 1792억 7780만</t>
+  </si>
+  <si>
+    <t>퓨엉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%93%A8%EC%97%89</t>
+  </si>
+  <si>
+    <t>30조 202억 2782만</t>
+  </si>
+  <si>
+    <t>공성현</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EC%84%B1%ED%98%84</t>
+  </si>
+  <si>
+    <t>25조 2717억 3412만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B6%EA%B0%90%EB%A7%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>20조 4796억 8556만</t>
+  </si>
+  <si>
+    <t>존잘녀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B4%EC%9E%98%EB%85%80</t>
+  </si>
+  <si>
+    <t>15조 8893억 8955만</t>
+  </si>
+  <si>
+    <t>품쪽이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%92%88%EC%AA%BD%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>14조 9503억 8211만</t>
+  </si>
+  <si>
+    <t>웨아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%A8%EC%95%84</t>
+  </si>
+  <si>
+    <t>14조 5279억 9312만</t>
+  </si>
+  <si>
+    <t>통영고니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%B5%EC%98%81%EA%B3%A0%EB%8B%88</t>
+  </si>
+  <si>
+    <t>10조 9549억 7607만</t>
+  </si>
+  <si>
+    <t>으니림</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%BC%EB%8B%88%EB%A6%BC</t>
+  </si>
+  <si>
+    <t>9조 4561억 5315만</t>
+  </si>
+  <si>
+    <t>쪼재맨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%AA%BC%EC%9E%AC%EB%A7%A8</t>
+  </si>
+  <si>
+    <t>7조 9617억 3798만</t>
+  </si>
+  <si>
+    <t>창목</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%BD%EB%AA%A9</t>
+  </si>
+  <si>
+    <t>6조 7256억 5217만</t>
+  </si>
+  <si>
+    <t>기동2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%8F%992</t>
+  </si>
+  <si>
+    <t>6조 1981억 9910만</t>
+  </si>
+  <si>
+    <t>코몽잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EB%AA%BD%EC%9E%89</t>
+  </si>
+  <si>
+    <t>5조 2837억 7438만</t>
+  </si>
+  <si>
+    <t>치쵸치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B9%98%EC%B5%B8%EC%B9%98</t>
+  </si>
+  <si>
+    <t>5조 1751억 2244만</t>
+  </si>
+  <si>
+    <t>그대로꿀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%8C%80%EB%A1%9C%EA%BF%80</t>
+  </si>
+  <si>
+    <t>4조 5162억 334만</t>
+  </si>
+  <si>
+    <t>다둉이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%91%89%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>4조 912억 9312만</t>
+  </si>
+  <si>
+    <t>코뭉잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EB%AD%89%EC%9E%89</t>
+  </si>
+  <si>
+    <t>3조 7459억 1815만</t>
+  </si>
+  <si>
+    <t>문뚝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%9A%9D</t>
+  </si>
+  <si>
+    <t>3조 5340억 5619만</t>
+  </si>
+  <si>
+    <t>황금어금니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%A9%EA%B8%88%EC%96%B4%EA%B8%88%EB%8B%88</t>
+  </si>
+  <si>
+    <t>3조 223억 3320만</t>
+  </si>
+  <si>
+    <t>가을호떡</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%9D%84%ED%98%B8%EB%96%A1</t>
+  </si>
+  <si>
+    <t>1경 63조 622억 9806만</t>
+  </si>
+  <si>
+    <t>군보</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EB%B3%B4</t>
+  </si>
+  <si>
+    <t>5773조 3543억 1445만</t>
+  </si>
+  <si>
+    <t>낭만김갑룡</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%EA%B9%80%EA%B0%91%EB%A3%A1</t>
+  </si>
+  <si>
+    <t>447조 6100억 6586만</t>
+  </si>
+  <si>
+    <t>칭구야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B9%AD%EA%B5%AC%EC%95%BC</t>
+  </si>
+  <si>
+    <t>191조 4184억 141만</t>
+  </si>
+  <si>
+    <t>새우탕z</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%88%EC%9A%B0%ED%83%95z</t>
+  </si>
+  <si>
+    <t>95조 1286억 8281만</t>
+  </si>
+  <si>
+    <t>ykm21cc</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=ykm21cc</t>
+  </si>
+  <si>
+    <t>84조 3275억 7238만</t>
+  </si>
+  <si>
+    <t>껌정색</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%A0%95%EC%83%89</t>
+  </si>
+  <si>
+    <t>64조 4806억 578만</t>
+  </si>
+  <si>
+    <t>ggggg</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=ggggg</t>
+  </si>
+  <si>
+    <t>50조 5041억 4549만</t>
+  </si>
+  <si>
+    <t>리피트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%ED%94%BC%ED%8A%B8</t>
+  </si>
+  <si>
+    <t>47조 108억 7018만</t>
   </si>
   <si>
     <t>친구닷</t>
   </si>
   <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>스타냥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>1경 720조 3865억 2152만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>진자이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>4143조 7347억 1708만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>돈스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>3322조 3154억 8065만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>말레이히어로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>1744조 8442억 4005만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>1549조 1560억 6234만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>빌런투킬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>1123조 3986억 1263만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>스타뎀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%8E%80</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>475조 5893억 7767만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>여사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
-  </si>
-  <si>
-    <t>400조 1307억 6796만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>단풍노비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>348조 1289억 3205만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>부엉이없다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>258조 4957억 4006만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>니달리신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>228조 665억 3930만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>213조 2895억 1154만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>프리프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>186조 1628억 3024만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>144조 7908억 1983만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>쾌감</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
-  </si>
-  <si>
-    <t>135조 8070억 5784만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>108조 7648억 9596만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>98조 2925억 9574만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>89조 6997억 8504만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>88조 2570억 6478만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>POSCO</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
-  </si>
-  <si>
-    <t>65조 7697억 3285만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>두근푸근연근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>54조 6890억 4120만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>53조 5004억 3815만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>포뇨야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
-  </si>
-  <si>
-    <t>46조 2787억 8294만</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>울힝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>41조 2396억 8935만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>대방어조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>38조 8158억 1231만</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>김치싸대기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>38조 2204억 6124만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>37조 9202억 5357만</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>악의꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>36조 6837억 5297만</t>
-  </si>
-  <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>35조 6131억 7297만</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>몽호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
-  </si>
-  <si>
-    <t>26조 3627억 5765만</t>
-  </si>
-  <si>
-    <t>람볼기니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9E%8C%EB%B3%BC%EA%B8%B0%EB%8B%88</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>1경 338조 5600억 633만</t>
-  </si>
-  <si>
-    <t>봉띤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%EB%9D%A4</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>5499조 5083억 2830만</t>
-  </si>
-  <si>
-    <t>레몬깜바뉴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EB%AA%AC%EA%B9%9C%EB%B0%94%EB%89%B4</t>
-  </si>
-  <si>
-    <t>1146조 7952억 5682만</t>
-  </si>
-  <si>
-    <t>예나는못말려</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%82%98%EB%8A%94%EB%AA%BB%EB%A7%90%EB%A0%A4</t>
-  </si>
-  <si>
-    <t>1141조 4696억 7703만</t>
-  </si>
-  <si>
-    <t>불풍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%ED%92%8D</t>
-  </si>
-  <si>
-    <t>730조 6494억 130만</t>
-  </si>
-  <si>
-    <t>허동</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%97%88%EB%8F%99</t>
-  </si>
-  <si>
-    <t>425조 7969억 6473만</t>
-  </si>
-  <si>
-    <t>삼뚝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%BC%EB%9A%9D</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>128조 7408억 9965만</t>
-  </si>
-  <si>
-    <t>똑순</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%91%EC%88%9C</t>
-  </si>
-  <si>
-    <t>115조 8519억 5949만</t>
-  </si>
-  <si>
-    <t>매워요</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EC%9B%8C%EC%9A%94</t>
-  </si>
-  <si>
-    <t>91조 4052억 2736만</t>
-  </si>
-  <si>
-    <t>문군</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EA%B5%B0</t>
-  </si>
-  <si>
-    <t>77조 1258억 6746만</t>
-  </si>
-  <si>
-    <t>클이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%81%B4%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>72조 6650억 9844만</t>
-  </si>
-  <si>
-    <t>이클릿</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%ED%81%B4%EB%A6%BF</t>
-  </si>
-  <si>
-    <t>46조 4119억 1969만</t>
-  </si>
-  <si>
-    <t>지흠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%ED%9D%A0</t>
-  </si>
-  <si>
-    <t>41조 6492억 4351만</t>
-  </si>
-  <si>
-    <t>해로니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%A1%9C%EB%8B%88</t>
-  </si>
-  <si>
-    <t>38조 3367억 8619만</t>
-  </si>
-  <si>
-    <t>조업</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%97%85</t>
-  </si>
-  <si>
-    <t>30조 3588억 9127만</t>
-  </si>
-  <si>
-    <t>오버츄어리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%B2%84%EC%B8%84%EC%96%B4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>29조 1577억 9107만</t>
-  </si>
-  <si>
-    <t>매스리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EC%8A%A4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>25조 8585억 4752만</t>
-  </si>
-  <si>
-    <t>썬콜미르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%AF%B8%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>22조 7314억 3436만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%94%B8%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>19조 1698억 9413만</t>
-  </si>
-  <si>
-    <t>화질</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A7%88</t>
-  </si>
-  <si>
-    <t>18조 6656억 6209만</t>
-  </si>
-  <si>
-    <t>꽁칫</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EC%B9%AB</t>
-  </si>
-  <si>
-    <t>18조 2637억 2876만</t>
-  </si>
-  <si>
-    <t>앵찬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%B5%EC%B0%AC</t>
-  </si>
-  <si>
-    <t>16조 3268억 463만</t>
-  </si>
-  <si>
-    <t>레펠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%ED%8E%A0</t>
-  </si>
-  <si>
-    <t>15조 223억 8334만</t>
-  </si>
-  <si>
-    <t>LifeLegend</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=LifeLegend</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>9조 5714억 1172만</t>
-  </si>
-  <si>
-    <t>ArtCoin</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=ArtCoin</t>
-  </si>
-  <si>
-    <t>9조 1974억 3957만</t>
-  </si>
-  <si>
-    <t>멍눈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%8D%EB%88%88</t>
-  </si>
-  <si>
-    <t>8조 8137억 7864만</t>
-  </si>
-  <si>
-    <t>할거없곰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EA%B1%B0%EC%97%86%EA%B3%B0</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>5조 8875억 2959만</t>
-  </si>
-  <si>
-    <t>무지성사냥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%A7%80%EC%84%B1%EC%82%AC%EB%83%A5</t>
-  </si>
-  <si>
-    <t>4조 5207억 8343만</t>
-  </si>
-  <si>
-    <t>때꾸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%95%8C%EA%BE%B8</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>4조 16억 4833만</t>
-  </si>
-  <si>
-    <t>딱뎀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%B1%EB%8E%80</t>
-  </si>
-  <si>
-    <t>1경 427조 4390억 9252만</t>
-  </si>
-  <si>
-    <t>왕이된사나이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EC%9D%B4%EB%90%9C%EC%82%AC%EB%82%98%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>3180조 8876억 2671만</t>
-  </si>
-  <si>
-    <t>또르뱅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%A5%B4%EB%B1%85</t>
-  </si>
-  <si>
-    <t>2665조 4140억 2953만</t>
-  </si>
-  <si>
-    <t>Hoood</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Hoood</t>
-  </si>
-  <si>
-    <t>330조 5193억 6227만</t>
-  </si>
-  <si>
-    <t>클리닝티슈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%81%B4%EB%A6%AC%EB%8B%9D%ED%8B%B0%EC%8A%88</t>
-  </si>
-  <si>
-    <t>182조 4025억 7396만</t>
-  </si>
-  <si>
-    <t>상깅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B9%85</t>
-  </si>
-  <si>
-    <t>158조 1670억 5914만</t>
-  </si>
-  <si>
-    <t>내사랑로제</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%B4%EC%82%AC%EB%9E%91%EB%A1%9C%EC%A0%9C</t>
-  </si>
-  <si>
-    <t>104조 807억 4044만</t>
-  </si>
-  <si>
-    <t>유대표</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%8C%80%ED%91%9C</t>
-  </si>
-  <si>
-    <t>103조 1493억 1597만</t>
-  </si>
-  <si>
-    <t>손끝의예리함</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%90%EB%81%9D%EC%9D%98%EC%98%88%EB%A6%AC%ED%95%A8</t>
-  </si>
-  <si>
-    <t>55조 226억 9129만</t>
-  </si>
-  <si>
-    <t>얘인</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%98%EC%9D%B8</t>
-  </si>
-  <si>
-    <t>53조 5972억 1240만</t>
-  </si>
-  <si>
-    <t>쌈싸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8C%88%EC%8B%B8</t>
-  </si>
-  <si>
-    <t>34조 1766억 2670만</t>
-  </si>
-  <si>
-    <t>쑹쓩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%91%B9%EC%93%A9</t>
-  </si>
-  <si>
-    <t>30조 1792억 7780만</t>
-  </si>
-  <si>
-    <t>퓨엉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%93%A8%EC%97%89</t>
-  </si>
-  <si>
-    <t>28조 5056억 6577만</t>
-  </si>
-  <si>
-    <t>공성현</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EC%84%B1%ED%98%84</t>
-  </si>
-  <si>
-    <t>25조 2717억 3412만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B6%EA%B0%90%EB%A7%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>20조 4796억 8556만</t>
-  </si>
-  <si>
-    <t>존잘녀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B4%EC%9E%98%EB%85%80</t>
-  </si>
-  <si>
-    <t>15조 8542억 9118만</t>
-  </si>
-  <si>
-    <t>품쪽이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%92%88%EC%AA%BD%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>14조 9503억 8211만</t>
-  </si>
-  <si>
-    <t>웨아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%A8%EC%95%84</t>
-  </si>
-  <si>
-    <t>14조 5279억 9312만</t>
-  </si>
-  <si>
-    <t>통영고니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%B5%EC%98%81%EA%B3%A0%EB%8B%88</t>
-  </si>
-  <si>
-    <t>10조 327억 468만</t>
-  </si>
-  <si>
-    <t>으니림</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%BC%EB%8B%88%EB%A6%BC</t>
-  </si>
-  <si>
-    <t>9조 4561억 5315만</t>
-  </si>
-  <si>
-    <t>쪼재맨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%AA%BC%EC%9E%AC%EB%A7%A8</t>
-  </si>
-  <si>
-    <t>7조 8933억 9551만</t>
-  </si>
-  <si>
-    <t>창목</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%BD%EB%AA%A9</t>
-  </si>
-  <si>
-    <t>6조 7256억 5217만</t>
-  </si>
-  <si>
-    <t>기동2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%8F%992</t>
-  </si>
-  <si>
-    <t>6조 1981억 9910만</t>
-  </si>
-  <si>
-    <t>코몽잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EB%AA%BD%EC%9E%89</t>
-  </si>
-  <si>
-    <t>5조 2829억 6422만</t>
-  </si>
-  <si>
-    <t>치쵸치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B9%98%EC%B5%B8%EC%B9%98</t>
-  </si>
-  <si>
-    <t>5조 1072억 4498만</t>
-  </si>
-  <si>
-    <t>그대로꿀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%8C%80%EB%A1%9C%EA%BF%80</t>
-  </si>
-  <si>
-    <t>4조 3121억 9489만</t>
-  </si>
-  <si>
-    <t>다둉이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%91%89%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>3조 9727억 306만</t>
-  </si>
-  <si>
-    <t>코뭉잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EB%AD%89%EC%9E%89</t>
-  </si>
-  <si>
-    <t>3조 7459억 1815만</t>
-  </si>
-  <si>
-    <t>문뚝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%9A%9D</t>
-  </si>
-  <si>
-    <t>3조 5340억 5619만</t>
-  </si>
-  <si>
-    <t>황금어금니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%A9%EA%B8%88%EC%96%B4%EA%B8%88%EB%8B%88</t>
-  </si>
-  <si>
-    <t>2조 5398억 5991만</t>
-  </si>
-  <si>
-    <t>o빠이o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EB%B9%A0%EC%9D%B4o</t>
-  </si>
-  <si>
-    <t>5170조 7801억 5796만</t>
-  </si>
-  <si>
-    <t>양먼지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%A8%BC%EC%A7%80</t>
-  </si>
-  <si>
-    <t>2991조 3367억 1605만</t>
-  </si>
-  <si>
-    <t>요르v</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EB%A5%B4v</t>
-  </si>
-  <si>
-    <t>2681조 1894억 5721만</t>
-  </si>
-  <si>
-    <t>o베베o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EB%B2%A0%EB%B2%A0o</t>
-  </si>
-  <si>
-    <t>2213조 4765억 5571만</t>
-  </si>
-  <si>
-    <t>o원기o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EC%9B%90%EA%B8%B0o</t>
-  </si>
-  <si>
-    <t>1575조 724억 1646만</t>
-  </si>
-  <si>
-    <t>집단범죄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%91%EB%8B%A8%EB%B2%94%EC%A3%84</t>
-  </si>
-  <si>
-    <t>583조 4549억 1044만</t>
-  </si>
-  <si>
-    <t>마법사김영욱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%B2%95%EC%82%AC%EA%B9%80%EC%98%81%EC%9A%B1</t>
-  </si>
-  <si>
-    <t>297조 9041억 4419만</t>
-  </si>
-  <si>
-    <t>o후국o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%ED%9B%84%EA%B5%ADo</t>
-  </si>
-  <si>
-    <t>182조 3363억 5373만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EB%B3%BC%EB%A5%A8o</t>
-  </si>
-  <si>
-    <t>180조 6234억 842만</t>
-  </si>
-  <si>
-    <t>워워이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%8C%EC%9B%8C%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>162조 9938억 8153만</t>
-  </si>
-  <si>
-    <t>캔느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BA%94%EB%8A%90</t>
-  </si>
-  <si>
-    <t>149조 8372억 549만</t>
-  </si>
-  <si>
-    <t>이원일</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9B%90%EC%9D%BC</t>
-  </si>
-  <si>
-    <t>140조 676억 6205만</t>
-  </si>
-  <si>
-    <t>빵섭이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%EC%84%AD%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>119조 8276억 8744만</t>
-  </si>
-  <si>
-    <t>김규평</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B7%9C%ED%8F%89</t>
-  </si>
-  <si>
-    <t>115조 7340억 3872만</t>
-  </si>
-  <si>
-    <t>o진이o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EC%A7%84%EC%9D%B4o</t>
-  </si>
-  <si>
-    <t>108조 2832억 3996만</t>
-  </si>
-  <si>
-    <t>화욤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%9A%A4</t>
-  </si>
-  <si>
-    <t>85조 6670억 293만</t>
-  </si>
-  <si>
-    <t>뭥끼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AD%A5%EB%81%BC</t>
-  </si>
-  <si>
-    <t>82조 313억 638만</t>
-  </si>
-  <si>
-    <t>후니와동동</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EB%8B%88%EC%99%80%EB%8F%99%EB%8F%99</t>
-  </si>
-  <si>
-    <t>72조 9493억 7864만</t>
-  </si>
-  <si>
-    <t>o엉댕o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EC%97%89%EB%8C%95o</t>
-  </si>
-  <si>
-    <t>69조 6654억 4397만</t>
-  </si>
-  <si>
-    <t>FFFK</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=FFFK</t>
-  </si>
-  <si>
-    <t>66조 5786억 899만</t>
-  </si>
-  <si>
-    <t>o아윤o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EC%95%84%EC%9C%A4o</t>
-  </si>
-  <si>
-    <t>58조 6086억 2075만</t>
-  </si>
-  <si>
-    <t>보마할래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%A7%88%ED%95%A0%EB%9E%98</t>
-  </si>
-  <si>
-    <t>50조 3678억 2760만</t>
-  </si>
-  <si>
-    <t>호이호이포이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9D%B4%ED%98%B8%EC%9D%B4%ED%8F%AC%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>30조 770억 4470만</t>
-  </si>
-  <si>
-    <t>동부마트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%B6%80%EB%A7%88%ED%8A%B8</t>
-  </si>
-  <si>
-    <t>28조 7639억 2637만</t>
-  </si>
-  <si>
-    <t>겨울난방</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%EB%82%9C%EB%B0%A9</t>
-  </si>
-  <si>
-    <t>17조 5702억 5135만</t>
-  </si>
-  <si>
-    <t>우패밀리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%8C%A8%EB%B0%80%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>15조 9007억 5609만</t>
-  </si>
-  <si>
-    <t>옹이잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%B9%EC%9D%B4%EC%9E%89</t>
-  </si>
-  <si>
-    <t>15조 952억 3467만</t>
-  </si>
-  <si>
-    <t>담훌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%B4%ED%9B%8C</t>
-  </si>
-  <si>
-    <t>14조 256억 4755만</t>
-  </si>
-  <si>
-    <t>뚠뚠냥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9A%A0%EB%9A%A0%EB%83%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>11조 4025억 5100만</t>
-  </si>
-  <si>
-    <t>비뉴송</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%89%B4%EC%86%A1</t>
-  </si>
-  <si>
-    <t>9조 6648억 1204만</t>
-  </si>
-  <si>
-    <t>가을호떡</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%9D%84%ED%98%B8%EB%96%A1</t>
-  </si>
-  <si>
-    <t>1경 63조 622억 9806만</t>
-  </si>
-  <si>
-    <t>군보</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EB%B3%B4</t>
-  </si>
-  <si>
-    <t>5773조 3543억 1445만</t>
-  </si>
-  <si>
-    <t>낭만김갑룡</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%EA%B9%80%EA%B0%91%EB%A3%A1</t>
-  </si>
-  <si>
-    <t>447조 6100억 6586만</t>
-  </si>
-  <si>
-    <t>칭구야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B9%AD%EA%B5%AC%EC%95%BC</t>
-  </si>
-  <si>
-    <t>191조 4184억 141만</t>
-  </si>
-  <si>
-    <t>새우탕z</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%88%EC%9A%B0%ED%83%95z</t>
-  </si>
-  <si>
-    <t>94조 9601억 1819만</t>
-  </si>
-  <si>
-    <t>ykm21cc</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=ykm21cc</t>
-  </si>
-  <si>
-    <t>84조 3275억 7238만</t>
-  </si>
-  <si>
-    <t>껌정색</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%A0%95%EC%83%89</t>
-  </si>
-  <si>
-    <t>64조 4806억 578만</t>
-  </si>
-  <si>
-    <t>ggggg</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=ggggg</t>
-  </si>
-  <si>
-    <t>50조 5041억 4549만</t>
-  </si>
-  <si>
-    <t>리피트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%ED%94%BC%ED%8A%B8</t>
-  </si>
-  <si>
-    <t>46조 9145억 684만</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%9C%EA%B5%AC%EB%8B%B7</t>
   </si>
   <si>
-    <t>40조 8176억 9358만</t>
+    <t>42조 4357억 5444만</t>
   </si>
   <si>
     <t>다헐</t>
@@ -1541,7 +1544,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%ED%97%90</t>
   </si>
   <si>
-    <t>37조 9937억 4362만</t>
+    <t>38조 1647억 1810만</t>
   </si>
   <si>
     <t>신림동물개</t>
@@ -1589,9 +1592,6 @@
     <t>19조 3096억 4766만</t>
   </si>
   <si>
-    <t>친구둘리</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%9C%EA%B5%AC%EB%91%98%EB%A6%AC</t>
   </si>
   <si>
@@ -1604,7 +1604,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%99%EC%88%9C%EC%95%84</t>
   </si>
   <si>
-    <t>18조 9495억 9251만</t>
+    <t>18조 9699억 6528만</t>
   </si>
   <si>
     <t>조은거임</t>
@@ -1613,7 +1613,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%9D%80%EA%B1%B0%EC%9E%84</t>
   </si>
   <si>
-    <t>15조 3649억 8959만</t>
+    <t>15조 8467억 1311만</t>
   </si>
   <si>
     <t>v지훈왕자v</t>
@@ -1631,7 +1631,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EC%9A%B0%EB%AA%A8%EB%AA%A8</t>
   </si>
   <si>
-    <t>13조 736억 5725만</t>
+    <t>13조 2864억 6494만</t>
   </si>
   <si>
     <t>네모인간</t>
@@ -1649,7 +1649,7 @@
     <t>https://mgf.gg/contents/character.php?n=Silas</t>
   </si>
   <si>
-    <t>9조 3316억 4136만</t>
+    <t>9조 3475억 3185만</t>
   </si>
   <si>
     <t>뿡풍</t>
@@ -1667,7 +1667,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EB%B9%84</t>
   </si>
   <si>
-    <t>7조 2067억 753만</t>
+    <t>7조 5387억 8833만</t>
   </si>
   <si>
     <t>진성규</t>
@@ -1676,7 +1676,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%84%B1%EA%B7%9C</t>
   </si>
   <si>
-    <t>5조 394억 6894만</t>
+    <t>5조 471억 6881만</t>
   </si>
   <si>
     <t>갓친</t>
@@ -1685,7 +1685,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EC%B9%9C</t>
   </si>
   <si>
-    <t>4조 3340억 4378만</t>
+    <t>4조 3384억 5023만</t>
   </si>
   <si>
     <t>잘좀해봐</t>
@@ -1694,7 +1694,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%98%EC%A2%80%ED%95%B4%EB%B4%90</t>
   </si>
   <si>
-    <t>3조 6899억 4209만</t>
+    <t>4조 1820억 7513만</t>
   </si>
   <si>
     <t>예끔이</t>
@@ -2184,22 +2184,22 @@
         <v>28</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>24</v>
@@ -2207,31 +2207,31 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>38</v>
@@ -2313,7 +2313,7 @@
         <v>53</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>54</v>
@@ -2507,10 +2507,10 @@
         <v>86</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2521,28 +2521,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2553,28 +2553,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2585,28 +2585,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2617,28 +2617,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2649,16 +2649,16 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>68</v>
@@ -2667,10 +2667,10 @@
         <v>81</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2681,28 +2681,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2713,16 +2713,16 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>68</v>
@@ -2731,10 +2731,10 @@
         <v>81</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2745,16 +2745,16 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>68</v>
@@ -2763,10 +2763,10 @@
         <v>69</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2777,28 +2777,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2809,16 +2809,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>68</v>
@@ -2827,10 +2827,10 @@
         <v>86</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2841,28 +2841,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2873,28 +2873,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2905,28 +2905,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2937,16 +2937,16 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>68</v>
@@ -2955,10 +2955,10 @@
         <v>75</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2969,16 +2969,16 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>68</v>
@@ -2987,10 +2987,10 @@
         <v>75</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3001,28 +3001,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3033,16 +3033,16 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>68</v>
@@ -3051,10 +3051,10 @@
         <v>86</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3065,28 +3065,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3097,16 +3097,16 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>68</v>
@@ -3115,10 +3115,10 @@
         <v>75</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3129,16 +3129,16 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>68</v>
@@ -3147,10 +3147,10 @@
         <v>75</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3161,28 +3161,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3193,28 +3193,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3225,7 +3225,7 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>23</v>
@@ -3234,19 +3234,19 @@
         <v>23</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>75</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3257,16 +3257,16 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>68</v>
@@ -3275,10 +3275,10 @@
         <v>69</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3289,28 +3289,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>17</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3321,28 +3321,28 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>199</v>
+        <v>17</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -3388,1018 +3388,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J30"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
-    <hyperlink ref="E20" r:id="rId19"/>
-    <hyperlink ref="E21" r:id="rId20"/>
-    <hyperlink ref="E22" r:id="rId21"/>
-    <hyperlink ref="E23" r:id="rId22"/>
-    <hyperlink ref="E24" r:id="rId23"/>
-    <hyperlink ref="E25" r:id="rId24"/>
-    <hyperlink ref="E26" r:id="rId25"/>
-    <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -4409,7 +3397,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4447,31 +3435,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>295</v>
+        <v>204</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>295</v>
+        <v>204</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>296</v>
+        <v>205</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>209</v>
+        <v>76</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>297</v>
+        <v>206</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4479,31 +3467,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>298</v>
+        <v>207</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>298</v>
+        <v>207</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>299</v>
+        <v>208</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>300</v>
+        <v>209</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4511,31 +3499,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>301</v>
+        <v>210</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>301</v>
+        <v>210</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>302</v>
+        <v>211</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>102</v>
+        <v>199</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>303</v>
+        <v>212</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4543,31 +3531,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>304</v>
+        <v>213</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>304</v>
+        <v>213</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>305</v>
+        <v>214</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>306</v>
+        <v>215</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4575,31 +3563,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>307</v>
+        <v>216</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>307</v>
+        <v>216</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>308</v>
+        <v>217</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>309</v>
+        <v>218</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4607,31 +3595,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>310</v>
+        <v>219</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>310</v>
+        <v>219</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>311</v>
+        <v>220</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>312</v>
+        <v>221</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4639,31 +3627,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>313</v>
+        <v>222</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>313</v>
+        <v>222</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>314</v>
+        <v>223</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>315</v>
+        <v>224</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4671,31 +3659,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>316</v>
+        <v>225</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>316</v>
+        <v>225</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>317</v>
+        <v>226</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>318</v>
+        <v>227</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4703,31 +3691,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>319</v>
+        <v>228</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>319</v>
+        <v>228</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>320</v>
+        <v>229</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>321</v>
+        <v>230</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4735,31 +3723,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>322</v>
+        <v>231</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>322</v>
+        <v>231</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>323</v>
+        <v>232</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>324</v>
+        <v>233</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4767,31 +3755,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>325</v>
+        <v>31</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>325</v>
+        <v>31</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>326</v>
+        <v>234</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>68</v>
+        <v>189</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>327</v>
+        <v>235</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4799,31 +3787,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>328</v>
+        <v>236</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>328</v>
+        <v>236</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>329</v>
+        <v>237</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>330</v>
+        <v>238</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4831,31 +3819,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>331</v>
+        <v>239</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>331</v>
+        <v>239</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>332</v>
+        <v>240</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>193</v>
+        <v>144</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>333</v>
+        <v>241</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4863,31 +3851,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>334</v>
+        <v>242</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>334</v>
+        <v>242</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>335</v>
+        <v>243</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>336</v>
+        <v>244</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4895,31 +3883,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>40</v>
+        <v>245</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>40</v>
+        <v>245</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>337</v>
+        <v>246</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>188</v>
+        <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>338</v>
+        <v>248</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4927,31 +3915,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>339</v>
+        <v>249</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>339</v>
+        <v>249</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>340</v>
+        <v>250</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>193</v>
+        <v>118</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>341</v>
+        <v>251</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4959,31 +3947,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>342</v>
+        <v>252</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>342</v>
+        <v>252</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>343</v>
+        <v>253</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>193</v>
+        <v>144</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>344</v>
+        <v>254</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -4991,31 +3979,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>345</v>
+        <v>255</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>345</v>
+        <v>255</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>346</v>
+        <v>256</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>347</v>
+        <v>257</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5023,19 +4011,19 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>348</v>
+        <v>258</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>348</v>
+        <v>258</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>349</v>
+        <v>259</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>68</v>
@@ -5044,10 +4032,10 @@
         <v>75</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>276</v>
+        <v>177</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>350</v>
+        <v>260</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5055,31 +4043,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>351</v>
+        <v>261</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>351</v>
+        <v>261</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>352</v>
+        <v>262</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>276</v>
+        <v>118</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>353</v>
+        <v>263</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5087,31 +4075,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>354</v>
+        <v>264</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>354</v>
+        <v>264</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>355</v>
+        <v>265</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>276</v>
+        <v>177</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>356</v>
+        <v>266</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5119,31 +4107,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>357</v>
+        <v>267</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>357</v>
+        <v>267</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>358</v>
+        <v>268</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>91</v>
+        <v>269</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>276</v>
+        <v>144</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>359</v>
+        <v>270</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5151,31 +4139,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>360</v>
+        <v>271</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>360</v>
+        <v>271</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>361</v>
+        <v>272</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>293</v>
+        <v>92</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>276</v>
+        <v>177</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>362</v>
+        <v>273</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5183,19 +4171,19 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>363</v>
+        <v>274</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>363</v>
+        <v>274</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>364</v>
+        <v>275</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>68</v>
@@ -5204,10 +4192,10 @@
         <v>75</v>
       </c>
       <c r="H25" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>365</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5215,31 +4203,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>366</v>
+        <v>277</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>366</v>
+        <v>277</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>367</v>
+        <v>278</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>225</v>
+        <v>81</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>286</v>
+        <v>177</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>368</v>
+        <v>279</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5247,31 +4235,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>369</v>
+        <v>280</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>369</v>
+        <v>280</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>370</v>
+        <v>281</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>225</v>
+        <v>92</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>276</v>
+        <v>194</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>371</v>
+        <v>282</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5279,31 +4267,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>372</v>
+        <v>283</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>372</v>
+        <v>283</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>373</v>
+        <v>284</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>197</v>
+        <v>92</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>286</v>
+        <v>177</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>374</v>
+        <v>285</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5311,31 +4299,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>375</v>
+        <v>286</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>375</v>
+        <v>286</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>376</v>
+        <v>287</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>377</v>
+        <v>289</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5343,31 +4331,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>17</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>378</v>
+        <v>290</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>378</v>
+        <v>290</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>379</v>
+        <v>291</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>286</v>
+        <v>194</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>380</v>
+        <v>292</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5375,31 +4363,31 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>199</v>
+        <v>17</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>381</v>
+        <v>293</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>381</v>
+        <v>293</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>382</v>
+        <v>294</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>383</v>
+        <v>296</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5443,6 +4431,1018 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J30"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
@@ -5454,7 +5454,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5510,10 +5510,10 @@
         <v>68</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>209</v>
+        <v>76</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>386</v>
@@ -5542,10 +5542,10 @@
         <v>68</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>389</v>
@@ -5574,10 +5574,10 @@
         <v>68</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>197</v>
+        <v>103</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>392</v>
@@ -5606,10 +5606,10 @@
         <v>68</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>395</v>
@@ -5623,7 +5623,7 @@
         <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>396</v>
@@ -5638,10 +5638,10 @@
         <v>68</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>398</v>
@@ -5655,7 +5655,7 @@
         <v>41</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>399</v>
@@ -5670,10 +5670,10 @@
         <v>68</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>401</v>
@@ -5687,7 +5687,7 @@
         <v>41</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>402</v>
@@ -5702,10 +5702,10 @@
         <v>68</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>404</v>
@@ -5719,7 +5719,7 @@
         <v>41</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>405</v>
@@ -5734,10 +5734,10 @@
         <v>68</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>407</v>
@@ -5751,28 +5751,28 @@
         <v>41</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>47</v>
+        <v>408</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>47</v>
+        <v>408</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>188</v>
+        <v>68</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>117</v>
+        <v>177</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5783,28 +5783,28 @@
         <v>41</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5815,28 +5815,28 @@
         <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5847,28 +5847,28 @@
         <v>41</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5879,28 +5879,28 @@
         <v>41</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>143</v>
+        <v>194</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5911,28 +5911,28 @@
         <v>41</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5943,25 +5943,25 @@
         <v>41</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>425</v>
+        <v>47</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>425</v>
+        <v>47</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>426</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>68</v>
+        <v>189</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>427</v>
@@ -5975,7 +5975,7 @@
         <v>41</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>428</v>
@@ -5990,10 +5990,10 @@
         <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>117</v>
+        <v>194</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>430</v>
@@ -6007,7 +6007,7 @@
         <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>431</v>
@@ -6022,10 +6022,10 @@
         <v>68</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>143</v>
+        <v>194</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>433</v>
@@ -6039,7 +6039,7 @@
         <v>41</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>434</v>
@@ -6054,10 +6054,10 @@
         <v>68</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>436</v>
@@ -6071,7 +6071,7 @@
         <v>41</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>437</v>
@@ -6089,7 +6089,7 @@
         <v>75</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>176</v>
+        <v>288</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>439</v>
@@ -6103,7 +6103,7 @@
         <v>41</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>440</v>
@@ -6118,10 +6118,10 @@
         <v>68</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>117</v>
+        <v>288</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>442</v>
@@ -6135,7 +6135,7 @@
         <v>41</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>443</v>
@@ -6150,10 +6150,10 @@
         <v>68</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>176</v>
+        <v>288</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>445</v>
@@ -6167,7 +6167,7 @@
         <v>41</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>446</v>
@@ -6182,10 +6182,10 @@
         <v>68</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>293</v>
+        <v>92</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>143</v>
+        <v>288</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>448</v>
@@ -6199,7 +6199,7 @@
         <v>41</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>449</v>
@@ -6214,10 +6214,10 @@
         <v>68</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>91</v>
+        <v>269</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>176</v>
+        <v>288</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>451</v>
@@ -6231,7 +6231,7 @@
         <v>41</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>452</v>
@@ -6249,7 +6249,7 @@
         <v>75</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>193</v>
+        <v>288</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>454</v>
@@ -6263,7 +6263,7 @@
         <v>41</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>455</v>
@@ -6278,10 +6278,10 @@
         <v>68</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>91</v>
+        <v>247</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>193</v>
+        <v>295</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>457</v>
@@ -6295,7 +6295,7 @@
         <v>41</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>458</v>
@@ -6310,10 +6310,10 @@
         <v>68</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>91</v>
+        <v>247</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>176</v>
+        <v>288</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>460</v>
@@ -6327,7 +6327,7 @@
         <v>41</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>461</v>
@@ -6342,10 +6342,10 @@
         <v>68</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>81</v>
+        <v>199</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>193</v>
+        <v>295</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>463</v>
@@ -6359,7 +6359,7 @@
         <v>41</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>464</v>
@@ -6374,10 +6374,10 @@
         <v>68</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>466</v>
@@ -6391,7 +6391,7 @@
         <v>41</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>17</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>467</v>
@@ -6406,10 +6406,10 @@
         <v>68</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>193</v>
+        <v>295</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>469</v>
@@ -6423,7 +6423,7 @@
         <v>41</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>199</v>
+        <v>17</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>470</v>
@@ -6438,10 +6438,10 @@
         <v>68</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>472</v>
@@ -6558,7 +6558,7 @@
         <v>81</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>209</v>
+        <v>76</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>475</v>
@@ -6590,7 +6590,7 @@
         <v>75</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>209</v>
+        <v>76</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>478</v>
@@ -6619,10 +6619,10 @@
         <v>68</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>481</v>
@@ -6651,10 +6651,10 @@
         <v>68</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>484</v>
@@ -6668,7 +6668,7 @@
         <v>48</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>485</v>
@@ -6686,7 +6686,7 @@
         <v>69</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>487</v>
@@ -6700,7 +6700,7 @@
         <v>48</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>488</v>
@@ -6718,7 +6718,7 @@
         <v>75</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>490</v>
@@ -6732,7 +6732,7 @@
         <v>48</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>491</v>
@@ -6747,10 +6747,10 @@
         <v>68</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>493</v>
@@ -6764,7 +6764,7 @@
         <v>48</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>494</v>
@@ -6782,7 +6782,7 @@
         <v>86</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>496</v>
@@ -6796,7 +6796,7 @@
         <v>48</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>497</v>
@@ -6811,10 +6811,10 @@
         <v>68</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>499</v>
@@ -6828,28 +6828,28 @@
         <v>48</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>56</v>
+        <v>500</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>56</v>
+        <v>500</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>188</v>
+        <v>68</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6860,28 +6860,28 @@
         <v>48</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6892,16 +6892,16 @@
         <v>48</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>68</v>
@@ -6910,10 +6910,10 @@
         <v>75</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6924,16 +6924,16 @@
         <v>48</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>68</v>
@@ -6942,10 +6942,10 @@
         <v>75</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6956,28 +6956,28 @@
         <v>48</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6988,28 +6988,28 @@
         <v>48</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -7020,28 +7020,28 @@
         <v>48</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7052,25 +7052,25 @@
         <v>48</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>520</v>
+        <v>56</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>520</v>
+        <v>56</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>521</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>68</v>
+        <v>189</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>522</v>
@@ -7084,7 +7084,7 @@
         <v>48</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>523</v>
@@ -7099,10 +7099,10 @@
         <v>68</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>525</v>
@@ -7116,7 +7116,7 @@
         <v>48</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>526</v>
@@ -7134,7 +7134,7 @@
         <v>69</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>528</v>
@@ -7148,7 +7148,7 @@
         <v>48</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>529</v>
@@ -7166,7 +7166,7 @@
         <v>75</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>531</v>
@@ -7180,7 +7180,7 @@
         <v>48</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>532</v>
@@ -7198,7 +7198,7 @@
         <v>69</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>534</v>
@@ -7212,7 +7212,7 @@
         <v>48</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>535</v>
@@ -7227,10 +7227,10 @@
         <v>68</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>537</v>
@@ -7244,7 +7244,7 @@
         <v>48</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>538</v>
@@ -7259,10 +7259,10 @@
         <v>68</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>540</v>
@@ -7276,7 +7276,7 @@
         <v>48</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>541</v>
@@ -7291,10 +7291,10 @@
         <v>68</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>543</v>
@@ -7308,7 +7308,7 @@
         <v>48</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>544</v>
@@ -7323,10 +7323,10 @@
         <v>68</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>546</v>
@@ -7340,7 +7340,7 @@
         <v>48</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>547</v>
@@ -7355,10 +7355,10 @@
         <v>68</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>549</v>
@@ -7372,7 +7372,7 @@
         <v>48</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>550</v>
@@ -7387,10 +7387,10 @@
         <v>68</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>552</v>
@@ -7404,7 +7404,7 @@
         <v>48</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>553</v>
@@ -7419,10 +7419,10 @@
         <v>68</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>555</v>
@@ -7436,7 +7436,7 @@
         <v>48</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>17</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>556</v>
@@ -7451,10 +7451,10 @@
         <v>68</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>558</v>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">RAINBOW!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">RAINBOW!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">동물들의낙원!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">빠따!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">셀린느!$A$1:$J$31</definedName>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="557">
   <si>
     <t>guild_name</t>
   </si>
@@ -92,7 +92,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>2경 6540조 1317억 3567만</t>
+    <t>2경 6796조 388억 1382만</t>
   </si>
   <si>
     <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
@@ -101,7 +101,7 @@
     <t>혜영</t>
   </si>
   <si>
-    <t>2026.04.24</t>
+    <t>2026.04.25</t>
   </si>
   <si>
     <t>빠따</t>
@@ -116,7 +116,7 @@
     <t>41</t>
   </si>
   <si>
-    <t>1경 7729조 8595억 5527만</t>
+    <t>1경 8115조 5222억 7692만</t>
   </si>
   <si>
     <t>자유가입</t>
@@ -134,64 +134,67 @@
     <t>Scania 6</t>
   </si>
   <si>
-    <t>38</t>
+    <t>39</t>
   </si>
   <si>
     <t>2위</t>
   </si>
   <si>
+    <t>28명</t>
+  </si>
+  <si>
+    <t>2경 702조 3737억 9391만</t>
+  </si>
+  <si>
+    <t>가입문의: 한딸기, 화질, 람볼기니 토벌100등 안쪽 귓 주세요. 길컨 , 파퀘, 자쿰, 혼테일 모든 컨테츠 활발하게 즐길 사람!!</t>
+  </si>
+  <si>
+    <t>화질</t>
+  </si>
+  <si>
+    <t>동물들의낙원</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%8F%99%EB%AC%BC%EB%93%A4%EC%9D%98%EB%82%99%EC%9B%90</t>
+  </si>
+  <si>
+    <t>Scania 13</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>1경 7676조 6046억 7943만</t>
+  </si>
+  <si>
+    <t>일일연구 길드토벌 길드대전 하루이상 안하시거나 이틀미접시 통지없이 내보냅니다</t>
+  </si>
+  <si>
+    <t>곶감말이</t>
+  </si>
+  <si>
+    <t>친구들</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%B9%9C%EA%B5%AC%EB%93%A4</t>
+  </si>
+  <si>
+    <t>Scania 11</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>3위</t>
+  </si>
+  <si>
+    <t>Lv.10</t>
+  </si>
+  <si>
     <t>29명</t>
   </si>
   <si>
-    <t>2경 318조 2661억 789만</t>
-  </si>
-  <si>
-    <t>가입문의: 한딸기, 화질, 람볼기니 토벌100등 안쪽 귓 주세요</t>
-  </si>
-  <si>
-    <t>한딸기</t>
-  </si>
-  <si>
-    <t>동물들의낙원</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%8F%99%EB%AC%BC%EB%93%A4%EC%9D%98%EB%82%99%EC%9B%90</t>
-  </si>
-  <si>
-    <t>Scania 13</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>1경 7619조 7683억 2136만</t>
-  </si>
-  <si>
-    <t>일일연구 길드토벌 길드대전 하루이상 안하시거나 이틀미접시 통지없이 내보냅니다</t>
-  </si>
-  <si>
-    <t>곶감말이</t>
-  </si>
-  <si>
-    <t>친구들</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%B9%9C%EA%B5%AC%EB%93%A4</t>
-  </si>
-  <si>
-    <t>Scania 11</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>3위</t>
-  </si>
-  <si>
-    <t>Lv.10</t>
-  </si>
-  <si>
-    <t>1경 7160조 3903억 5403만</t>
+    <t>1경 7192조 6624억 391만</t>
   </si>
   <si>
     <t>www.친구들.com 보고 가입 문의</t>
@@ -242,7 +245,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>1경 720조 3865억 2152만</t>
+    <t>1경 1424조 663억 2805만</t>
   </si>
   <si>
     <t>2</t>
@@ -308,355 +311,355 @@
     <t>섀도어</t>
   </si>
   <si>
+    <t>1645조 8595억 7138만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>빌런투킬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>1185조 7524억 3872만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>스타뎀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%8E%80</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>475조 5893억 7767만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>여사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
+  </si>
+  <si>
+    <t>400조 1307억 6796만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>단풍노비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>348조 1289억 3205만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>부엉이없다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>304조 6773억 166만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>230조 3464억 5320만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>213조 2895억 1154만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>프리프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>186조 1628억 3024만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>146조 2654억 7912만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>쾌감</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
+  </si>
+  <si>
+    <t>142조 8456억 49만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>소소채2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>110조 3430억 5093만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>99조 5084억 4454만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>96조 4965억 8645만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>89조 6690억 4023만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>POSCO</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
+  </si>
+  <si>
+    <t>65조 7697억 3285만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>두근푸근연근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>56조 5716억 833만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>53조 5004억 3815만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>포뇨야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
+  </si>
+  <si>
+    <t>46조 2787억 8294만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>울힝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>41조 2396억 8935만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>김치싸대기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>39조 8824억 3269만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>38조 8158억 1231만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>악의꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>38조 2904억 9899만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>37조 9202억 5357만</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>35조 8282억 7914만</t>
+  </si>
+  <si>
+    <t>몽호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
+  </si>
+  <si>
+    <t>31조 9151억 3336만</t>
+  </si>
+  <si>
+    <t>o빠이o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EB%B9%A0%EC%9D%B4o</t>
+  </si>
+  <si>
+    <t>5170조 7801억 5796만</t>
+  </si>
+  <si>
+    <t>양먼지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%A8%BC%EC%A7%80</t>
+  </si>
+  <si>
     <t>109</t>
   </si>
   <si>
-    <t>1618조 8914억 2140만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>빌런투킬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>1126조 6292억 5948만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>스타뎀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%8E%80</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>475조 5893억 7767만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>여사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
-  </si>
-  <si>
-    <t>400조 1307억 6796만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>단풍노비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>348조 1289억 3205만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>부엉이없다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>301조 1417억 6857만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>니달리신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>228조 9399억 6339만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>213조 2895억 1154만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>프리프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>186조 1628억 3024만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>145조 9670억 5980만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>쾌감</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
-  </si>
-  <si>
-    <t>138조 322억 6447만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>110조 2424억 1921만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>98조 5974억 8085만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>96조 4965억 8645만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>88조 2570억 6478만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>POSCO</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
-  </si>
-  <si>
-    <t>65조 7697억 3285만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>두근푸근연근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>55조 2480억 5502만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>53조 5004억 3815만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>포뇨야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
-  </si>
-  <si>
-    <t>46조 2787억 8294만</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>울힝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>41조 2396억 8935만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>김치싸대기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>39조 8824억 3269만</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>대방어조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>38조 8158억 1231만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>37조 9202억 5357만</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>악의꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>36조 6837억 5297만</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>35조 7411억 3365만</t>
-  </si>
-  <si>
-    <t>몽호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
-  </si>
-  <si>
-    <t>31조 9151억 3336만</t>
-  </si>
-  <si>
-    <t>o빠이o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EB%B9%A0%EC%9D%B4o</t>
-  </si>
-  <si>
-    <t>5170조 7801억 5796만</t>
-  </si>
-  <si>
-    <t>양먼지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%A8%BC%EC%A7%80</t>
-  </si>
-  <si>
-    <t>3255조 8744억 1510만</t>
+    <t>3341조 2739억 4499만</t>
   </si>
   <si>
     <t>요르v</t>
@@ -665,7 +668,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EB%A5%B4v</t>
   </si>
   <si>
-    <t>2710조 4846억 3760만</t>
+    <t>2775조 6394억 3940만</t>
   </si>
   <si>
     <t>o베베o</t>
@@ -674,7 +677,7 @@
     <t>https://mgf.gg/contents/character.php?n=o%EB%B2%A0%EB%B2%A0o</t>
   </si>
   <si>
-    <t>2214조 2393억 964만</t>
+    <t>2224조 2119억 198만</t>
   </si>
   <si>
     <t>o원기o</t>
@@ -683,7 +686,7 @@
     <t>https://mgf.gg/contents/character.php?n=o%EC%9B%90%EA%B8%B0o</t>
   </si>
   <si>
-    <t>1619조 1355억 9048만</t>
+    <t>1738조 2910억 1598만</t>
   </si>
   <si>
     <t>집단범죄</t>
@@ -701,7 +704,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%B2%95%EC%82%AC%EA%B9%80%EC%98%81%EC%9A%B1</t>
   </si>
   <si>
-    <t>301조 9364억 5330만</t>
+    <t>307조 5314억 80만</t>
   </si>
   <si>
     <t>워워이</t>
@@ -710,7 +713,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%8C%EC%9B%8C%EC%9D%B4</t>
   </si>
   <si>
-    <t>195조 4934억 6315만</t>
+    <t>243조 7416억 9047만</t>
+  </si>
+  <si>
+    <t>o후국o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%ED%9B%84%EA%B5%ADo</t>
+  </si>
+  <si>
+    <t>200조 1341억 2359만</t>
   </si>
   <si>
     <t>캔느</t>
@@ -722,15 +734,6 @@
     <t>189조 9962억 510만</t>
   </si>
   <si>
-    <t>o후국o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%ED%9B%84%EA%B5%ADo</t>
-  </si>
-  <si>
-    <t>182조 3363억 5373만</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=o%EB%B3%BC%EB%A5%A8o</t>
   </si>
   <si>
@@ -746,6 +749,18 @@
     <t>143조 5472억 4797만</t>
   </si>
   <si>
+    <t>o진이o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EC%A7%84%EC%9D%B4o</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>136조 6367억 1816만</t>
+  </si>
+  <si>
     <t>빵섭이</t>
   </si>
   <si>
@@ -764,18 +779,6 @@
     <t>115조 7340억 3872만</t>
   </si>
   <si>
-    <t>o진이o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EC%A7%84%EC%9D%B4o</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>108조 2832억 3996만</t>
-  </si>
-  <si>
     <t>화욤</t>
   </si>
   <si>
@@ -809,7 +812,7 @@
     <t>https://mgf.gg/contents/character.php?n=o%EC%97%89%EB%8C%95o</t>
   </si>
   <si>
-    <t>71조 6042억 609만</t>
+    <t>72조 843억 8310만</t>
   </si>
   <si>
     <t>FFFK</t>
@@ -839,7 +842,16 @@
     <t>보우마스터</t>
   </si>
   <si>
-    <t>50조 3678억 2760만</t>
+    <t>51조 811억 1462만</t>
+  </si>
+  <si>
+    <t>동부마트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%B6%80%EB%A7%88%ED%8A%B8</t>
+  </si>
+  <si>
+    <t>31조 1082억 4428만</t>
   </si>
   <si>
     <t>호이호이포이</t>
@@ -851,15 +863,6 @@
     <t>30조 770억 4470만</t>
   </si>
   <si>
-    <t>동부마트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%B6%80%EB%A7%88%ED%8A%B8</t>
-  </si>
-  <si>
-    <t>28조 7639억 2637만</t>
-  </si>
-  <si>
     <t>옹이잉</t>
   </si>
   <si>
@@ -875,7 +878,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%EB%82%9C%EB%B0%A9</t>
   </si>
   <si>
-    <t>17조 5844억 3259만</t>
+    <t>17조 6938억 6100만</t>
   </si>
   <si>
     <t>우패밀리</t>
@@ -884,7 +887,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%8C%A8%EB%B0%80%EB%A6%AC</t>
   </si>
   <si>
-    <t>15조 9007억 5609만</t>
+    <t>16조 8961억 7543만</t>
   </si>
   <si>
     <t>담훌</t>
@@ -893,247 +896,247 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%B4%ED%9B%8C</t>
   </si>
   <si>
+    <t>15조 442억 9951만</t>
+  </si>
+  <si>
+    <t>뚠뚠냥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9A%A0%EB%9A%A0%EB%83%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>11조 4025억 5100만</t>
+  </si>
+  <si>
+    <t>비뉴송</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%89%B4%EC%86%A1</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>9조 9894억 7962만</t>
+  </si>
+  <si>
+    <t>람볼기니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9E%8C%EB%B3%BC%EA%B8%B0%EB%8B%88</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>1경 804조 5011억 19만</t>
+  </si>
+  <si>
+    <t>봉띤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%EB%9D%A4</t>
+  </si>
+  <si>
+    <t>5499조 5083억 2830만</t>
+  </si>
+  <si>
+    <t>레몬깜바뉴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EB%AA%AC%EA%B9%9C%EB%B0%94%EB%89%B4</t>
+  </si>
+  <si>
+    <t>1197조 330억 5524만</t>
+  </si>
+  <si>
+    <t>예나는못말려</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%82%98%EB%8A%94%EB%AA%BB%EB%A7%90%EB%A0%A4</t>
+  </si>
+  <si>
+    <t>1141조 4696억 7703만</t>
+  </si>
+  <si>
+    <t>불풍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%ED%92%8D</t>
+  </si>
+  <si>
+    <t>730조 6494억 130만</t>
+  </si>
+  <si>
+    <t>허동</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%97%88%EB%8F%99</t>
+  </si>
+  <si>
+    <t>427조 67억 2399만</t>
+  </si>
+  <si>
+    <t>삼뚝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%BC%EB%9A%9D</t>
+  </si>
+  <si>
+    <t>158조 5282억 6438만</t>
+  </si>
+  <si>
+    <t>똑순</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%91%EC%88%9C</t>
+  </si>
+  <si>
+    <t>122조 9125억 1716만</t>
+  </si>
+  <si>
+    <t>매워요</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EC%9B%8C%EC%9A%94</t>
+  </si>
+  <si>
+    <t>91조 4052억 2736만</t>
+  </si>
+  <si>
+    <t>문군</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EA%B5%B0</t>
+  </si>
+  <si>
+    <t>80조 6841억 5612만</t>
+  </si>
+  <si>
+    <t>클이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%81%B4%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>74조 7631억 3241만</t>
+  </si>
+  <si>
+    <t>지흠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%ED%9D%A0</t>
+  </si>
+  <si>
+    <t>51조 8772억 5719만</t>
+  </si>
+  <si>
+    <t>이클릿</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%ED%81%B4%EB%A6%BF</t>
+  </si>
+  <si>
+    <t>46조 4119억 1969만</t>
+  </si>
+  <si>
+    <t>해로니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%A1%9C%EB%8B%88</t>
+  </si>
+  <si>
+    <t>38조 3367억 8619만</t>
+  </si>
+  <si>
+    <t>조업</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%97%85</t>
+  </si>
+  <si>
+    <t>31조 4877억 5588만</t>
+  </si>
+  <si>
+    <t>오버츄어리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%B2%84%EC%B8%84%EC%96%B4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>29조 1643억 3603만</t>
+  </si>
+  <si>
+    <t>매스리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EC%8A%A4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>26조 2186억 1691만</t>
+  </si>
+  <si>
+    <t>썬콜미르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%AF%B8%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>22조 7314억 3436만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A7%88</t>
+  </si>
+  <si>
+    <t>18조 8175억 7945만</t>
+  </si>
+  <si>
+    <t>꽁칫</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EC%B9%AB</t>
+  </si>
+  <si>
+    <t>18조 6334억 109만</t>
+  </si>
+  <si>
+    <t>앵찬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%B5%EC%B0%AC</t>
+  </si>
+  <si>
+    <t>16조 3268억 463만</t>
+  </si>
+  <si>
+    <t>레펠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%ED%8E%A0</t>
+  </si>
+  <si>
+    <t>15조 5808억 2263만</t>
+  </si>
+  <si>
+    <t>LifeLegend</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=LifeLegend</t>
+  </si>
+  <si>
     <t>101</t>
   </si>
   <si>
-    <t>14조 256억 4755만</t>
-  </si>
-  <si>
-    <t>뚠뚠냥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9A%A0%EB%9A%A0%EB%83%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>11조 4025억 5100만</t>
-  </si>
-  <si>
-    <t>비뉴송</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%89%B4%EC%86%A1</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>9조 6648억 1204만</t>
-  </si>
-  <si>
-    <t>람볼기니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9E%8C%EB%B3%BC%EA%B8%B0%EB%8B%88</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>1경 430조 6210억 5429만</t>
-  </si>
-  <si>
-    <t>봉띤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%EB%9D%A4</t>
-  </si>
-  <si>
-    <t>5499조 5083억 2830만</t>
-  </si>
-  <si>
-    <t>레몬깜바뉴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EB%AA%AC%EA%B9%9C%EB%B0%94%EB%89%B4</t>
-  </si>
-  <si>
-    <t>1197조 330억 5524만</t>
-  </si>
-  <si>
-    <t>예나는못말려</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%82%98%EB%8A%94%EB%AA%BB%EB%A7%90%EB%A0%A4</t>
-  </si>
-  <si>
-    <t>1141조 4696억 7703만</t>
-  </si>
-  <si>
-    <t>불풍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%ED%92%8D</t>
-  </si>
-  <si>
-    <t>730조 6494억 130만</t>
-  </si>
-  <si>
-    <t>허동</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%97%88%EB%8F%99</t>
-  </si>
-  <si>
-    <t>426조 2541억 1873만</t>
-  </si>
-  <si>
-    <t>삼뚝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%BC%EB%9A%9D</t>
-  </si>
-  <si>
-    <t>158조 5282억 6438만</t>
-  </si>
-  <si>
-    <t>똑순</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%91%EC%88%9C</t>
-  </si>
-  <si>
-    <t>115조 8519억 5949만</t>
-  </si>
-  <si>
-    <t>매워요</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EC%9B%8C%EC%9A%94</t>
-  </si>
-  <si>
-    <t>91조 4052억 2736만</t>
-  </si>
-  <si>
-    <t>문군</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EA%B5%B0</t>
-  </si>
-  <si>
-    <t>79조 5173억 3429만</t>
-  </si>
-  <si>
-    <t>클이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%81%B4%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>72조 9268억 5948만</t>
-  </si>
-  <si>
-    <t>지흠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%ED%9D%A0</t>
-  </si>
-  <si>
-    <t>49조 4805억 9760만</t>
-  </si>
-  <si>
-    <t>이클릿</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%ED%81%B4%EB%A6%BF</t>
-  </si>
-  <si>
-    <t>46조 4119억 1969만</t>
-  </si>
-  <si>
-    <t>해로니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%A1%9C%EB%8B%88</t>
-  </si>
-  <si>
-    <t>38조 3367억 8619만</t>
-  </si>
-  <si>
-    <t>조업</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%97%85</t>
-  </si>
-  <si>
-    <t>31조 4877억 5588만</t>
-  </si>
-  <si>
-    <t>오버츄어리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%B2%84%EC%B8%84%EC%96%B4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>29조 1577억 9107만</t>
-  </si>
-  <si>
-    <t>매스리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EC%8A%A4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>26조 995억 5897만</t>
-  </si>
-  <si>
-    <t>썬콜미르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%AF%B8%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>22조 7314억 3436만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%94%B8%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>19조 1698억 9413만</t>
-  </si>
-  <si>
-    <t>화질</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A7%88</t>
-  </si>
-  <si>
-    <t>18조 8033억 7854만</t>
-  </si>
-  <si>
-    <t>꽁칫</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EC%B9%AB</t>
-  </si>
-  <si>
-    <t>18조 3265억 9096만</t>
-  </si>
-  <si>
-    <t>앵찬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%B5%EC%B0%AC</t>
-  </si>
-  <si>
-    <t>16조 3268억 463만</t>
-  </si>
-  <si>
-    <t>레펠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%ED%8E%A0</t>
-  </si>
-  <si>
-    <t>15조 5426억 1436만</t>
-  </si>
-  <si>
-    <t>LifeLegend</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=LifeLegend</t>
-  </si>
-  <si>
-    <t>10조 1668억 6473만</t>
+    <t>10조 6952억 5950만</t>
+  </si>
+  <si>
+    <t>멍눈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%8D%EB%88%88</t>
+  </si>
+  <si>
+    <t>9조 3737억 2513만</t>
   </si>
   <si>
     <t>ArtCoin</t>
@@ -1145,15 +1148,6 @@
     <t>9조 1974억 3957만</t>
   </si>
   <si>
-    <t>멍눈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%8D%EB%88%88</t>
-  </si>
-  <si>
-    <t>8조 8514억 3584만</t>
-  </si>
-  <si>
     <t>할거없곰</t>
   </si>
   <si>
@@ -1205,7 +1199,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%A5%B4%EB%B1%85</t>
   </si>
   <si>
-    <t>2720조 5494억 7647만</t>
+    <t>2730조 7758억 8782만</t>
   </si>
   <si>
     <t>Hoood</t>
@@ -1214,7 +1208,7 @@
     <t>https://mgf.gg/contents/character.php?n=Hoood</t>
   </si>
   <si>
-    <t>376조 4200억 6821만</t>
+    <t>391조 159억 8557만</t>
   </si>
   <si>
     <t>클리닝티슈</t>
@@ -1232,7 +1226,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B9%85</t>
   </si>
   <si>
-    <t>158조 6598억 942만</t>
+    <t>175조 3099억 190만</t>
   </si>
   <si>
     <t>내사랑로제</t>
@@ -1241,7 +1235,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%B4%EC%82%AC%EB%9E%91%EB%A1%9C%EC%A0%9C</t>
   </si>
   <si>
-    <t>105조 4797억 1819만</t>
+    <t>115조 2108억 9933만</t>
   </si>
   <si>
     <t>유대표</t>
@@ -1295,7 +1289,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%93%A8%EC%97%89</t>
   </si>
   <si>
-    <t>30조 202억 2782만</t>
+    <t>30조 697억 8315만</t>
   </si>
   <si>
     <t>공성현</t>
@@ -1304,7 +1298,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EC%84%B1%ED%98%84</t>
   </si>
   <si>
-    <t>25조 2717억 3412만</t>
+    <t>26조 7316억 9260만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%B6%EA%B0%90%EB%A7%90%EC%9D%B4</t>
@@ -1313,22 +1307,22 @@
     <t>20조 4796억 8556만</t>
   </si>
   <si>
+    <t>품쪽이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%92%88%EC%AA%BD%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>16조 6966억 5014만</t>
+  </si>
+  <si>
     <t>존잘녀</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B4%EC%9E%98%EB%85%80</t>
   </si>
   <si>
-    <t>15조 8893억 8955만</t>
-  </si>
-  <si>
-    <t>품쪽이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%92%88%EC%AA%BD%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>14조 9503억 8211만</t>
+    <t>15조 9597억 6754만</t>
   </si>
   <si>
     <t>웨아</t>
@@ -1337,7 +1331,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%A8%EC%95%84</t>
   </si>
   <si>
-    <t>14조 5279억 9312만</t>
+    <t>14조 7810억 9980만</t>
   </si>
   <si>
     <t>통영고니</t>
@@ -1346,7 +1340,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%86%B5%EC%98%81%EA%B3%A0%EB%8B%88</t>
   </si>
   <si>
-    <t>10조 9549억 7607만</t>
+    <t>11조 162억 8215만</t>
   </si>
   <si>
     <t>으니림</t>
@@ -1355,7 +1349,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%BC%EB%8B%88%EB%A6%BC</t>
   </si>
   <si>
-    <t>9조 4561억 5315만</t>
+    <t>10조 1807억 7116만</t>
   </si>
   <si>
     <t>쪼재맨</t>
@@ -1364,7 +1358,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%AA%BC%EC%9E%AC%EB%A7%A8</t>
   </si>
   <si>
-    <t>7조 9617억 3798만</t>
+    <t>7조 9917억 2451만</t>
   </si>
   <si>
     <t>창목</t>
@@ -1373,7 +1367,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%BD%EB%AA%A9</t>
   </si>
   <si>
-    <t>6조 7256억 5217만</t>
+    <t>7조 4251억 6822만</t>
   </si>
   <si>
     <t>기동2</t>
@@ -1409,7 +1403,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%8C%80%EB%A1%9C%EA%BF%80</t>
   </si>
   <si>
-    <t>4조 5162억 334만</t>
+    <t>4조 6324억 5747만</t>
   </si>
   <si>
     <t>다둉이</t>
@@ -1418,7 +1412,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%91%89%EC%9D%B4</t>
   </si>
   <si>
-    <t>4조 912억 9312만</t>
+    <t>4조 3376억 8585만</t>
   </si>
   <si>
     <t>코뭉잉</t>
@@ -1436,7 +1430,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%9A%9D</t>
   </si>
   <si>
-    <t>3조 5340억 5619만</t>
+    <t>3조 5368억 434만</t>
   </si>
   <si>
     <t>황금어금니</t>
@@ -1445,7 +1439,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%A9%EA%B8%88%EC%96%B4%EA%B8%88%EB%8B%88</t>
   </si>
   <si>
-    <t>3조 223억 3320만</t>
+    <t>3조 1950억 73만</t>
   </si>
   <si>
     <t>가을호떡</t>
@@ -1481,7 +1475,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%AD%EA%B5%AC%EC%95%BC</t>
   </si>
   <si>
-    <t>191조 4184억 141만</t>
+    <t>205조 8777억 5636만</t>
   </si>
   <si>
     <t>새우탕z</t>
@@ -1490,7 +1484,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%88%EC%9A%B0%ED%83%95z</t>
   </si>
   <si>
-    <t>95조 1286억 8281만</t>
+    <t>101조 1858억 7562만</t>
   </si>
   <si>
     <t>ykm21cc</t>
@@ -1517,7 +1511,7 @@
     <t>https://mgf.gg/contents/character.php?n=ggggg</t>
   </si>
   <si>
-    <t>50조 5041억 4549만</t>
+    <t>52조 8962억 4056만</t>
   </si>
   <si>
     <t>리피트</t>
@@ -1526,7 +1520,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%ED%94%BC%ED%8A%B8</t>
   </si>
   <si>
-    <t>47조 108억 7018만</t>
+    <t>47조 1972억 766만</t>
   </si>
   <si>
     <t>친구닷</t>
@@ -1535,7 +1529,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%9C%EA%B5%AC%EB%8B%B7</t>
   </si>
   <si>
-    <t>42조 4357억 5444만</t>
+    <t>43조 1431억 6430만</t>
   </si>
   <si>
     <t>다헐</t>
@@ -1544,7 +1538,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%ED%97%90</t>
   </si>
   <si>
-    <t>38조 1647억 1810만</t>
+    <t>42조 6055억 3374만</t>
   </si>
   <si>
     <t>신림동물개</t>
@@ -1571,7 +1565,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EA%B7%BC%ED%98%9C%EC%8A%98</t>
   </si>
   <si>
-    <t>22조 9130억 8394만</t>
+    <t>24조 4449억 9045만</t>
   </si>
   <si>
     <t>이남선</t>
@@ -1580,7 +1574,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%82%A8%EC%84%A0</t>
   </si>
   <si>
-    <t>22조 3660억 3131만</t>
+    <t>22조 3839억 5868만</t>
   </si>
   <si>
     <t>냉동붕어</t>
@@ -1604,7 +1598,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%99%EC%88%9C%EC%95%84</t>
   </si>
   <si>
-    <t>18조 9699억 6528만</t>
+    <t>18조 9841억 8947만</t>
   </si>
   <si>
     <t>조은거임</t>
@@ -1613,7 +1607,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%9D%80%EA%B1%B0%EC%9E%84</t>
   </si>
   <si>
-    <t>15조 8467억 1311만</t>
+    <t>16조 2506억 1533만</t>
   </si>
   <si>
     <t>v지훈왕자v</t>
@@ -1631,7 +1625,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EC%9A%B0%EB%AA%A8%EB%AA%A8</t>
   </si>
   <si>
-    <t>13조 2864억 6494만</t>
+    <t>13조 5475억 1075만</t>
   </si>
   <si>
     <t>네모인간</t>
@@ -1640,7 +1634,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EB%AA%A8%EC%9D%B8%EA%B0%84</t>
   </si>
   <si>
-    <t>11조 754억 918만</t>
+    <t>12조 7863억 1640만</t>
   </si>
   <si>
     <t>Silas</t>
@@ -1649,7 +1643,7 @@
     <t>https://mgf.gg/contents/character.php?n=Silas</t>
   </si>
   <si>
-    <t>9조 3475억 3185만</t>
+    <t>9조 3760억 8346만</t>
   </si>
   <si>
     <t>뿡풍</t>
@@ -1676,7 +1670,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%84%B1%EA%B7%9C</t>
   </si>
   <si>
-    <t>5조 471억 6881만</t>
+    <t>5조 1031억 4143만</t>
   </si>
   <si>
     <t>갓친</t>
@@ -1685,7 +1679,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EC%B9%9C</t>
   </si>
   <si>
-    <t>4조 3384억 5023만</t>
+    <t>4조 3428억 5673만</t>
   </si>
   <si>
     <t>잘좀해봐</t>
@@ -2077,7 +2071,7 @@
     <col min="6" max="8" width="13.7109375" customWidth="1"/>
     <col min="9" max="9" width="14.7109375" customWidth="1"/>
     <col min="10" max="10" width="22.7109375" customWidth="1"/>
-    <col min="11" max="11" width="44.7109375" customWidth="1"/>
+    <col min="11" max="11" width="50.7109375" customWidth="1"/>
     <col min="12" max="12" width="19.7109375" customWidth="1"/>
     <col min="13" max="13" width="12.7109375" customWidth="1"/>
   </cols>
@@ -2313,16 +2307,16 @@
         <v>53</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>24</v>
@@ -2361,28 +2355,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -2393,28 +2387,28 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -2425,28 +2419,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2457,28 +2451,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2489,28 +2483,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2521,25 +2515,25 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>94</v>
@@ -2565,13 +2559,13 @@
         <v>97</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>98</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>99</v>
@@ -2597,7 +2591,7 @@
         <v>102</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>103</v>
@@ -2629,7 +2623,7 @@
         <v>108</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>103</v>
@@ -2661,10 +2655,10 @@
         <v>112</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>113</v>
@@ -2693,10 +2687,10 @@
         <v>117</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>118</v>
@@ -2725,10 +2719,10 @@
         <v>122</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>123</v>
@@ -2757,10 +2751,10 @@
         <v>127</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>123</v>
@@ -2789,10 +2783,10 @@
         <v>131</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>123</v>
@@ -2821,10 +2815,10 @@
         <v>135</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>123</v>
@@ -2853,13 +2847,13 @@
         <v>139</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>140</v>
@@ -2885,10 +2879,10 @@
         <v>143</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>144</v>
@@ -2917,10 +2911,10 @@
         <v>148</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>123</v>
@@ -2949,10 +2943,10 @@
         <v>152</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>118</v>
@@ -2981,10 +2975,10 @@
         <v>156</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>118</v>
@@ -3013,7 +3007,7 @@
         <v>160</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>103</v>
@@ -3045,10 +3039,10 @@
         <v>164</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>144</v>
@@ -3077,10 +3071,10 @@
         <v>168</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>118</v>
@@ -3109,10 +3103,10 @@
         <v>172</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>144</v>
@@ -3141,10 +3135,10 @@
         <v>176</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>177</v>
@@ -3173,10 +3167,10 @@
         <v>181</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>177</v>
@@ -3205,10 +3199,10 @@
         <v>185</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>144</v>
@@ -3228,25 +3222,25 @@
         <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>23</v>
+        <v>188</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>23</v>
+        <v>188</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>189</v>
+        <v>69</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3257,25 +3251,25 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>192</v>
+        <v>23</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>192</v>
+        <v>23</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>193</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>68</v>
+        <v>194</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>195</v>
@@ -3301,7 +3295,7 @@
         <v>198</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>199</v>
@@ -3333,7 +3327,7 @@
         <v>202</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>103</v>
@@ -3406,28 +3400,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3438,7 +3432,7 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>204</v>
@@ -3450,13 +3444,13 @@
         <v>205</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>103</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>206</v>
@@ -3470,7 +3464,7 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>207</v>
@@ -3482,16 +3476,16 @@
         <v>208</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>93</v>
+        <v>209</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -3502,28 +3496,28 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>199</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3534,28 +3528,28 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>93</v>
+        <v>209</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3566,28 +3560,28 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>93</v>
+        <v>209</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3601,16 +3595,16 @@
         <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>103</v>
@@ -3619,7 +3613,7 @@
         <v>113</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -3633,25 +3627,25 @@
         <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>123</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -3665,25 +3659,25 @@
         <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3697,25 +3691,25 @@
         <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>103</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3729,25 +3723,25 @@
         <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>103</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3767,19 +3761,19 @@
         <v>31</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>118</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3793,25 +3787,25 @@
         <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>118</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3825,25 +3819,25 @@
         <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>103</v>
+        <v>242</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -3857,25 +3851,25 @@
         <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3889,25 +3883,25 @@
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>247</v>
+        <v>87</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3921,25 +3915,25 @@
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>118</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3953,25 +3947,25 @@
         <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3985,16 +3979,16 @@
         <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>98</v>
@@ -4003,7 +3997,7 @@
         <v>177</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4017,25 +4011,25 @@
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>177</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4049,25 +4043,25 @@
         <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>118</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4081,25 +4075,25 @@
         <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>177</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4113,25 +4107,25 @@
         <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -4145,25 +4139,25 @@
         <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4177,25 +4171,25 @@
         <v>174</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -4209,25 +4203,25 @@
         <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>177</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4241,25 +4235,25 @@
         <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -4273,25 +4267,25 @@
         <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -4302,25 +4296,25 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>288</v>
+        <v>190</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>289</v>
@@ -4346,13 +4340,13 @@
         <v>291</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>292</v>
@@ -4378,10 +4372,10 @@
         <v>294</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>295</v>
@@ -4433,7 +4427,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -4442,7 +4436,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4451,28 +4445,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -4483,7 +4477,7 @@
         <v>32</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>297</v>
@@ -4495,7 +4489,7 @@
         <v>298</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>98</v>
@@ -4515,7 +4509,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>301</v>
@@ -4527,13 +4521,13 @@
         <v>302</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>303</v>
@@ -4547,7 +4541,7 @@
         <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>304</v>
@@ -4559,13 +4553,13 @@
         <v>305</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>93</v>
+        <v>209</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>306</v>
@@ -4579,7 +4573,7 @@
         <v>32</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>307</v>
@@ -4591,7 +4585,7 @@
         <v>308</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>103</v>
@@ -4611,7 +4605,7 @@
         <v>32</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>310</v>
@@ -4623,10 +4617,10 @@
         <v>311</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>113</v>
@@ -4655,10 +4649,10 @@
         <v>314</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>113</v>
@@ -4687,10 +4681,10 @@
         <v>317</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>118</v>
@@ -4719,10 +4713,10 @@
         <v>320</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>118</v>
@@ -4751,10 +4745,10 @@
         <v>323</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>118</v>
@@ -4783,10 +4777,10 @@
         <v>326</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>118</v>
@@ -4815,10 +4809,10 @@
         <v>329</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>118</v>
@@ -4847,10 +4841,10 @@
         <v>332</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>177</v>
@@ -4879,10 +4873,10 @@
         <v>335</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>144</v>
@@ -4911,10 +4905,10 @@
         <v>338</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>144</v>
@@ -4943,10 +4937,10 @@
         <v>341</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>177</v>
@@ -4975,10 +4969,10 @@
         <v>344</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>177</v>
@@ -5007,10 +5001,10 @@
         <v>347</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>177</v>
@@ -5039,10 +5033,10 @@
         <v>350</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>144</v>
@@ -5071,10 +5065,10 @@
         <v>352</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>177</v>
@@ -5103,13 +5097,13 @@
         <v>355</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>356</v>
@@ -5135,13 +5129,13 @@
         <v>358</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>359</v>
@@ -5167,13 +5161,13 @@
         <v>361</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>362</v>
@@ -5199,16 +5193,16 @@
         <v>364</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>194</v>
+        <v>365</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5222,25 +5216,25 @@
         <v>174</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>288</v>
+        <v>190</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5254,25 +5248,25 @@
         <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>288</v>
+        <v>365</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5286,25 +5280,25 @@
         <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5318,25 +5312,25 @@
         <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>295</v>
+        <v>365</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5347,67 +5341,35 @@
         <v>32</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>69</v>
+        <v>270</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>288</v>
+        <v>365</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J29"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -5437,7 +5399,6 @@
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5463,28 +5424,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -5495,28 +5456,28 @@
         <v>41</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>98</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>76</v>
+        <v>299</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5527,28 +5488,28 @@
         <v>41</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>387</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5559,28 +5520,28 @@
         <v>41</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>103</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>93</v>
+        <v>209</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5591,28 +5552,28 @@
         <v>41</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>123</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5623,28 +5584,28 @@
         <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>123</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5658,25 +5619,25 @@
         <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>123</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5690,16 +5651,16 @@
         <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>103</v>
@@ -5708,7 +5669,7 @@
         <v>118</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5722,25 +5683,25 @@
         <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5754,25 +5715,25 @@
         <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>408</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>410</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5786,16 +5747,16 @@
         <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>103</v>
@@ -5804,7 +5765,7 @@
         <v>144</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5818,25 +5779,25 @@
         <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>177</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5850,25 +5811,25 @@
         <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5882,25 +5843,25 @@
         <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>420</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>422</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5914,25 +5875,25 @@
         <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5952,19 +5913,19 @@
         <v>47</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>177</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5978,25 +5939,25 @@
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>428</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>430</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6010,25 +5971,25 @@
         <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>431</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>433</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6042,25 +6003,25 @@
         <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>434</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>436</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6074,25 +6035,25 @@
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>437</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>439</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6106,25 +6067,25 @@
         <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>440</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>442</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6138,25 +6099,25 @@
         <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>443</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>445</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6170,25 +6131,25 @@
         <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>446</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>448</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6202,25 +6163,25 @@
         <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>451</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6234,25 +6195,25 @@
         <v>174</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>454</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6266,25 +6227,25 @@
         <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>295</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6298,25 +6259,25 @@
         <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>458</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>460</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6330,16 +6291,16 @@
         <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>199</v>
@@ -6348,7 +6309,7 @@
         <v>295</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6359,28 +6320,28 @@
         <v>41</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>464</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>466</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6394,25 +6355,25 @@
         <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>467</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>469</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6426,25 +6387,25 @@
         <v>17</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>470</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>472</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6508,28 +6469,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -6540,28 +6501,28 @@
         <v>48</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>473</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>475</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6572,28 +6533,28 @@
         <v>48</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>476</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>478</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6604,28 +6565,28 @@
         <v>48</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>479</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>481</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6636,28 +6597,28 @@
         <v>48</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>199</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6668,28 +6629,28 @@
         <v>48</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>118</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6703,25 +6664,25 @@
         <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>118</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6735,16 +6696,16 @@
         <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>103</v>
@@ -6753,7 +6714,7 @@
         <v>118</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6767,25 +6728,25 @@
         <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6799,25 +6760,25 @@
         <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>497</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>499</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6831,16 +6792,16 @@
         <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>103</v>
@@ -6849,7 +6810,7 @@
         <v>177</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6863,25 +6824,25 @@
         <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>503</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>505</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6895,25 +6856,25 @@
         <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>506</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>508</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6927,25 +6888,25 @@
         <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>509</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>511</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6959,25 +6920,25 @@
         <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>177</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6991,25 +6952,25 @@
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>177</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -7023,25 +6984,25 @@
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>518</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>520</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7055,25 +7016,25 @@
         <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7087,25 +7048,25 @@
         <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>523</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>525</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7119,25 +7080,25 @@
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>177</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7151,25 +7112,25 @@
         <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>295</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7183,25 +7144,25 @@
         <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>532</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>534</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7215,25 +7176,25 @@
         <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>535</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>537</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7247,25 +7208,25 @@
         <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>538</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>540</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7279,25 +7240,25 @@
         <v>174</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>541</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>543</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7311,25 +7272,25 @@
         <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>544</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>546</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7343,25 +7304,25 @@
         <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>547</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>549</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7375,16 +7336,16 @@
         <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>199</v>
@@ -7393,7 +7354,7 @@
         <v>295</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7404,28 +7365,28 @@
         <v>48</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>553</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>555</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -7439,25 +7400,25 @@
         <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>295</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -92,7 +92,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>2경 6796조 388억 1382만</t>
+    <t>2경 7502조 1979억 4만</t>
   </si>
   <si>
     <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
@@ -101,7 +101,7 @@
     <t>혜영</t>
   </si>
   <si>
-    <t>2026.04.25</t>
+    <t>2026.04.26</t>
   </si>
   <si>
     <t>빠따</t>
@@ -116,7 +116,7 @@
     <t>41</t>
   </si>
   <si>
-    <t>1경 8115조 5222억 7692만</t>
+    <t>1경 8334조 7528억 1738만</t>
   </si>
   <si>
     <t>자유가입</t>
@@ -143,7 +143,7 @@
     <t>28명</t>
   </si>
   <si>
-    <t>2경 702조 3737억 9391만</t>
+    <t>2경 1010조 3722억 7342만</t>
   </si>
   <si>
     <t>가입문의: 한딸기, 화질, 람볼기니 토벌100등 안쪽 귓 주세요. 길컨 , 파퀘, 자쿰, 혼테일 모든 컨테츠 활발하게 즐길 사람!!</t>
@@ -164,7 +164,7 @@
     <t>42</t>
   </si>
   <si>
-    <t>1경 7676조 6046억 7943만</t>
+    <t>1경 8110조 4181억 3714만</t>
   </si>
   <si>
     <t>일일연구 길드토벌 길드대전 하루이상 안하시거나 이틀미접시 통지없이 내보냅니다</t>
@@ -194,7 +194,7 @@
     <t>29명</t>
   </si>
   <si>
-    <t>1경 7192조 6624억 391만</t>
+    <t>1경 7210조 8368억 6406만</t>
   </si>
   <si>
     <t>www.친구들.com 보고 가입 문의</t>
@@ -245,7 +245,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>1경 1424조 663억 2805만</t>
+    <t>1경 2008조 4332억 5078만</t>
   </si>
   <si>
     <t>2</t>
@@ -371,7 +371,7 @@
     <t>107</t>
   </si>
   <si>
-    <t>348조 1289억 3205만</t>
+    <t>397조 7120억 8955만</t>
   </si>
   <si>
     <t>10</t>
@@ -383,111 +383,111 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
   </si>
   <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>333조 3422억 5764만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>258조 3204억 368만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>213조 2895억 1154만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>프리프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>186조 1628억 3024만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>149조 1517억 6031만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>쾌감</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
+  </si>
+  <si>
+    <t>145조 2700억 5418만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>소소채2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>110조 3430억 5093만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>101조 1343억 8739만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
     <t>105</t>
   </si>
   <si>
-    <t>304조 6773억 166만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>니달리신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>230조 3464억 5320만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>213조 2895억 1154만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>프리프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>186조 1628억 3024만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>146조 2654억 7912만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>쾌감</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
-  </si>
-  <si>
-    <t>142조 8456억 49만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>110조 3430억 5093만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>99조 5084억 4454만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
     <t>96조 4965억 8645만</t>
   </si>
   <si>
@@ -500,7 +500,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
   </si>
   <si>
-    <t>89조 6690억 4023만</t>
+    <t>92조 9372억 1789만</t>
   </si>
   <si>
     <t>20</t>
@@ -524,7 +524,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
   </si>
   <si>
-    <t>56조 5716억 833만</t>
+    <t>59조 6154억 5137만</t>
   </si>
   <si>
     <t>22</t>
@@ -536,7 +536,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
   </si>
   <si>
-    <t>53조 5004억 3815만</t>
+    <t>54조 3689억 898만</t>
   </si>
   <si>
     <t>23</t>
@@ -563,7 +563,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>41조 2396억 8935만</t>
+    <t>43조 3112억 2854만</t>
   </si>
   <si>
     <t>25</t>
@@ -629,7 +629,7 @@
     <t>아크메이지(불,독)</t>
   </si>
   <si>
-    <t>35조 8282억 7914만</t>
+    <t>35조 9640억 2609만</t>
   </si>
   <si>
     <t>몽호</t>
@@ -659,7 +659,7 @@
     <t>109</t>
   </si>
   <si>
-    <t>3341조 2739억 4499만</t>
+    <t>3390조 2926억 6569만</t>
   </si>
   <si>
     <t>요르v</t>
@@ -668,7 +668,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EB%A5%B4v</t>
   </si>
   <si>
-    <t>2775조 6394억 3940만</t>
+    <t>2918조 4745억 6691만</t>
   </si>
   <si>
     <t>o베베o</t>
@@ -677,7 +677,7 @@
     <t>https://mgf.gg/contents/character.php?n=o%EB%B2%A0%EB%B2%A0o</t>
   </si>
   <si>
-    <t>2224조 2119억 198만</t>
+    <t>2230조 4002억 5849만</t>
   </si>
   <si>
     <t>o원기o</t>
@@ -704,7 +704,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%B2%95%EC%82%AC%EA%B9%80%EC%98%81%EC%9A%B1</t>
   </si>
   <si>
-    <t>307조 5314억 80만</t>
+    <t>309조 3796억 2689만</t>
   </si>
   <si>
     <t>워워이</t>
@@ -713,7 +713,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%8C%EC%9B%8C%EC%9D%B4</t>
   </si>
   <si>
-    <t>243조 7416억 9047만</t>
+    <t>243조 9380억 150만</t>
   </si>
   <si>
     <t>o후국o</t>
@@ -746,7 +746,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9B%90%EC%9D%BC</t>
   </si>
   <si>
-    <t>143조 5472억 4797만</t>
+    <t>148조 486억 7521만</t>
   </si>
   <si>
     <t>o진이o</t>
@@ -758,7 +758,7 @@
     <t>나이트로드</t>
   </si>
   <si>
-    <t>136조 6367억 1816만</t>
+    <t>137조 4015억 3332만</t>
   </si>
   <si>
     <t>빵섭이</t>
@@ -785,7 +785,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%9A%A4</t>
   </si>
   <si>
-    <t>85조 6670억 293만</t>
+    <t>97조 9798억 2864만</t>
   </si>
   <si>
     <t>뭥끼</t>
@@ -812,7 +812,7 @@
     <t>https://mgf.gg/contents/character.php?n=o%EC%97%89%EB%8C%95o</t>
   </si>
   <si>
-    <t>72조 843억 8310만</t>
+    <t>72조 1216억 2747만</t>
   </si>
   <si>
     <t>FFFK</t>
@@ -842,7 +842,16 @@
     <t>보우마스터</t>
   </si>
   <si>
-    <t>51조 811억 1462만</t>
+    <t>53조 9822억 4468만</t>
+  </si>
+  <si>
+    <t>호이호이포이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9D%B4%ED%98%B8%EC%9D%B4%ED%8F%AC%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>35조 9382억 9079만</t>
   </si>
   <si>
     <t>동부마트</t>
@@ -851,16 +860,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%B6%80%EB%A7%88%ED%8A%B8</t>
   </si>
   <si>
-    <t>31조 1082억 4428만</t>
-  </si>
-  <si>
-    <t>호이호이포이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9D%B4%ED%98%B8%EC%9D%B4%ED%8F%AC%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>30조 770억 4470만</t>
+    <t>31조 1973억 4624만</t>
+  </si>
+  <si>
+    <t>겨울난방</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%EB%82%9C%EB%B0%A9</t>
+  </si>
+  <si>
+    <t>17조 7176억 4343만</t>
   </si>
   <si>
     <t>옹이잉</t>
@@ -872,22 +881,13 @@
     <t>17조 7165억 8053만</t>
   </si>
   <si>
-    <t>겨울난방</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%EB%82%9C%EB%B0%A9</t>
-  </si>
-  <si>
-    <t>17조 6938억 6100만</t>
-  </si>
-  <si>
     <t>우패밀리</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%8C%A8%EB%B0%80%EB%A6%AC</t>
   </si>
   <si>
-    <t>16조 8961억 7543만</t>
+    <t>16조 9648억 7675만</t>
   </si>
   <si>
     <t>담훌</t>
@@ -896,7 +896,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%B4%ED%9B%8C</t>
   </si>
   <si>
-    <t>15조 442억 9951만</t>
+    <t>16조 4001억 3804만</t>
   </si>
   <si>
     <t>뚠뚠냥이</t>
@@ -917,7 +917,7 @@
     <t>100</t>
   </si>
   <si>
-    <t>9조 9894억 7962만</t>
+    <t>10조 127억 6629만</t>
   </si>
   <si>
     <t>람볼기니</t>
@@ -929,7 +929,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>1경 804조 5011억 19만</t>
+    <t>1경 1034조 8839억 5566만</t>
   </si>
   <si>
     <t>봉띤</t>
@@ -974,7 +974,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%97%88%EB%8F%99</t>
   </si>
   <si>
-    <t>427조 67억 2399만</t>
+    <t>528조 3828억 8938만</t>
   </si>
   <si>
     <t>삼뚝</t>
@@ -1019,7 +1019,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%81%B4%EC%9D%B4</t>
   </si>
   <si>
-    <t>74조 7631억 3241만</t>
+    <t>78조 1737억 2570만</t>
   </si>
   <si>
     <t>지흠</t>
@@ -1055,7 +1055,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%97%85</t>
   </si>
   <si>
-    <t>31조 4877억 5588만</t>
+    <t>32조 6501억 7545만</t>
   </si>
   <si>
     <t>오버츄어리</t>
@@ -1064,7 +1064,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%B2%84%EC%B8%84%EC%96%B4%EB%A6%AC</t>
   </si>
   <si>
-    <t>29조 1643억 3603만</t>
+    <t>29조 9539억 5478만</t>
   </si>
   <si>
     <t>매스리</t>
@@ -1088,7 +1088,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A7%88</t>
   </si>
   <si>
-    <t>18조 8175억 7945만</t>
+    <t>18조 8340억 7797만</t>
   </si>
   <si>
     <t>꽁칫</t>
@@ -1097,7 +1097,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EC%B9%AB</t>
   </si>
   <si>
-    <t>18조 6334억 109만</t>
+    <t>18조 7049억 4818만</t>
   </si>
   <si>
     <t>앵찬</t>
@@ -1115,7 +1115,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%ED%8E%A0</t>
   </si>
   <si>
-    <t>15조 5808억 2263만</t>
+    <t>15조 7047억 8789만</t>
   </si>
   <si>
     <t>LifeLegend</t>
@@ -1172,7 +1172,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%95%8C%EA%BE%B8</t>
   </si>
   <si>
-    <t>4조 16억 4833만</t>
+    <t>4조 962억 7800만</t>
   </si>
   <si>
     <t>딱뎀</t>
@@ -1190,7 +1190,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EC%9D%B4%EB%90%9C%EC%82%AC%EB%82%98%EC%9D%B4</t>
   </si>
   <si>
-    <t>3180조 8876억 2671만</t>
+    <t>3588조 6011억 8501만</t>
   </si>
   <si>
     <t>또르뱅</t>
@@ -1199,7 +1199,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%A5%B4%EB%B1%85</t>
   </si>
   <si>
-    <t>2730조 7758억 8782만</t>
+    <t>2731조 7186억 2486만</t>
   </si>
   <si>
     <t>Hoood</t>
@@ -1208,7 +1208,7 @@
     <t>https://mgf.gg/contents/character.php?n=Hoood</t>
   </si>
   <si>
-    <t>391조 159억 8557만</t>
+    <t>402조 9905억 2284만</t>
   </si>
   <si>
     <t>클리닝티슈</t>
@@ -1226,7 +1226,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B9%85</t>
   </si>
   <si>
-    <t>175조 3099억 190만</t>
+    <t>175조 4483억 4392만</t>
   </si>
   <si>
     <t>내사랑로제</t>
@@ -1247,6 +1247,15 @@
     <t>103조 1493억 1597만</t>
   </si>
   <si>
+    <t>얘인</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%98%EC%9D%B8</t>
+  </si>
+  <si>
+    <t>57조 5323억 515만</t>
+  </si>
+  <si>
     <t>손끝의예리함</t>
   </si>
   <si>
@@ -1256,22 +1265,22 @@
     <t>55조 226억 9129만</t>
   </si>
   <si>
-    <t>얘인</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%98%EC%9D%B8</t>
-  </si>
-  <si>
-    <t>53조 5972억 1240만</t>
-  </si>
-  <si>
     <t>쌈싸</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8C%88%EC%8B%B8</t>
   </si>
   <si>
-    <t>34조 1766억 2670만</t>
+    <t>37조 3540억 6780만</t>
+  </si>
+  <si>
+    <t>퓨엉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%93%A8%EC%97%89</t>
+  </si>
+  <si>
+    <t>30조 1885억 1701만</t>
   </si>
   <si>
     <t>쑹쓩</t>
@@ -1283,22 +1292,13 @@
     <t>30조 1792억 7780만</t>
   </si>
   <si>
-    <t>퓨엉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%93%A8%EC%97%89</t>
-  </si>
-  <si>
-    <t>30조 697억 8315만</t>
-  </si>
-  <si>
     <t>공성현</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EC%84%B1%ED%98%84</t>
   </si>
   <si>
-    <t>26조 7316억 9260만</t>
+    <t>27조 1546억 3975만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%B6%EA%B0%90%EB%A7%90%EC%9D%B4</t>
@@ -1307,6 +1307,15 @@
     <t>20조 4796억 8556만</t>
   </si>
   <si>
+    <t>존잘녀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B4%EC%9E%98%EB%85%80</t>
+  </si>
+  <si>
+    <t>19조 5580억 6011만</t>
+  </si>
+  <si>
     <t>품쪽이</t>
   </si>
   <si>
@@ -1316,22 +1325,13 @@
     <t>16조 6966억 5014만</t>
   </si>
   <si>
-    <t>존잘녀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B4%EC%9E%98%EB%85%80</t>
-  </si>
-  <si>
-    <t>15조 9597억 6754만</t>
-  </si>
-  <si>
     <t>웨아</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%A8%EC%95%84</t>
   </si>
   <si>
-    <t>14조 7810억 9980만</t>
+    <t>14조 8134억 7477만</t>
   </si>
   <si>
     <t>통영고니</t>
@@ -1349,7 +1349,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%BC%EB%8B%88%EB%A6%BC</t>
   </si>
   <si>
-    <t>10조 1807억 7116만</t>
+    <t>10조 2504억 7055만</t>
   </si>
   <si>
     <t>쪼재맨</t>
@@ -1358,7 +1358,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%AA%BC%EC%9E%AC%EB%A7%A8</t>
   </si>
   <si>
-    <t>7조 9917억 2451만</t>
+    <t>8조 9454억 2665만</t>
   </si>
   <si>
     <t>창목</t>
@@ -1376,7 +1376,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%8F%992</t>
   </si>
   <si>
-    <t>6조 1981억 9910만</t>
+    <t>6조 9087억 8647만</t>
   </si>
   <si>
     <t>코몽잉</t>
@@ -1394,7 +1394,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%98%EC%B5%B8%EC%B9%98</t>
   </si>
   <si>
-    <t>5조 1751억 2244만</t>
+    <t>5조 1953억 5606만</t>
   </si>
   <si>
     <t>그대로꿀</t>
@@ -1412,7 +1412,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EB%91%89%EC%9D%B4</t>
   </si>
   <si>
-    <t>4조 3376억 8585만</t>
+    <t>4조 3405억 3852만</t>
   </si>
   <si>
     <t>코뭉잉</t>
@@ -1430,7 +1430,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%9A%9D</t>
   </si>
   <si>
-    <t>3조 5368억 434만</t>
+    <t>3조 5390억 2985만</t>
   </si>
   <si>
     <t>황금어금니</t>
@@ -1484,7 +1484,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%88%EC%9A%B0%ED%83%95z</t>
   </si>
   <si>
-    <t>101조 1858억 7562만</t>
+    <t>103조 4259억 524만</t>
   </si>
   <si>
     <t>ykm21cc</t>
@@ -1502,7 +1502,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%A0%95%EC%83%89</t>
   </si>
   <si>
-    <t>64조 4806억 578만</t>
+    <t>68조 7190억 6046만</t>
   </si>
   <si>
     <t>ggggg</t>
@@ -1514,13 +1514,22 @@
     <t>52조 8962억 4056만</t>
   </si>
   <si>
+    <t>다헐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%ED%97%90</t>
+  </si>
+  <si>
+    <t>49조 7577억 9577만</t>
+  </si>
+  <si>
     <t>리피트</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%ED%94%BC%ED%8A%B8</t>
   </si>
   <si>
-    <t>47조 1972억 766만</t>
+    <t>47조 7713억 1276만</t>
   </si>
   <si>
     <t>친구닷</t>
@@ -1529,16 +1538,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%9C%EA%B5%AC%EB%8B%B7</t>
   </si>
   <si>
-    <t>43조 1431억 6430만</t>
-  </si>
-  <si>
-    <t>다헐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%ED%97%90</t>
-  </si>
-  <si>
-    <t>42조 6055억 3374만</t>
+    <t>43조 1750억 5861만</t>
   </si>
   <si>
     <t>신림동물개</t>
@@ -1574,7 +1574,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%82%A8%EC%84%A0</t>
   </si>
   <si>
-    <t>22조 3839억 5868만</t>
+    <t>22조 5670억 2297만</t>
   </si>
   <si>
     <t>냉동붕어</t>
@@ -1607,7 +1607,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%9D%80%EA%B1%B0%EC%9E%84</t>
   </si>
   <si>
-    <t>16조 2506억 1533만</t>
+    <t>16조 2896억 6257만</t>
   </si>
   <si>
     <t>v지훈왕자v</t>
@@ -1625,7 +1625,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EC%9A%B0%EB%AA%A8%EB%AA%A8</t>
   </si>
   <si>
-    <t>13조 5475억 1075만</t>
+    <t>13조 5968억 5417만</t>
   </si>
   <si>
     <t>네모인간</t>
@@ -1637,22 +1637,31 @@
     <t>12조 7863억 1640만</t>
   </si>
   <si>
+    <t>뿡풍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%ED%92%8D</t>
+  </si>
+  <si>
+    <t>10조 9781억 3116만</t>
+  </si>
+  <si>
     <t>Silas</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=Silas</t>
   </si>
   <si>
-    <t>9조 3760억 8346만</t>
-  </si>
-  <si>
-    <t>뿡풍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%ED%92%8D</t>
-  </si>
-  <si>
-    <t>7조 7723억 3025만</t>
+    <t>10조 9751억 5209만</t>
+  </si>
+  <si>
+    <t>진성규</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%84%B1%EA%B7%9C</t>
+  </si>
+  <si>
+    <t>7조 7443억 9675만</t>
   </si>
   <si>
     <t>후비</t>
@@ -1664,15 +1673,6 @@
     <t>7조 5387억 8833만</t>
   </si>
   <si>
-    <t>진성규</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%84%B1%EA%B7%9C</t>
-  </si>
-  <si>
-    <t>5조 1031억 4143만</t>
-  </si>
-  <si>
     <t>갓친</t>
   </si>
   <si>
@@ -1688,7 +1688,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%98%EC%A2%80%ED%95%B4%EB%B4%90</t>
   </si>
   <si>
-    <t>4조 1820억 7513만</t>
+    <t>4조 3067억 7586만</t>
   </si>
   <si>
     <t>예끔이</t>
@@ -1697,7 +1697,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%81%94%EC%9D%B4</t>
   </si>
   <si>
-    <t>3조 4639억 9187만</t>
+    <t>3조 5309억 180만</t>
   </si>
 </sst>
 </file>
@@ -2346,7 +2346,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2725,10 +2725,10 @@
         <v>82</v>
       </c>
       <c r="H12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2739,16 +2739,16 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>69</v>
@@ -2757,10 +2757,10 @@
         <v>70</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2771,16 +2771,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>69</v>
@@ -2789,10 +2789,10 @@
         <v>93</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2803,16 +2803,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>69</v>
@@ -2821,10 +2821,10 @@
         <v>87</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2835,16 +2835,16 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>69</v>
@@ -2856,7 +2856,7 @@
         <v>113</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2867,16 +2867,16 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>69</v>
@@ -2885,10 +2885,10 @@
         <v>93</v>
       </c>
       <c r="H17" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2899,16 +2899,16 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>69</v>
@@ -2917,10 +2917,10 @@
         <v>93</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2931,16 +2931,16 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>69</v>
@@ -2949,7 +2949,7 @@
         <v>76</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>153</v>
@@ -2981,7 +2981,7 @@
         <v>76</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>157</v>
@@ -3013,7 +3013,7 @@
         <v>103</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>161</v>
@@ -3045,7 +3045,7 @@
         <v>87</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>165</v>
@@ -3077,7 +3077,7 @@
         <v>93</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>169</v>
@@ -3109,7 +3109,7 @@
         <v>76</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>173</v>
@@ -3205,7 +3205,7 @@
         <v>93</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>186</v>
@@ -3269,7 +3269,7 @@
         <v>76</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>195</v>
@@ -3301,7 +3301,7 @@
         <v>199</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>200</v>
@@ -3333,7 +3333,7 @@
         <v>103</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>203</v>
@@ -3578,7 +3578,7 @@
         <v>76</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>209</v>
+        <v>88</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>219</v>
@@ -3642,7 +3642,7 @@
         <v>82</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>225</v>
@@ -3674,7 +3674,7 @@
         <v>93</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>228</v>
@@ -3706,7 +3706,7 @@
         <v>103</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>231</v>
@@ -3738,7 +3738,7 @@
         <v>103</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>234</v>
@@ -3770,7 +3770,7 @@
         <v>93</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>236</v>
@@ -3784,7 +3784,7 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>237</v>
@@ -3802,7 +3802,7 @@
         <v>93</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>239</v>
@@ -3816,7 +3816,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>240</v>
@@ -3834,7 +3834,7 @@
         <v>242</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>243</v>
@@ -3848,7 +3848,7 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>244</v>
@@ -3866,7 +3866,7 @@
         <v>103</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>246</v>
@@ -3880,7 +3880,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>247</v>
@@ -3898,7 +3898,7 @@
         <v>87</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>249</v>
@@ -3912,7 +3912,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>250</v>
@@ -3930,7 +3930,7 @@
         <v>70</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>252</v>
@@ -3944,7 +3944,7 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>253</v>
@@ -3962,7 +3962,7 @@
         <v>87</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>255</v>
@@ -3976,7 +3976,7 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>256</v>
@@ -4058,7 +4058,7 @@
         <v>93</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>264</v>
@@ -4122,7 +4122,7 @@
         <v>270</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>271</v>
@@ -4151,10 +4151,10 @@
         <v>69</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>274</v>
@@ -4183,10 +4183,10 @@
         <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>277</v>
@@ -4215,10 +4215,10 @@
         <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>280</v>
@@ -4247,10 +4247,10 @@
         <v>69</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>283</v>
@@ -4282,7 +4282,7 @@
         <v>93</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>286</v>
@@ -4436,7 +4436,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4687,7 +4687,7 @@
         <v>242</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>318</v>
@@ -4719,7 +4719,7 @@
         <v>70</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>321</v>
@@ -4751,7 +4751,7 @@
         <v>70</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>324</v>
@@ -4783,7 +4783,7 @@
         <v>87</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>327</v>
@@ -4815,7 +4815,7 @@
         <v>93</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>330</v>
@@ -4829,7 +4829,7 @@
         <v>32</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>331</v>
@@ -4861,7 +4861,7 @@
         <v>32</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>334</v>
@@ -4879,7 +4879,7 @@
         <v>87</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>336</v>
@@ -4893,7 +4893,7 @@
         <v>32</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>337</v>
@@ -4911,7 +4911,7 @@
         <v>76</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>339</v>
@@ -4925,7 +4925,7 @@
         <v>32</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>340</v>
@@ -4957,7 +4957,7 @@
         <v>32</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>343</v>
@@ -4989,7 +4989,7 @@
         <v>32</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>346</v>
@@ -5021,7 +5021,7 @@
         <v>32</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>349</v>
@@ -5039,7 +5039,7 @@
         <v>76</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>351</v>
@@ -5506,7 +5506,7 @@
         <v>93</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>209</v>
+        <v>88</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>387</v>
@@ -5570,7 +5570,7 @@
         <v>76</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>393</v>
@@ -5602,7 +5602,7 @@
         <v>70</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>396</v>
@@ -5634,7 +5634,7 @@
         <v>76</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>399</v>
@@ -5666,7 +5666,7 @@
         <v>103</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>402</v>
@@ -5698,7 +5698,7 @@
         <v>87</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>405</v>
@@ -5727,10 +5727,10 @@
         <v>69</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>408</v>
@@ -5759,10 +5759,10 @@
         <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>411</v>
@@ -5808,7 +5808,7 @@
         <v>41</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>415</v>
@@ -5823,10 +5823,10 @@
         <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>144</v>
+        <v>190</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>417</v>
@@ -5840,7 +5840,7 @@
         <v>41</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>418</v>
@@ -5855,10 +5855,10 @@
         <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>190</v>
+        <v>143</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>420</v>
@@ -5872,7 +5872,7 @@
         <v>41</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>421</v>
@@ -5890,7 +5890,7 @@
         <v>93</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>423</v>
@@ -5904,7 +5904,7 @@
         <v>41</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>47</v>
@@ -5936,7 +5936,7 @@
         <v>41</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>426</v>
@@ -5951,7 +5951,7 @@
         <v>69</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>190</v>
@@ -5968,7 +5968,7 @@
         <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>429</v>
@@ -5983,7 +5983,7 @@
         <v>69</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>190</v>
@@ -6000,7 +6000,7 @@
         <v>41</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>432</v>
@@ -6114,7 +6114,7 @@
         <v>93</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>365</v>
+        <v>190</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>443</v>
@@ -6615,7 +6615,7 @@
         <v>199</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>482</v>
@@ -6647,7 +6647,7 @@
         <v>70</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>485</v>
@@ -6679,7 +6679,7 @@
         <v>76</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>488</v>
@@ -6711,7 +6711,7 @@
         <v>103</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>491</v>
@@ -6743,7 +6743,7 @@
         <v>87</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>494</v>
@@ -6775,7 +6775,7 @@
         <v>93</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>497</v>
@@ -6804,7 +6804,7 @@
         <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>177</v>
@@ -6836,10 +6836,10 @@
         <v>69</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>118</v>
+        <v>177</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>503</v>
@@ -6853,7 +6853,7 @@
         <v>48</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>504</v>
@@ -6885,7 +6885,7 @@
         <v>48</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>507</v>
@@ -6917,7 +6917,7 @@
         <v>48</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>510</v>
@@ -6949,7 +6949,7 @@
         <v>48</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>513</v>
@@ -6981,7 +6981,7 @@
         <v>48</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>516</v>
@@ -7013,7 +7013,7 @@
         <v>48</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>57</v>
@@ -7045,7 +7045,7 @@
         <v>48</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>521</v>
@@ -7415,7 +7415,7 @@
         <v>93</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>295</v>
+        <v>365</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>556</v>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">RAINBOW!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">RAINBOW!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">동물들의낙원!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">빠따!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">셀린느!$A$1:$J$31</definedName>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="560">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,787 +80,787 @@
     <t>Scania 2</t>
   </si>
   <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>1위</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>2경 7731조 1714억 2883만</t>
+  </si>
+  <si>
+    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
+  </si>
+  <si>
+    <t>혜영</t>
+  </si>
+  <si>
+    <t>2026.04.27</t>
+  </si>
+  <si>
+    <t>빠따</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%A0%EB%94%B0</t>
+  </si>
+  <si>
+    <t>Scania 12</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>1경 8750조 4613억 1676만</t>
+  </si>
+  <si>
+    <t>자유가입</t>
+  </si>
+  <si>
+    <t>o볼륨o</t>
+  </si>
+  <si>
+    <t>RAINBOW</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=RAINBOW</t>
+  </si>
+  <si>
+    <t>Scania 6</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>2위</t>
+  </si>
+  <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>2경 1095조 826억 2157만</t>
+  </si>
+  <si>
+    <t>가입문의: 화질, 한딸기, 람볼기니 토벌100등 안쪽 귓 주세요. 길컨 , 파퀘, 자쿰, 혼테일 모든 컨테츠 활발하게 즐길 사람!!</t>
+  </si>
+  <si>
+    <t>화질</t>
+  </si>
+  <si>
+    <t>동물들의낙원</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%8F%99%EB%AC%BC%EB%93%A4%EC%9D%98%EB%82%99%EC%9B%90</t>
+  </si>
+  <si>
+    <t>Scania 13</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>1경 8489조 841억 8194만</t>
+  </si>
+  <si>
+    <t>일일연구 길드토벌 길드대전 하루이상 안하시거나 이틀미접시 통지없이 내보냅니다</t>
+  </si>
+  <si>
+    <t>곶감말이</t>
+  </si>
+  <si>
+    <t>친구들</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%B9%9C%EA%B5%AC%EB%93%A4</t>
+  </si>
+  <si>
+    <t>Scania 11</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>3위</t>
+  </si>
+  <si>
+    <t>Lv.10</t>
+  </si>
+  <si>
+    <t>1경 7270조 5714억 211만</t>
+  </si>
+  <si>
+    <t>www.친구들.com 보고 가입 문의</t>
+  </si>
+  <si>
+    <t>친구둘리</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>스타냥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>1경 2008조 4332억 5078만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>진자이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>4143조 7347억 1708만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>돈스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>3322조 3154억 8065만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>말레이히어로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>1904조 7904억 7321만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>스타캐치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>1645조 8595억 7138만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>빌런투킬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>1185조 7524억 3872만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>스타뎀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%8E%80</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>475조 5893억 7767만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>단풍노비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>405조 7175억 7562만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>여사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
+  </si>
+  <si>
+    <t>400조 1307억 6796만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>부엉이없다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>338조 9646억 7953만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>262조 2999억 524만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>225조 7000억 9512만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>프리프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>186조 1628억 3024만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>쾌감</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
+  </si>
+  <si>
+    <t>149조 2169억 9071만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>149조 1517억 6031만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>소소채2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>121조 611억 949만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>107조 5816억 7176만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>106조 419억 1690만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>96조 866억 2864만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>POSCO</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
+  </si>
+  <si>
+    <t>65조 7697억 3285만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>두근푸근연근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>59조 6154억 5137만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>58조 7294억 5027만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>포뇨야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
+  </si>
+  <si>
+    <t>46조 2787억 8294만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>울힝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>43조 3112억 2854만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>김치싸대기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>39조 8824억 3269만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>38조 8158억 1231만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>악의꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
+  </si>
+  <si>
+    <t>38조 2904억 9899만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>37조 9202억 5357만</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>36조 514억 1080만</t>
+  </si>
+  <si>
     <t>30</t>
   </si>
   <si>
-    <t>1위</t>
-  </si>
-  <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>2경 7502조 1979억 4만</t>
-  </si>
-  <si>
-    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
-  </si>
-  <si>
-    <t>혜영</t>
-  </si>
-  <si>
-    <t>2026.04.26</t>
-  </si>
-  <si>
-    <t>빠따</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%A0%EB%94%B0</t>
-  </si>
-  <si>
-    <t>Scania 12</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>1경 8334조 7528억 1738만</t>
-  </si>
-  <si>
-    <t>자유가입</t>
-  </si>
-  <si>
-    <t>o볼륨o</t>
-  </si>
-  <si>
-    <t>RAINBOW</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=RAINBOW</t>
-  </si>
-  <si>
-    <t>Scania 6</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>2위</t>
-  </si>
-  <si>
-    <t>28명</t>
-  </si>
-  <si>
-    <t>2경 1010조 3722억 7342만</t>
-  </si>
-  <si>
-    <t>가입문의: 한딸기, 화질, 람볼기니 토벌100등 안쪽 귓 주세요. 길컨 , 파퀘, 자쿰, 혼테일 모든 컨테츠 활발하게 즐길 사람!!</t>
-  </si>
-  <si>
-    <t>화질</t>
-  </si>
-  <si>
-    <t>동물들의낙원</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%8F%99%EB%AC%BC%EB%93%A4%EC%9D%98%EB%82%99%EC%9B%90</t>
-  </si>
-  <si>
-    <t>Scania 13</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>1경 8110조 4181억 3714만</t>
-  </si>
-  <si>
-    <t>일일연구 길드토벌 길드대전 하루이상 안하시거나 이틀미접시 통지없이 내보냅니다</t>
-  </si>
-  <si>
-    <t>곶감말이</t>
-  </si>
-  <si>
-    <t>친구들</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%B9%9C%EA%B5%AC%EB%93%A4</t>
-  </si>
-  <si>
-    <t>Scania 11</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>3위</t>
-  </si>
-  <si>
-    <t>Lv.10</t>
-  </si>
-  <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>1경 7210조 8368억 6406만</t>
-  </si>
-  <si>
-    <t>www.친구들.com 보고 가입 문의</t>
-  </si>
-  <si>
-    <t>친구둘리</t>
-  </si>
-  <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>스타냥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%83%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>1경 2008조 4332억 5078만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>진자이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9E%90%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>4143조 7347억 1708만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>돈스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>3322조 3154억 8065만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>말레이히어로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%90%EB%A0%88%EC%9D%B4%ED%9E%88%EC%96%B4%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>1744조 8442억 4005만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>스타캐치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EC%BA%90%EC%B9%98</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>1645조 8595억 7138만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>빌런투킬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%8C%EB%9F%B0%ED%88%AC%ED%82%AC</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>1185조 7524억 3872만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>스타뎀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%8E%80</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>475조 5893억 7767만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>여사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
-  </si>
-  <si>
-    <t>400조 1307억 6796만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>단풍노비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EB%85%B8%EB%B9%84</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>397조 7120억 8955만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>부엉이없다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>333조 3422억 5764만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>니달리신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>258조 3204억 368만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>213조 2895억 1154만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>프리프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>186조 1628억 3024만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>149조 1517억 6031만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>쾌감</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
-  </si>
-  <si>
-    <t>145조 2700억 5418만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>110조 3430억 5093만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>101조 1343억 8739만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>96조 4965억 8645만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>92조 9372억 1789만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>POSCO</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
-  </si>
-  <si>
-    <t>65조 7697억 3285만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>두근푸근연근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%EA%B7%BC%ED%91%B8%EA%B7%BC%EC%97%B0%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>59조 6154억 5137만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>54조 3689억 898만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>포뇨야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
-  </si>
-  <si>
-    <t>46조 2787억 8294만</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>울힝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>43조 3112억 2854만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>김치싸대기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>39조 8824억 3269만</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>대방어조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>38조 8158억 1231만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>악의꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
+    <t>몽호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
+  </si>
+  <si>
+    <t>31조 9151억 3336만</t>
+  </si>
+  <si>
+    <t>o빠이o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EB%B9%A0%EC%9D%B4o</t>
+  </si>
+  <si>
+    <t>5174조 2119억 1456만</t>
+  </si>
+  <si>
+    <t>양먼지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%A8%BC%EC%A7%80</t>
+  </si>
+  <si>
+    <t>3569조 5128억 1676만</t>
+  </si>
+  <si>
+    <t>요르v</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EB%A5%B4v</t>
+  </si>
+  <si>
+    <t>3078조 8992억 5069만</t>
+  </si>
+  <si>
+    <t>o베베o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EB%B2%A0%EB%B2%A0o</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>2236조 5144억 5223만</t>
+  </si>
+  <si>
+    <t>o원기o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EC%9B%90%EA%B8%B0o</t>
+  </si>
+  <si>
+    <t>1738조 4620억 714만</t>
+  </si>
+  <si>
+    <t>집단범죄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%91%EB%8B%A8%EB%B2%94%EC%A3%84</t>
+  </si>
+  <si>
+    <t>586조 4140억 3923만</t>
+  </si>
+  <si>
+    <t>마법사김영욱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%B2%95%EC%82%AC%EA%B9%80%EC%98%81%EC%9A%B1</t>
+  </si>
+  <si>
+    <t>327조 3497억 6570만</t>
+  </si>
+  <si>
+    <t>워워이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%8C%EC%9B%8C%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>262조 6292억 5536만</t>
+  </si>
+  <si>
+    <t>o후국o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%ED%9B%84%EA%B5%ADo</t>
+  </si>
+  <si>
+    <t>200조 1341억 2359만</t>
+  </si>
+  <si>
+    <t>캔느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BA%94%EB%8A%90</t>
+  </si>
+  <si>
+    <t>189조 9962억 510만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EB%B3%BC%EB%A5%A8o</t>
+  </si>
+  <si>
+    <t>180조 6234억 842만</t>
+  </si>
+  <si>
+    <t>이원일</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9B%90%EC%9D%BC</t>
+  </si>
+  <si>
+    <t>149조 308억 1325만</t>
+  </si>
+  <si>
+    <t>o진이o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EC%A7%84%EC%9D%B4o</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>137조 9858억 3942만</t>
+  </si>
+  <si>
+    <t>빵섭이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%EC%84%AD%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>124조 9974억 2134만</t>
+  </si>
+  <si>
+    <t>김규평</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B7%9C%ED%8F%89</t>
+  </si>
+  <si>
+    <t>115조 7340억 3872만</t>
+  </si>
+  <si>
+    <t>화욤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%9A%A4</t>
+  </si>
+  <si>
+    <t>97조 9798억 2864만</t>
+  </si>
+  <si>
+    <t>뭥끼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AD%A5%EB%81%BC</t>
+  </si>
+  <si>
+    <t>82조 1917억 4270만</t>
+  </si>
+  <si>
+    <t>o엉댕o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EC%97%89%EB%8C%95o</t>
+  </si>
+  <si>
+    <t>79조 1549억 5375만</t>
+  </si>
+  <si>
+    <t>후니와동동</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EB%8B%88%EC%99%80%EB%8F%99%EB%8F%99</t>
+  </si>
+  <si>
+    <t>72조 9493억 7864만</t>
+  </si>
+  <si>
+    <t>FFFK</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=FFFK</t>
+  </si>
+  <si>
+    <t>66조 5786억 899만</t>
+  </si>
+  <si>
+    <t>o아윤o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EC%95%84%EC%9C%A4o</t>
+  </si>
+  <si>
+    <t>63조 122억 1653만</t>
+  </si>
+  <si>
+    <t>보마할래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%A7%88%ED%95%A0%EB%9E%98</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>54조 92억 859만</t>
+  </si>
+  <si>
+    <t>호이호이포이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9D%B4%ED%98%B8%EC%9D%B4%ED%8F%AC%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>35조 9382억 9079만</t>
+  </si>
+  <si>
+    <t>동부마트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%B6%80%EB%A7%88%ED%8A%B8</t>
   </si>
   <si>
     <t>102</t>
   </si>
   <si>
-    <t>38조 2904억 9899만</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>37조 9202억 5357만</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>35조 9640억 2609만</t>
-  </si>
-  <si>
-    <t>몽호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
-  </si>
-  <si>
-    <t>31조 9151억 3336만</t>
-  </si>
-  <si>
-    <t>o빠이o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EB%B9%A0%EC%9D%B4o</t>
-  </si>
-  <si>
-    <t>5170조 7801억 5796만</t>
-  </si>
-  <si>
-    <t>양먼지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%A8%BC%EC%A7%80</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>3390조 2926억 6569만</t>
-  </si>
-  <si>
-    <t>요르v</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EB%A5%B4v</t>
-  </si>
-  <si>
-    <t>2918조 4745억 6691만</t>
-  </si>
-  <si>
-    <t>o베베o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EB%B2%A0%EB%B2%A0o</t>
-  </si>
-  <si>
-    <t>2230조 4002억 5849만</t>
-  </si>
-  <si>
-    <t>o원기o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EC%9B%90%EA%B8%B0o</t>
-  </si>
-  <si>
-    <t>1738조 2910억 1598만</t>
-  </si>
-  <si>
-    <t>집단범죄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%91%EB%8B%A8%EB%B2%94%EC%A3%84</t>
-  </si>
-  <si>
-    <t>583조 4549억 1044만</t>
-  </si>
-  <si>
-    <t>마법사김영욱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%B2%95%EC%82%AC%EA%B9%80%EC%98%81%EC%9A%B1</t>
-  </si>
-  <si>
-    <t>309조 3796억 2689만</t>
-  </si>
-  <si>
-    <t>워워이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%8C%EC%9B%8C%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>243조 9380억 150만</t>
-  </si>
-  <si>
-    <t>o후국o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%ED%9B%84%EA%B5%ADo</t>
-  </si>
-  <si>
-    <t>200조 1341억 2359만</t>
-  </si>
-  <si>
-    <t>캔느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BA%94%EB%8A%90</t>
-  </si>
-  <si>
-    <t>189조 9962억 510만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EB%B3%BC%EB%A5%A8o</t>
-  </si>
-  <si>
-    <t>180조 6234억 842만</t>
-  </si>
-  <si>
-    <t>이원일</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9B%90%EC%9D%BC</t>
-  </si>
-  <si>
-    <t>148조 486억 7521만</t>
-  </si>
-  <si>
-    <t>o진이o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EC%A7%84%EC%9D%B4o</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>137조 4015억 3332만</t>
-  </si>
-  <si>
-    <t>빵섭이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%EC%84%AD%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>124조 9974억 2134만</t>
-  </si>
-  <si>
-    <t>김규평</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B7%9C%ED%8F%89</t>
-  </si>
-  <si>
-    <t>115조 7340억 3872만</t>
-  </si>
-  <si>
-    <t>화욤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%9A%A4</t>
-  </si>
-  <si>
-    <t>97조 9798억 2864만</t>
-  </si>
-  <si>
-    <t>뭥끼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AD%A5%EB%81%BC</t>
-  </si>
-  <si>
-    <t>82조 313억 638만</t>
-  </si>
-  <si>
-    <t>후니와동동</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EB%8B%88%EC%99%80%EB%8F%99%EB%8F%99</t>
-  </si>
-  <si>
-    <t>72조 9493억 7864만</t>
-  </si>
-  <si>
-    <t>o엉댕o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EC%97%89%EB%8C%95o</t>
-  </si>
-  <si>
-    <t>72조 1216억 2747만</t>
-  </si>
-  <si>
-    <t>FFFK</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=FFFK</t>
-  </si>
-  <si>
-    <t>66조 5786억 899만</t>
-  </si>
-  <si>
-    <t>o아윤o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EC%95%84%EC%9C%A4o</t>
-  </si>
-  <si>
-    <t>58조 6086억 2075만</t>
-  </si>
-  <si>
-    <t>보마할래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%A7%88%ED%95%A0%EB%9E%98</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>53조 9822억 4468만</t>
-  </si>
-  <si>
-    <t>호이호이포이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9D%B4%ED%98%B8%EC%9D%B4%ED%8F%AC%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>35조 9382억 9079만</t>
-  </si>
-  <si>
-    <t>동부마트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%B6%80%EB%A7%88%ED%8A%B8</t>
-  </si>
-  <si>
-    <t>31조 1973억 4624만</t>
+    <t>31조 7396억 6713만</t>
   </si>
   <si>
     <t>겨울난방</t>
@@ -869,7 +869,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%EB%82%9C%EB%B0%A9</t>
   </si>
   <si>
-    <t>17조 7176억 4343만</t>
+    <t>17조 8367억 8467만</t>
   </si>
   <si>
     <t>옹이잉</t>
@@ -881,22 +881,22 @@
     <t>17조 7165억 8053만</t>
   </si>
   <si>
+    <t>담훌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%B4%ED%9B%8C</t>
+  </si>
+  <si>
+    <t>17조 2860억 3718만</t>
+  </si>
+  <si>
     <t>우패밀리</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%8C%A8%EB%B0%80%EB%A6%AC</t>
   </si>
   <si>
-    <t>16조 9648억 7675만</t>
-  </si>
-  <si>
-    <t>담훌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%B4%ED%9B%8C</t>
-  </si>
-  <si>
-    <t>16조 4001억 3804만</t>
+    <t>17조 2333억 5444만</t>
   </si>
   <si>
     <t>뚠뚠냥이</t>
@@ -905,7 +905,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9A%A0%EB%9A%A0%EB%83%A5%EC%9D%B4</t>
   </si>
   <si>
-    <t>11조 4025억 5100만</t>
+    <t>12조 9603억 4085만</t>
   </si>
   <si>
     <t>비뉴송</t>
@@ -917,7 +917,7 @@
     <t>100</t>
   </si>
   <si>
-    <t>10조 127억 6629만</t>
+    <t>11조 3789억 7166만</t>
   </si>
   <si>
     <t>람볼기니</t>
@@ -974,7 +974,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%97%88%EB%8F%99</t>
   </si>
   <si>
-    <t>528조 3828억 8938만</t>
+    <t>556조 3385억 2634만</t>
   </si>
   <si>
     <t>삼뚝</t>
@@ -992,7 +992,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%91%EC%88%9C</t>
   </si>
   <si>
-    <t>122조 9125억 1716만</t>
+    <t>127조 4976억 5318만</t>
   </si>
   <si>
     <t>매워요</t>
@@ -1001,7 +1001,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EC%9B%8C%EC%9A%94</t>
   </si>
   <si>
-    <t>91조 4052억 2736만</t>
+    <t>94조 9038억 402만</t>
   </si>
   <si>
     <t>문군</t>
@@ -1019,7 +1019,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%81%B4%EC%9D%B4</t>
   </si>
   <si>
-    <t>78조 1737억 2570만</t>
+    <t>79조 6577억 8944만</t>
   </si>
   <si>
     <t>지흠</t>
@@ -1028,7 +1028,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%ED%9D%A0</t>
   </si>
   <si>
-    <t>51조 8772억 5719만</t>
+    <t>52조 9423억 3702만</t>
   </si>
   <si>
     <t>이클릿</t>
@@ -1055,7 +1055,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%97%85</t>
   </si>
   <si>
-    <t>32조 6501억 7545만</t>
+    <t>33조 1745억 2789만</t>
   </si>
   <si>
     <t>오버츄어리</t>
@@ -1064,7 +1064,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%B2%84%EC%B8%84%EC%96%B4%EB%A6%AC</t>
   </si>
   <si>
-    <t>29조 9539억 5478만</t>
+    <t>30조 8101억 8029만</t>
   </si>
   <si>
     <t>매스리</t>
@@ -1073,7 +1073,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EC%8A%A4%EB%A6%AC</t>
   </si>
   <si>
-    <t>26조 2186억 1691만</t>
+    <t>27조 2439억 3792만</t>
   </si>
   <si>
     <t>썬콜미르</t>
@@ -1082,13 +1082,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%AF%B8%EB%A5%B4</t>
   </si>
   <si>
-    <t>22조 7314억 3436만</t>
+    <t>23조 2299억 9831만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A7%88</t>
   </si>
   <si>
-    <t>18조 8340억 7797만</t>
+    <t>19조 8814억 7540만</t>
   </si>
   <si>
     <t>꽁칫</t>
@@ -1097,7 +1097,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EC%B9%AB</t>
   </si>
   <si>
-    <t>18조 7049억 4818만</t>
+    <t>18조 7679억 2985만</t>
   </si>
   <si>
     <t>앵찬</t>
@@ -1106,7 +1106,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%B5%EC%B0%AC</t>
   </si>
   <si>
-    <t>16조 3268억 463만</t>
+    <t>16조 9665억 4898만</t>
   </si>
   <si>
     <t>레펠</t>
@@ -1130,13 +1130,22 @@
     <t>10조 6952억 5950만</t>
   </si>
   <si>
+    <t>페이꺼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8E%98%EC%9D%B4%EA%BA%BC</t>
+  </si>
+  <si>
+    <t>10조 6623억 3538만</t>
+  </si>
+  <si>
     <t>멍눈</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%8D%EB%88%88</t>
   </si>
   <si>
-    <t>9조 3737억 2513만</t>
+    <t>9조 9863억 5509만</t>
   </si>
   <si>
     <t>ArtCoin</t>
@@ -1145,7 +1154,7 @@
     <t>https://mgf.gg/contents/character.php?n=ArtCoin</t>
   </si>
   <si>
-    <t>9조 1974억 3957만</t>
+    <t>9조 6853억 1877만</t>
   </si>
   <si>
     <t>할거없곰</t>
@@ -1154,7 +1163,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EA%B1%B0%EC%97%86%EA%B3%B0</t>
   </si>
   <si>
-    <t>5조 8875억 2959만</t>
+    <t>6조 1154억 7858만</t>
   </si>
   <si>
     <t>무지성사냥</t>
@@ -1172,7 +1181,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%95%8C%EA%BE%B8</t>
   </si>
   <si>
-    <t>4조 962억 7800만</t>
+    <t>4조 1429억 3954만</t>
   </si>
   <si>
     <t>딱뎀</t>
@@ -1190,7 +1199,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EC%9D%B4%EB%90%9C%EC%82%AC%EB%82%98%EC%9D%B4</t>
   </si>
   <si>
-    <t>3588조 6011억 8501만</t>
+    <t>3857조 153억 3597만</t>
   </si>
   <si>
     <t>또르뱅</t>
@@ -1199,7 +1208,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%A5%B4%EB%B1%85</t>
   </si>
   <si>
-    <t>2731조 7186억 2486만</t>
+    <t>2750조 3249억 132만</t>
   </si>
   <si>
     <t>Hoood</t>
@@ -1208,7 +1217,7 @@
     <t>https://mgf.gg/contents/character.php?n=Hoood</t>
   </si>
   <si>
-    <t>402조 9905억 2284만</t>
+    <t>430조 1672억 6332만</t>
   </si>
   <si>
     <t>클리닝티슈</t>
@@ -1217,7 +1226,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%81%B4%EB%A6%AC%EB%8B%9D%ED%8B%B0%EC%8A%88</t>
   </si>
   <si>
-    <t>182조 4025억 7396만</t>
+    <t>212조 9458억 4578만</t>
   </si>
   <si>
     <t>상깅</t>
@@ -1226,7 +1235,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B9%85</t>
   </si>
   <si>
-    <t>175조 4483억 4392만</t>
+    <t>175조 5868억 3424만</t>
   </si>
   <si>
     <t>내사랑로제</t>
@@ -1247,6 +1256,15 @@
     <t>103조 1493억 1597만</t>
   </si>
   <si>
+    <t>손끝의예리함</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%90%EB%81%9D%EC%9D%98%EC%98%88%EB%A6%AC%ED%95%A8</t>
+  </si>
+  <si>
+    <t>67조 39억 2258만</t>
+  </si>
+  <si>
     <t>얘인</t>
   </si>
   <si>
@@ -1256,22 +1274,13 @@
     <t>57조 5323억 515만</t>
   </si>
   <si>
-    <t>손끝의예리함</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%90%EB%81%9D%EC%9D%98%EC%98%88%EB%A6%AC%ED%95%A8</t>
-  </si>
-  <si>
-    <t>55조 226억 9129만</t>
-  </si>
-  <si>
     <t>쌈싸</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8C%88%EC%8B%B8</t>
   </si>
   <si>
-    <t>37조 3540억 6780만</t>
+    <t>37조 5037억 997만</t>
   </si>
   <si>
     <t>퓨엉</t>
@@ -1280,7 +1289,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%93%A8%EC%97%89</t>
   </si>
   <si>
-    <t>30조 1885억 1701만</t>
+    <t>33조 3882억 4094만</t>
   </si>
   <si>
     <t>쑹쓩</t>
@@ -1289,7 +1298,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%91%B9%EC%93%A9</t>
   </si>
   <si>
-    <t>30조 1792억 7780만</t>
+    <t>31조 3108억 2659만</t>
   </si>
   <si>
     <t>공성현</t>
@@ -1298,13 +1307,22 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EC%84%B1%ED%98%84</t>
   </si>
   <si>
-    <t>27조 1546억 3975만</t>
+    <t>28조 3975억 5246만</t>
+  </si>
+  <si>
+    <t>품쪽이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%92%88%EC%AA%BD%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>25조 560억 696만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%B6%EA%B0%90%EB%A7%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>20조 4796억 8556만</t>
+    <t>23조 4525억 7505만</t>
   </si>
   <si>
     <t>존잘녀</t>
@@ -1316,22 +1334,22 @@
     <t>19조 5580억 6011만</t>
   </si>
   <si>
-    <t>품쪽이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%92%88%EC%AA%BD%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>16조 6966억 5014만</t>
-  </si>
-  <si>
     <t>웨아</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%A8%EC%95%84</t>
   </si>
   <si>
-    <t>14조 8134억 7477만</t>
+    <t>17조 4224억 7538만</t>
+  </si>
+  <si>
+    <t>으니림</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%BC%EB%8B%88%EB%A6%BC</t>
+  </si>
+  <si>
+    <t>11조 3298억 9715만</t>
   </si>
   <si>
     <t>통영고니</t>
@@ -1340,16 +1358,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%86%B5%EC%98%81%EA%B3%A0%EB%8B%88</t>
   </si>
   <si>
-    <t>11조 162억 8215만</t>
-  </si>
-  <si>
-    <t>으니림</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%BC%EB%8B%88%EB%A6%BC</t>
-  </si>
-  <si>
-    <t>10조 2504억 7055만</t>
+    <t>11조 1733억 9592만</t>
   </si>
   <si>
     <t>쪼재맨</t>
@@ -1385,7 +1394,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EB%AA%BD%EC%9E%89</t>
   </si>
   <si>
-    <t>5조 2837억 7438만</t>
+    <t>5조 3367억 1971만</t>
   </si>
   <si>
     <t>치쵸치</t>
@@ -1394,7 +1403,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%98%EC%B5%B8%EC%B9%98</t>
   </si>
   <si>
-    <t>5조 1953억 5606만</t>
+    <t>5조 2851억 8500만</t>
   </si>
   <si>
     <t>그대로꿀</t>
@@ -1403,7 +1412,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%8C%80%EB%A1%9C%EA%BF%80</t>
   </si>
   <si>
-    <t>4조 6324억 5747만</t>
+    <t>4조 9515억 999만</t>
   </si>
   <si>
     <t>다둉이</t>
@@ -1421,7 +1430,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EB%AD%89%EC%9E%89</t>
   </si>
   <si>
-    <t>3조 7459억 1815만</t>
+    <t>3조 9710억 6083만</t>
   </si>
   <si>
     <t>문뚝</t>
@@ -1430,7 +1439,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%9A%9D</t>
   </si>
   <si>
-    <t>3조 5390억 2985만</t>
+    <t>3조 7024억 1062만</t>
   </si>
   <si>
     <t>황금어금니</t>
@@ -1439,7 +1448,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%A9%EA%B8%88%EC%96%B4%EA%B8%88%EB%8B%88</t>
   </si>
   <si>
-    <t>3조 1950억 73만</t>
+    <t>3조 2489억 1908만</t>
   </si>
   <si>
     <t>가을호떡</t>
@@ -1466,7 +1475,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%AD%EB%A7%8C%EA%B9%80%EA%B0%91%EB%A3%A1</t>
   </si>
   <si>
-    <t>447조 6100억 6586만</t>
+    <t>460조 3194억 5542만</t>
   </si>
   <si>
     <t>칭구야</t>
@@ -1475,7 +1484,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%AD%EA%B5%AC%EC%95%BC</t>
   </si>
   <si>
-    <t>205조 8777억 5636만</t>
+    <t>218조 8950억 9683만</t>
   </si>
   <si>
     <t>새우탕z</t>
@@ -1484,7 +1493,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%88%EC%9A%B0%ED%83%95z</t>
   </si>
   <si>
-    <t>103조 4259억 524만</t>
+    <t>103조 6356억 7177만</t>
   </si>
   <si>
     <t>ykm21cc</t>
@@ -1502,7 +1511,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BB%8C%EC%A0%95%EC%83%89</t>
   </si>
   <si>
-    <t>68조 7190억 6046만</t>
+    <t>71조 862억 5029만</t>
   </si>
   <si>
     <t>ggggg</t>
@@ -1511,7 +1520,7 @@
     <t>https://mgf.gg/contents/character.php?n=ggggg</t>
   </si>
   <si>
-    <t>52조 8962억 4056만</t>
+    <t>62조 4984억 9593만</t>
   </si>
   <si>
     <t>다헐</t>
@@ -1520,7 +1529,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%ED%97%90</t>
   </si>
   <si>
-    <t>49조 7577억 9577만</t>
+    <t>50조 6676억 6407만</t>
   </si>
   <si>
     <t>리피트</t>
@@ -1529,7 +1538,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%ED%94%BC%ED%8A%B8</t>
   </si>
   <si>
-    <t>47조 7713억 1276만</t>
+    <t>49조 721억 2782만</t>
   </si>
   <si>
     <t>친구닷</t>
@@ -1538,7 +1547,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%9C%EA%B5%AC%EB%8B%B7</t>
   </si>
   <si>
-    <t>43조 1750억 5861만</t>
+    <t>44조 9288억 6205만</t>
   </si>
   <si>
     <t>신림동물개</t>
@@ -1559,13 +1568,19 @@
     <t>29조 5050억 9944만</t>
   </si>
   <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B9%9C%EA%B5%AC%EB%91%98%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>27조 7039억 5531만</t>
+  </si>
+  <si>
     <t>마근혜슘</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EA%B7%BC%ED%98%9C%EC%8A%98</t>
   </si>
   <si>
-    <t>24조 4449억 9045만</t>
+    <t>24조 7689억 4279만</t>
   </si>
   <si>
     <t>이남선</t>
@@ -1574,7 +1589,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%82%A8%EC%84%A0</t>
   </si>
   <si>
-    <t>22조 5670억 2297만</t>
+    <t>24조 2472억 9989만</t>
+  </si>
+  <si>
+    <t>앙순아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%99%EC%88%9C%EC%95%84</t>
+  </si>
+  <si>
+    <t>20조 3494억 1834만</t>
   </si>
   <si>
     <t>냉동붕어</t>
@@ -1583,22 +1607,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%89%EB%8F%99%EB%B6%95%EC%96%B4</t>
   </si>
   <si>
-    <t>19조 3096억 4766만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B9%9C%EA%B5%AC%EB%91%98%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>19조 619억 502만</t>
-  </si>
-  <si>
-    <t>앙순아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%99%EC%88%9C%EC%95%84</t>
-  </si>
-  <si>
-    <t>18조 9841억 8947만</t>
+    <t>19조 3960억 1480만</t>
   </si>
   <si>
     <t>조은거임</t>
@@ -1607,7 +1616,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%9D%80%EA%B1%B0%EC%9E%84</t>
   </si>
   <si>
-    <t>16조 2896억 6257만</t>
+    <t>16조 4644억 9775만</t>
+  </si>
+  <si>
+    <t>보우모모</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EC%9A%B0%EB%AA%A8%EB%AA%A8</t>
+  </si>
+  <si>
+    <t>14조 2289억 1820만</t>
   </si>
   <si>
     <t>v지훈왕자v</t>
@@ -1619,15 +1637,6 @@
     <t>13조 8718억 749만</t>
   </si>
   <si>
-    <t>보우모모</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EC%9A%B0%EB%AA%A8%EB%AA%A8</t>
-  </si>
-  <si>
-    <t>13조 5968억 5417만</t>
-  </si>
-  <si>
     <t>네모인간</t>
   </si>
   <si>
@@ -1637,6 +1646,15 @@
     <t>12조 7863억 1640만</t>
   </si>
   <si>
+    <t>Silas</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Silas</t>
+  </si>
+  <si>
+    <t>11조 660억 9778만</t>
+  </si>
+  <si>
     <t>뿡풍</t>
   </si>
   <si>
@@ -1646,13 +1664,13 @@
     <t>10조 9781억 3116만</t>
   </si>
   <si>
-    <t>Silas</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Silas</t>
-  </si>
-  <si>
-    <t>10조 9751억 5209만</t>
+    <t>후비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EB%B9%84</t>
+  </si>
+  <si>
+    <t>8조 2959억 1669만</t>
   </si>
   <si>
     <t>진성규</t>
@@ -1664,22 +1682,13 @@
     <t>7조 7443억 9675만</t>
   </si>
   <si>
-    <t>후비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EB%B9%84</t>
-  </si>
-  <si>
-    <t>7조 5387억 8833만</t>
-  </si>
-  <si>
     <t>갓친</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EC%B9%9C</t>
   </si>
   <si>
-    <t>4조 3428억 5673만</t>
+    <t>4조 4784억 6522만</t>
   </si>
   <si>
     <t>잘좀해봐</t>
@@ -1688,7 +1697,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%98%EC%A2%80%ED%95%B4%EB%B4%90</t>
   </si>
   <si>
-    <t>4조 3067억 7586만</t>
+    <t>4조 3109억 5195만</t>
   </si>
   <si>
     <t>예끔이</t>
@@ -2307,16 +2316,16 @@
         <v>53</v>
       </c>
       <c r="I6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>24</v>
@@ -2355,28 +2364,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -2387,28 +2396,28 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="F2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -2419,28 +2428,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2451,28 +2460,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2483,28 +2492,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2515,28 +2524,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2547,28 +2556,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2579,28 +2588,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2611,25 +2620,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>109</v>
@@ -2655,16 +2664,16 @@
         <v>112</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="H10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2675,28 +2684,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2707,28 +2716,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2739,28 +2748,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2771,28 +2780,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2803,28 +2812,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2835,28 +2844,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2867,28 +2876,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H17" s="2" t="s">
+      <c r="I17" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2899,28 +2908,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2931,28 +2940,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2963,28 +2972,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>157</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -2995,28 +3004,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3027,28 +3036,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="I22" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>165</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3059,28 +3068,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>169</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3091,28 +3100,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3123,28 +3132,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H25" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H25" s="2" t="s">
+      <c r="I25" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>178</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3155,28 +3164,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3187,28 +3196,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>186</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3219,28 +3228,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>191</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3251,7 +3260,7 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>23</v>
@@ -3260,19 +3269,19 @@
         <v>23</v>
       </c>
       <c r="E29" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>195</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3283,28 +3292,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="H30" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3315,28 +3324,28 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>17</v>
+        <v>199</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>203</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -3400,28 +3409,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3432,28 +3441,28 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>206</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -3464,28 +3473,28 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -3496,28 +3505,28 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>213</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3528,28 +3537,28 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>216</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3560,28 +3569,28 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>218</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>219</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3592,28 +3601,28 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -3624,28 +3633,28 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>224</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>225</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -3656,28 +3665,28 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>227</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>228</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3691,25 +3700,25 @@
         <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>231</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3720,28 +3729,28 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>233</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>234</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3752,7 +3761,7 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>31</v>
@@ -3761,19 +3770,19 @@
         <v>31</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>236</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3784,28 +3793,28 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>239</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3816,28 +3825,28 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G14" s="2" t="s">
+      <c r="H14" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>243</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -3848,28 +3857,28 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>246</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3880,28 +3889,28 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>249</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3912,28 +3921,28 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>252</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3944,28 +3953,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>255</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3976,28 +3985,28 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>257</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>258</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4008,28 +4017,28 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>261</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4040,28 +4049,28 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4072,28 +4081,28 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>267</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4104,28 +4113,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G23" s="2" t="s">
+      <c r="H23" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>271</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -4136,28 +4145,28 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>273</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>274</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4168,25 +4177,25 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H25" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>277</v>
@@ -4200,7 +4209,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>278</v>
@@ -4212,13 +4221,13 @@
         <v>279</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>190</v>
+        <v>276</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>280</v>
@@ -4232,7 +4241,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>281</v>
@@ -4244,13 +4253,13 @@
         <v>282</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>283</v>
@@ -4264,7 +4273,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>284</v>
@@ -4276,13 +4285,13 @@
         <v>285</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>143</v>
+        <v>276</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>286</v>
@@ -4296,7 +4305,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>287</v>
@@ -4308,13 +4317,13 @@
         <v>288</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>289</v>
@@ -4328,7 +4337,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>290</v>
@@ -4340,13 +4349,13 @@
         <v>291</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>190</v>
+        <v>276</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>292</v>
@@ -4360,7 +4369,7 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>17</v>
+        <v>199</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>293</v>
@@ -4372,10 +4381,10 @@
         <v>294</v>
       </c>
       <c r="F31" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>295</v>
@@ -4427,7 +4436,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -4445,28 +4454,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -4477,7 +4486,7 @@
         <v>32</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>297</v>
@@ -4489,10 +4498,10 @@
         <v>298</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>299</v>
@@ -4509,7 +4518,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>301</v>
@@ -4521,13 +4530,13 @@
         <v>302</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>303</v>
@@ -4541,7 +4550,7 @@
         <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>304</v>
@@ -4553,13 +4562,13 @@
         <v>305</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>306</v>
@@ -4573,7 +4582,7 @@
         <v>32</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>307</v>
@@ -4585,13 +4594,13 @@
         <v>308</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>309</v>
@@ -4605,7 +4614,7 @@
         <v>32</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>310</v>
@@ -4617,13 +4626,13 @@
         <v>311</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>312</v>
@@ -4637,7 +4646,7 @@
         <v>32</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>313</v>
@@ -4649,13 +4658,13 @@
         <v>314</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>315</v>
@@ -4669,7 +4678,7 @@
         <v>32</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>316</v>
@@ -4681,13 +4690,13 @@
         <v>317</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>318</v>
@@ -4701,7 +4710,7 @@
         <v>32</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>319</v>
@@ -4713,13 +4722,13 @@
         <v>320</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="H9" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>321</v>
@@ -4745,13 +4754,13 @@
         <v>323</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="H10" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>324</v>
@@ -4765,7 +4774,7 @@
         <v>32</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>325</v>
@@ -4777,13 +4786,13 @@
         <v>326</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>327</v>
@@ -4797,7 +4806,7 @@
         <v>32</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>328</v>
@@ -4809,13 +4818,13 @@
         <v>329</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>330</v>
@@ -4829,7 +4838,7 @@
         <v>32</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>331</v>
@@ -4841,13 +4850,13 @@
         <v>332</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>333</v>
@@ -4861,7 +4870,7 @@
         <v>32</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>334</v>
@@ -4873,13 +4882,13 @@
         <v>335</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>336</v>
@@ -4893,7 +4902,7 @@
         <v>32</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>337</v>
@@ -4905,13 +4914,13 @@
         <v>338</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>339</v>
@@ -4925,7 +4934,7 @@
         <v>32</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>340</v>
@@ -4937,13 +4946,13 @@
         <v>341</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>342</v>
@@ -4957,7 +4966,7 @@
         <v>32</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>343</v>
@@ -4969,13 +4978,13 @@
         <v>344</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>345</v>
@@ -4989,7 +4998,7 @@
         <v>32</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>346</v>
@@ -5001,13 +5010,13 @@
         <v>347</v>
       </c>
       <c r="F18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="H18" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>348</v>
@@ -5021,7 +5030,7 @@
         <v>32</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>349</v>
@@ -5033,13 +5042,13 @@
         <v>350</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>351</v>
@@ -5053,7 +5062,7 @@
         <v>32</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>40</v>
@@ -5065,13 +5074,13 @@
         <v>352</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>353</v>
@@ -5085,7 +5094,7 @@
         <v>32</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>354</v>
@@ -5097,13 +5106,13 @@
         <v>355</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>190</v>
+        <v>276</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>356</v>
@@ -5117,7 +5126,7 @@
         <v>32</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>357</v>
@@ -5129,13 +5138,13 @@
         <v>358</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>359</v>
@@ -5149,7 +5158,7 @@
         <v>32</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>360</v>
@@ -5161,13 +5170,13 @@
         <v>361</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>190</v>
+        <v>276</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>362</v>
@@ -5181,7 +5190,7 @@
         <v>32</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>363</v>
@@ -5193,10 +5202,10 @@
         <v>364</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>365</v>
@@ -5213,7 +5222,7 @@
         <v>32</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>367</v>
@@ -5225,13 +5234,13 @@
         <v>368</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>190</v>
+        <v>276</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>369</v>
@@ -5245,7 +5254,7 @@
         <v>32</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>370</v>
@@ -5257,13 +5266,13 @@
         <v>371</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>242</v>
+        <v>92</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>365</v>
+        <v>276</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>372</v>
@@ -5277,7 +5286,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>373</v>
@@ -5289,13 +5298,13 @@
         <v>374</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>70</v>
+        <v>241</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>295</v>
+        <v>365</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>375</v>
@@ -5309,7 +5318,7 @@
         <v>32</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>376</v>
@@ -5321,13 +5330,13 @@
         <v>377</v>
       </c>
       <c r="F28" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="H28" s="2" t="s">
-        <v>365</v>
+        <v>295</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>378</v>
@@ -5341,7 +5350,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>379</v>
@@ -5353,10 +5362,10 @@
         <v>380</v>
       </c>
       <c r="F29" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>270</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>365</v>
@@ -5368,8 +5377,40 @@
         <v>24</v>
       </c>
     </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J29"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -5399,6 +5440,7 @@
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5424,28 +5466,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -5456,28 +5498,28 @@
         <v>41</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>299</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5488,28 +5530,28 @@
         <v>41</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5520,28 +5562,28 @@
         <v>41</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5552,28 +5594,28 @@
         <v>41</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5584,28 +5626,28 @@
         <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5616,28 +5658,28 @@
         <v>41</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5648,28 +5690,28 @@
         <v>41</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5680,28 +5722,28 @@
         <v>41</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5715,25 +5757,25 @@
         <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5744,28 +5786,28 @@
         <v>41</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5776,28 +5818,28 @@
         <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5808,28 +5850,28 @@
         <v>41</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>190</v>
+        <v>276</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5840,28 +5882,28 @@
         <v>41</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="H14" s="2" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5872,28 +5914,28 @@
         <v>41</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5904,28 +5946,28 @@
         <v>41</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>47</v>
+        <v>427</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>47</v>
+        <v>427</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>194</v>
+        <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>242</v>
+        <v>92</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5936,28 +5978,28 @@
         <v>41</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>426</v>
+        <v>47</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>426</v>
+        <v>47</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>69</v>
+        <v>192</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>76</v>
+        <v>241</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5968,28 +6010,28 @@
         <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>190</v>
+        <v>276</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6000,28 +6042,28 @@
         <v>41</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>190</v>
+        <v>276</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6032,28 +6074,28 @@
         <v>41</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>365</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6064,28 +6106,28 @@
         <v>41</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>365</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6096,28 +6138,28 @@
         <v>41</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>190</v>
+        <v>276</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6128,28 +6170,28 @@
         <v>41</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>365</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6160,28 +6202,28 @@
         <v>41</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>365</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6192,28 +6234,28 @@
         <v>41</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>365</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6224,28 +6266,28 @@
         <v>41</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>295</v>
+        <v>365</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6256,28 +6298,28 @@
         <v>41</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>365</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6288,28 +6330,28 @@
         <v>41</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>295</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6320,28 +6362,28 @@
         <v>41</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>365</v>
+        <v>276</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6352,28 +6394,28 @@
         <v>41</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>365</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6384,28 +6426,28 @@
         <v>41</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>17</v>
+        <v>199</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>365</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6469,28 +6511,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -6501,28 +6543,28 @@
         <v>48</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6533,28 +6575,28 @@
         <v>48</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6565,28 +6607,28 @@
         <v>48</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6597,28 +6639,28 @@
         <v>48</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6629,28 +6671,28 @@
         <v>48</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6661,28 +6703,28 @@
         <v>48</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6693,28 +6735,28 @@
         <v>48</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6725,28 +6767,28 @@
         <v>48</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6760,25 +6802,25 @@
         <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6789,28 +6831,28 @@
         <v>48</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6821,28 +6863,28 @@
         <v>48</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6853,28 +6895,28 @@
         <v>48</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6885,28 +6927,28 @@
         <v>48</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>190</v>
+        <v>276</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6917,28 +6959,28 @@
         <v>48</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>510</v>
+        <v>56</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>510</v>
+        <v>56</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>69</v>
+        <v>192</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>177</v>
+        <v>276</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6949,28 +6991,28 @@
         <v>48</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6981,28 +7023,28 @@
         <v>48</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7013,28 +7055,28 @@
         <v>48</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>57</v>
+        <v>521</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>57</v>
+        <v>521</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>194</v>
+        <v>68</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>190</v>
+        <v>276</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7045,28 +7087,28 @@
         <v>48</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>365</v>
+        <v>176</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7077,28 +7119,28 @@
         <v>48</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="F20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G20" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="H20" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7109,28 +7151,28 @@
         <v>48</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="F21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="H21" s="2" t="s">
-        <v>295</v>
+        <v>365</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7141,28 +7183,28 @@
         <v>48</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>365</v>
+        <v>295</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7173,28 +7215,28 @@
         <v>48</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>190</v>
+        <v>276</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7205,28 +7247,28 @@
         <v>48</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>365</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7237,28 +7279,28 @@
         <v>48</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>365</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7269,28 +7311,28 @@
         <v>48</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>365</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7301,28 +7343,28 @@
         <v>48</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>365</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7333,28 +7375,28 @@
         <v>48</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>295</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7365,28 +7407,28 @@
         <v>48</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>365</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -7397,28 +7439,28 @@
         <v>48</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>365</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -16,10 +16,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">RAINBOW!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">RAINBOW!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">동물들의낙원!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">빠따!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">셀린느!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">빠따!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">셀린느!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">친구들!$A$1:$J$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="557">
   <si>
     <t>guild_name</t>
   </si>
@@ -89,61 +89,61 @@
     <t>Lv.8</t>
   </si>
   <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>2경 7582조 5935억 3301만</t>
+  </si>
+  <si>
+    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
+  </si>
+  <si>
+    <t>혜영</t>
+  </si>
+  <si>
+    <t>2026.04.28</t>
+  </si>
+  <si>
+    <t>빠따</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%A0%EB%94%B0</t>
+  </si>
+  <si>
+    <t>Scania 12</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>2위</t>
+  </si>
+  <si>
+    <t>1경 5404조 4239억 9560만</t>
+  </si>
+  <si>
+    <t>자유가입</t>
+  </si>
+  <si>
+    <t>o볼륨o</t>
+  </si>
+  <si>
+    <t>RAINBOW</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=RAINBOW</t>
+  </si>
+  <si>
+    <t>Scania 6</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
     <t>30명</t>
   </si>
   <si>
-    <t>2경 7731조 1714억 2883만</t>
-  </si>
-  <si>
-    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
-  </si>
-  <si>
-    <t>혜영</t>
-  </si>
-  <si>
-    <t>2026.04.27</t>
-  </si>
-  <si>
-    <t>빠따</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%A0%EB%94%B0</t>
-  </si>
-  <si>
-    <t>Scania 12</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>1경 8750조 4613억 1676만</t>
-  </si>
-  <si>
-    <t>자유가입</t>
-  </si>
-  <si>
-    <t>o볼륨o</t>
-  </si>
-  <si>
-    <t>RAINBOW</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=RAINBOW</t>
-  </si>
-  <si>
-    <t>Scania 6</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>2위</t>
-  </si>
-  <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>2경 1095조 826억 2157만</t>
+    <t>2경 1900조 5052억 8265만</t>
   </si>
   <si>
     <t>가입문의: 화질, 한딸기, 람볼기니 토벌100등 안쪽 귓 주세요. 길컨 , 파퀘, 자쿰, 혼테일 모든 컨테츠 활발하게 즐길 사람!!</t>
@@ -161,10 +161,10 @@
     <t>Scania 13</t>
   </si>
   <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>1경 8489조 841억 8194만</t>
+    <t>44</t>
+  </si>
+  <si>
+    <t>1경 8864조 2737억 7844만</t>
   </si>
   <si>
     <t>일일연구 길드토벌 길드대전 하루이상 안하시거나 이틀미접시 통지없이 내보냅니다</t>
@@ -182,7 +182,7 @@
     <t>Scania 11</t>
   </si>
   <si>
-    <t>45</t>
+    <t>46</t>
   </si>
   <si>
     <t>3위</t>
@@ -191,7 +191,7 @@
     <t>Lv.10</t>
   </si>
   <si>
-    <t>1경 7270조 5714억 211만</t>
+    <t>1경 8030조 5797억 4014만</t>
   </si>
   <si>
     <t>www.친구들.com 보고 가입 문의</t>
@@ -293,7 +293,7 @@
     <t>110</t>
   </si>
   <si>
-    <t>1904조 7904억 7321만</t>
+    <t>1909조 8116억 1324만</t>
   </si>
   <si>
     <t>5</t>
@@ -308,7 +308,7 @@
     <t>섀도어</t>
   </si>
   <si>
-    <t>1645조 8595억 7138만</t>
+    <t>1650조 7226억 8092만</t>
   </si>
   <si>
     <t>6</t>
@@ -329,10 +329,10 @@
     <t>7</t>
   </si>
   <si>
-    <t>스타뎀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%83%80%EB%8E%80</t>
+    <t>여사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
   </si>
   <si>
     <t>다크나이트</t>
@@ -341,7 +341,7 @@
     <t>108</t>
   </si>
   <si>
-    <t>475조 5893억 7767만</t>
+    <t>526조 6208억 5372만</t>
   </si>
   <si>
     <t>8</t>
@@ -356,70 +356,70 @@
     <t>107</t>
   </si>
   <si>
-    <t>405조 7175억 7562만</t>
+    <t>406조 3881억 7021만</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>여사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%82%AC</t>
-  </si>
-  <si>
-    <t>400조 1307억 6796만</t>
+    <t>부엉이없다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>393조 780억 8682만</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>부엉이없다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%97%89%EC%9D%B4%EC%97%86%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>338조 9646억 7953만</t>
+    <t>니달리신</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
+  </si>
+  <si>
+    <t>350조 4340억 3477만</t>
   </si>
   <si>
     <t>11</t>
   </si>
   <si>
-    <t>니달리신</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%AC%EB%A6%AC%EC%8B%A0</t>
-  </si>
-  <si>
-    <t>262조 2999억 524만</t>
+    <t>약어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
+  </si>
+  <si>
+    <t>225조 7000억 9512만</t>
   </si>
   <si>
     <t>12</t>
   </si>
   <si>
-    <t>약어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%EC%96%B4</t>
-  </si>
-  <si>
-    <t>225조 7000억 9512만</t>
+    <t>프리프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>207조 6130억 4892만</t>
   </si>
   <si>
     <t>13</t>
   </si>
   <si>
-    <t>프리프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%84%EB%A6%AC%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>186조 1628억 3024만</t>
+    <t>꽃을든남자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>154조 5081억 5059만</t>
   </si>
   <si>
     <t>14</t>
@@ -431,82 +431,82 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BE%8C%EA%B0%90</t>
   </si>
   <si>
-    <t>149조 2169억 9071만</t>
+    <t>149조 4558억 4805만</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
-    <t>꽃을든남자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%83%EC%9D%84%EB%93%A0%EB%82%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>149조 1517억 6031만</t>
+    <t>소소채2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>125조 3589억 6621만</t>
   </si>
   <si>
     <t>16</t>
   </si>
   <si>
-    <t>소소채2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%86%8C%EC%B1%842</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>121조 611억 949만</t>
+    <t>하후돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
+  </si>
+  <si>
+    <t>110조 7620억 8911만</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
-    <t>하후돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9B%84%EB%8F%88</t>
-  </si>
-  <si>
-    <t>107조 5816억 7176만</t>
+    <t>잼포즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
+  </si>
+  <si>
+    <t>106조 419억 1690만</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
-    <t>잼포즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%BC%ED%8F%AC%EC%A6%88</t>
-  </si>
-  <si>
-    <t>106조 419억 1690만</t>
+    <t>할룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>96조 866억 2864만</t>
   </si>
   <si>
     <t>19</t>
   </si>
   <si>
-    <t>할룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>96조 866억 2864만</t>
+    <t>POSCO</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
+  </si>
+  <si>
+    <t>65조 7697억 3285만</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
-    <t>POSCO</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=POSCO</t>
-  </si>
-  <si>
-    <t>65조 7697억 3285만</t>
+    <t>루넨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
+  </si>
+  <si>
+    <t>61조 106억 7951만</t>
   </si>
   <si>
     <t>21</t>
@@ -527,75 +527,78 @@
     <t>22</t>
   </si>
   <si>
-    <t>루넨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%84%A8</t>
-  </si>
-  <si>
-    <t>58조 7294억 5027만</t>
+    <t>포뇨야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
+  </si>
+  <si>
+    <t>46조 2787억 8294만</t>
   </si>
   <si>
     <t>23</t>
   </si>
   <si>
-    <t>포뇨야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%87%A8%EC%95%BC</t>
-  </si>
-  <si>
-    <t>46조 2787억 8294만</t>
+    <t>울힝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
+  </si>
+  <si>
+    <t>46조 2442억 5637만</t>
   </si>
   <si>
     <t>24</t>
   </si>
   <si>
-    <t>울힝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
+    <t>제로슈가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>44조 324억 2846만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>김치싸대기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>39조 8824억 3269만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>38조 8158억 1231만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>악의꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
   </si>
   <si>
     <t>103</t>
   </si>
   <si>
-    <t>43조 3112억 2854만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>김치싸대기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>39조 8824억 3269만</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>대방어조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>38조 8158억 1231만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>악의꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%85%EC%9D%98%EA%BD%83</t>
-  </si>
-  <si>
     <t>38조 2904억 9899만</t>
   </si>
   <si>
@@ -614,574 +617,562 @@
     <t>29</t>
   </si>
   <si>
-    <t>제로슈가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EB%A1%9C%EC%8A%88%EA%B0%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>36조 514억 1080만</t>
+    <t>몽호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
+  </si>
+  <si>
+    <t>31조 9151억 3336만</t>
+  </si>
+  <si>
+    <t>o빠이o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EB%B9%A0%EC%9D%B4o</t>
+  </si>
+  <si>
+    <t>5174조 2119억 1456만</t>
+  </si>
+  <si>
+    <t>요르v</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EB%A5%B4v</t>
+  </si>
+  <si>
+    <t>3087조 2095억 1591만</t>
+  </si>
+  <si>
+    <t>o베베o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EB%B2%A0%EB%B2%A0o</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>2280조 9807억 8648만</t>
+  </si>
+  <si>
+    <t>o원기o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EC%9B%90%EA%B8%B0o</t>
+  </si>
+  <si>
+    <t>1759조 9101억 4132만</t>
+  </si>
+  <si>
+    <t>집단범죄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%91%EB%8B%A8%EB%B2%94%EC%A3%84</t>
+  </si>
+  <si>
+    <t>588조 3383억 488만</t>
+  </si>
+  <si>
+    <t>마법사김영욱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%B2%95%EC%82%AC%EA%B9%80%EC%98%81%EC%9A%B1</t>
+  </si>
+  <si>
+    <t>334조 9430억 1138만</t>
+  </si>
+  <si>
+    <t>캔느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BA%94%EB%8A%90</t>
+  </si>
+  <si>
+    <t>312조 9463억 1387만</t>
+  </si>
+  <si>
+    <t>워워이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%8C%EC%9B%8C%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>262조 6292억 5536만</t>
+  </si>
+  <si>
+    <t>o후국o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%ED%9B%84%EA%B5%ADo</t>
+  </si>
+  <si>
+    <t>200조 1341억 2359만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EB%B3%BC%EB%A5%A8o</t>
+  </si>
+  <si>
+    <t>180조 6234억 842만</t>
+  </si>
+  <si>
+    <t>이원일</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9B%90%EC%9D%BC</t>
+  </si>
+  <si>
+    <t>149조 308억 1325만</t>
+  </si>
+  <si>
+    <t>o진이o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EC%A7%84%EC%9D%B4o</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>137조 9858억 3942만</t>
+  </si>
+  <si>
+    <t>빵섭이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%EC%84%AD%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>124조 9974억 2134만</t>
+  </si>
+  <si>
+    <t>김규평</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B7%9C%ED%8F%89</t>
+  </si>
+  <si>
+    <t>115조 7340억 3872만</t>
+  </si>
+  <si>
+    <t>화욤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%9A%A4</t>
+  </si>
+  <si>
+    <t>105조 8956억 1083만</t>
+  </si>
+  <si>
+    <t>뭥끼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AD%A5%EB%81%BC</t>
+  </si>
+  <si>
+    <t>82조 2590억 1153만</t>
+  </si>
+  <si>
+    <t>o엉댕o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EC%97%89%EB%8C%95o</t>
+  </si>
+  <si>
+    <t>79조 3176억 3887만</t>
+  </si>
+  <si>
+    <t>후니와동동</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EB%8B%88%EC%99%80%EB%8F%99%EB%8F%99</t>
+  </si>
+  <si>
+    <t>72조 9493억 7864만</t>
+  </si>
+  <si>
+    <t>FFFK</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=FFFK</t>
+  </si>
+  <si>
+    <t>66조 5786억 899만</t>
+  </si>
+  <si>
+    <t>o아윤o</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=o%EC%95%84%EC%9C%A4o</t>
+  </si>
+  <si>
+    <t>63조 122억 1653만</t>
+  </si>
+  <si>
+    <t>보마할래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%A7%88%ED%95%A0%EB%9E%98</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>59조 3576억 6092만</t>
+  </si>
+  <si>
+    <t>호이호이포이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9D%B4%ED%98%B8%EC%9D%B4%ED%8F%AC%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>35조 9382억 9079만</t>
+  </si>
+  <si>
+    <t>동부마트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%B6%80%EB%A7%88%ED%8A%B8</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>33조 1410억 8669만</t>
+  </si>
+  <si>
+    <t>담훌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%B4%ED%9B%8C</t>
+  </si>
+  <si>
+    <t>18조 2160억 6263만</t>
+  </si>
+  <si>
+    <t>겨울난방</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%EB%82%9C%EB%B0%A9</t>
+  </si>
+  <si>
+    <t>18조 1270억 7876만</t>
+  </si>
+  <si>
+    <t>옹이잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%B9%EC%9D%B4%EC%9E%89</t>
+  </si>
+  <si>
+    <t>18조 91억 950만</t>
+  </si>
+  <si>
+    <t>우패밀리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%8C%A8%EB%B0%80%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>17조 2772억 2848만</t>
+  </si>
+  <si>
+    <t>뚠뚠냥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9A%A0%EB%9A%A0%EB%83%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>12조 9603억 4085만</t>
+  </si>
+  <si>
+    <t>비뉴송</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%89%B4%EC%86%A1</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>11조 7097억 8297만</t>
+  </si>
+  <si>
+    <t>람볼기니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9E%8C%EB%B3%BC%EA%B8%B0%EB%8B%88</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>1경 1274조 4956억 1115만</t>
+  </si>
+  <si>
+    <t>봉띤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%EB%9D%A4</t>
+  </si>
+  <si>
+    <t>5499조 5083억 2830만</t>
+  </si>
+  <si>
+    <t>예나는못말려</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%82%98%EB%8A%94%EB%AA%BB%EB%A7%90%EB%A0%A4</t>
+  </si>
+  <si>
+    <t>1437조 4091억 2121만</t>
+  </si>
+  <si>
+    <t>레몬깜바뉴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EB%AA%AC%EA%B9%9C%EB%B0%94%EB%89%B4</t>
+  </si>
+  <si>
+    <t>1197조 330억 5524만</t>
+  </si>
+  <si>
+    <t>불풍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%ED%92%8D</t>
+  </si>
+  <si>
+    <t>730조 6494억 130만</t>
+  </si>
+  <si>
+    <t>허동</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%97%88%EB%8F%99</t>
+  </si>
+  <si>
+    <t>559조 2267억 8616만</t>
+  </si>
+  <si>
+    <t>비화살</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%ED%99%94%EC%82%B4</t>
+  </si>
+  <si>
+    <t>230조 2631억 6497만</t>
+  </si>
+  <si>
+    <t>삼뚝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%BC%EB%9A%9D</t>
+  </si>
+  <si>
+    <t>160조 2604억 868만</t>
+  </si>
+  <si>
+    <t>똑순</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%91%EC%88%9C</t>
+  </si>
+  <si>
+    <t>127조 6880억 2670만</t>
+  </si>
+  <si>
+    <t>매워요</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EC%9B%8C%EC%9A%94</t>
+  </si>
+  <si>
+    <t>94조 9038억 402만</t>
+  </si>
+  <si>
+    <t>클이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%81%B4%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>86조 4580억 4180만</t>
+  </si>
+  <si>
+    <t>문군</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EA%B5%B0</t>
+  </si>
+  <si>
+    <t>80조 6841억 5612만</t>
+  </si>
+  <si>
+    <t>지흠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%ED%9D%A0</t>
+  </si>
+  <si>
+    <t>53조 3654억 5229만</t>
+  </si>
+  <si>
+    <t>이클릿</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%ED%81%B4%EB%A6%BF</t>
+  </si>
+  <si>
+    <t>46조 4119억 1969만</t>
+  </si>
+  <si>
+    <t>해로니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%A1%9C%EB%8B%88</t>
+  </si>
+  <si>
+    <t>38조 3367억 8619만</t>
+  </si>
+  <si>
+    <t>조업</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%97%85</t>
+  </si>
+  <si>
+    <t>33조 1928억 5597만</t>
+  </si>
+  <si>
+    <t>귀성</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%80%EC%84%B1</t>
+  </si>
+  <si>
+    <t>31조 2134억 8126만</t>
+  </si>
+  <si>
+    <t>오버츄어리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%B2%84%EC%B8%84%EC%96%B4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>31조 1428억 8799만</t>
+  </si>
+  <si>
+    <t>매스리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EC%8A%A4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>28조 4994억 6752만</t>
+  </si>
+  <si>
+    <t>썬콜미르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%AF%B8%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>23조 2691억 5987만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A7%88</t>
+  </si>
+  <si>
+    <t>19조 8814억 7540만</t>
+  </si>
+  <si>
+    <t>꽁칫</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EC%B9%AB</t>
+  </si>
+  <si>
+    <t>19조 1314억 5579만</t>
+  </si>
+  <si>
+    <t>앵찬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%B5%EC%B0%AC</t>
+  </si>
+  <si>
+    <t>16조 9665억 4898만</t>
+  </si>
+  <si>
+    <t>레펠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%ED%8E%A0</t>
+  </si>
+  <si>
+    <t>15조 7047억 8789만</t>
+  </si>
+  <si>
+    <t>LifeLegend</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=LifeLegend</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>10조 6952억 5950만</t>
+  </si>
+  <si>
+    <t>페이꺼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8E%98%EC%9D%B4%EA%BA%BC</t>
+  </si>
+  <si>
+    <t>10조 6623억 3538만</t>
+  </si>
+  <si>
+    <t>멍눈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%8D%EB%88%88</t>
+  </si>
+  <si>
+    <t>10조 514억 8551만</t>
+  </si>
+  <si>
+    <t>ArtCoin</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=ArtCoin</t>
+  </si>
+  <si>
+    <t>9조 7273억 6511만</t>
+  </si>
+  <si>
+    <t>무지성사냥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%A7%80%EC%84%B1%EC%82%AC%EB%83%A5</t>
+  </si>
+  <si>
+    <t>4조 5207억 8343만</t>
   </si>
   <si>
     <t>30</t>
   </si>
   <si>
-    <t>몽호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
-  </si>
-  <si>
-    <t>31조 9151억 3336만</t>
-  </si>
-  <si>
-    <t>o빠이o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EB%B9%A0%EC%9D%B4o</t>
-  </si>
-  <si>
-    <t>5174조 2119억 1456만</t>
-  </si>
-  <si>
-    <t>양먼지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%A8%BC%EC%A7%80</t>
-  </si>
-  <si>
-    <t>3569조 5128억 1676만</t>
-  </si>
-  <si>
-    <t>요르v</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EB%A5%B4v</t>
-  </si>
-  <si>
-    <t>3078조 8992억 5069만</t>
-  </si>
-  <si>
-    <t>o베베o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EB%B2%A0%EB%B2%A0o</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>2236조 5144억 5223만</t>
-  </si>
-  <si>
-    <t>o원기o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EC%9B%90%EA%B8%B0o</t>
-  </si>
-  <si>
-    <t>1738조 4620억 714만</t>
-  </si>
-  <si>
-    <t>집단범죄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%91%EB%8B%A8%EB%B2%94%EC%A3%84</t>
-  </si>
-  <si>
-    <t>586조 4140억 3923만</t>
-  </si>
-  <si>
-    <t>마법사김영욱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%B2%95%EC%82%AC%EA%B9%80%EC%98%81%EC%9A%B1</t>
-  </si>
-  <si>
-    <t>327조 3497억 6570만</t>
-  </si>
-  <si>
-    <t>워워이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%8C%EC%9B%8C%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>262조 6292억 5536만</t>
-  </si>
-  <si>
-    <t>o후국o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%ED%9B%84%EA%B5%ADo</t>
-  </si>
-  <si>
-    <t>200조 1341억 2359만</t>
-  </si>
-  <si>
-    <t>캔느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BA%94%EB%8A%90</t>
-  </si>
-  <si>
-    <t>189조 9962억 510만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EB%B3%BC%EB%A5%A8o</t>
-  </si>
-  <si>
-    <t>180조 6234억 842만</t>
-  </si>
-  <si>
-    <t>이원일</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9B%90%EC%9D%BC</t>
-  </si>
-  <si>
-    <t>149조 308억 1325만</t>
-  </si>
-  <si>
-    <t>o진이o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EC%A7%84%EC%9D%B4o</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>137조 9858억 3942만</t>
-  </si>
-  <si>
-    <t>빵섭이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%EC%84%AD%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>124조 9974억 2134만</t>
-  </si>
-  <si>
-    <t>김규평</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EA%B7%9C%ED%8F%89</t>
-  </si>
-  <si>
-    <t>115조 7340억 3872만</t>
-  </si>
-  <si>
-    <t>화욤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%9A%A4</t>
-  </si>
-  <si>
-    <t>97조 9798억 2864만</t>
-  </si>
-  <si>
-    <t>뭥끼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AD%A5%EB%81%BC</t>
-  </si>
-  <si>
-    <t>82조 1917억 4270만</t>
-  </si>
-  <si>
-    <t>o엉댕o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EC%97%89%EB%8C%95o</t>
-  </si>
-  <si>
-    <t>79조 1549억 5375만</t>
-  </si>
-  <si>
-    <t>후니와동동</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EB%8B%88%EC%99%80%EB%8F%99%EB%8F%99</t>
-  </si>
-  <si>
-    <t>72조 9493억 7864만</t>
-  </si>
-  <si>
-    <t>FFFK</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=FFFK</t>
-  </si>
-  <si>
-    <t>66조 5786억 899만</t>
-  </si>
-  <si>
-    <t>o아윤o</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=o%EC%95%84%EC%9C%A4o</t>
-  </si>
-  <si>
-    <t>63조 122억 1653만</t>
-  </si>
-  <si>
-    <t>보마할래</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%A7%88%ED%95%A0%EB%9E%98</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>54조 92억 859만</t>
-  </si>
-  <si>
-    <t>호이호이포이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9D%B4%ED%98%B8%EC%9D%B4%ED%8F%AC%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>35조 9382억 9079만</t>
-  </si>
-  <si>
-    <t>동부마트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EB%B6%80%EB%A7%88%ED%8A%B8</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>31조 7396억 6713만</t>
-  </si>
-  <si>
-    <t>겨울난방</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%EB%82%9C%EB%B0%A9</t>
-  </si>
-  <si>
-    <t>17조 8367억 8467만</t>
-  </si>
-  <si>
-    <t>옹이잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%B9%EC%9D%B4%EC%9E%89</t>
-  </si>
-  <si>
-    <t>17조 7165억 8053만</t>
-  </si>
-  <si>
-    <t>담훌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%B4%ED%9B%8C</t>
-  </si>
-  <si>
-    <t>17조 2860억 3718만</t>
-  </si>
-  <si>
-    <t>우패밀리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%8C%A8%EB%B0%80%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>17조 2333억 5444만</t>
-  </si>
-  <si>
-    <t>뚠뚠냥이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9A%A0%EB%9A%A0%EB%83%A5%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>12조 9603억 4085만</t>
-  </si>
-  <si>
-    <t>비뉴송</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%89%B4%EC%86%A1</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>11조 3789억 7166만</t>
-  </si>
-  <si>
-    <t>람볼기니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9E%8C%EB%B3%BC%EA%B8%B0%EB%8B%88</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>1경 1034조 8839억 5566만</t>
-  </si>
-  <si>
-    <t>봉띤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%EB%9D%A4</t>
-  </si>
-  <si>
-    <t>5499조 5083억 2830만</t>
-  </si>
-  <si>
-    <t>레몬깜바뉴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EB%AA%AC%EA%B9%9C%EB%B0%94%EB%89%B4</t>
-  </si>
-  <si>
-    <t>1197조 330억 5524만</t>
-  </si>
-  <si>
-    <t>예나는못말려</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%EB%82%98%EB%8A%94%EB%AA%BB%EB%A7%90%EB%A0%A4</t>
-  </si>
-  <si>
-    <t>1141조 4696억 7703만</t>
-  </si>
-  <si>
-    <t>불풍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%ED%92%8D</t>
-  </si>
-  <si>
-    <t>730조 6494억 130만</t>
-  </si>
-  <si>
-    <t>허동</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%97%88%EB%8F%99</t>
-  </si>
-  <si>
-    <t>556조 3385억 2634만</t>
-  </si>
-  <si>
-    <t>삼뚝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%BC%EB%9A%9D</t>
-  </si>
-  <si>
-    <t>158조 5282억 6438만</t>
-  </si>
-  <si>
-    <t>똑순</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%91%EC%88%9C</t>
-  </si>
-  <si>
-    <t>127조 4976억 5318만</t>
-  </si>
-  <si>
-    <t>매워요</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EC%9B%8C%EC%9A%94</t>
-  </si>
-  <si>
-    <t>94조 9038억 402만</t>
-  </si>
-  <si>
-    <t>문군</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EA%B5%B0</t>
-  </si>
-  <si>
-    <t>80조 6841억 5612만</t>
-  </si>
-  <si>
-    <t>클이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%81%B4%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>79조 6577억 8944만</t>
-  </si>
-  <si>
-    <t>지흠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%ED%9D%A0</t>
-  </si>
-  <si>
-    <t>52조 9423억 3702만</t>
-  </si>
-  <si>
-    <t>이클릿</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%ED%81%B4%EB%A6%BF</t>
-  </si>
-  <si>
-    <t>46조 4119억 1969만</t>
-  </si>
-  <si>
-    <t>해로니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%A1%9C%EB%8B%88</t>
-  </si>
-  <si>
-    <t>38조 3367억 8619만</t>
-  </si>
-  <si>
-    <t>조업</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%97%85</t>
-  </si>
-  <si>
-    <t>33조 1745억 2789만</t>
-  </si>
-  <si>
-    <t>오버츄어리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%B2%84%EC%B8%84%EC%96%B4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>30조 8101억 8029만</t>
-  </si>
-  <si>
-    <t>매스리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EC%8A%A4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>27조 2439억 3792만</t>
-  </si>
-  <si>
-    <t>썬콜미르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%AF%B8%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>23조 2299억 9831만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%A7%88</t>
-  </si>
-  <si>
-    <t>19조 8814억 7540만</t>
-  </si>
-  <si>
-    <t>꽁칫</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BD%81%EC%B9%AB</t>
-  </si>
-  <si>
-    <t>18조 7679억 2985만</t>
-  </si>
-  <si>
-    <t>앵찬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%B5%EC%B0%AC</t>
-  </si>
-  <si>
-    <t>16조 9665억 4898만</t>
-  </si>
-  <si>
-    <t>레펠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%ED%8E%A0</t>
-  </si>
-  <si>
-    <t>15조 7047억 8789만</t>
-  </si>
-  <si>
-    <t>LifeLegend</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=LifeLegend</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>10조 6952억 5950만</t>
-  </si>
-  <si>
-    <t>페이꺼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8E%98%EC%9D%B4%EA%BA%BC</t>
-  </si>
-  <si>
-    <t>10조 6623억 3538만</t>
-  </si>
-  <si>
-    <t>멍눈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%8D%EB%88%88</t>
-  </si>
-  <si>
-    <t>9조 9863억 5509만</t>
-  </si>
-  <si>
-    <t>ArtCoin</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=ArtCoin</t>
-  </si>
-  <si>
-    <t>9조 6853억 1877만</t>
-  </si>
-  <si>
-    <t>할거없곰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%A0%EA%B1%B0%EC%97%86%EA%B3%B0</t>
-  </si>
-  <si>
-    <t>6조 1154억 7858만</t>
-  </si>
-  <si>
-    <t>무지성사냥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%A7%80%EC%84%B1%EC%82%AC%EB%83%A5</t>
-  </si>
-  <si>
-    <t>4조 5207억 8343만</t>
-  </si>
-  <si>
     <t>때꾸</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%95%8C%EA%BE%B8</t>
   </si>
   <si>
-    <t>4조 1429억 3954만</t>
+    <t>4조 5027억 5839만</t>
   </si>
   <si>
     <t>딱뎀</t>
@@ -1208,7 +1199,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%A5%B4%EB%B1%85</t>
   </si>
   <si>
-    <t>2750조 3249억 132만</t>
+    <t>3122조 2538억 3369만</t>
   </si>
   <si>
     <t>Hoood</t>
@@ -1235,7 +1226,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EA%B9%85</t>
   </si>
   <si>
-    <t>175조 5868억 3424만</t>
+    <t>175조 7033억 41만</t>
   </si>
   <si>
     <t>내사랑로제</t>
@@ -1280,7 +1271,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8C%88%EC%8B%B8</t>
   </si>
   <si>
-    <t>37조 5037억 997만</t>
+    <t>37조 9834억 1553만</t>
   </si>
   <si>
     <t>퓨엉</t>
@@ -1289,7 +1280,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%93%A8%EC%97%89</t>
   </si>
   <si>
-    <t>33조 3882억 4094만</t>
+    <t>34조 6399억 4323만</t>
   </si>
   <si>
     <t>쑹쓩</t>
@@ -1322,7 +1313,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%B6%EA%B0%90%EB%A7%90%EC%9D%B4</t>
   </si>
   <si>
-    <t>23조 4525억 7505만</t>
+    <t>23조 5634억 8082만</t>
   </si>
   <si>
     <t>존잘녀</t>
@@ -1340,7 +1331,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%A8%EC%95%84</t>
   </si>
   <si>
-    <t>17조 4224억 7538만</t>
+    <t>17조 7287억 3490만</t>
   </si>
   <si>
     <t>으니림</t>
@@ -1367,7 +1358,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%AA%BC%EC%9E%AC%EB%A7%A8</t>
   </si>
   <si>
-    <t>8조 9454억 2665만</t>
+    <t>8조 9697억 9455만</t>
   </si>
   <si>
     <t>창목</t>
@@ -1376,7 +1367,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%BD%EB%AA%A9</t>
   </si>
   <si>
-    <t>7조 4251억 6822만</t>
+    <t>7조 5581억 5183만</t>
   </si>
   <si>
     <t>기동2</t>
@@ -1385,7 +1376,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%8F%992</t>
   </si>
   <si>
-    <t>6조 9087억 8647만</t>
+    <t>7조 5282억 1635만</t>
   </si>
   <si>
     <t>코몽잉</t>
@@ -1394,7 +1385,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EB%AA%BD%EC%9E%89</t>
   </si>
   <si>
-    <t>5조 3367억 1971만</t>
+    <t>5조 4232억 2584만</t>
   </si>
   <si>
     <t>치쵸치</t>
@@ -1412,7 +1403,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%8C%80%EB%A1%9C%EA%BF%80</t>
   </si>
   <si>
-    <t>4조 9515억 999만</t>
+    <t>5조 412억 8208만</t>
   </si>
   <si>
     <t>다둉이</t>
@@ -1430,7 +1421,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EB%AD%89%EC%9E%89</t>
   </si>
   <si>
-    <t>3조 9710억 6083만</t>
+    <t>3조 9781억 1413만</t>
   </si>
   <si>
     <t>문뚝</t>
@@ -1448,7 +1439,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%A9%EA%B8%88%EC%96%B4%EA%B8%88%EB%8B%88</t>
   </si>
   <si>
-    <t>3조 2489억 1908만</t>
+    <t>3조 2844억 3097만</t>
   </si>
   <si>
     <t>가을호떡</t>
@@ -1466,7 +1457,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EB%B3%B4</t>
   </si>
   <si>
-    <t>5773조 3543억 1445만</t>
+    <t>6482조 2991억 9620만</t>
   </si>
   <si>
     <t>낭만김갑룡</t>
@@ -1484,7 +1475,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%AD%EA%B5%AC%EC%95%BC</t>
   </si>
   <si>
-    <t>218조 8950억 9683만</t>
+    <t>256조 118억 6636만</t>
   </si>
   <si>
     <t>새우탕z</t>
@@ -1520,7 +1511,7 @@
     <t>https://mgf.gg/contents/character.php?n=ggggg</t>
   </si>
   <si>
-    <t>62조 4984억 9593만</t>
+    <t>65조 1340억 3243만</t>
   </si>
   <si>
     <t>다헐</t>
@@ -1529,7 +1520,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%ED%97%90</t>
   </si>
   <si>
-    <t>50조 6676억 6407만</t>
+    <t>52조 111억 9462만</t>
   </si>
   <si>
     <t>리피트</t>
@@ -1538,7 +1529,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%ED%94%BC%ED%8A%B8</t>
   </si>
   <si>
-    <t>49조 721억 2782만</t>
+    <t>50조 4611억 4021만</t>
   </si>
   <si>
     <t>친구닷</t>
@@ -1547,7 +1538,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%9C%EA%B5%AC%EB%8B%B7</t>
   </si>
   <si>
-    <t>44조 9288억 6205만</t>
+    <t>44조 9361억 5739만</t>
   </si>
   <si>
     <t>신림동물개</t>
@@ -1565,7 +1556,7 @@
     <t>https://mgf.gg/contents/character.php?n=Malgogi</t>
   </si>
   <si>
-    <t>29조 5050억 9944만</t>
+    <t>31조 3810억 899만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%9C%EA%B5%AC%EB%91%98%EB%A6%AC</t>
@@ -1580,7 +1571,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EA%B7%BC%ED%98%9C%EC%8A%98</t>
   </si>
   <si>
-    <t>24조 7689억 4279만</t>
+    <t>24조 9142억 6988만</t>
   </si>
   <si>
     <t>이남선</t>
@@ -1589,7 +1580,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%82%A8%EC%84%A0</t>
   </si>
   <si>
-    <t>24조 2472억 9989만</t>
+    <t>24조 2999억 1002만</t>
   </si>
   <si>
     <t>앙순아</t>
@@ -1598,7 +1589,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%99%EC%88%9C%EC%95%84</t>
   </si>
   <si>
-    <t>20조 3494억 1834만</t>
+    <t>22조 686억 5172만</t>
   </si>
   <si>
     <t>냉동붕어</t>
@@ -1607,7 +1598,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%89%EB%8F%99%EB%B6%95%EC%96%B4</t>
   </si>
   <si>
-    <t>19조 3960억 1480만</t>
+    <t>21조 9277억 4203만</t>
   </si>
   <si>
     <t>조은거임</t>
@@ -1616,7 +1607,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%9D%80%EA%B1%B0%EC%9E%84</t>
   </si>
   <si>
-    <t>16조 4644억 9775만</t>
+    <t>16조 5139억 612만</t>
   </si>
   <si>
     <t>보우모모</t>
@@ -1625,7 +1616,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EC%9A%B0%EB%AA%A8%EB%AA%A8</t>
   </si>
   <si>
-    <t>14조 2289억 1820만</t>
+    <t>15조 8088억 7487만</t>
   </si>
   <si>
     <t>v지훈왕자v</t>
@@ -1643,7 +1634,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EB%AA%A8%EC%9D%B8%EA%B0%84</t>
   </si>
   <si>
-    <t>12조 7863억 1640만</t>
+    <t>13조 1870억 1629만</t>
   </si>
   <si>
     <t>Silas</t>
@@ -1652,7 +1643,7 @@
     <t>https://mgf.gg/contents/character.php?n=Silas</t>
   </si>
   <si>
-    <t>11조 660억 9778만</t>
+    <t>11조 1020억 1506만</t>
   </si>
   <si>
     <t>뿡풍</t>
@@ -1679,7 +1670,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%84%B1%EA%B7%9C</t>
   </si>
   <si>
-    <t>7조 7443억 9675만</t>
+    <t>7조 8893억 576만</t>
   </si>
   <si>
     <t>갓친</t>
@@ -1697,7 +1688,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%98%EC%A2%80%ED%95%B4%EB%B4%90</t>
   </si>
   <si>
-    <t>4조 3109억 5195만</t>
+    <t>4조 3465억 6534만</t>
   </si>
   <si>
     <t>예끔이</t>
@@ -2187,7 +2178,7 @@
         <v>28</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>19</v>
@@ -2196,13 +2187,13 @@
         <v>20</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>24</v>
@@ -2210,25 +2201,25 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>19</v>
@@ -2275,7 +2266,7 @@
         <v>19</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>45</v>
@@ -2316,7 +2307,7 @@
         <v>53</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>54</v>
@@ -2345,6 +2336,2030 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J30"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J30"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2393,31 +4408,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>66</v>
+        <v>290</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>66</v>
+        <v>290</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>67</v>
+        <v>291</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>70</v>
+        <v>292</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>71</v>
+        <v>293</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -2425,19 +4440,19 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>73</v>
+        <v>294</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>73</v>
+        <v>294</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>74</v>
+        <v>295</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>68</v>
@@ -2449,7 +4464,7 @@
         <v>76</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>77</v>
+        <v>296</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2457,31 +4472,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>79</v>
+        <v>297</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>79</v>
+        <v>297</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>80</v>
+        <v>298</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2489,31 +4504,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>84</v>
+        <v>300</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>84</v>
+        <v>300</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>85</v>
+        <v>301</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>87</v>
+        <v>207</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>88</v>
+        <v>302</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2521,31 +4536,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>90</v>
+        <v>303</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>90</v>
+        <v>303</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>91</v>
+        <v>304</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>93</v>
+        <v>305</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2553,31 +4568,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>95</v>
+        <v>306</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>95</v>
+        <v>306</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>96</v>
+        <v>307</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>98</v>
+        <v>308</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2585,31 +4600,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>100</v>
+        <v>309</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>100</v>
+        <v>309</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>101</v>
+        <v>310</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>104</v>
+        <v>311</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2617,31 +4632,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>106</v>
+        <v>312</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>106</v>
+        <v>312</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>107</v>
+        <v>313</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>81</v>
+        <v>234</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>109</v>
+        <v>314</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2649,31 +4664,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>111</v>
+        <v>315</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>111</v>
+        <v>315</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>112</v>
+        <v>316</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>113</v>
+        <v>317</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2681,31 +4696,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>115</v>
+        <v>318</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>115</v>
+        <v>318</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>116</v>
+        <v>319</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>118</v>
+        <v>320</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2713,31 +4728,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>120</v>
+        <v>321</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>120</v>
+        <v>321</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>121</v>
+        <v>322</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>122</v>
+        <v>323</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2745,31 +4760,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>124</v>
+        <v>324</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>124</v>
+        <v>324</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>126</v>
+        <v>326</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2777,19 +4792,19 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>128</v>
+        <v>327</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>128</v>
+        <v>327</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>129</v>
+        <v>328</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>68</v>
@@ -2798,10 +4813,10 @@
         <v>92</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>117</v>
+        <v>189</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>130</v>
+        <v>329</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2809,31 +4824,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>132</v>
+        <v>330</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>132</v>
+        <v>330</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>133</v>
+        <v>331</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>108</v>
+        <v>163</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>134</v>
+        <v>332</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2841,31 +4856,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>136</v>
+        <v>333</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>136</v>
+        <v>333</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>137</v>
+        <v>334</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>108</v>
+        <v>163</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>138</v>
+        <v>335</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2873,31 +4888,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>140</v>
+        <v>336</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>140</v>
+        <v>336</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>141</v>
+        <v>337</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>143</v>
+        <v>338</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2905,19 +4920,19 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>145</v>
+        <v>339</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>145</v>
+        <v>339</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>146</v>
+        <v>340</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>68</v>
@@ -2926,10 +4941,10 @@
         <v>92</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>117</v>
+        <v>189</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>147</v>
+        <v>341</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2937,31 +4952,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>149</v>
+        <v>342</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>149</v>
+        <v>342</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>150</v>
+        <v>343</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>151</v>
+        <v>344</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2969,31 +4984,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>152</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>153</v>
+        <v>345</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>153</v>
+        <v>345</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>154</v>
+        <v>346</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>155</v>
+        <v>347</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3001,31 +5016,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>157</v>
+        <v>348</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>157</v>
+        <v>348</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>158</v>
+        <v>349</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>159</v>
+        <v>350</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3033,31 +5048,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>160</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>161</v>
+        <v>40</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>161</v>
+        <v>40</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>162</v>
+        <v>351</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>68</v>
+        <v>193</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>163</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>164</v>
+        <v>352</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3065,19 +5080,19 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>165</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>166</v>
+        <v>353</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>166</v>
+        <v>353</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>167</v>
+        <v>354</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>68</v>
@@ -3086,10 +5101,10 @@
         <v>92</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>142</v>
+        <v>269</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>168</v>
+        <v>355</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3097,31 +5112,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>169</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>170</v>
+        <v>356</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>170</v>
+        <v>356</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>171</v>
+        <v>357</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>172</v>
+        <v>358</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3129,31 +5144,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>173</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>174</v>
+        <v>359</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>174</v>
+        <v>359</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>175</v>
+        <v>360</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>176</v>
+        <v>269</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>177</v>
+        <v>361</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3161,31 +5176,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>179</v>
+        <v>362</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>179</v>
+        <v>362</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>180</v>
+        <v>363</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>176</v>
+        <v>364</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>181</v>
+        <v>365</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3193,31 +5208,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>183</v>
+        <v>366</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>183</v>
+        <v>366</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>184</v>
+        <v>367</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>185</v>
+        <v>368</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3225,31 +5240,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>187</v>
+        <v>369</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>187</v>
+        <v>369</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>188</v>
+        <v>370</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>176</v>
+        <v>269</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>189</v>
+        <v>371</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3257,31 +5272,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>23</v>
+        <v>372</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>23</v>
+        <v>372</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>191</v>
+        <v>373</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>192</v>
+        <v>68</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>75</v>
+        <v>234</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>193</v>
+        <v>374</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3289,31 +5304,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>195</v>
+        <v>375</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>195</v>
+        <v>375</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>196</v>
+        <v>376</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>197</v>
+        <v>69</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>198</v>
+        <v>377</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3321,31 +5336,31 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>199</v>
+        <v>378</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>200</v>
+        <v>379</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>200</v>
+        <v>379</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>201</v>
+        <v>380</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>102</v>
+        <v>262</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>202</v>
+        <v>381</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -3389,2063 +5404,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J31"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
-    <hyperlink ref="E20" r:id="rId19"/>
-    <hyperlink ref="E21" r:id="rId20"/>
-    <hyperlink ref="E22" r:id="rId21"/>
-    <hyperlink ref="E23" r:id="rId22"/>
-    <hyperlink ref="E24" r:id="rId23"/>
-    <hyperlink ref="E25" r:id="rId24"/>
-    <hyperlink ref="E26" r:id="rId25"/>
-    <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
-    <hyperlink ref="E31" r:id="rId30"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J30"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
-    <hyperlink ref="E20" r:id="rId19"/>
-    <hyperlink ref="E21" r:id="rId20"/>
-    <hyperlink ref="E22" r:id="rId21"/>
-    <hyperlink ref="E23" r:id="rId22"/>
-    <hyperlink ref="E24" r:id="rId23"/>
-    <hyperlink ref="E25" r:id="rId24"/>
-    <hyperlink ref="E26" r:id="rId25"/>
-    <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
@@ -5501,13 +5459,13 @@
         <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>68</v>
@@ -5516,10 +5474,10 @@
         <v>97</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5533,13 +5491,13 @@
         <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>68</v>
@@ -5551,7 +5509,7 @@
         <v>87</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5565,13 +5523,13 @@
         <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>68</v>
@@ -5580,10 +5538,10 @@
         <v>102</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5597,13 +5555,13 @@
         <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>68</v>
@@ -5612,10 +5570,10 @@
         <v>75</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5629,13 +5587,13 @@
         <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>68</v>
@@ -5644,10 +5602,10 @@
         <v>69</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5661,13 +5619,13 @@
         <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>68</v>
@@ -5676,10 +5634,10 @@
         <v>75</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5693,13 +5651,13 @@
         <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>68</v>
@@ -5708,10 +5666,10 @@
         <v>102</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5725,13 +5683,13 @@
         <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>68</v>
@@ -5740,10 +5698,10 @@
         <v>86</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5757,13 +5715,13 @@
         <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>68</v>
@@ -5775,7 +5733,7 @@
         <v>163</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5786,16 +5744,16 @@
         <v>41</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>68</v>
@@ -5807,7 +5765,7 @@
         <v>163</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5821,13 +5779,13 @@
         <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>68</v>
@@ -5836,10 +5794,10 @@
         <v>75</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5853,13 +5811,13 @@
         <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>68</v>
@@ -5868,10 +5826,10 @@
         <v>75</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5885,13 +5843,13 @@
         <v>127</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>68</v>
@@ -5903,7 +5861,7 @@
         <v>163</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5917,13 +5875,13 @@
         <v>131</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>68</v>
@@ -5935,7 +5893,7 @@
         <v>163</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5949,13 +5907,13 @@
         <v>135</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>68</v>
@@ -5964,10 +5922,10 @@
         <v>92</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5978,7 +5936,7 @@
         <v>41</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>47</v>
@@ -5987,19 +5945,19 @@
         <v>47</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6013,13 +5971,13 @@
         <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>68</v>
@@ -6028,10 +5986,10 @@
         <v>75</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6045,13 +6003,13 @@
         <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>68</v>
@@ -6060,10 +6018,10 @@
         <v>75</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6077,13 +6035,13 @@
         <v>152</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>68</v>
@@ -6092,10 +6050,10 @@
         <v>69</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>365</v>
+        <v>269</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6109,13 +6067,13 @@
         <v>156</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>68</v>
@@ -6124,10 +6082,10 @@
         <v>75</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6141,13 +6099,13 @@
         <v>160</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>68</v>
@@ -6156,10 +6114,10 @@
         <v>92</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6173,13 +6131,13 @@
         <v>165</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>68</v>
@@ -6188,10 +6146,10 @@
         <v>92</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6205,25 +6163,25 @@
         <v>169</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6237,13 +6195,13 @@
         <v>173</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>68</v>
@@ -6252,10 +6210,10 @@
         <v>75</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6269,25 +6227,25 @@
         <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6301,25 +6259,25 @@
         <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6333,25 +6291,25 @@
         <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6362,16 +6320,16 @@
         <v>41</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>68</v>
@@ -6380,10 +6338,10 @@
         <v>92</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6394,16 +6352,16 @@
         <v>41</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>68</v>
@@ -6412,10 +6370,10 @@
         <v>75</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6426,16 +6384,16 @@
         <v>41</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>199</v>
+        <v>378</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>68</v>
@@ -6444,10 +6402,10 @@
         <v>92</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6546,13 +6504,13 @@
         <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>68</v>
@@ -6564,7 +6522,7 @@
         <v>76</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6578,13 +6536,13 @@
         <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>68</v>
@@ -6596,7 +6554,7 @@
         <v>76</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6610,13 +6568,13 @@
         <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>68</v>
@@ -6628,7 +6586,7 @@
         <v>108</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6642,25 +6600,25 @@
         <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>163</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6674,13 +6632,13 @@
         <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>68</v>
@@ -6689,10 +6647,10 @@
         <v>69</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6706,13 +6664,13 @@
         <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>68</v>
@@ -6721,10 +6679,10 @@
         <v>75</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6738,13 +6696,13 @@
         <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>68</v>
@@ -6753,10 +6711,10 @@
         <v>102</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6770,13 +6728,13 @@
         <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>68</v>
@@ -6785,10 +6743,10 @@
         <v>86</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6802,13 +6760,13 @@
         <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>68</v>
@@ -6817,10 +6775,10 @@
         <v>92</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6831,16 +6789,16 @@
         <v>48</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>68</v>
@@ -6849,10 +6807,10 @@
         <v>92</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6866,13 +6824,13 @@
         <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>68</v>
@@ -6881,10 +6839,10 @@
         <v>102</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6898,13 +6856,13 @@
         <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>68</v>
@@ -6913,10 +6871,10 @@
         <v>75</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6930,13 +6888,13 @@
         <v>127</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>68</v>
@@ -6945,10 +6903,10 @@
         <v>75</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6968,19 +6926,19 @@
         <v>56</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>92</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6994,13 +6952,13 @@
         <v>135</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>68</v>
@@ -7009,10 +6967,10 @@
         <v>92</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -7023,16 +6981,16 @@
         <v>48</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>68</v>
@@ -7041,10 +6999,10 @@
         <v>92</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7058,13 +7016,13 @@
         <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>68</v>
@@ -7073,10 +7031,10 @@
         <v>92</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7090,13 +7048,13 @@
         <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>68</v>
@@ -7105,10 +7063,10 @@
         <v>92</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7122,13 +7080,13 @@
         <v>152</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>68</v>
@@ -7137,10 +7095,10 @@
         <v>69</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7154,13 +7112,13 @@
         <v>156</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>68</v>
@@ -7169,10 +7127,10 @@
         <v>69</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7186,13 +7144,13 @@
         <v>160</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>68</v>
@@ -7201,10 +7159,10 @@
         <v>75</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7218,13 +7176,13 @@
         <v>165</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>68</v>
@@ -7233,10 +7191,10 @@
         <v>92</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7250,13 +7208,13 @@
         <v>169</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>68</v>
@@ -7265,10 +7223,10 @@
         <v>92</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7282,13 +7240,13 @@
         <v>173</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>68</v>
@@ -7297,10 +7255,10 @@
         <v>92</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7314,13 +7272,13 @@
         <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>68</v>
@@ -7329,10 +7287,10 @@
         <v>92</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7346,13 +7304,13 @@
         <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>68</v>
@@ -7361,10 +7319,10 @@
         <v>92</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7378,25 +7336,25 @@
         <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7407,16 +7365,16 @@
         <v>48</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>68</v>
@@ -7425,10 +7383,10 @@
         <v>92</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -7439,16 +7397,16 @@
         <v>48</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>68</v>
@@ -7457,10 +7415,10 @@
         <v>92</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>

--- a/reports/셀린느/셀린느_league_mgf_report.xlsx
+++ b/reports/셀린느/셀린느_league_mgf_report.xlsx
@@ -16,10 +16,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">RAINBOW!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">RAINBOW!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">동물들의낙원!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">빠따!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">셀린느!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">빠따!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">셀린느!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">친구들!$A$1:$J$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="559">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,7 +80,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>31</t>
+    <t>30</t>
   </si>
   <si>
     <t>1위</t>
@@ -89,61 +89,61 @@
     <t>Lv.8</t>
   </si>
   <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>2경 7876조 2110억 7224만</t>
+  </si>
+  <si>
+    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
+  </si>
+  <si>
+    <t>혜영</t>
+  </si>
+  <si>
+    <t>2026.04.29</t>
+  </si>
+  <si>
+    <t>빠따</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%A0%EB%94%B0</t>
+  </si>
+  <si>
+    <t>Scania 12</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>1경 9648조 9888억 5558만</t>
+  </si>
+  <si>
+    <t>자유가입</t>
+  </si>
+  <si>
+    <t>o볼륨o</t>
+  </si>
+  <si>
+    <t>RAINBOW</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=RAINBOW</t>
+  </si>
+  <si>
+    <t>Scania 6</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>2위</t>
+  </si>
+  <si>
     <t>29명</t>
   </si>
   <si>
-    <t>2경 7582조 5935억 3301만</t>
-  </si>
-  <si>
-    <t>[통합2섭1위] [토벌전1위 최종뎀10%][IN50위] 문의 [혜영]</t>
-  </si>
-  <si>
-    <t>혜영</t>
-  </si>
-  <si>
-    <t>2026.04.28</t>
-  </si>
-  <si>
-    <t>빠따</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%A0%EB%94%B0</t>
-  </si>
-  <si>
-    <t>Scania 12</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <